--- a/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
+++ b/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="669">
   <si>
     <t>§4. 照査の前提</t>
   </si>
@@ -2042,10 +2042,16 @@
     <t>0.482 %</t>
   </si>
   <si>
-    <t>照査は「12.5 最小鉄筋量及び最大鉄筋量」に示す。</t>
-  </si>
-  <si>
-    <t>照査は「12.3 耐久性の照査」に示す。</t>
+    <t>照査は、フーチングの断面照査で地震時以外の照査を行うときに「最小鉄筋量及び最大鉄筋</t>
+  </si>
+  <si>
+    <t>量」で確かめる。</t>
+  </si>
+  <si>
+    <t>照査は、フーチングの断面照査で地震時以外の照査を行うときに「耐久性の照査」で確かめ</t>
+  </si>
+  <si>
+    <t>る。</t>
   </si>
   <si>
     <t>150.0 − 32 = 118.0 mm</t>
@@ -2136,9 +2142,6 @@
     <t>・配力鉄筋として、引張鉄筋の単位幅当りの断面積の1/6以上を単位幅当りに対して配置す</t>
   </si>
   <si>
-    <t>る。</t>
-  </si>
-  <si>
     <t>・圧縮鉄筋として、引張鉄筋の単位幅当りの断面積の1/6以上を単位幅当りに対して配置す</t>
   </si>
   <si>
@@ -2173,12 +2176,6 @@
   </si>
   <si>
     <t>下側</t>
-  </si>
-  <si>
-    <t>照査は「12.9 最小鉄筋量及び最大鉄筋量」に示す。</t>
-  </si>
-  <si>
-    <t>照査は「12.7 耐久性の照査」に示す。</t>
   </si>
   <si>
     <t>4.5 杭の構造細目</t>
@@ -9694,51 +9691,63 @@
         <v>259</v>
       </c>
     </row>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1">
-      <c r="E737" s="1" t="s">
+    <row r="736" ht="15.75" customHeight="1">
+      <c r="E736" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1">
+      <c r="E738" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1">
-      <c r="E739" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
+    <row r="739" ht="15.75" customHeight="1"/>
     <row r="740" ht="15.75" customHeight="1">
       <c r="E740" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="741" ht="15.75" customHeight="1">
       <c r="E741" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="742" ht="15.75" customHeight="1">
+      <c r="E742" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="742" ht="15.75" customHeight="1"/>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="D743" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S743" s="1" t="s">
-        <v>43</v>
+      <c r="E743" s="2" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="744" ht="15.75" customHeight="1"/>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="E745" s="2" t="s">
+      <c r="D745" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S745" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1">
+      <c r="E747" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
-      <c r="E746" s="2" t="s">
+    <row r="748" ht="15.75" customHeight="1">
+      <c r="E748" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1">
+      <c r="E749" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
     <row r="750" ht="15.75" customHeight="1"/>
     <row r="751" ht="15.75" customHeight="1"/>
     <row r="752" ht="15.75" customHeight="1"/>
@@ -9818,180 +9827,168 @@
     </row>
     <row r="767" ht="15.75" customHeight="1">
       <c r="E767" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1">
-      <c r="D769" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="768" ht="15.75" customHeight="1">
+      <c r="E768" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1">
+      <c r="D770" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S769" s="1" t="s">
+      <c r="S770" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1">
-      <c r="E771" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
+    <row r="771" ht="15.75" customHeight="1"/>
     <row r="772" ht="15.75" customHeight="1">
       <c r="E772" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="773" ht="15.75" customHeight="1">
       <c r="E773" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="774" ht="15.75" customHeight="1">
+      <c r="E774" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1">
-      <c r="J775" s="3" t="s">
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1">
+      <c r="J776" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="R775" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S775" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="776" ht="15.75" customHeight="1">
-      <c r="M776" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="R776" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S776" s="2" t="s">
-        <v>226</v>
+        <v>65</v>
       </c>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="J777" s="3" t="s">
-        <v>227</v>
+      <c r="M777" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="R777" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S777" s="2" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
     </row>
     <row r="778" ht="15.75" customHeight="1">
       <c r="J778" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="R778" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S778" s="2" t="s">
-        <v>65</v>
+        <v>263</v>
       </c>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="M779" s="3" t="s">
-        <v>231</v>
+      <c r="J779" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="R779" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S779" s="2" t="s">
-        <v>226</v>
+        <v>65</v>
       </c>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="J780" s="3" t="s">
-        <v>233</v>
+      <c r="M780" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="R780" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S780" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1">
-      <c r="E782" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="781" ht="15.75" customHeight="1">
+      <c r="J781" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="R781" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S781" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1">
+      <c r="E783" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
-      <c r="E783" s="7" t="s">
+    <row r="784" ht="15.75" customHeight="1">
+      <c r="E784" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F783" s="8"/>
-      <c r="G783" s="8"/>
-      <c r="H783" s="8"/>
-      <c r="I783" s="8"/>
-      <c r="J783" s="8"/>
-      <c r="K783" s="8"/>
-      <c r="L783" s="9" t="s">
+      <c r="F784" s="8"/>
+      <c r="G784" s="8"/>
+      <c r="H784" s="8"/>
+      <c r="I784" s="8"/>
+      <c r="J784" s="8"/>
+      <c r="K784" s="8"/>
+      <c r="L784" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M783" s="8"/>
-      <c r="N783" s="8"/>
-      <c r="O783" s="8"/>
-      <c r="P783" s="8"/>
-      <c r="Q783" s="8"/>
-      <c r="R783" s="8"/>
-      <c r="S783" s="8"/>
-      <c r="T783" s="9" t="s">
+      <c r="M784" s="8"/>
+      <c r="N784" s="8"/>
+      <c r="O784" s="8"/>
+      <c r="P784" s="8"/>
+      <c r="Q784" s="8"/>
+      <c r="R784" s="8"/>
+      <c r="S784" s="8"/>
+      <c r="T784" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="U783" s="8"/>
-      <c r="V783" s="8"/>
-      <c r="W783" s="8"/>
-      <c r="X783" s="8"/>
-      <c r="Y783" s="8"/>
-      <c r="Z783" s="8"/>
-      <c r="AA783" s="8"/>
-      <c r="AB783" s="8"/>
-      <c r="AC783" s="8"/>
-      <c r="AD783" s="10"/>
-    </row>
-    <row r="784" ht="15.75" customHeight="1">
-      <c r="E784" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="F784" s="12"/>
-      <c r="G784" s="12"/>
-      <c r="H784" s="12"/>
-      <c r="I784" s="12"/>
-      <c r="J784" s="12"/>
-      <c r="K784" s="12"/>
-      <c r="L784" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="M784" s="12"/>
-      <c r="N784" s="12"/>
-      <c r="O784" s="12"/>
-      <c r="P784" s="12"/>
-      <c r="Q784" s="12"/>
-      <c r="R784" s="12"/>
-      <c r="S784" s="12"/>
-      <c r="T784" s="14" t="s">
+      <c r="U784" s="8"/>
+      <c r="V784" s="8"/>
+      <c r="W784" s="8"/>
+      <c r="X784" s="8"/>
+      <c r="Y784" s="8"/>
+      <c r="Z784" s="8"/>
+      <c r="AA784" s="8"/>
+      <c r="AB784" s="8"/>
+      <c r="AC784" s="8"/>
+      <c r="AD784" s="10"/>
+    </row>
+    <row r="785" ht="15.75" customHeight="1">
+      <c r="E785" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="F785" s="12"/>
+      <c r="G785" s="12"/>
+      <c r="H785" s="12"/>
+      <c r="I785" s="12"/>
+      <c r="J785" s="12"/>
+      <c r="K785" s="12"/>
+      <c r="L785" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="M785" s="12"/>
+      <c r="N785" s="12"/>
+      <c r="O785" s="12"/>
+      <c r="P785" s="12"/>
+      <c r="Q785" s="12"/>
+      <c r="R785" s="12"/>
+      <c r="S785" s="12"/>
+      <c r="T785" s="14" t="s">
         <v>237</v>
-      </c>
-      <c r="U784" s="12"/>
-      <c r="V784" s="12"/>
-      <c r="W784" s="12"/>
-      <c r="X784" s="12"/>
-      <c r="Y784" s="12"/>
-      <c r="Z784" s="12"/>
-      <c r="AA784" s="12"/>
-      <c r="AB784" s="12"/>
-      <c r="AC784" s="12"/>
-      <c r="AD784" s="10"/>
-    </row>
-    <row r="785" ht="15.75" customHeight="1">
-      <c r="E785" s="10"/>
-      <c r="L785" s="15"/>
-      <c r="T785" s="14" t="s">
-        <v>238</v>
       </c>
       <c r="U785" s="12"/>
       <c r="V785" s="12"/>
@@ -10008,7 +10005,7 @@
       <c r="E786" s="10"/>
       <c r="L786" s="15"/>
       <c r="T786" s="14" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="U786" s="12"/>
       <c r="V786" s="12"/>
@@ -10022,27 +10019,10 @@
       <c r="AD786" s="10"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="E787" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="F787" s="12"/>
-      <c r="G787" s="12"/>
-      <c r="H787" s="12"/>
-      <c r="I787" s="12"/>
-      <c r="J787" s="12"/>
-      <c r="K787" s="12"/>
-      <c r="L787" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="M787" s="12"/>
-      <c r="N787" s="12"/>
-      <c r="O787" s="12"/>
-      <c r="P787" s="12"/>
-      <c r="Q787" s="12"/>
-      <c r="R787" s="12"/>
-      <c r="S787" s="12"/>
+      <c r="E787" s="10"/>
+      <c r="L787" s="15"/>
       <c r="T787" s="14" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="U787" s="12"/>
       <c r="V787" s="12"/>
@@ -10056,10 +10036,27 @@
       <c r="AD787" s="10"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="E788" s="10"/>
-      <c r="L788" s="15"/>
+      <c r="E788" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="F788" s="12"/>
+      <c r="G788" s="12"/>
+      <c r="H788" s="12"/>
+      <c r="I788" s="12"/>
+      <c r="J788" s="12"/>
+      <c r="K788" s="12"/>
+      <c r="L788" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="M788" s="12"/>
+      <c r="N788" s="12"/>
+      <c r="O788" s="12"/>
+      <c r="P788" s="12"/>
+      <c r="Q788" s="12"/>
+      <c r="R788" s="12"/>
+      <c r="S788" s="12"/>
       <c r="T788" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="U788" s="12"/>
       <c r="V788" s="12"/>
@@ -10076,7 +10073,7 @@
       <c r="E789" s="10"/>
       <c r="L789" s="15"/>
       <c r="T789" s="14" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="U789" s="12"/>
       <c r="V789" s="12"/>
@@ -10090,38 +10087,54 @@
       <c r="AD789" s="10"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="E790" s="8"/>
-      <c r="F790" s="8"/>
-      <c r="G790" s="8"/>
-      <c r="H790" s="8"/>
-      <c r="I790" s="8"/>
-      <c r="J790" s="8"/>
-      <c r="K790" s="8"/>
-      <c r="L790" s="8"/>
-      <c r="M790" s="8"/>
-      <c r="N790" s="8"/>
-      <c r="O790" s="8"/>
-      <c r="P790" s="8"/>
-      <c r="Q790" s="8"/>
-      <c r="R790" s="8"/>
-      <c r="S790" s="8"/>
-      <c r="T790" s="8"/>
-      <c r="U790" s="8"/>
-      <c r="V790" s="8"/>
-      <c r="W790" s="8"/>
-      <c r="X790" s="8"/>
-      <c r="Y790" s="8"/>
-      <c r="Z790" s="8"/>
-      <c r="AA790" s="8"/>
-      <c r="AB790" s="8"/>
-      <c r="AC790" s="8"/>
+      <c r="E790" s="10"/>
+      <c r="L790" s="15"/>
+      <c r="T790" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="U790" s="12"/>
+      <c r="V790" s="12"/>
+      <c r="W790" s="12"/>
+      <c r="X790" s="12"/>
+      <c r="Y790" s="12"/>
+      <c r="Z790" s="12"/>
+      <c r="AA790" s="12"/>
+      <c r="AB790" s="12"/>
+      <c r="AC790" s="12"/>
+      <c r="AD790" s="10"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="E791" s="2" t="s">
+      <c r="E791" s="8"/>
+      <c r="F791" s="8"/>
+      <c r="G791" s="8"/>
+      <c r="H791" s="8"/>
+      <c r="I791" s="8"/>
+      <c r="J791" s="8"/>
+      <c r="K791" s="8"/>
+      <c r="L791" s="8"/>
+      <c r="M791" s="8"/>
+      <c r="N791" s="8"/>
+      <c r="O791" s="8"/>
+      <c r="P791" s="8"/>
+      <c r="Q791" s="8"/>
+      <c r="R791" s="8"/>
+      <c r="S791" s="8"/>
+      <c r="T791" s="8"/>
+      <c r="U791" s="8"/>
+      <c r="V791" s="8"/>
+      <c r="W791" s="8"/>
+      <c r="X791" s="8"/>
+      <c r="Y791" s="8"/>
+      <c r="Z791" s="8"/>
+      <c r="AA791" s="8"/>
+      <c r="AB791" s="8"/>
+      <c r="AC791" s="8"/>
+    </row>
+    <row r="792" ht="15.75" customHeight="1">
+      <c r="E792" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="792" ht="15.75" customHeight="1"/>
     <row r="793" ht="15.75" customHeight="1"/>
     <row r="794" ht="15.75" customHeight="1"/>
     <row r="795" ht="15.75" customHeight="1"/>
@@ -10151,7 +10164,7 @@
     <row r="804" ht="15.75" customHeight="1"/>
     <row r="805" ht="15.75" customHeight="1">
       <c r="F805" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="806" ht="15.75" customHeight="1">
@@ -10174,7 +10187,7 @@
         <v>27</v>
       </c>
       <c r="P806" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="U806" s="4" t="s">
         <v>28</v>
@@ -10188,7 +10201,7 @@
         <v>26</v>
       </c>
       <c r="J807" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M807" s="3" t="s">
         <v>30</v>
@@ -10381,7 +10394,7 @@
     <row r="828" ht="15.75" customHeight="1"/>
     <row r="829" ht="15.75" customHeight="1">
       <c r="F829" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="830" ht="15.75" customHeight="1"/>
@@ -10442,7 +10455,7 @@
         <v>27</v>
       </c>
       <c r="N839" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S839" s="4" t="s">
         <v>28</v>
@@ -10462,7 +10475,7 @@
     </row>
     <row r="840" ht="15.75" customHeight="1">
       <c r="F840" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="841" ht="15.75" customHeight="1"/>
@@ -10499,7 +10512,7 @@
         <v>15</v>
       </c>
       <c r="K852" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="853" ht="15.75" customHeight="1">
@@ -10565,7 +10578,7 @@
         <v>15</v>
       </c>
       <c r="K858" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="859" ht="15.75" customHeight="1">
@@ -10582,37 +10595,37 @@
     <row r="860" ht="15.75" customHeight="1"/>
     <row r="861" ht="15.75" customHeight="1">
       <c r="F861" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="862" ht="15.75" customHeight="1"/>
     <row r="863" ht="15.75" customHeight="1">
       <c r="D863" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="S863" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="864" ht="15.75" customHeight="1"/>
     <row r="865" ht="15.75" customHeight="1">
       <c r="E865" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="866" ht="15.75" customHeight="1">
       <c r="E866" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="867" ht="15.75" customHeight="1">
       <c r="E867" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="868" ht="15.75" customHeight="1">
       <c r="E868" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="869" ht="15.75" customHeight="1"/>
@@ -10621,7 +10634,7 @@
       <c r="C870" s="8"/>
       <c r="D870" s="8"/>
       <c r="E870" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F870" s="8"/>
       <c r="G870" s="8"/>
@@ -10630,18 +10643,18 @@
       <c r="J870" s="8"/>
       <c r="K870" s="19"/>
       <c r="L870" s="20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M870" s="8"/>
       <c r="N870" s="8"/>
       <c r="O870" s="19"/>
       <c r="P870" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q870" s="8"/>
       <c r="R870" s="8"/>
       <c r="S870" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="T870" s="8"/>
       <c r="U870" s="8"/>
@@ -10649,7 +10662,7 @@
       <c r="W870" s="8"/>
       <c r="X870" s="8"/>
       <c r="Y870" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z870" s="8"/>
       <c r="AA870" s="8"/>
@@ -10662,30 +10675,30 @@
       <c r="E871" s="15"/>
       <c r="K871" s="15"/>
       <c r="L871" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O871" s="15"/>
       <c r="P871" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S871" s="15"/>
       <c r="T871" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Y871" s="15"/>
       <c r="Z871" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AD871" s="22"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
       <c r="B872" s="23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C872" s="12"/>
       <c r="D872" s="12"/>
       <c r="E872" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F872" s="12"/>
       <c r="G872" s="12"/>
@@ -10705,7 +10718,7 @@
       <c r="Q872" s="12"/>
       <c r="R872" s="12"/>
       <c r="S872" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="T872" s="12"/>
       <c r="U872" s="12"/>
@@ -10713,7 +10726,7 @@
       <c r="W872" s="12"/>
       <c r="X872" s="12"/>
       <c r="Y872" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z872" s="12"/>
       <c r="AA872" s="12"/>
@@ -10723,12 +10736,12 @@
     </row>
     <row r="873" ht="15.75" customHeight="1">
       <c r="B873" s="23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C873" s="12"/>
       <c r="D873" s="12"/>
       <c r="E873" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F873" s="12"/>
       <c r="G873" s="12"/>
@@ -10748,7 +10761,7 @@
       <c r="Q873" s="12"/>
       <c r="R873" s="12"/>
       <c r="S873" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="T873" s="12"/>
       <c r="U873" s="12"/>
@@ -10756,7 +10769,7 @@
       <c r="W873" s="12"/>
       <c r="X873" s="12"/>
       <c r="Y873" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z873" s="12"/>
       <c r="AA873" s="12"/>
@@ -10981,54 +10994,66 @@
     </row>
     <row r="921" ht="15.75" customHeight="1">
       <c r="E921" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1">
-      <c r="E923" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="922" ht="15.75" customHeight="1">
+      <c r="E922" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1">
+      <c r="E924" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1">
-      <c r="E925" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
+    <row r="925" ht="15.75" customHeight="1"/>
     <row r="926" ht="15.75" customHeight="1">
       <c r="E926" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="927" ht="15.75" customHeight="1">
       <c r="E927" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="928" ht="15.75" customHeight="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="928" ht="15.75" customHeight="1">
+      <c r="E928" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="D929" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S929" s="1" t="s">
-        <v>43</v>
+      <c r="E929" s="2" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="930" ht="15.75" customHeight="1"/>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="E931" s="2" t="s">
+      <c r="D931" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S931" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1">
+      <c r="E933" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
-      <c r="E932" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1">
+      <c r="E934" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="935" ht="15.75" customHeight="1">
+      <c r="E935" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
     <row r="936" ht="15.75" customHeight="1"/>
     <row r="937" ht="15.75" customHeight="1"/>
     <row r="938" ht="15.75" customHeight="1"/>
@@ -11110,180 +11135,168 @@
     </row>
     <row r="955" ht="15.75" customHeight="1">
       <c r="E955" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1">
-      <c r="D957" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="956" ht="15.75" customHeight="1">
+      <c r="E956" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1">
+      <c r="D958" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S957" s="1" t="s">
+      <c r="S958" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1">
-      <c r="E959" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
+    <row r="959" ht="15.75" customHeight="1"/>
     <row r="960" ht="15.75" customHeight="1">
       <c r="E960" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="961" ht="15.75" customHeight="1">
       <c r="E961" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="962" ht="15.75" customHeight="1">
+      <c r="E962" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1">
-      <c r="J963" s="3" t="s">
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1">
+      <c r="J964" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="R963" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S963" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="964" ht="15.75" customHeight="1">
-      <c r="M964" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="R964" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S964" s="2" t="s">
-        <v>226</v>
+        <v>65</v>
       </c>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="J965" s="3" t="s">
-        <v>227</v>
+      <c r="M965" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="R965" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S965" s="2" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
     </row>
     <row r="966" ht="15.75" customHeight="1">
       <c r="J966" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="R966" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S966" s="2" t="s">
-        <v>65</v>
+        <v>263</v>
       </c>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="M967" s="3" t="s">
-        <v>231</v>
+      <c r="J967" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="R967" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S967" s="2" t="s">
-        <v>226</v>
+        <v>65</v>
       </c>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="J968" s="3" t="s">
-        <v>233</v>
+      <c r="M968" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="R968" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S968" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1">
-      <c r="E970" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="969" ht="15.75" customHeight="1">
+      <c r="J969" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="R969" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S969" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1">
+      <c r="E971" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
-      <c r="E971" s="7" t="s">
+    <row r="972" ht="15.75" customHeight="1">
+      <c r="E972" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F971" s="8"/>
-      <c r="G971" s="8"/>
-      <c r="H971" s="8"/>
-      <c r="I971" s="8"/>
-      <c r="J971" s="8"/>
-      <c r="K971" s="8"/>
-      <c r="L971" s="9" t="s">
+      <c r="F972" s="8"/>
+      <c r="G972" s="8"/>
+      <c r="H972" s="8"/>
+      <c r="I972" s="8"/>
+      <c r="J972" s="8"/>
+      <c r="K972" s="8"/>
+      <c r="L972" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M971" s="8"/>
-      <c r="N971" s="8"/>
-      <c r="O971" s="8"/>
-      <c r="P971" s="8"/>
-      <c r="Q971" s="8"/>
-      <c r="R971" s="8"/>
-      <c r="S971" s="8"/>
-      <c r="T971" s="9" t="s">
+      <c r="M972" s="8"/>
+      <c r="N972" s="8"/>
+      <c r="O972" s="8"/>
+      <c r="P972" s="8"/>
+      <c r="Q972" s="8"/>
+      <c r="R972" s="8"/>
+      <c r="S972" s="8"/>
+      <c r="T972" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="U971" s="8"/>
-      <c r="V971" s="8"/>
-      <c r="W971" s="8"/>
-      <c r="X971" s="8"/>
-      <c r="Y971" s="8"/>
-      <c r="Z971" s="8"/>
-      <c r="AA971" s="8"/>
-      <c r="AB971" s="8"/>
-      <c r="AC971" s="8"/>
-      <c r="AD971" s="10"/>
-    </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="E972" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="F972" s="12"/>
-      <c r="G972" s="12"/>
-      <c r="H972" s="12"/>
-      <c r="I972" s="12"/>
-      <c r="J972" s="12"/>
-      <c r="K972" s="12"/>
-      <c r="L972" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="M972" s="12"/>
-      <c r="N972" s="12"/>
-      <c r="O972" s="12"/>
-      <c r="P972" s="12"/>
-      <c r="Q972" s="12"/>
-      <c r="R972" s="12"/>
-      <c r="S972" s="12"/>
-      <c r="T972" s="14" t="s">
+      <c r="U972" s="8"/>
+      <c r="V972" s="8"/>
+      <c r="W972" s="8"/>
+      <c r="X972" s="8"/>
+      <c r="Y972" s="8"/>
+      <c r="Z972" s="8"/>
+      <c r="AA972" s="8"/>
+      <c r="AB972" s="8"/>
+      <c r="AC972" s="8"/>
+      <c r="AD972" s="10"/>
+    </row>
+    <row r="973" ht="15.75" customHeight="1">
+      <c r="E973" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="F973" s="12"/>
+      <c r="G973" s="12"/>
+      <c r="H973" s="12"/>
+      <c r="I973" s="12"/>
+      <c r="J973" s="12"/>
+      <c r="K973" s="12"/>
+      <c r="L973" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="M973" s="12"/>
+      <c r="N973" s="12"/>
+      <c r="O973" s="12"/>
+      <c r="P973" s="12"/>
+      <c r="Q973" s="12"/>
+      <c r="R973" s="12"/>
+      <c r="S973" s="12"/>
+      <c r="T973" s="14" t="s">
         <v>237</v>
-      </c>
-      <c r="U972" s="12"/>
-      <c r="V972" s="12"/>
-      <c r="W972" s="12"/>
-      <c r="X972" s="12"/>
-      <c r="Y972" s="12"/>
-      <c r="Z972" s="12"/>
-      <c r="AA972" s="12"/>
-      <c r="AB972" s="12"/>
-      <c r="AC972" s="12"/>
-      <c r="AD972" s="10"/>
-    </row>
-    <row r="973" ht="15.75" customHeight="1">
-      <c r="E973" s="10"/>
-      <c r="L973" s="15"/>
-      <c r="T973" s="14" t="s">
-        <v>238</v>
       </c>
       <c r="U973" s="12"/>
       <c r="V973" s="12"/>
@@ -11300,7 +11313,7 @@
       <c r="E974" s="10"/>
       <c r="L974" s="15"/>
       <c r="T974" s="14" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="U974" s="12"/>
       <c r="V974" s="12"/>
@@ -11314,27 +11327,10 @@
       <c r="AD974" s="10"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="E975" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="F975" s="12"/>
-      <c r="G975" s="12"/>
-      <c r="H975" s="12"/>
-      <c r="I975" s="12"/>
-      <c r="J975" s="12"/>
-      <c r="K975" s="12"/>
-      <c r="L975" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="M975" s="12"/>
-      <c r="N975" s="12"/>
-      <c r="O975" s="12"/>
-      <c r="P975" s="12"/>
-      <c r="Q975" s="12"/>
-      <c r="R975" s="12"/>
-      <c r="S975" s="12"/>
+      <c r="E975" s="10"/>
+      <c r="L975" s="15"/>
       <c r="T975" s="14" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="U975" s="12"/>
       <c r="V975" s="12"/>
@@ -11348,10 +11344,27 @@
       <c r="AD975" s="10"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="E976" s="10"/>
-      <c r="L976" s="15"/>
+      <c r="E976" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="F976" s="12"/>
+      <c r="G976" s="12"/>
+      <c r="H976" s="12"/>
+      <c r="I976" s="12"/>
+      <c r="J976" s="12"/>
+      <c r="K976" s="12"/>
+      <c r="L976" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="M976" s="12"/>
+      <c r="N976" s="12"/>
+      <c r="O976" s="12"/>
+      <c r="P976" s="12"/>
+      <c r="Q976" s="12"/>
+      <c r="R976" s="12"/>
+      <c r="S976" s="12"/>
       <c r="T976" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="U976" s="12"/>
       <c r="V976" s="12"/>
@@ -11368,7 +11381,7 @@
       <c r="E977" s="10"/>
       <c r="L977" s="15"/>
       <c r="T977" s="14" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="U977" s="12"/>
       <c r="V977" s="12"/>
@@ -11382,38 +11395,54 @@
       <c r="AD977" s="10"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="E978" s="8"/>
-      <c r="F978" s="8"/>
-      <c r="G978" s="8"/>
-      <c r="H978" s="8"/>
-      <c r="I978" s="8"/>
-      <c r="J978" s="8"/>
-      <c r="K978" s="8"/>
-      <c r="L978" s="8"/>
-      <c r="M978" s="8"/>
-      <c r="N978" s="8"/>
-      <c r="O978" s="8"/>
-      <c r="P978" s="8"/>
-      <c r="Q978" s="8"/>
-      <c r="R978" s="8"/>
-      <c r="S978" s="8"/>
-      <c r="T978" s="8"/>
-      <c r="U978" s="8"/>
-      <c r="V978" s="8"/>
-      <c r="W978" s="8"/>
-      <c r="X978" s="8"/>
-      <c r="Y978" s="8"/>
-      <c r="Z978" s="8"/>
-      <c r="AA978" s="8"/>
-      <c r="AB978" s="8"/>
-      <c r="AC978" s="8"/>
+      <c r="E978" s="10"/>
+      <c r="L978" s="15"/>
+      <c r="T978" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="U978" s="12"/>
+      <c r="V978" s="12"/>
+      <c r="W978" s="12"/>
+      <c r="X978" s="12"/>
+      <c r="Y978" s="12"/>
+      <c r="Z978" s="12"/>
+      <c r="AA978" s="12"/>
+      <c r="AB978" s="12"/>
+      <c r="AC978" s="12"/>
+      <c r="AD978" s="10"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="E979" s="2" t="s">
+      <c r="E979" s="8"/>
+      <c r="F979" s="8"/>
+      <c r="G979" s="8"/>
+      <c r="H979" s="8"/>
+      <c r="I979" s="8"/>
+      <c r="J979" s="8"/>
+      <c r="K979" s="8"/>
+      <c r="L979" s="8"/>
+      <c r="M979" s="8"/>
+      <c r="N979" s="8"/>
+      <c r="O979" s="8"/>
+      <c r="P979" s="8"/>
+      <c r="Q979" s="8"/>
+      <c r="R979" s="8"/>
+      <c r="S979" s="8"/>
+      <c r="T979" s="8"/>
+      <c r="U979" s="8"/>
+      <c r="V979" s="8"/>
+      <c r="W979" s="8"/>
+      <c r="X979" s="8"/>
+      <c r="Y979" s="8"/>
+      <c r="Z979" s="8"/>
+      <c r="AA979" s="8"/>
+      <c r="AB979" s="8"/>
+      <c r="AC979" s="8"/>
+    </row>
+    <row r="980" ht="15.75" customHeight="1">
+      <c r="E980" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="980" ht="15.75" customHeight="1"/>
     <row r="981" ht="15.75" customHeight="1"/>
     <row r="982" ht="15.75" customHeight="1"/>
     <row r="983" ht="15.75" customHeight="1"/>
@@ -11443,7 +11472,7 @@
     <row r="992" ht="15.75" customHeight="1"/>
     <row r="993" ht="15.75" customHeight="1">
       <c r="F993" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="994" ht="15.75" customHeight="1">
@@ -11466,7 +11495,7 @@
         <v>27</v>
       </c>
       <c r="P994" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="U994" s="4" t="s">
         <v>28</v>
@@ -11480,7 +11509,7 @@
         <v>26</v>
       </c>
       <c r="J995" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M995" s="3" t="s">
         <v>30</v>
@@ -11673,7 +11702,7 @@
     <row r="1016" ht="15.75" customHeight="1"/>
     <row r="1017" ht="15.75" customHeight="1">
       <c r="F1017" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="1018" ht="15.75" customHeight="1"/>
@@ -11734,7 +11763,7 @@
         <v>27</v>
       </c>
       <c r="N1027" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S1027" s="4" t="s">
         <v>28</v>
@@ -11754,7 +11783,7 @@
     </row>
     <row r="1028" ht="15.75" customHeight="1">
       <c r="F1028" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="1029" ht="15.75" customHeight="1"/>
@@ -11791,7 +11820,7 @@
         <v>15</v>
       </c>
       <c r="K1040" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1041" ht="15.75" customHeight="1">
@@ -11857,7 +11886,7 @@
         <v>15</v>
       </c>
       <c r="K1046" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1047" ht="15.75" customHeight="1">
@@ -11874,37 +11903,37 @@
     <row r="1048" ht="15.75" customHeight="1"/>
     <row r="1049" ht="15.75" customHeight="1">
       <c r="F1049" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="1050" ht="15.75" customHeight="1"/>
     <row r="1051" ht="15.75" customHeight="1">
       <c r="D1051" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="S1051" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1052" ht="15.75" customHeight="1"/>
     <row r="1053" ht="15.75" customHeight="1">
       <c r="E1053" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="1054" ht="15.75" customHeight="1">
       <c r="E1054" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1055" ht="15.75" customHeight="1">
       <c r="E1055" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1056" ht="15.75" customHeight="1">
       <c r="E1056" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1057" ht="15.75" customHeight="1"/>
@@ -11913,7 +11942,7 @@
       <c r="C1058" s="8"/>
       <c r="D1058" s="8"/>
       <c r="E1058" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F1058" s="8"/>
       <c r="G1058" s="8"/>
@@ -11922,18 +11951,18 @@
       <c r="J1058" s="8"/>
       <c r="K1058" s="19"/>
       <c r="L1058" s="20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M1058" s="8"/>
       <c r="N1058" s="8"/>
       <c r="O1058" s="19"/>
       <c r="P1058" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q1058" s="8"/>
       <c r="R1058" s="8"/>
       <c r="S1058" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="T1058" s="8"/>
       <c r="U1058" s="8"/>
@@ -11941,7 +11970,7 @@
       <c r="W1058" s="8"/>
       <c r="X1058" s="8"/>
       <c r="Y1058" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z1058" s="8"/>
       <c r="AA1058" s="8"/>
@@ -11954,30 +11983,30 @@
       <c r="E1059" s="15"/>
       <c r="K1059" s="15"/>
       <c r="L1059" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O1059" s="15"/>
       <c r="P1059" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S1059" s="15"/>
       <c r="T1059" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Y1059" s="15"/>
       <c r="Z1059" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AD1059" s="22"/>
     </row>
     <row r="1060" ht="15.75" customHeight="1">
       <c r="B1060" s="23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C1060" s="12"/>
       <c r="D1060" s="12"/>
       <c r="E1060" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F1060" s="12"/>
       <c r="G1060" s="12"/>
@@ -11997,7 +12026,7 @@
       <c r="Q1060" s="12"/>
       <c r="R1060" s="12"/>
       <c r="S1060" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="T1060" s="12"/>
       <c r="U1060" s="12"/>
@@ -12005,7 +12034,7 @@
       <c r="W1060" s="12"/>
       <c r="X1060" s="12"/>
       <c r="Y1060" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z1060" s="12"/>
       <c r="AA1060" s="12"/>
@@ -12015,12 +12044,12 @@
     </row>
     <row r="1061" ht="15.75" customHeight="1">
       <c r="B1061" s="23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1061" s="12"/>
       <c r="D1061" s="12"/>
       <c r="E1061" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F1061" s="12"/>
       <c r="G1061" s="12"/>
@@ -12040,7 +12069,7 @@
       <c r="Q1061" s="12"/>
       <c r="R1061" s="12"/>
       <c r="S1061" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="T1061" s="12"/>
       <c r="U1061" s="12"/>
@@ -12048,7 +12077,7 @@
       <c r="W1061" s="12"/>
       <c r="X1061" s="12"/>
       <c r="Y1061" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z1061" s="12"/>
       <c r="AA1061" s="12"/>
@@ -12108,193 +12137,193 @@
     <row r="1081" ht="15.75" customHeight="1"/>
     <row r="1082" ht="15.75" customHeight="1">
       <c r="B1082" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="1083" ht="15.75" customHeight="1"/>
     <row r="1084" ht="15.75" customHeight="1">
       <c r="C1084" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="1085" ht="15.75" customHeight="1"/>
     <row r="1086" ht="15.75" customHeight="1">
       <c r="D1086" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="S1086" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="S1086" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="1087" ht="15.75" customHeight="1"/>
     <row r="1088" ht="15.75" customHeight="1">
       <c r="E1088" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="1089" ht="15.75" customHeight="1">
       <c r="E1089" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1090" ht="15.75" customHeight="1"/>
     <row r="1091" ht="15.75" customHeight="1">
       <c r="D1091" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="S1091" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="S1091" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="1092" ht="15.75" customHeight="1"/>
     <row r="1093" ht="15.75" customHeight="1">
       <c r="E1093" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="1094" ht="15.75" customHeight="1"/>
     <row r="1095" ht="15.75" customHeight="1">
       <c r="N1095" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R1095" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1095" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1096" ht="15.75" customHeight="1">
       <c r="K1096" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R1096" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1096" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="1097" ht="15.75" customHeight="1"/>
     <row r="1098" ht="15.75" customHeight="1">
       <c r="F1098" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="1099" ht="15.75" customHeight="1"/>
     <row r="1100" ht="15.75" customHeight="1">
       <c r="E1100" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1101" ht="15.75" customHeight="1">
       <c r="E1101" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="1102" ht="15.75" customHeight="1">
       <c r="E1102" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="1103" ht="15.75" customHeight="1"/>
     <row r="1104" ht="15.75" customHeight="1">
       <c r="N1104" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R1104" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1104" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1105" ht="15.75" customHeight="1">
       <c r="L1105" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R1105" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1105" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1106" ht="15.75" customHeight="1"/>
     <row r="1107" ht="15.75" customHeight="1">
       <c r="F1107" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="1108" ht="15.75" customHeight="1"/>
     <row r="1109" ht="15.75" customHeight="1">
       <c r="E1109" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1110" ht="15.75" customHeight="1"/>
     <row r="1111" ht="15.75" customHeight="1">
       <c r="D1111" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="S1111" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="S1111" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="1112" ht="15.75" customHeight="1"/>
     <row r="1113" ht="15.75" customHeight="1">
       <c r="E1113" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1114" ht="15.75" customHeight="1">
       <c r="E1114" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1115" ht="15.75" customHeight="1">
       <c r="E1115" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1116" ht="15.75" customHeight="1">
       <c r="E1116" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1117" ht="15.75" customHeight="1">
       <c r="E1117" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1118" ht="15.75" customHeight="1">
       <c r="E1118" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1119" ht="15.75" customHeight="1">
       <c r="E1119" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1120" ht="15.75" customHeight="1">
       <c r="E1120" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="1121" ht="15.75" customHeight="1">
       <c r="E1121" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="1122" ht="15.75" customHeight="1">
       <c r="E1122" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1123" ht="15.75" customHeight="1">
       <c r="E1123" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="1124" ht="15.75" customHeight="1"/>
@@ -12304,71 +12333,71 @@
     <row r="1128" ht="15.75" customHeight="1"/>
     <row r="1129" ht="15.75" customHeight="1">
       <c r="D1129" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1130" ht="15.75" customHeight="1"/>
     <row r="1131" ht="15.75" customHeight="1">
       <c r="E1131" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="S1131" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="S1131" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="1132" ht="15.75" customHeight="1"/>
     <row r="1133" ht="15.75" customHeight="1">
       <c r="E1133" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1134" ht="15.75" customHeight="1">
       <c r="E1134" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1135" ht="15.75" customHeight="1">
       <c r="E1135" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="1136" ht="15.75" customHeight="1">
       <c r="E1136" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1137" ht="15.75" customHeight="1">
       <c r="E1137" s="18"/>
       <c r="F1137" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G1137" s="8"/>
       <c r="H1137" s="8"/>
       <c r="I1137" s="8"/>
       <c r="J1137" s="19"/>
       <c r="K1137" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L1137" s="8"/>
       <c r="M1137" s="8"/>
       <c r="N1137" s="8"/>
       <c r="O1137" s="19"/>
       <c r="P1137" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q1137" s="8"/>
       <c r="R1137" s="8"/>
       <c r="S1137" s="8"/>
       <c r="T1137" s="19"/>
       <c r="U1137" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="V1137" s="8"/>
       <c r="W1137" s="8"/>
       <c r="X1137" s="8"/>
       <c r="Y1137" s="19"/>
       <c r="Z1137" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AA1137" s="8"/>
       <c r="AB1137" s="8"/>
@@ -12378,23 +12407,23 @@
     <row r="1138" ht="15.75" customHeight="1">
       <c r="E1138" s="10"/>
       <c r="F1138" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J1138" s="15"/>
       <c r="K1138" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O1138" s="15"/>
       <c r="P1138" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="T1138" s="15"/>
       <c r="U1138" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Y1138" s="15"/>
       <c r="Z1138" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AD1138" s="10"/>
     </row>
@@ -12617,93 +12646,93 @@
     </row>
     <row r="1145" ht="15.75" customHeight="1">
       <c r="E1145" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1146" ht="15.75" customHeight="1">
       <c r="E1146" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="1147" ht="15.75" customHeight="1"/>
     <row r="1148" ht="15.75" customHeight="1">
       <c r="E1148" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S1148" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1149" ht="15.75" customHeight="1"/>
     <row r="1150" ht="15.75" customHeight="1">
       <c r="E1150" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1151" ht="15.75" customHeight="1"/>
     <row r="1152" ht="15.75" customHeight="1">
       <c r="F1152" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="1153" ht="15.75" customHeight="1"/>
     <row r="1154" ht="15.75" customHeight="1">
       <c r="E1154" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="1155" ht="15.75" customHeight="1"/>
     <row r="1156" ht="15.75" customHeight="1">
       <c r="E1156" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="S1156" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1157" ht="15.75" customHeight="1"/>
     <row r="1158" ht="15.75" customHeight="1">
       <c r="E1158" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="1159" ht="15.75" customHeight="1"/>
     <row r="1160" ht="15.75" customHeight="1">
       <c r="F1160" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1161" ht="15.75" customHeight="1"/>
     <row r="1162" ht="15.75" customHeight="1">
       <c r="E1162" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1163" ht="15.75" customHeight="1"/>
     <row r="1164" ht="15.75" customHeight="1">
       <c r="E1164" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S1164" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1165" ht="15.75" customHeight="1"/>
     <row r="1166" ht="15.75" customHeight="1">
       <c r="E1166" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="1167" ht="15.75" customHeight="1"/>
     <row r="1168" ht="15.75" customHeight="1">
       <c r="F1168" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="1169" ht="15.75" customHeight="1"/>
     <row r="1170" ht="15.75" customHeight="1">
       <c r="E1170" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1171" ht="15.75" customHeight="1"/>
@@ -12713,18 +12742,18 @@
     <row r="1175" ht="15.75" customHeight="1"/>
     <row r="1176" ht="15.75" customHeight="1">
       <c r="D1176" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="1177" ht="15.75" customHeight="1"/>
     <row r="1178" ht="15.75" customHeight="1">
       <c r="B1178" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1179" ht="15.75" customHeight="1">
       <c r="B1179" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1179" s="8"/>
       <c r="D1179" s="8"/>
@@ -12734,7 +12763,7 @@
       <c r="H1179" s="8"/>
       <c r="I1179" s="8"/>
       <c r="J1179" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K1179" s="8"/>
       <c r="L1179" s="8"/>
@@ -12745,7 +12774,7 @@
       <c r="Q1179" s="8"/>
       <c r="R1179" s="8"/>
       <c r="S1179" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T1179" s="8"/>
       <c r="U1179" s="8"/>
@@ -12753,7 +12782,7 @@
       <c r="W1179" s="8"/>
       <c r="X1179" s="8"/>
       <c r="Y1179" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z1179" s="8"/>
       <c r="AA1179" s="9" t="s">
@@ -12765,7 +12794,7 @@
     </row>
     <row r="1180" ht="15.75" customHeight="1">
       <c r="B1180" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C1180" s="12"/>
       <c r="D1180" s="12"/>
@@ -12775,7 +12804,7 @@
       <c r="H1180" s="12"/>
       <c r="I1180" s="12"/>
       <c r="J1180" s="14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K1180" s="12"/>
       <c r="L1180" s="12"/>
@@ -12786,7 +12815,7 @@
       <c r="Q1180" s="12"/>
       <c r="R1180" s="12"/>
       <c r="S1180" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T1180" s="12"/>
       <c r="U1180" s="12"/>
@@ -12794,11 +12823,11 @@
       <c r="W1180" s="12"/>
       <c r="X1180" s="12"/>
       <c r="Y1180" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1180" s="12"/>
       <c r="AA1180" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1180" s="12"/>
       <c r="AC1180" s="12"/>
@@ -12806,7 +12835,7 @@
     </row>
     <row r="1181" ht="15.75" customHeight="1">
       <c r="B1181" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C1181" s="12"/>
       <c r="D1181" s="12"/>
@@ -12816,7 +12845,7 @@
       <c r="H1181" s="12"/>
       <c r="I1181" s="12"/>
       <c r="J1181" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K1181" s="12"/>
       <c r="L1181" s="12"/>
@@ -12827,7 +12856,7 @@
       <c r="Q1181" s="12"/>
       <c r="R1181" s="12"/>
       <c r="S1181" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="T1181" s="12"/>
       <c r="U1181" s="12"/>
@@ -12835,11 +12864,11 @@
       <c r="W1181" s="12"/>
       <c r="X1181" s="12"/>
       <c r="Y1181" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1181" s="12"/>
       <c r="AA1181" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1181" s="12"/>
       <c r="AC1181" s="12"/>
@@ -12848,7 +12877,7 @@
     <row r="1182" ht="15.75" customHeight="1">
       <c r="B1182" s="10"/>
       <c r="J1182" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K1182" s="12"/>
       <c r="L1182" s="12"/>
@@ -12859,7 +12888,7 @@
       <c r="Q1182" s="12"/>
       <c r="R1182" s="12"/>
       <c r="S1182" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="T1182" s="12"/>
       <c r="U1182" s="12"/>
@@ -12867,7 +12896,7 @@
       <c r="W1182" s="12"/>
       <c r="X1182" s="12"/>
       <c r="Y1182" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1182" s="12"/>
       <c r="AA1182" s="15"/>
@@ -12875,7 +12904,7 @@
     </row>
     <row r="1183" ht="15.75" customHeight="1">
       <c r="B1183" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C1183" s="12"/>
       <c r="D1183" s="12"/>
@@ -12885,7 +12914,7 @@
       <c r="H1183" s="12"/>
       <c r="I1183" s="12"/>
       <c r="J1183" s="14" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K1183" s="12"/>
       <c r="L1183" s="12"/>
@@ -12896,7 +12925,7 @@
       <c r="Q1183" s="12"/>
       <c r="R1183" s="12"/>
       <c r="S1183" s="14" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="T1183" s="12"/>
       <c r="U1183" s="12"/>
@@ -12904,11 +12933,11 @@
       <c r="W1183" s="12"/>
       <c r="X1183" s="12"/>
       <c r="Y1183" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1183" s="12"/>
       <c r="AA1183" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1183" s="12"/>
       <c r="AC1183" s="12"/>
@@ -12917,7 +12946,7 @@
     <row r="1184" ht="15.75" customHeight="1">
       <c r="B1184" s="10"/>
       <c r="J1184" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K1184" s="12"/>
       <c r="L1184" s="12"/>
@@ -12928,7 +12957,7 @@
       <c r="Q1184" s="12"/>
       <c r="R1184" s="12"/>
       <c r="S1184" s="14" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="T1184" s="12"/>
       <c r="U1184" s="12"/>
@@ -12936,7 +12965,7 @@
       <c r="W1184" s="12"/>
       <c r="X1184" s="12"/>
       <c r="Y1184" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1184" s="12"/>
       <c r="AA1184" s="15"/>
@@ -12944,7 +12973,7 @@
     </row>
     <row r="1185" ht="15.75" customHeight="1">
       <c r="B1185" s="23" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C1185" s="12"/>
       <c r="D1185" s="12"/>
@@ -12954,7 +12983,7 @@
       <c r="H1185" s="12"/>
       <c r="I1185" s="12"/>
       <c r="J1185" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K1185" s="12"/>
       <c r="L1185" s="12"/>
@@ -12965,7 +12994,7 @@
       <c r="Q1185" s="12"/>
       <c r="R1185" s="12"/>
       <c r="S1185" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="T1185" s="12"/>
       <c r="U1185" s="12"/>
@@ -12973,11 +13002,11 @@
       <c r="W1185" s="12"/>
       <c r="X1185" s="12"/>
       <c r="Y1185" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1185" s="12"/>
       <c r="AA1185" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1185" s="12"/>
       <c r="AC1185" s="12"/>
@@ -12985,7 +13014,7 @@
     </row>
     <row r="1186" ht="15.75" customHeight="1">
       <c r="B1186" s="23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C1186" s="12"/>
       <c r="D1186" s="12"/>
@@ -12995,7 +13024,7 @@
       <c r="H1186" s="12"/>
       <c r="I1186" s="12"/>
       <c r="J1186" s="14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K1186" s="12"/>
       <c r="L1186" s="12"/>
@@ -13006,7 +13035,7 @@
       <c r="Q1186" s="12"/>
       <c r="R1186" s="12"/>
       <c r="S1186" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="T1186" s="12"/>
       <c r="U1186" s="12"/>
@@ -13014,11 +13043,11 @@
       <c r="W1186" s="12"/>
       <c r="X1186" s="12"/>
       <c r="Y1186" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1186" s="12"/>
       <c r="AA1186" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1186" s="12"/>
       <c r="AC1186" s="12"/>
@@ -13026,7 +13055,7 @@
     </row>
     <row r="1187" ht="15.75" customHeight="1">
       <c r="B1187" s="23" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C1187" s="12"/>
       <c r="D1187" s="12"/>
@@ -13036,7 +13065,7 @@
       <c r="H1187" s="12"/>
       <c r="I1187" s="12"/>
       <c r="J1187" s="14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K1187" s="12"/>
       <c r="L1187" s="12"/>
@@ -13047,7 +13076,7 @@
       <c r="Q1187" s="12"/>
       <c r="R1187" s="12"/>
       <c r="S1187" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T1187" s="12"/>
       <c r="U1187" s="12"/>
@@ -13055,11 +13084,11 @@
       <c r="W1187" s="12"/>
       <c r="X1187" s="12"/>
       <c r="Y1187" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1187" s="12"/>
       <c r="AA1187" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1187" s="12"/>
       <c r="AC1187" s="12"/>
@@ -13067,7 +13096,7 @@
     </row>
     <row r="1188" ht="15.75" customHeight="1">
       <c r="B1188" s="23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C1188" s="12"/>
       <c r="D1188" s="12"/>
@@ -13077,7 +13106,7 @@
       <c r="H1188" s="12"/>
       <c r="I1188" s="12"/>
       <c r="J1188" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K1188" s="12"/>
       <c r="L1188" s="12"/>
@@ -13088,7 +13117,7 @@
       <c r="Q1188" s="12"/>
       <c r="R1188" s="12"/>
       <c r="S1188" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T1188" s="12"/>
       <c r="U1188" s="12"/>
@@ -13096,11 +13125,11 @@
       <c r="W1188" s="12"/>
       <c r="X1188" s="12"/>
       <c r="Y1188" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1188" s="12"/>
       <c r="AA1188" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1188" s="12"/>
       <c r="AC1188" s="12"/>
@@ -13139,69 +13168,69 @@
     </row>
     <row r="1190" ht="15.75" customHeight="1">
       <c r="C1190" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1191" ht="15.75" customHeight="1"/>
     <row r="1192" ht="15.75" customHeight="1">
       <c r="D1192" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="S1192" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="S1192" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="1193" ht="15.75" customHeight="1"/>
     <row r="1194" ht="15.75" customHeight="1">
       <c r="E1194" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="1195" ht="15.75" customHeight="1">
       <c r="E1195" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="1196" ht="15.75" customHeight="1">
       <c r="E1196" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="1197" ht="15.75" customHeight="1"/>
     <row r="1198" ht="15.75" customHeight="1">
       <c r="D1198" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="S1198" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="S1198" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="1199" ht="15.75" customHeight="1"/>
     <row r="1200" ht="15.75" customHeight="1">
       <c r="E1200" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="1201" ht="15.75" customHeight="1"/>
     <row r="1202" ht="15.75" customHeight="1">
       <c r="E1202" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="1203" ht="15.75" customHeight="1">
       <c r="E1203" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="1204" ht="15.75" customHeight="1">
       <c r="F1204" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="1205" ht="15.75" customHeight="1"/>
     <row r="1206" ht="15.75" customHeight="1">
       <c r="E1206" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="1207" ht="15.75" customHeight="1"/>
@@ -13222,27 +13251,27 @@
     <row r="1222" ht="15.75" customHeight="1"/>
     <row r="1223" ht="15.75" customHeight="1">
       <c r="D1223" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="S1223" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="S1223" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="1224" ht="15.75" customHeight="1"/>
     <row r="1225" ht="15.75" customHeight="1">
       <c r="E1225" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1226" ht="15.75" customHeight="1">
       <c r="E1226" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="1227" ht="15.75" customHeight="1"/>
     <row r="1228" ht="15.75" customHeight="1">
       <c r="F1228" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="1229" ht="15.75" customHeight="1"/>
@@ -13254,18 +13283,18 @@
         <v>15</v>
       </c>
       <c r="S1230" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1231" ht="15.75" customHeight="1">
       <c r="M1231" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R1231" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1231" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="1232" ht="15.75" customHeight="1">
@@ -13276,7 +13305,7 @@
         <v>15</v>
       </c>
       <c r="S1232" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="1233" ht="15.75" customHeight="1"/>
@@ -13306,7 +13335,7 @@
       <c r="R1235" s="8"/>
       <c r="S1235" s="8"/>
       <c r="T1235" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U1235" s="8"/>
       <c r="V1235" s="8"/>
@@ -13321,7 +13350,7 @@
     </row>
     <row r="1236" ht="15.75" customHeight="1">
       <c r="E1236" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F1236" s="12"/>
       <c r="G1236" s="12"/>
@@ -13330,7 +13359,7 @@
       <c r="J1236" s="12"/>
       <c r="K1236" s="12"/>
       <c r="L1236" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M1236" s="12"/>
       <c r="N1236" s="12"/>
@@ -13357,7 +13386,7 @@
       <c r="E1237" s="10"/>
       <c r="L1237" s="15"/>
       <c r="T1237" s="14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U1237" s="12"/>
       <c r="V1237" s="12"/>
@@ -13374,7 +13403,7 @@
       <c r="E1238" s="10"/>
       <c r="L1238" s="15"/>
       <c r="T1238" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="U1238" s="12"/>
       <c r="V1238" s="12"/>
@@ -13416,84 +13445,84 @@
     </row>
     <row r="1240" ht="15.75" customHeight="1">
       <c r="E1240" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="1241" ht="15.75" customHeight="1">
       <c r="E1241" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1242" ht="15.75" customHeight="1"/>
     <row r="1243" ht="15.75" customHeight="1">
       <c r="E1243" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="1244" ht="15.75" customHeight="1">
       <c r="F1244" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="1245" ht="15.75" customHeight="1"/>
     <row r="1246" ht="15.75" customHeight="1">
       <c r="E1246" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="1247" ht="15.75" customHeight="1"/>
     <row r="1248" ht="15.75" customHeight="1">
       <c r="D1248" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="S1248" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1249" ht="15.75" customHeight="1"/>
     <row r="1250" ht="15.75" customHeight="1">
       <c r="E1250" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="1251" ht="15.75" customHeight="1"/>
     <row r="1252" ht="15.75" customHeight="1">
       <c r="E1252" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1253" ht="15.75" customHeight="1">
       <c r="F1253" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="1254" ht="15.75" customHeight="1"/>
     <row r="1255" ht="15.75" customHeight="1">
       <c r="F1255" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J1255" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1255" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="1256" ht="15.75" customHeight="1">
       <c r="I1256" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J1256" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1256" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="1257" ht="15.75" customHeight="1"/>
     <row r="1258" ht="15.75" customHeight="1">
       <c r="H1258" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I1258" s="4" t="s">
         <v>26</v>
@@ -13505,7 +13534,7 @@
         <v>27</v>
       </c>
       <c r="N1258" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="T1258" s="4" t="s">
         <v>28</v>
@@ -13525,28 +13554,28 @@
     </row>
     <row r="1259" ht="15.75" customHeight="1">
       <c r="F1259" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="1260" ht="15.75" customHeight="1"/>
     <row r="1261" ht="15.75" customHeight="1">
       <c r="E1261" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="1262" ht="15.75" customHeight="1"/>
     <row r="1263" ht="15.75" customHeight="1">
       <c r="D1263" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="S1263" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1264" ht="15.75" customHeight="1"/>
     <row r="1265" ht="15.75" customHeight="1">
       <c r="E1265" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="1266" ht="15.75" customHeight="1"/>
@@ -13555,12 +13584,12 @@
     <row r="1269" ht="15.75" customHeight="1"/>
     <row r="1270" ht="15.75" customHeight="1">
       <c r="E1270" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1271" ht="15.75" customHeight="1">
       <c r="H1271" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I1271" s="4" t="s">
         <v>26</v>
@@ -13572,7 +13601,7 @@
         <v>27</v>
       </c>
       <c r="N1271" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="T1271" s="4" t="s">
         <v>28</v>
@@ -13592,62 +13621,62 @@
     </row>
     <row r="1272" ht="15.75" customHeight="1">
       <c r="F1272" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1273" ht="15.75" customHeight="1"/>
     <row r="1274" ht="15.75" customHeight="1">
       <c r="E1274" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="1275" ht="15.75" customHeight="1"/>
     <row r="1276" ht="15.75" customHeight="1">
       <c r="D1276" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="1277" ht="15.75" customHeight="1"/>
     <row r="1278" ht="15.75" customHeight="1">
       <c r="E1278" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="T1278" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="T1278" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="1279" ht="15.75" customHeight="1"/>
     <row r="1280" ht="15.75" customHeight="1">
       <c r="E1280" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="1281" ht="15.75" customHeight="1">
       <c r="F1281" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="1282" ht="15.75" customHeight="1"/>
     <row r="1283" ht="15.75" customHeight="1">
       <c r="E1283" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J1283" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1283" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1284" ht="15.75" customHeight="1">
       <c r="H1284" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J1284" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1284" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="1285" ht="15.75" customHeight="1">
@@ -13658,7 +13687,7 @@
         <v>15</v>
       </c>
       <c r="K1285" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="1286" ht="15.75" customHeight="1">
@@ -13669,51 +13698,51 @@
         <v>15</v>
       </c>
       <c r="K1286" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1287" ht="15.75" customHeight="1">
       <c r="H1287" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J1287" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1287" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="1288" ht="15.75" customHeight="1">
       <c r="H1288" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J1288" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1288" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1289" ht="15.75" customHeight="1">
       <c r="H1289" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J1289" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1289" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1290" ht="15.75" customHeight="1">
       <c r="H1290" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J1290" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1290" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1291" ht="15.75" customHeight="1"/>
@@ -13740,12 +13769,12 @@
         <v>20.8</v>
       </c>
       <c r="AC1292" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1293" ht="15.75" customHeight="1">
       <c r="H1293" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I1293" s="4" t="s">
         <v>26</v>
@@ -13754,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="K1293" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L1293" s="5">
         <v>0.5</v>
@@ -13780,7 +13809,7 @@
     </row>
     <row r="1294" ht="15.75" customHeight="1">
       <c r="G1294" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I1294" s="4" t="s">
         <v>26</v>
@@ -13792,7 +13821,7 @@
         <v>28</v>
       </c>
       <c r="M1294" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="U1294" s="4" t="s">
         <v>28</v>
@@ -13813,130 +13842,130 @@
     <row r="1295" ht="15.75" customHeight="1"/>
     <row r="1296" ht="15.75" customHeight="1">
       <c r="E1296" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1297" ht="15.75" customHeight="1">
       <c r="E1297" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1298" ht="15.75" customHeight="1"/>
     <row r="1299" ht="15.75" customHeight="1">
       <c r="F1299" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="1300" ht="15.75" customHeight="1"/>
     <row r="1301" ht="15.75" customHeight="1">
       <c r="E1301" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1302" ht="15.75" customHeight="1"/>
     <row r="1303" ht="15.75" customHeight="1">
       <c r="F1303" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1304" ht="15.75" customHeight="1"/>
     <row r="1305" ht="15.75" customHeight="1">
       <c r="E1305" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S1305" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1306" ht="15.75" customHeight="1"/>
     <row r="1307" ht="15.75" customHeight="1">
       <c r="E1307" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="1308" ht="15.75" customHeight="1">
       <c r="E1308" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1309" ht="15.75" customHeight="1"/>
     <row r="1310" ht="15.75" customHeight="1">
       <c r="F1310" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1311" ht="15.75" customHeight="1"/>
     <row r="1312" ht="15.75" customHeight="1">
       <c r="F1312" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J1312" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1312" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="1313" ht="15.75" customHeight="1">
       <c r="H1313" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J1313" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1313" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1314" ht="15.75" customHeight="1"/>
     <row r="1315" ht="15.75" customHeight="1">
       <c r="F1315" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1316" ht="15.75" customHeight="1">
       <c r="F1316" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1317" ht="15.75" customHeight="1">
       <c r="E1317" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="S1317" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1318" ht="15.75" customHeight="1"/>
     <row r="1319" ht="15.75" customHeight="1">
       <c r="E1319" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1320" ht="15.75" customHeight="1">
       <c r="E1320" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1321" ht="15.75" customHeight="1">
       <c r="E1321" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1322" ht="15.75" customHeight="1"/>
     <row r="1323" ht="15.75" customHeight="1">
       <c r="F1323" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1324" ht="15.75" customHeight="1">
       <c r="F1324" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1325" ht="15.75" customHeight="1">
       <c r="G1325" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I1325" s="4" t="s">
         <v>26</v>
@@ -13954,7 +13983,7 @@
         <v>27</v>
       </c>
       <c r="P1325" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="T1325" s="4" t="s">
         <v>28</v>
@@ -13974,7 +14003,7 @@
     </row>
     <row r="1326" ht="15.75" customHeight="1">
       <c r="H1326" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I1326" s="4" t="s">
         <v>26</v>
@@ -13983,7 +14012,7 @@
         <v>100</v>
       </c>
       <c r="L1326" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M1326" s="6">
         <v>1170</v>
@@ -14001,92 +14030,92 @@
     <row r="1327" ht="15.75" customHeight="1"/>
     <row r="1328" ht="15.75" customHeight="1">
       <c r="D1328" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="S1328" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1329" ht="15.75" customHeight="1"/>
     <row r="1330" ht="15.75" customHeight="1">
       <c r="E1330" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1331" ht="15.75" customHeight="1">
       <c r="E1331" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1332" ht="15.75" customHeight="1">
       <c r="E1332" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1333" ht="15.75" customHeight="1"/>
     <row r="1334" ht="15.75" customHeight="1">
       <c r="F1334" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1335" ht="15.75" customHeight="1"/>
     <row r="1336" ht="15.75" customHeight="1">
       <c r="F1336" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J1336" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1336" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1337" ht="15.75" customHeight="1"/>
     <row r="1338" ht="15.75" customHeight="1">
       <c r="F1338" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1339" ht="15.75" customHeight="1">
       <c r="F1339" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1340" ht="15.75" customHeight="1">
       <c r="F1340" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1341" ht="15.75" customHeight="1"/>
     <row r="1342" ht="15.75" customHeight="1">
       <c r="D1342" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1343" ht="15.75" customHeight="1"/>
     <row r="1344" ht="15.75" customHeight="1">
       <c r="E1344" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="S1344" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1345" ht="15.75" customHeight="1"/>
     <row r="1346" ht="15.75" customHeight="1">
       <c r="E1346" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1347" ht="15.75" customHeight="1">
       <c r="E1347" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1348" ht="15.75" customHeight="1"/>
     <row r="1349" ht="15.75" customHeight="1">
       <c r="L1349" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="R1349" s="4" t="s">
         <v>15</v>
@@ -14097,24 +14126,24 @@
     </row>
     <row r="1350" ht="15.75" customHeight="1">
       <c r="N1350" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="R1350" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1350" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1351" ht="15.75" customHeight="1"/>
     <row r="1352" ht="15.75" customHeight="1">
       <c r="E1352" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1353" ht="15.75" customHeight="1">
       <c r="E1353" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1354" ht="15.75" customHeight="1"/>
@@ -14129,36 +14158,36 @@
     <row r="1363" ht="15.75" customHeight="1"/>
     <row r="1364" ht="15.75" customHeight="1">
       <c r="E1364" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="S1364" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1365" ht="15.75" customHeight="1"/>
     <row r="1366" ht="15.75" customHeight="1">
       <c r="E1366" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1367" ht="15.75" customHeight="1">
       <c r="E1367" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1368" ht="15.75" customHeight="1">
       <c r="E1368" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1369" ht="15.75" customHeight="1">
       <c r="E1369" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1370" ht="15.75" customHeight="1">
       <c r="E1370" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F1370" s="8"/>
       <c r="G1370" s="8"/>
@@ -14175,14 +14204,14 @@
       <c r="R1370" s="8"/>
       <c r="S1370" s="8"/>
       <c r="T1370" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="U1370" s="8"/>
       <c r="V1370" s="8"/>
       <c r="W1370" s="8"/>
       <c r="X1370" s="8"/>
       <c r="Y1370" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Z1370" s="8"/>
       <c r="AA1370" s="8"/>
@@ -14192,14 +14221,14 @@
     </row>
     <row r="1371" ht="15.75" customHeight="1">
       <c r="E1371" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F1371" s="12"/>
       <c r="G1371" s="12"/>
       <c r="H1371" s="12"/>
       <c r="I1371" s="12"/>
       <c r="J1371" s="14" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K1371" s="12"/>
       <c r="L1371" s="12"/>
@@ -14211,14 +14240,14 @@
       <c r="R1371" s="12"/>
       <c r="S1371" s="12"/>
       <c r="T1371" s="14" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U1371" s="12"/>
       <c r="V1371" s="12"/>
       <c r="W1371" s="12"/>
       <c r="X1371" s="12"/>
       <c r="Y1371" s="14" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Z1371" s="12"/>
       <c r="AA1371" s="12"/>
@@ -14229,7 +14258,7 @@
     <row r="1372" ht="15.75" customHeight="1">
       <c r="E1372" s="10"/>
       <c r="J1372" s="14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K1372" s="12"/>
       <c r="L1372" s="12"/>
@@ -14241,14 +14270,14 @@
       <c r="R1372" s="12"/>
       <c r="S1372" s="12"/>
       <c r="T1372" s="14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="U1372" s="12"/>
       <c r="V1372" s="12"/>
       <c r="W1372" s="12"/>
       <c r="X1372" s="12"/>
       <c r="Y1372" s="14" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Z1372" s="12"/>
       <c r="AA1372" s="12"/>
@@ -14258,14 +14287,14 @@
     </row>
     <row r="1373" ht="15.75" customHeight="1">
       <c r="E1373" s="23" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F1373" s="12"/>
       <c r="G1373" s="12"/>
       <c r="H1373" s="12"/>
       <c r="I1373" s="12"/>
       <c r="J1373" s="14" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K1373" s="12"/>
       <c r="L1373" s="12"/>
@@ -14277,7 +14306,7 @@
       <c r="R1373" s="12"/>
       <c r="S1373" s="12"/>
       <c r="T1373" s="13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="U1373" s="12"/>
       <c r="V1373" s="12"/>
@@ -14319,23 +14348,23 @@
     </row>
     <row r="1375" ht="15.75" customHeight="1">
       <c r="F1375" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1376" ht="15.75" customHeight="1">
       <c r="F1376" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1377" ht="15.75" customHeight="1">
       <c r="F1377" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1378" ht="15.75" customHeight="1"/>
     <row r="1379" ht="15.75" customHeight="1">
       <c r="E1379" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1380" ht="15.75" customHeight="1"/>
@@ -14371,110 +14400,110 @@
     <row r="1410" ht="15.75" customHeight="1"/>
     <row r="1411" ht="15.75" customHeight="1">
       <c r="D1411" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1412" ht="15.75" customHeight="1"/>
     <row r="1413" ht="15.75" customHeight="1">
       <c r="E1413" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S1413" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="1414" ht="15.75" customHeight="1"/>
     <row r="1415" ht="15.75" customHeight="1">
       <c r="E1415" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1416" ht="15.75" customHeight="1">
       <c r="E1416" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1417" ht="15.75" customHeight="1">
       <c r="E1417" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1418" ht="15.75" customHeight="1"/>
     <row r="1419" ht="15.75" customHeight="1">
       <c r="L1419" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R1419" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1419" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1420" ht="15.75" customHeight="1">
       <c r="L1420" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="R1420" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1420" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1421" ht="15.75" customHeight="1"/>
     <row r="1422" ht="15.75" customHeight="1">
       <c r="E1422" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="1423" ht="15.75" customHeight="1">
       <c r="E1423" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1424" ht="15.75" customHeight="1"/>
     <row r="1425" ht="15.75" customHeight="1">
       <c r="J1425" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R1425" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1425" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1426" ht="15.75" customHeight="1">
       <c r="M1426" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="R1426" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1426" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1427" ht="15.75" customHeight="1"/>
     <row r="1428" ht="15.75" customHeight="1">
       <c r="E1428" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="1429" ht="15.75" customHeight="1">
       <c r="E1429" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1430" ht="15.75" customHeight="1">
       <c r="E1430" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1431" ht="15.75" customHeight="1">
       <c r="E1431" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F1431" s="8"/>
       <c r="G1431" s="8"/>
@@ -14482,25 +14511,25 @@
       <c r="I1431" s="8"/>
       <c r="J1431" s="8"/>
       <c r="K1431" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L1431" s="8"/>
       <c r="M1431" s="8"/>
       <c r="N1431" s="8"/>
       <c r="O1431" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P1431" s="8"/>
       <c r="Q1431" s="8"/>
       <c r="R1431" s="8"/>
       <c r="S1431" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="T1431" s="8"/>
       <c r="U1431" s="8"/>
       <c r="V1431" s="8"/>
       <c r="W1431" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="X1431" s="8"/>
       <c r="Y1431" s="8"/>
@@ -14509,7 +14538,7 @@
     </row>
     <row r="1432" ht="15.75" customHeight="1">
       <c r="E1432" s="23" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F1432" s="12"/>
       <c r="G1432" s="12"/>
@@ -14568,60 +14597,60 @@
     </row>
     <row r="1434" ht="15.75" customHeight="1">
       <c r="F1434" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1435" ht="15.75" customHeight="1"/>
     <row r="1436" ht="15.75" customHeight="1">
       <c r="E1436" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1437" ht="15.75" customHeight="1">
       <c r="E1437" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1438" ht="15.75" customHeight="1">
       <c r="E1438" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1439" ht="15.75" customHeight="1">
       <c r="E1439" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="1440" ht="15.75" customHeight="1"/>
     <row r="1441" ht="15.75" customHeight="1">
       <c r="F1441" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1442" ht="15.75" customHeight="1">
       <c r="F1442" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1443" ht="15.75" customHeight="1"/>
     <row r="1444" ht="15.75" customHeight="1">
       <c r="E1444" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1445" ht="15.75" customHeight="1">
       <c r="E1445" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1446" ht="15.75" customHeight="1">
       <c r="E1446" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1447" ht="15.75" customHeight="1">
       <c r="E1447" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1448" ht="15.75" customHeight="1"/>
@@ -14636,18 +14665,18 @@
     <row r="1457" ht="15.75" customHeight="1"/>
     <row r="1458" ht="15.75" customHeight="1">
       <c r="D1458" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1459" ht="15.75" customHeight="1"/>
     <row r="1460" ht="15.75" customHeight="1">
       <c r="B1460" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1461" ht="15.75" customHeight="1">
       <c r="B1461" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1461" s="8"/>
       <c r="D1461" s="8"/>
@@ -14657,7 +14686,7 @@
       <c r="H1461" s="8"/>
       <c r="I1461" s="8"/>
       <c r="J1461" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K1461" s="8"/>
       <c r="L1461" s="8"/>
@@ -14668,7 +14697,7 @@
       <c r="Q1461" s="8"/>
       <c r="R1461" s="8"/>
       <c r="S1461" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T1461" s="8"/>
       <c r="U1461" s="8"/>
@@ -14676,7 +14705,7 @@
       <c r="W1461" s="8"/>
       <c r="X1461" s="8"/>
       <c r="Y1461" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z1461" s="8"/>
       <c r="AA1461" s="9" t="s">
@@ -14688,7 +14717,7 @@
     </row>
     <row r="1462" ht="15.75" customHeight="1">
       <c r="B1462" s="23" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C1462" s="12"/>
       <c r="D1462" s="12"/>
@@ -14698,7 +14727,7 @@
       <c r="H1462" s="12"/>
       <c r="I1462" s="12"/>
       <c r="J1462" s="14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K1462" s="12"/>
       <c r="L1462" s="12"/>
@@ -14709,7 +14738,7 @@
       <c r="Q1462" s="12"/>
       <c r="R1462" s="12"/>
       <c r="S1462" s="14" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="T1462" s="12"/>
       <c r="U1462" s="12"/>
@@ -14717,11 +14746,11 @@
       <c r="W1462" s="12"/>
       <c r="X1462" s="12"/>
       <c r="Y1462" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1462" s="12"/>
       <c r="AA1462" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1462" s="12"/>
       <c r="AC1462" s="12"/>
@@ -14729,7 +14758,7 @@
     </row>
     <row r="1463" ht="15.75" customHeight="1">
       <c r="B1463" s="23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C1463" s="12"/>
       <c r="D1463" s="12"/>
@@ -14739,7 +14768,7 @@
       <c r="H1463" s="12"/>
       <c r="I1463" s="12"/>
       <c r="J1463" s="14" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K1463" s="12"/>
       <c r="L1463" s="12"/>
@@ -14758,11 +14787,11 @@
       <c r="W1463" s="12"/>
       <c r="X1463" s="12"/>
       <c r="Y1463" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1463" s="12"/>
       <c r="AA1463" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1463" s="12"/>
       <c r="AC1463" s="12"/>
@@ -14770,7 +14799,7 @@
     </row>
     <row r="1464" ht="15.75" customHeight="1">
       <c r="B1464" s="23" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C1464" s="12"/>
       <c r="D1464" s="12"/>
@@ -14780,7 +14809,7 @@
       <c r="H1464" s="12"/>
       <c r="I1464" s="12"/>
       <c r="J1464" s="14" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K1464" s="12"/>
       <c r="L1464" s="12"/>
@@ -14791,7 +14820,7 @@
       <c r="Q1464" s="12"/>
       <c r="R1464" s="12"/>
       <c r="S1464" s="14" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="T1464" s="12"/>
       <c r="U1464" s="12"/>
@@ -14799,11 +14828,11 @@
       <c r="W1464" s="12"/>
       <c r="X1464" s="12"/>
       <c r="Y1464" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1464" s="12"/>
       <c r="AA1464" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1464" s="12"/>
       <c r="AC1464" s="12"/>
@@ -14811,7 +14840,7 @@
     </row>
     <row r="1465" ht="15.75" customHeight="1">
       <c r="B1465" s="23" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C1465" s="12"/>
       <c r="D1465" s="12"/>
@@ -14821,7 +14850,7 @@
       <c r="H1465" s="12"/>
       <c r="I1465" s="12"/>
       <c r="J1465" s="14" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K1465" s="12"/>
       <c r="L1465" s="12"/>
@@ -14832,7 +14861,7 @@
       <c r="Q1465" s="12"/>
       <c r="R1465" s="12"/>
       <c r="S1465" s="14" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="T1465" s="12"/>
       <c r="U1465" s="12"/>
@@ -14840,11 +14869,11 @@
       <c r="W1465" s="12"/>
       <c r="X1465" s="12"/>
       <c r="Y1465" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1465" s="12"/>
       <c r="AA1465" s="14" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AB1465" s="12"/>
       <c r="AC1465" s="12"/>
@@ -14852,7 +14881,7 @@
     </row>
     <row r="1466" ht="15.75" customHeight="1">
       <c r="B1466" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C1466" s="12"/>
       <c r="D1466" s="12"/>
@@ -14862,7 +14891,7 @@
       <c r="H1466" s="12"/>
       <c r="I1466" s="12"/>
       <c r="J1466" s="14" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K1466" s="12"/>
       <c r="L1466" s="12"/>
@@ -14873,7 +14902,7 @@
       <c r="Q1466" s="12"/>
       <c r="R1466" s="12"/>
       <c r="S1466" s="14" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="T1466" s="12"/>
       <c r="U1466" s="12"/>
@@ -14881,11 +14910,11 @@
       <c r="W1466" s="12"/>
       <c r="X1466" s="12"/>
       <c r="Y1466" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1466" s="12"/>
       <c r="AA1466" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1466" s="12"/>
       <c r="AC1466" s="12"/>
@@ -14893,7 +14922,7 @@
     </row>
     <row r="1467" ht="15.75" customHeight="1">
       <c r="B1467" s="23" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C1467" s="12"/>
       <c r="D1467" s="12"/>
@@ -14903,7 +14932,7 @@
       <c r="H1467" s="12"/>
       <c r="I1467" s="12"/>
       <c r="J1467" s="14" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K1467" s="12"/>
       <c r="L1467" s="12"/>
@@ -14914,7 +14943,7 @@
       <c r="Q1467" s="12"/>
       <c r="R1467" s="12"/>
       <c r="S1467" s="14" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="T1467" s="12"/>
       <c r="U1467" s="12"/>
@@ -14922,7 +14951,7 @@
       <c r="W1467" s="12"/>
       <c r="X1467" s="12"/>
       <c r="Y1467" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1467" s="12"/>
       <c r="AA1467" s="29"/>
@@ -14932,7 +14961,7 @@
     </row>
     <row r="1468" ht="15.75" customHeight="1">
       <c r="B1468" s="23" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C1468" s="12"/>
       <c r="D1468" s="12"/>
@@ -14942,7 +14971,7 @@
       <c r="H1468" s="12"/>
       <c r="I1468" s="12"/>
       <c r="J1468" s="14" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K1468" s="12"/>
       <c r="L1468" s="12"/>
@@ -14953,7 +14982,7 @@
       <c r="Q1468" s="12"/>
       <c r="R1468" s="12"/>
       <c r="S1468" s="14" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="T1468" s="12"/>
       <c r="U1468" s="12"/>
@@ -14961,7 +14990,7 @@
       <c r="W1468" s="12"/>
       <c r="X1468" s="12"/>
       <c r="Y1468" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1468" s="12"/>
       <c r="AA1468" s="29"/>
@@ -14971,7 +15000,7 @@
     </row>
     <row r="1469" ht="15.75" customHeight="1">
       <c r="B1469" s="23" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C1469" s="12"/>
       <c r="D1469" s="12"/>
@@ -14981,7 +15010,7 @@
       <c r="H1469" s="12"/>
       <c r="I1469" s="12"/>
       <c r="J1469" s="14" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K1469" s="12"/>
       <c r="L1469" s="12"/>
@@ -14992,7 +15021,7 @@
       <c r="Q1469" s="12"/>
       <c r="R1469" s="12"/>
       <c r="S1469" s="14" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="T1469" s="12"/>
       <c r="U1469" s="12"/>
@@ -15000,11 +15029,11 @@
       <c r="W1469" s="12"/>
       <c r="X1469" s="12"/>
       <c r="Y1469" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1469" s="12"/>
       <c r="AA1469" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1469" s="12"/>
       <c r="AC1469" s="12"/>
@@ -15012,7 +15041,7 @@
     </row>
     <row r="1470" ht="15.75" customHeight="1">
       <c r="B1470" s="23" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C1470" s="12"/>
       <c r="D1470" s="12"/>
@@ -15022,7 +15051,7 @@
       <c r="H1470" s="12"/>
       <c r="I1470" s="12"/>
       <c r="J1470" s="14" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K1470" s="12"/>
       <c r="L1470" s="12"/>
@@ -15033,7 +15062,7 @@
       <c r="Q1470" s="12"/>
       <c r="R1470" s="12"/>
       <c r="S1470" s="14" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="T1470" s="12"/>
       <c r="U1470" s="12"/>
@@ -15041,11 +15070,11 @@
       <c r="W1470" s="12"/>
       <c r="X1470" s="12"/>
       <c r="Y1470" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1470" s="12"/>
       <c r="AA1470" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1470" s="12"/>
       <c r="AC1470" s="12"/>
@@ -15053,7 +15082,7 @@
     </row>
     <row r="1471" ht="15.75" customHeight="1">
       <c r="B1471" s="23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C1471" s="12"/>
       <c r="D1471" s="12"/>
@@ -15063,7 +15092,7 @@
       <c r="H1471" s="12"/>
       <c r="I1471" s="12"/>
       <c r="J1471" s="14" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K1471" s="12"/>
       <c r="L1471" s="12"/>
@@ -15082,11 +15111,11 @@
       <c r="W1471" s="12"/>
       <c r="X1471" s="12"/>
       <c r="Y1471" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1471" s="12"/>
       <c r="AA1471" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1471" s="12"/>
       <c r="AC1471" s="12"/>
@@ -15094,7 +15123,7 @@
     </row>
     <row r="1472" ht="15.75" customHeight="1">
       <c r="B1472" s="11" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C1472" s="12"/>
       <c r="D1472" s="12"/>
@@ -15104,7 +15133,7 @@
       <c r="H1472" s="12"/>
       <c r="I1472" s="12"/>
       <c r="J1472" s="14" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K1472" s="12"/>
       <c r="L1472" s="12"/>
@@ -15115,7 +15144,7 @@
       <c r="Q1472" s="12"/>
       <c r="R1472" s="12"/>
       <c r="S1472" s="14" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="T1472" s="12"/>
       <c r="U1472" s="12"/>
@@ -15123,11 +15152,11 @@
       <c r="W1472" s="12"/>
       <c r="X1472" s="12"/>
       <c r="Y1472" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1472" s="12"/>
       <c r="AA1472" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1472" s="12"/>
       <c r="AC1472" s="12"/>
@@ -15136,7 +15165,7 @@
     <row r="1473" ht="15.75" customHeight="1">
       <c r="B1473" s="10"/>
       <c r="J1473" s="30" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="S1473" s="15"/>
       <c r="Y1473" s="15"/>
@@ -15146,7 +15175,7 @@
     <row r="1474" ht="15.75" customHeight="1">
       <c r="B1474" s="10"/>
       <c r="J1474" s="14" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K1474" s="12"/>
       <c r="L1474" s="12"/>
@@ -15157,7 +15186,7 @@
       <c r="Q1474" s="12"/>
       <c r="R1474" s="12"/>
       <c r="S1474" s="14" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="T1474" s="12"/>
       <c r="U1474" s="12"/>
@@ -15165,7 +15194,7 @@
       <c r="W1474" s="12"/>
       <c r="X1474" s="12"/>
       <c r="Y1474" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1474" s="12"/>
       <c r="AA1474" s="15"/>
@@ -15174,7 +15203,7 @@
     <row r="1475" ht="15.75" customHeight="1">
       <c r="B1475" s="10"/>
       <c r="J1475" s="14" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K1475" s="12"/>
       <c r="L1475" s="12"/>
@@ -15185,7 +15214,7 @@
       <c r="Q1475" s="12"/>
       <c r="R1475" s="12"/>
       <c r="S1475" s="14" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="T1475" s="12"/>
       <c r="U1475" s="12"/>
@@ -15193,7 +15222,7 @@
       <c r="W1475" s="12"/>
       <c r="X1475" s="12"/>
       <c r="Y1475" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1475" s="12"/>
       <c r="AA1475" s="15"/>
@@ -15201,7 +15230,7 @@
     </row>
     <row r="1476" ht="15.75" customHeight="1">
       <c r="B1476" s="23" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C1476" s="12"/>
       <c r="D1476" s="12"/>
@@ -15211,7 +15240,7 @@
       <c r="H1476" s="12"/>
       <c r="I1476" s="12"/>
       <c r="J1476" s="14" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K1476" s="12"/>
       <c r="L1476" s="12"/>
@@ -15222,7 +15251,7 @@
       <c r="Q1476" s="12"/>
       <c r="R1476" s="12"/>
       <c r="S1476" s="14" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T1476" s="12"/>
       <c r="U1476" s="12"/>
@@ -15230,11 +15259,11 @@
       <c r="W1476" s="12"/>
       <c r="X1476" s="12"/>
       <c r="Y1476" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1476" s="12"/>
       <c r="AA1476" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1476" s="12"/>
       <c r="AC1476" s="12"/>
@@ -15242,7 +15271,7 @@
     </row>
     <row r="1477" ht="15.75" customHeight="1">
       <c r="B1477" s="23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C1477" s="12"/>
       <c r="D1477" s="12"/>
@@ -15252,7 +15281,7 @@
       <c r="H1477" s="12"/>
       <c r="I1477" s="12"/>
       <c r="J1477" s="14" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K1477" s="12"/>
       <c r="L1477" s="12"/>
@@ -15263,7 +15292,7 @@
       <c r="Q1477" s="12"/>
       <c r="R1477" s="12"/>
       <c r="S1477" s="14" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="T1477" s="12"/>
       <c r="U1477" s="12"/>
@@ -15271,11 +15300,11 @@
       <c r="W1477" s="12"/>
       <c r="X1477" s="12"/>
       <c r="Y1477" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1477" s="12"/>
       <c r="AA1477" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1477" s="12"/>
       <c r="AC1477" s="12"/>
@@ -15283,7 +15312,7 @@
     </row>
     <row r="1478" ht="15.75" customHeight="1">
       <c r="B1478" s="23" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C1478" s="12"/>
       <c r="D1478" s="12"/>
@@ -15293,7 +15322,7 @@
       <c r="H1478" s="12"/>
       <c r="I1478" s="12"/>
       <c r="J1478" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K1478" s="12"/>
       <c r="L1478" s="12"/>
@@ -15304,7 +15333,7 @@
       <c r="Q1478" s="12"/>
       <c r="R1478" s="12"/>
       <c r="S1478" s="14" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T1478" s="12"/>
       <c r="U1478" s="12"/>
@@ -15312,11 +15341,11 @@
       <c r="W1478" s="12"/>
       <c r="X1478" s="12"/>
       <c r="Y1478" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1478" s="12"/>
       <c r="AA1478" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1478" s="12"/>
       <c r="AC1478" s="12"/>
@@ -15324,7 +15353,7 @@
     </row>
     <row r="1479" ht="15.75" customHeight="1">
       <c r="B1479" s="23" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C1479" s="12"/>
       <c r="D1479" s="12"/>
@@ -15334,7 +15363,7 @@
       <c r="H1479" s="12"/>
       <c r="I1479" s="12"/>
       <c r="J1479" s="14" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K1479" s="12"/>
       <c r="L1479" s="12"/>
@@ -15345,7 +15374,7 @@
       <c r="Q1479" s="12"/>
       <c r="R1479" s="12"/>
       <c r="S1479" s="14" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="T1479" s="12"/>
       <c r="U1479" s="12"/>
@@ -15353,11 +15382,11 @@
       <c r="W1479" s="12"/>
       <c r="X1479" s="12"/>
       <c r="Y1479" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1479" s="12"/>
       <c r="AA1479" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1479" s="12"/>
       <c r="AC1479" s="12"/>
@@ -15365,7 +15394,7 @@
     </row>
     <row r="1480" ht="15.75" customHeight="1">
       <c r="B1480" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C1480" s="12"/>
       <c r="D1480" s="12"/>
@@ -15375,7 +15404,7 @@
       <c r="H1480" s="12"/>
       <c r="I1480" s="12"/>
       <c r="J1480" s="14" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="K1480" s="12"/>
       <c r="L1480" s="12"/>
@@ -15386,7 +15415,7 @@
       <c r="Q1480" s="12"/>
       <c r="R1480" s="12"/>
       <c r="S1480" s="14" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="T1480" s="12"/>
       <c r="U1480" s="12"/>
@@ -15394,11 +15423,11 @@
       <c r="W1480" s="12"/>
       <c r="X1480" s="12"/>
       <c r="Y1480" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1480" s="12"/>
       <c r="AA1480" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1480" s="12"/>
       <c r="AC1480" s="12"/>
@@ -15407,7 +15436,7 @@
     <row r="1481" ht="15.75" customHeight="1">
       <c r="B1481" s="10"/>
       <c r="J1481" s="14" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="K1481" s="12"/>
       <c r="L1481" s="12"/>
@@ -15418,7 +15447,7 @@
       <c r="Q1481" s="12"/>
       <c r="R1481" s="12"/>
       <c r="S1481" s="14" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="T1481" s="12"/>
       <c r="U1481" s="12"/>
@@ -15426,7 +15455,7 @@
       <c r="W1481" s="12"/>
       <c r="X1481" s="12"/>
       <c r="Y1481" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1481" s="12"/>
       <c r="AA1481" s="15"/>
@@ -15434,7 +15463,7 @@
     </row>
     <row r="1482" ht="15.75" customHeight="1">
       <c r="B1482" s="23" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C1482" s="12"/>
       <c r="D1482" s="12"/>
@@ -15444,7 +15473,7 @@
       <c r="H1482" s="12"/>
       <c r="I1482" s="12"/>
       <c r="J1482" s="14" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K1482" s="12"/>
       <c r="L1482" s="12"/>
@@ -15455,7 +15484,7 @@
       <c r="Q1482" s="12"/>
       <c r="R1482" s="12"/>
       <c r="S1482" s="14" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="T1482" s="12"/>
       <c r="U1482" s="12"/>
@@ -15463,11 +15492,11 @@
       <c r="W1482" s="12"/>
       <c r="X1482" s="12"/>
       <c r="Y1482" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1482" s="12"/>
       <c r="AA1482" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1482" s="12"/>
       <c r="AC1482" s="12"/>
@@ -15506,33 +15535,33 @@
     </row>
     <row r="1484" ht="15.75" customHeight="1">
       <c r="C1484" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1485" ht="15.75" customHeight="1"/>
     <row r="1486" ht="15.75" customHeight="1">
       <c r="D1486" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1487" ht="15.75" customHeight="1"/>
     <row r="1488" ht="15.75" customHeight="1">
       <c r="E1488" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="T1488" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="T1488" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="1489" ht="15.75" customHeight="1"/>
     <row r="1490" ht="15.75" customHeight="1">
       <c r="E1490" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1491" ht="15.75" customHeight="1">
       <c r="E1491" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1492" ht="15.75" customHeight="1"/>
@@ -15550,92 +15579,92 @@
     <row r="1504" ht="15.75" customHeight="1"/>
     <row r="1505" ht="15.75" customHeight="1">
       <c r="E1505" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1506" ht="15.75" customHeight="1">
       <c r="F1506" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1507" ht="15.75" customHeight="1"/>
     <row r="1508" ht="15.75" customHeight="1">
       <c r="F1508" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J1508" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1508" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1509" ht="15.75" customHeight="1">
       <c r="H1509" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J1509" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1509" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="1510" ht="15.75" customHeight="1">
       <c r="H1510" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J1510" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1510" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="1511" ht="15.75" customHeight="1">
       <c r="H1511" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J1511" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1511" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="1512" ht="15.75" customHeight="1"/>
     <row r="1513" ht="15.75" customHeight="1">
       <c r="E1513" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="1514" ht="15.75" customHeight="1">
       <c r="E1514" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1515" ht="15.75" customHeight="1">
       <c r="E1515" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="1516" ht="15.75" customHeight="1">
       <c r="E1516" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F1516" s="8"/>
       <c r="G1516" s="8"/>
       <c r="H1516" s="8"/>
       <c r="I1516" s="8"/>
       <c r="J1516" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K1516" s="8"/>
       <c r="L1516" s="8"/>
       <c r="M1516" s="8"/>
       <c r="N1516" s="8"/>
       <c r="O1516" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P1516" s="8"/>
       <c r="Q1516" s="8"/>
@@ -15652,14 +15681,14 @@
     </row>
     <row r="1517" ht="15.75" customHeight="1">
       <c r="E1517" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F1517" s="12"/>
       <c r="G1517" s="12"/>
       <c r="H1517" s="12"/>
       <c r="I1517" s="12"/>
       <c r="J1517" s="14" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K1517" s="12"/>
       <c r="L1517" s="12"/>
@@ -15684,7 +15713,7 @@
     <row r="1518" ht="15.75" customHeight="1">
       <c r="E1518" s="10"/>
       <c r="J1518" s="14" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="K1518" s="12"/>
       <c r="L1518" s="12"/>
@@ -15732,183 +15761,183 @@
     </row>
     <row r="1520" ht="15.75" customHeight="1">
       <c r="E1520" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="T1520" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1521" ht="15.75" customHeight="1"/>
     <row r="1522" ht="15.75" customHeight="1">
       <c r="E1522" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1523" ht="15.75" customHeight="1">
       <c r="E1523" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1524" ht="15.75" customHeight="1"/>
     <row r="1525" ht="15.75" customHeight="1">
       <c r="E1525" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1526" ht="15.75" customHeight="1">
       <c r="F1526" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="1527" ht="15.75" customHeight="1">
       <c r="F1527" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1528" ht="15.75" customHeight="1"/>
     <row r="1529" ht="15.75" customHeight="1">
       <c r="F1529" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J1529" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1529" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1530" ht="15.75" customHeight="1">
       <c r="H1530" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J1530" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1530" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1531" ht="15.75" customHeight="1">
       <c r="H1531" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="J1531" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1531" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="1532" ht="15.75" customHeight="1">
       <c r="H1532" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J1532" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1532" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="1533" ht="15.75" customHeight="1">
       <c r="H1533" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="J1533" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1533" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="1534" ht="15.75" customHeight="1">
       <c r="H1534" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J1534" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1534" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1535" ht="15.75" customHeight="1">
       <c r="H1535" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J1535" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1535" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="1536" ht="15.75" customHeight="1">
       <c r="H1536" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J1536" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1536" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="1537" ht="15.75" customHeight="1">
       <c r="H1537" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="J1537" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1537" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1538" ht="15.75" customHeight="1">
       <c r="H1538" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J1538" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1538" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="1539" ht="15.75" customHeight="1"/>
     <row r="1540" ht="15.75" customHeight="1">
       <c r="E1540" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="1541" ht="15.75" customHeight="1">
       <c r="E1541" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1542" ht="15.75" customHeight="1">
       <c r="E1542" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="1543" ht="15.75" customHeight="1">
       <c r="E1543" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F1543" s="8"/>
       <c r="G1543" s="8"/>
       <c r="H1543" s="8"/>
       <c r="I1543" s="8"/>
       <c r="J1543" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K1543" s="8"/>
       <c r="L1543" s="8"/>
       <c r="M1543" s="8"/>
       <c r="N1543" s="8"/>
       <c r="O1543" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P1543" s="8"/>
       <c r="Q1543" s="8"/>
@@ -15925,14 +15954,14 @@
     </row>
     <row r="1544" ht="15.75" customHeight="1">
       <c r="E1544" s="23" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F1544" s="12"/>
       <c r="G1544" s="12"/>
       <c r="H1544" s="12"/>
       <c r="I1544" s="12"/>
       <c r="J1544" s="14" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="K1544" s="12"/>
       <c r="L1544" s="12"/>
@@ -15980,43 +16009,43 @@
     </row>
     <row r="1546" ht="15.75" customHeight="1">
       <c r="D1546" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="S1546" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1547" ht="15.75" customHeight="1"/>
     <row r="1548" ht="15.75" customHeight="1">
       <c r="E1548" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="1549" ht="15.75" customHeight="1">
       <c r="E1549" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="1550" ht="15.75" customHeight="1">
       <c r="E1550" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1551" ht="15.75" customHeight="1"/>
     <row r="1552" ht="15.75" customHeight="1">
       <c r="D1552" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="1553" ht="15.75" customHeight="1"/>
     <row r="1554" ht="15.75" customHeight="1">
       <c r="B1554" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="1555" ht="15.75" customHeight="1">
       <c r="B1555" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1555" s="8"/>
       <c r="D1555" s="8"/>
@@ -16027,7 +16056,7 @@
       <c r="I1555" s="8"/>
       <c r="J1555" s="8"/>
       <c r="K1555" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L1555" s="8"/>
       <c r="M1555" s="8"/>
@@ -16036,7 +16065,7 @@
       <c r="P1555" s="8"/>
       <c r="Q1555" s="8"/>
       <c r="R1555" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="S1555" s="8"/>
       <c r="T1555" s="8"/>
@@ -16045,7 +16074,7 @@
       <c r="W1555" s="8"/>
       <c r="X1555" s="8"/>
       <c r="Y1555" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z1555" s="8"/>
       <c r="AA1555" s="9" t="s">
@@ -16057,12 +16086,12 @@
     </row>
     <row r="1556" ht="15.75" customHeight="1">
       <c r="B1556" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C1556" s="12"/>
       <c r="D1556" s="12"/>
       <c r="E1556" s="14" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F1556" s="12"/>
       <c r="G1556" s="12"/>
@@ -16070,7 +16099,7 @@
       <c r="I1556" s="12"/>
       <c r="J1556" s="12"/>
       <c r="K1556" s="14" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L1556" s="12"/>
       <c r="M1556" s="12"/>
@@ -16079,7 +16108,7 @@
       <c r="P1556" s="12"/>
       <c r="Q1556" s="12"/>
       <c r="R1556" s="14" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="S1556" s="12"/>
       <c r="T1556" s="12"/>
@@ -16088,11 +16117,11 @@
       <c r="W1556" s="12"/>
       <c r="X1556" s="12"/>
       <c r="Y1556" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1556" s="12"/>
       <c r="AA1556" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1556" s="12"/>
       <c r="AC1556" s="12"/>
@@ -16100,10 +16129,10 @@
     </row>
     <row r="1557" ht="15.75" customHeight="1">
       <c r="B1557" s="32" t="s">
+        <v>657</v>
+      </c>
+      <c r="E1557" s="14" t="s">
         <v>658</v>
-      </c>
-      <c r="E1557" s="14" t="s">
-        <v>659</v>
       </c>
       <c r="F1557" s="12"/>
       <c r="G1557" s="12"/>
@@ -16111,7 +16140,7 @@
       <c r="I1557" s="12"/>
       <c r="J1557" s="12"/>
       <c r="K1557" s="14" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L1557" s="12"/>
       <c r="M1557" s="12"/>
@@ -16120,7 +16149,7 @@
       <c r="P1557" s="12"/>
       <c r="Q1557" s="12"/>
       <c r="R1557" s="14" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="S1557" s="12"/>
       <c r="T1557" s="12"/>
@@ -16129,7 +16158,7 @@
       <c r="W1557" s="12"/>
       <c r="X1557" s="12"/>
       <c r="Y1557" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1557" s="12"/>
       <c r="AA1557" s="15"/>
@@ -16137,10 +16166,10 @@
     </row>
     <row r="1558" ht="15.75" customHeight="1">
       <c r="B1558" s="32" t="s">
+        <v>661</v>
+      </c>
+      <c r="E1558" s="14" t="s">
         <v>662</v>
-      </c>
-      <c r="E1558" s="14" t="s">
-        <v>663</v>
       </c>
       <c r="F1558" s="12"/>
       <c r="G1558" s="12"/>
@@ -16148,7 +16177,7 @@
       <c r="I1558" s="12"/>
       <c r="J1558" s="12"/>
       <c r="K1558" s="14" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L1558" s="12"/>
       <c r="M1558" s="12"/>
@@ -16157,7 +16186,7 @@
       <c r="P1558" s="12"/>
       <c r="Q1558" s="12"/>
       <c r="R1558" s="14" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="S1558" s="12"/>
       <c r="T1558" s="12"/>
@@ -16166,7 +16195,7 @@
       <c r="W1558" s="12"/>
       <c r="X1558" s="12"/>
       <c r="Y1558" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1558" s="12"/>
       <c r="AA1558" s="15"/>
@@ -16174,7 +16203,7 @@
     </row>
     <row r="1559" ht="15.75" customHeight="1">
       <c r="B1559" s="11" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C1559" s="12"/>
       <c r="D1559" s="12"/>
@@ -16185,7 +16214,7 @@
       <c r="I1559" s="12"/>
       <c r="J1559" s="12"/>
       <c r="K1559" s="14" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L1559" s="12"/>
       <c r="M1559" s="12"/>
@@ -16194,7 +16223,7 @@
       <c r="P1559" s="12"/>
       <c r="Q1559" s="12"/>
       <c r="R1559" s="14" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="S1559" s="12"/>
       <c r="T1559" s="12"/>
@@ -16203,11 +16232,11 @@
       <c r="W1559" s="12"/>
       <c r="X1559" s="12"/>
       <c r="Y1559" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z1559" s="12"/>
       <c r="AA1559" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB1559" s="12"/>
       <c r="AC1559" s="12"/>
@@ -16217,7 +16246,7 @@
       <c r="B1560" s="10"/>
       <c r="K1560" s="15"/>
       <c r="R1560" s="30" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y1560" s="15"/>
       <c r="AA1560" s="15"/>
@@ -16292,7 +16321,7 @@
     <row r="1597" ht="15.75" customHeight="1"/>
     <row r="1598" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1429">
+  <mergeCells count="1437">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="C5:E5"/>
@@ -16832,15 +16861,18 @@
     <mergeCell ref="E731:X731"/>
     <mergeCell ref="E733:AD733"/>
     <mergeCell ref="E734:AB734"/>
-    <mergeCell ref="E735:T735"/>
-    <mergeCell ref="E737:R737"/>
-    <mergeCell ref="E739:AC739"/>
-    <mergeCell ref="E740:X740"/>
-    <mergeCell ref="E741:T741"/>
-    <mergeCell ref="D743:M743"/>
-    <mergeCell ref="S743:Z743"/>
-    <mergeCell ref="E745:AD745"/>
-    <mergeCell ref="E746:T746"/>
+    <mergeCell ref="E735:AD735"/>
+    <mergeCell ref="E736:J736"/>
+    <mergeCell ref="E738:R738"/>
+    <mergeCell ref="E740:AC740"/>
+    <mergeCell ref="E741:X741"/>
+    <mergeCell ref="E742:AD742"/>
+    <mergeCell ref="E743:J743"/>
+    <mergeCell ref="D745:M745"/>
+    <mergeCell ref="S745:Z745"/>
+    <mergeCell ref="E747:AD747"/>
+    <mergeCell ref="E748:AD748"/>
+    <mergeCell ref="E749:J749"/>
     <mergeCell ref="D753:Q753"/>
     <mergeCell ref="S753:Z753"/>
     <mergeCell ref="E755:AD755"/>
@@ -16855,39 +16887,40 @@
     <mergeCell ref="E764:AD764"/>
     <mergeCell ref="E765:AD765"/>
     <mergeCell ref="E766:W766"/>
-    <mergeCell ref="E767:P767"/>
-    <mergeCell ref="D769:H769"/>
-    <mergeCell ref="S769:Z769"/>
-    <mergeCell ref="E771:AD771"/>
+    <mergeCell ref="E767:AD767"/>
+    <mergeCell ref="E768:F768"/>
+    <mergeCell ref="D770:H770"/>
+    <mergeCell ref="S770:Z770"/>
     <mergeCell ref="E772:AD772"/>
-    <mergeCell ref="E773:M773"/>
-    <mergeCell ref="J775:Q775"/>
-    <mergeCell ref="S775:U775"/>
-    <mergeCell ref="M776:Q776"/>
-    <mergeCell ref="S776:T776"/>
-    <mergeCell ref="J777:Q777"/>
-    <mergeCell ref="S777:Z777"/>
+    <mergeCell ref="E773:AD773"/>
+    <mergeCell ref="E774:M774"/>
+    <mergeCell ref="J776:Q776"/>
+    <mergeCell ref="S776:U776"/>
+    <mergeCell ref="M777:Q777"/>
+    <mergeCell ref="S777:T777"/>
     <mergeCell ref="J778:Q778"/>
-    <mergeCell ref="S778:U778"/>
-    <mergeCell ref="M779:Q779"/>
-    <mergeCell ref="S779:T779"/>
-    <mergeCell ref="J780:Q780"/>
-    <mergeCell ref="S780:Z780"/>
-    <mergeCell ref="E782:I782"/>
-    <mergeCell ref="E783:K783"/>
-    <mergeCell ref="L783:S783"/>
-    <mergeCell ref="T783:AC783"/>
-    <mergeCell ref="E784:K786"/>
-    <mergeCell ref="L784:S786"/>
+    <mergeCell ref="S778:Z778"/>
+    <mergeCell ref="J779:Q779"/>
+    <mergeCell ref="S779:U779"/>
+    <mergeCell ref="M780:Q780"/>
+    <mergeCell ref="S780:T780"/>
+    <mergeCell ref="J781:Q781"/>
+    <mergeCell ref="S781:Z781"/>
+    <mergeCell ref="E783:I783"/>
+    <mergeCell ref="E784:K784"/>
+    <mergeCell ref="L784:S784"/>
     <mergeCell ref="T784:AC784"/>
+    <mergeCell ref="E785:K787"/>
+    <mergeCell ref="L785:S787"/>
     <mergeCell ref="T785:AC785"/>
     <mergeCell ref="T786:AC786"/>
-    <mergeCell ref="E787:K789"/>
-    <mergeCell ref="L787:S789"/>
     <mergeCell ref="T787:AC787"/>
+    <mergeCell ref="E788:K790"/>
+    <mergeCell ref="L788:S790"/>
     <mergeCell ref="T788:AC788"/>
     <mergeCell ref="T789:AC789"/>
-    <mergeCell ref="E791:T791"/>
+    <mergeCell ref="T790:AC790"/>
+    <mergeCell ref="E792:T792"/>
     <mergeCell ref="D800:M800"/>
     <mergeCell ref="O800:AB800"/>
     <mergeCell ref="E802:AD802"/>
@@ -17014,15 +17047,18 @@
     <mergeCell ref="E917:X917"/>
     <mergeCell ref="E919:AD919"/>
     <mergeCell ref="E920:AB920"/>
-    <mergeCell ref="E921:T921"/>
-    <mergeCell ref="E923:R923"/>
-    <mergeCell ref="E925:AC925"/>
-    <mergeCell ref="E926:X926"/>
-    <mergeCell ref="E927:T927"/>
-    <mergeCell ref="D929:M929"/>
-    <mergeCell ref="S929:Z929"/>
-    <mergeCell ref="E931:AD931"/>
-    <mergeCell ref="E932:T932"/>
+    <mergeCell ref="E921:AD921"/>
+    <mergeCell ref="E922:J922"/>
+    <mergeCell ref="E924:R924"/>
+    <mergeCell ref="E926:AC926"/>
+    <mergeCell ref="E927:X927"/>
+    <mergeCell ref="E928:AD928"/>
+    <mergeCell ref="E929:J929"/>
+    <mergeCell ref="D931:M931"/>
+    <mergeCell ref="S931:Z931"/>
+    <mergeCell ref="E933:AD933"/>
+    <mergeCell ref="E934:AD934"/>
+    <mergeCell ref="E935:J935"/>
     <mergeCell ref="D941:Q941"/>
     <mergeCell ref="S941:Z941"/>
     <mergeCell ref="E943:AD943"/>
@@ -17037,39 +17073,40 @@
     <mergeCell ref="E952:AD952"/>
     <mergeCell ref="E953:AD953"/>
     <mergeCell ref="E954:W954"/>
-    <mergeCell ref="E955:P955"/>
-    <mergeCell ref="D957:H957"/>
-    <mergeCell ref="S957:Z957"/>
-    <mergeCell ref="E959:AD959"/>
+    <mergeCell ref="E955:AD955"/>
+    <mergeCell ref="E956:F956"/>
+    <mergeCell ref="D958:H958"/>
+    <mergeCell ref="S958:Z958"/>
     <mergeCell ref="E960:AD960"/>
-    <mergeCell ref="E961:M961"/>
-    <mergeCell ref="J963:Q963"/>
-    <mergeCell ref="S963:U963"/>
-    <mergeCell ref="M964:Q964"/>
-    <mergeCell ref="S964:T964"/>
-    <mergeCell ref="J965:Q965"/>
-    <mergeCell ref="S965:Z965"/>
+    <mergeCell ref="E961:AD961"/>
+    <mergeCell ref="E962:M962"/>
+    <mergeCell ref="J964:Q964"/>
+    <mergeCell ref="S964:U964"/>
+    <mergeCell ref="M965:Q965"/>
+    <mergeCell ref="S965:T965"/>
     <mergeCell ref="J966:Q966"/>
-    <mergeCell ref="S966:U966"/>
-    <mergeCell ref="M967:Q967"/>
-    <mergeCell ref="S967:T967"/>
-    <mergeCell ref="J968:Q968"/>
-    <mergeCell ref="S968:Z968"/>
-    <mergeCell ref="E970:I970"/>
-    <mergeCell ref="E971:K971"/>
-    <mergeCell ref="L971:S971"/>
-    <mergeCell ref="T971:AC971"/>
-    <mergeCell ref="E972:K974"/>
-    <mergeCell ref="L972:S974"/>
+    <mergeCell ref="S966:Z966"/>
+    <mergeCell ref="J967:Q967"/>
+    <mergeCell ref="S967:U967"/>
+    <mergeCell ref="M968:Q968"/>
+    <mergeCell ref="S968:T968"/>
+    <mergeCell ref="J969:Q969"/>
+    <mergeCell ref="S969:Z969"/>
+    <mergeCell ref="E971:I971"/>
+    <mergeCell ref="E972:K972"/>
+    <mergeCell ref="L972:S972"/>
     <mergeCell ref="T972:AC972"/>
+    <mergeCell ref="E973:K975"/>
+    <mergeCell ref="L973:S975"/>
     <mergeCell ref="T973:AC973"/>
     <mergeCell ref="T974:AC974"/>
-    <mergeCell ref="E975:K977"/>
-    <mergeCell ref="L975:S977"/>
     <mergeCell ref="T975:AC975"/>
+    <mergeCell ref="E976:K978"/>
+    <mergeCell ref="L976:S978"/>
     <mergeCell ref="T976:AC976"/>
     <mergeCell ref="T977:AC977"/>
-    <mergeCell ref="E979:T979"/>
+    <mergeCell ref="T978:AC978"/>
+    <mergeCell ref="E980:T980"/>
     <mergeCell ref="D988:M988"/>
     <mergeCell ref="O988:AB988"/>
     <mergeCell ref="E990:AD990"/>

--- a/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
+++ b/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
@@ -1249,7 +1249,7 @@
     <t>(a) 曲げひび割れ発生と同時に部材が脆性的破壊することを防止</t>
   </si>
   <si>
-    <t>照査は「9.10 最小鉄筋量及び最大鉄筋量」に示す。</t>
+    <t>照査は「9.9 最小鉄筋量及び最大鉄筋量」に示す。</t>
   </si>
   <si>
     <t>(b) 軸方向力の最大値から定まる最小鉄筋量</t>

--- a/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
+++ b/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
@@ -8,13 +8,13 @@
     <sheet name="0400_照査の前提" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'0400_照査の前提'!$A$1:$AD$1598</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'0400_照査の前提'!$A$1:$AD$1692</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="760">
   <si>
     <t>§4. 照査の前提</t>
   </si>
@@ -4105,12 +4105,1186 @@
     <t>置は、中詰めコンクリート下端から 1100 mm なので、上記条件を満足する。</t>
   </si>
   <si>
-    <t>・ずれ止めの段数は2段以上とする。</t>
+    <t>・ずれ止めの段数は2段以上とし、(b) ずれ止めの杭頭反力に対する検討を満足する最小の段</t>
+  </si>
+  <si>
+    <t>数とする。</t>
   </si>
   <si>
     <t>実際に配置したずれ止めは、2 段なので、上記条件を満足する。</t>
   </si>
   <si>
+    <t>(b) ずれ止めの杭頭反力に対する検討</t>
+  </si>
+  <si>
+    <t>杭頭の圧縮軸力に対しては鋼管内部のずれ止めによる付着耐力と鋼管頭面のフーチングコン</t>
+  </si>
+  <si>
+    <t>クリートの支圧耐力の和によって抵抗するものとする。一方、引張軸力に対しては鋼管内部</t>
+  </si>
+  <si>
+    <t>のずれ止めによる付着耐力のみによって抵抗するものとする。【杭体設計の手引き 2.4】</t>
+  </si>
+  <si>
+    <t>①ずれ止めの付着強度の算定</t>
+  </si>
+  <si>
+    <t>ずれ止めを設けた場合の鋼管内面と中詰めコンクリートの付着強度τd (N/mm²) は、次式で</t>
+  </si>
+  <si>
+    <t>求める。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>τ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> ＝ (3.5 ＋ 190</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>f'</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>ck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>・t'／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve">・t／D)／γc ≦ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> N/mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>【杭体設計の手引き 解(2.4-19)】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>ここに、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>f'</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>ck</t>
+    </r>
+  </si>
+  <si>
+    <t>中詰めコンクリートの圧縮強度の特性値</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>（設計基準強度）(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N/mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>t'</t>
+  </si>
+  <si>
+    <t>ずれ止めの厚さ (mm)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>z</t>
+    </r>
+  </si>
+  <si>
+    <t>ずれ止めの間隔 (mm)</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>鋼管の有効肉厚 (mm)</t>
+  </si>
+  <si>
+    <t>鋼管外径 (mm)</t>
+  </si>
+  <si>
+    <t>コンクリートの材料係数（一般に1.3）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>f'</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>ck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> ＝ 27.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N/mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>（中詰めコンクリート）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>τ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> ＝ (3.5 ＋ 190 × 27.0 × 16 ／ 250 × 17 ／ 800) ／ 1.3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve">＝ 8.06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N/mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> ≦ 15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N/mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>②鋼管頭面の支圧耐力の算定</t>
+  </si>
+  <si>
+    <t>圧縮軸力に対する鋼管頭面の支圧耐力Rdについては、次式で求める。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> ＝ η・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>f'</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>ck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>／γc　　η ＝ (A／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>1/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> ≦ 2</t>
+    </r>
+  </si>
+  <si>
+    <t>【杭体設計の手引き 解(2.4-20)】</t>
+  </si>
+  <si>
+    <t>ここに、A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>コンクリートの支圧分布面積 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>鋼管の断面積 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>鋼管端部の過度の支圧力によるフーチングの損傷を回避するため、鋼管内面の付着耐力に対</t>
+  </si>
+  <si>
+    <t>して、鋼管頭面の支圧耐力は従たる抵抗力と考えることとし、コンクリートの支圧分布面積A</t>
+  </si>
+  <si>
+    <t>は、鋼管の断面積Aaと同一（すなわちη＝1）とする。</t>
+  </si>
+  <si>
+    <t>鋼管の内径（製造時の肉厚 18 mm）　：　800 － 2 × 18 ＝ 764 mm</t>
+  </si>
+  <si>
+    <t>π</t>
+  </si>
+  <si>
+    <t>(800² − 764²)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>f'</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>ck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> ＝ 27.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N/mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>（フーチング）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+  </si>
+  <si>
+    <t>918436</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>③ずれ止めの照査</t>
+  </si>
+  <si>
+    <t>鋼管杭の杭頭部におけるずれ止めの設計については、以下の式により照査を行う。なお、設</t>
+  </si>
+  <si>
+    <t>計最大引張軸力はＬ２地震時における最大応答時の値を、設計最大圧縮軸力はＬ１地震時に</t>
+  </si>
+  <si>
+    <t>おける最大応答時の値を用いて照査を行う。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>・引張軸力　γi・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>／[{π(D－2t)・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>τ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve">}／γb] ≦ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>1.00</t>
+    </r>
+  </si>
+  <si>
+    <t>【杭体設計の手引き 解(2.4-21)】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>・圧縮軸力　γi・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>／[{π(D－2t)・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>τ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve">}／γb] ≦ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>1.00</t>
+    </r>
+  </si>
+  <si>
+    <t>【杭体設計の手引き 解(2.4-22)】</t>
+  </si>
+  <si>
+    <t>ここに、D</t>
+  </si>
+  <si>
+    <t>鋼管外径 (= 800 mm)</t>
+  </si>
+  <si>
+    <t>鋼管の有効肉厚 (= 17 mm)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+  </si>
+  <si>
+    <t>鋼管と中詰めコンクリートとの付着の有効範囲</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>(= n・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> ＝ 2 × 250 ＝ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>ずれ止め段数 (= 2 段)</t>
+  </si>
+  <si>
+    <t>ずれ止めの間隔 (= 250 mm)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>τ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+  </si>
+  <si>
+    <t>鋼管内面と中詰めコンクリートの付着強度</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve">(= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>8.06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> N/mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>鋼管頭面の支圧耐力 (= 918436 N)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>d</t>
+    </r>
+  </si>
+  <si>
+    <t>杭1本当りの設計最大引張軸力 (= 6576140 N)</t>
+  </si>
+  <si>
+    <t>（Ｌ２地震時、線路直角方向の最大応答値）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>p</t>
+    </r>
+  </si>
+  <si>
+    <t>杭1本当りの設計最大圧縮軸力 (= 6910830 N)</t>
+  </si>
+  <si>
+    <t>（Ｌ１地震時、線路方向の最大応答値）</t>
+  </si>
+  <si>
+    <t>γb</t>
+  </si>
+  <si>
+    <t>部材係数 (= 1.0)</t>
+  </si>
+  <si>
+    <t>γi</t>
+  </si>
+  <si>
+    <t>構造物係数 (= 1.0)</t>
+  </si>
+  <si>
+    <t>一般に、設計最大軸力は、Ｌ２地震時の最大応答時の値を用いればよい。ただし、鋼管ソイ</t>
+  </si>
+  <si>
+    <t>ルセメント杭では、圧縮軸力に対して鋼管のみが抵抗するのではなく、鋼管内のソイルセメ</t>
+  </si>
+  <si>
+    <t>ントやコンクリート自体も一体として抵抗するため、地震時に生じる大きな圧縮軸力に対し</t>
+  </si>
+  <si>
+    <t>て杭頭部のずれ止めの付着耐力（および鋼管端部の支圧耐力）のみで抵抗する必要は無いと</t>
+  </si>
+  <si>
+    <t>考えられる。そのため、設計最大圧縮軸力はＬ１地震時の応答値を用いてよいこととする。</t>
+  </si>
+  <si>
+    <t>・引張軸力に対しての照査（Ｌ２地震時）</t>
+  </si>
+  <si>
+    <t>1.0 × 6576140 / [{π × (800 - 2 × 17) × 500 × 8.06} / 1.0]</t>
+  </si>
+  <si>
+    <t>＝ 0.68 ≦ 1.00 ・・・・・・ OK</t>
+  </si>
+  <si>
+    <t>・圧縮軸力に対しての照査（Ｌ１地震時）</t>
+  </si>
+  <si>
+    <t>1.0 × 6910830 / [{π × (800 - 2 × 17) × 500 × 8.06 + 918436} / 1.0]</t>
+  </si>
+  <si>
+    <t>＝ 0.65 ≦ 1.00 ・・・・・・ OK</t>
+  </si>
+  <si>
+    <t>以上より、ずれ止めの段数は、2段以上でこの検討を満足する最小の 2 段とする。</t>
+  </si>
+  <si>
     <t>10) 構造細目一覧</t>
   </si>
   <si>
@@ -4270,10 +5444,28 @@
     <t>ずれ止めの段数</t>
   </si>
   <si>
-    <t>2段以上</t>
+    <t>2段以上かつ(b)を満足</t>
   </si>
   <si>
     <t>2 段</t>
+  </si>
+  <si>
+    <t>ずれ止めの杭頭反力</t>
+  </si>
+  <si>
+    <t>照査値 ≦ 1.00</t>
+  </si>
+  <si>
+    <t>引張 0.68</t>
+  </si>
+  <si>
+    <t>(b)参照</t>
+  </si>
+  <si>
+    <t>に対する検討</t>
+  </si>
+  <si>
+    <t>圧縮 0.65</t>
   </si>
   <si>
     <t>(3) ソイルセメント</t>
@@ -5612,7 +6804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5702,6 +6894,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -5876,7 +7071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD1598"/>
+  <dimension ref="A1:AD1692"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="30" width="2.625" customWidth="1"/>
@@ -14653,920 +15848,312 @@
         <v>544</v>
       </c>
     </row>
-    <row r="1448" ht="15.75" customHeight="1"/>
+    <row r="1448" ht="15.75" customHeight="1">
+      <c r="E1448" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
     <row r="1449" ht="15.75" customHeight="1"/>
-    <row r="1450" ht="15.75" customHeight="1"/>
+    <row r="1450" ht="15.75" customHeight="1">
+      <c r="E1450" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
     <row r="1451" ht="15.75" customHeight="1"/>
-    <row r="1452" ht="15.75" customHeight="1"/>
-    <row r="1453" ht="15.75" customHeight="1"/>
-    <row r="1454" ht="15.75" customHeight="1"/>
+    <row r="1452" ht="15.75" customHeight="1">
+      <c r="E1452" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="1453" ht="15.75" customHeight="1">
+      <c r="E1453" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="1454" ht="15.75" customHeight="1">
+      <c r="E1454" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
     <row r="1455" ht="15.75" customHeight="1"/>
     <row r="1456" ht="15.75" customHeight="1"/>
     <row r="1457" ht="15.75" customHeight="1"/>
     <row r="1458" ht="15.75" customHeight="1">
-      <c r="D1458" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="1459" ht="15.75" customHeight="1"/>
+      <c r="E1458" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="1459" ht="15.75" customHeight="1">
+      <c r="E1459" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
     <row r="1460" ht="15.75" customHeight="1">
-      <c r="B1460" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="1461" ht="15.75" customHeight="1">
-      <c r="B1461" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C1461" s="8"/>
-      <c r="D1461" s="8"/>
-      <c r="E1461" s="8"/>
-      <c r="F1461" s="8"/>
-      <c r="G1461" s="8"/>
-      <c r="H1461" s="8"/>
-      <c r="I1461" s="8"/>
-      <c r="J1461" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="K1461" s="8"/>
-      <c r="L1461" s="8"/>
-      <c r="M1461" s="8"/>
-      <c r="N1461" s="8"/>
-      <c r="O1461" s="8"/>
-      <c r="P1461" s="8"/>
-      <c r="Q1461" s="8"/>
-      <c r="R1461" s="8"/>
-      <c r="S1461" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="T1461" s="8"/>
-      <c r="U1461" s="8"/>
-      <c r="V1461" s="8"/>
-      <c r="W1461" s="8"/>
-      <c r="X1461" s="8"/>
-      <c r="Y1461" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="Z1461" s="8"/>
-      <c r="AA1461" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB1461" s="8"/>
-      <c r="AC1461" s="8"/>
-      <c r="AD1461" s="21"/>
-    </row>
+      <c r="E1460" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="1461" ht="15.75" customHeight="1"/>
     <row r="1462" ht="15.75" customHeight="1">
-      <c r="B1462" s="23" t="s">
-        <v>546</v>
-      </c>
-      <c r="C1462" s="12"/>
-      <c r="D1462" s="12"/>
-      <c r="E1462" s="12"/>
-      <c r="F1462" s="12"/>
-      <c r="G1462" s="12"/>
-      <c r="H1462" s="12"/>
-      <c r="I1462" s="12"/>
-      <c r="J1462" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="K1462" s="12"/>
-      <c r="L1462" s="12"/>
-      <c r="M1462" s="12"/>
-      <c r="N1462" s="12"/>
-      <c r="O1462" s="12"/>
-      <c r="P1462" s="12"/>
-      <c r="Q1462" s="12"/>
-      <c r="R1462" s="12"/>
-      <c r="S1462" s="14" t="s">
-        <v>548</v>
-      </c>
-      <c r="T1462" s="12"/>
-      <c r="U1462" s="12"/>
-      <c r="V1462" s="12"/>
-      <c r="W1462" s="12"/>
-      <c r="X1462" s="12"/>
-      <c r="Y1462" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1462" s="12"/>
-      <c r="AA1462" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1462" s="12"/>
-      <c r="AC1462" s="12"/>
-      <c r="AD1462" s="26"/>
+      <c r="F1462" s="2" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="1463" ht="15.75" customHeight="1">
-      <c r="B1463" s="23" t="s">
-        <v>549</v>
-      </c>
-      <c r="C1463" s="12"/>
-      <c r="D1463" s="12"/>
-      <c r="E1463" s="12"/>
-      <c r="F1463" s="12"/>
-      <c r="G1463" s="12"/>
-      <c r="H1463" s="12"/>
-      <c r="I1463" s="12"/>
-      <c r="J1463" s="14" t="s">
-        <v>550</v>
-      </c>
-      <c r="K1463" s="12"/>
-      <c r="L1463" s="12"/>
-      <c r="M1463" s="12"/>
-      <c r="N1463" s="12"/>
-      <c r="O1463" s="12"/>
-      <c r="P1463" s="12"/>
-      <c r="Q1463" s="12"/>
-      <c r="R1463" s="12"/>
-      <c r="S1463" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="T1463" s="12"/>
-      <c r="U1463" s="12"/>
-      <c r="V1463" s="12"/>
-      <c r="W1463" s="12"/>
-      <c r="X1463" s="12"/>
-      <c r="Y1463" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1463" s="12"/>
-      <c r="AA1463" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1463" s="12"/>
-      <c r="AC1463" s="12"/>
-      <c r="AD1463" s="26"/>
-    </row>
-    <row r="1464" ht="15.75" customHeight="1">
-      <c r="B1464" s="23" t="s">
-        <v>551</v>
-      </c>
-      <c r="C1464" s="12"/>
-      <c r="D1464" s="12"/>
-      <c r="E1464" s="12"/>
-      <c r="F1464" s="12"/>
-      <c r="G1464" s="12"/>
-      <c r="H1464" s="12"/>
-      <c r="I1464" s="12"/>
-      <c r="J1464" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="K1464" s="12"/>
-      <c r="L1464" s="12"/>
-      <c r="M1464" s="12"/>
-      <c r="N1464" s="12"/>
-      <c r="O1464" s="12"/>
-      <c r="P1464" s="12"/>
-      <c r="Q1464" s="12"/>
-      <c r="R1464" s="12"/>
-      <c r="S1464" s="14" t="s">
-        <v>553</v>
-      </c>
-      <c r="T1464" s="12"/>
-      <c r="U1464" s="12"/>
-      <c r="V1464" s="12"/>
-      <c r="W1464" s="12"/>
-      <c r="X1464" s="12"/>
-      <c r="Y1464" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1464" s="12"/>
-      <c r="AA1464" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1464" s="12"/>
-      <c r="AC1464" s="12"/>
-      <c r="AD1464" s="26"/>
-    </row>
+      <c r="F1463" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="1464" ht="15.75" customHeight="1"/>
     <row r="1465" ht="15.75" customHeight="1">
-      <c r="B1465" s="23" t="s">
-        <v>554</v>
-      </c>
-      <c r="C1465" s="12"/>
-      <c r="D1465" s="12"/>
-      <c r="E1465" s="12"/>
-      <c r="F1465" s="12"/>
-      <c r="G1465" s="12"/>
-      <c r="H1465" s="12"/>
-      <c r="I1465" s="12"/>
-      <c r="J1465" s="14" t="s">
+      <c r="E1465" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="K1465" s="12"/>
-      <c r="L1465" s="12"/>
-      <c r="M1465" s="12"/>
-      <c r="N1465" s="12"/>
-      <c r="O1465" s="12"/>
-      <c r="P1465" s="12"/>
-      <c r="Q1465" s="12"/>
-      <c r="R1465" s="12"/>
-      <c r="S1465" s="14" t="s">
+      <c r="J1465" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1465" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="T1465" s="12"/>
-      <c r="U1465" s="12"/>
-      <c r="V1465" s="12"/>
-      <c r="W1465" s="12"/>
-      <c r="X1465" s="12"/>
-      <c r="Y1465" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1465" s="12"/>
-      <c r="AA1465" s="14" t="s">
+    </row>
+    <row r="1466" ht="15.75" customHeight="1">
+      <c r="J1466" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1466" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="AB1465" s="12"/>
-      <c r="AC1465" s="12"/>
-      <c r="AD1465" s="26"/>
-    </row>
-    <row r="1466" ht="15.75" customHeight="1">
-      <c r="B1466" s="23" t="s">
+    </row>
+    <row r="1467" ht="15.75" customHeight="1">
+      <c r="H1467" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="C1466" s="12"/>
-      <c r="D1466" s="12"/>
-      <c r="E1466" s="12"/>
-      <c r="F1466" s="12"/>
-      <c r="G1466" s="12"/>
-      <c r="H1466" s="12"/>
-      <c r="I1466" s="12"/>
-      <c r="J1466" s="14" t="s">
+      <c r="J1467" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1467" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="K1466" s="12"/>
-      <c r="L1466" s="12"/>
-      <c r="M1466" s="12"/>
-      <c r="N1466" s="12"/>
-      <c r="O1466" s="12"/>
-      <c r="P1466" s="12"/>
-      <c r="Q1466" s="12"/>
-      <c r="R1466" s="12"/>
-      <c r="S1466" s="14" t="s">
+    </row>
+    <row r="1468" ht="15.75" customHeight="1">
+      <c r="H1468" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="T1466" s="12"/>
-      <c r="U1466" s="12"/>
-      <c r="V1466" s="12"/>
-      <c r="W1466" s="12"/>
-      <c r="X1466" s="12"/>
-      <c r="Y1466" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1466" s="12"/>
-      <c r="AA1466" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1466" s="12"/>
-      <c r="AC1466" s="12"/>
-      <c r="AD1466" s="26"/>
-    </row>
-    <row r="1467" ht="15.75" customHeight="1">
-      <c r="B1467" s="23" t="s">
+      <c r="J1468" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1468" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="C1467" s="12"/>
-      <c r="D1467" s="12"/>
-      <c r="E1467" s="12"/>
-      <c r="F1467" s="12"/>
-      <c r="G1467" s="12"/>
-      <c r="H1467" s="12"/>
-      <c r="I1467" s="12"/>
-      <c r="J1467" s="14" t="s">
+    </row>
+    <row r="1469" ht="15.75" customHeight="1">
+      <c r="I1469" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="K1467" s="12"/>
-      <c r="L1467" s="12"/>
-      <c r="M1467" s="12"/>
-      <c r="N1467" s="12"/>
-      <c r="O1467" s="12"/>
-      <c r="P1467" s="12"/>
-      <c r="Q1467" s="12"/>
-      <c r="R1467" s="12"/>
-      <c r="S1467" s="14" t="s">
+      <c r="J1469" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1469" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="T1467" s="12"/>
-      <c r="U1467" s="12"/>
-      <c r="V1467" s="12"/>
-      <c r="W1467" s="12"/>
-      <c r="X1467" s="12"/>
-      <c r="Y1467" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1467" s="12"/>
-      <c r="AA1467" s="29"/>
-      <c r="AB1467" s="12"/>
-      <c r="AC1467" s="12"/>
-      <c r="AD1467" s="26"/>
-    </row>
-    <row r="1468" ht="15.75" customHeight="1">
-      <c r="B1468" s="23" t="s">
+    </row>
+    <row r="1470" ht="15.75" customHeight="1">
+      <c r="I1470" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="J1470" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1470" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C1468" s="12"/>
-      <c r="D1468" s="12"/>
-      <c r="E1468" s="12"/>
-      <c r="F1468" s="12"/>
-      <c r="G1468" s="12"/>
-      <c r="H1468" s="12"/>
-      <c r="I1468" s="12"/>
-      <c r="J1468" s="14" t="s">
+    </row>
+    <row r="1471" ht="15.75" customHeight="1">
+      <c r="H1471" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="J1471" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1471" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="K1468" s="12"/>
-      <c r="L1468" s="12"/>
-      <c r="M1468" s="12"/>
-      <c r="N1468" s="12"/>
-      <c r="O1468" s="12"/>
-      <c r="P1468" s="12"/>
-      <c r="Q1468" s="12"/>
-      <c r="R1468" s="12"/>
-      <c r="S1468" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="T1468" s="12"/>
-      <c r="U1468" s="12"/>
-      <c r="V1468" s="12"/>
-      <c r="W1468" s="12"/>
-      <c r="X1468" s="12"/>
-      <c r="Y1468" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1468" s="12"/>
-      <c r="AA1468" s="29"/>
-      <c r="AB1468" s="12"/>
-      <c r="AC1468" s="12"/>
-      <c r="AD1468" s="26"/>
-    </row>
-    <row r="1469" ht="15.75" customHeight="1">
-      <c r="B1469" s="23" t="s">
+    </row>
+    <row r="1472" ht="15.75" customHeight="1"/>
+    <row r="1473" ht="15.75" customHeight="1">
+      <c r="F1473" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="C1469" s="12"/>
-      <c r="D1469" s="12"/>
-      <c r="E1469" s="12"/>
-      <c r="F1469" s="12"/>
-      <c r="G1469" s="12"/>
-      <c r="H1469" s="12"/>
-      <c r="I1469" s="12"/>
-      <c r="J1469" s="14" t="s">
+    </row>
+    <row r="1474" ht="15.75" customHeight="1">
+      <c r="F1474" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="K1469" s="12"/>
-      <c r="L1469" s="12"/>
-      <c r="M1469" s="12"/>
-      <c r="N1469" s="12"/>
-      <c r="O1469" s="12"/>
-      <c r="P1469" s="12"/>
-      <c r="Q1469" s="12"/>
-      <c r="R1469" s="12"/>
-      <c r="S1469" s="14" t="s">
+    </row>
+    <row r="1475" ht="15.75" customHeight="1">
+      <c r="G1475" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="T1469" s="12"/>
-      <c r="U1469" s="12"/>
-      <c r="V1469" s="12"/>
-      <c r="W1469" s="12"/>
-      <c r="X1469" s="12"/>
-      <c r="Y1469" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1469" s="12"/>
-      <c r="AA1469" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1469" s="12"/>
-      <c r="AC1469" s="12"/>
-      <c r="AD1469" s="26"/>
-    </row>
-    <row r="1470" ht="15.75" customHeight="1">
-      <c r="B1470" s="23" t="s">
+    </row>
+    <row r="1476" ht="15.75" customHeight="1"/>
+    <row r="1477" ht="15.75" customHeight="1">
+      <c r="E1477" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C1470" s="12"/>
-      <c r="D1470" s="12"/>
-      <c r="E1470" s="12"/>
-      <c r="F1470" s="12"/>
-      <c r="G1470" s="12"/>
-      <c r="H1470" s="12"/>
-      <c r="I1470" s="12"/>
-      <c r="J1470" s="14" t="s">
+    </row>
+    <row r="1478" ht="15.75" customHeight="1">
+      <c r="E1478" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="K1470" s="12"/>
-      <c r="L1470" s="12"/>
-      <c r="M1470" s="12"/>
-      <c r="N1470" s="12"/>
-      <c r="O1470" s="12"/>
-      <c r="P1470" s="12"/>
-      <c r="Q1470" s="12"/>
-      <c r="R1470" s="12"/>
-      <c r="S1470" s="14" t="s">
+    </row>
+    <row r="1479" ht="15.75" customHeight="1"/>
+    <row r="1480" ht="15.75" customHeight="1">
+      <c r="F1480" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="T1470" s="12"/>
-      <c r="U1470" s="12"/>
-      <c r="V1470" s="12"/>
-      <c r="W1470" s="12"/>
-      <c r="X1470" s="12"/>
-      <c r="Y1470" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1470" s="12"/>
-      <c r="AA1470" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1470" s="12"/>
-      <c r="AC1470" s="12"/>
-      <c r="AD1470" s="26"/>
-    </row>
-    <row r="1471" ht="15.75" customHeight="1">
-      <c r="B1471" s="23" t="s">
+    </row>
+    <row r="1481" ht="15.75" customHeight="1">
+      <c r="F1481" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C1471" s="12"/>
-      <c r="D1471" s="12"/>
-      <c r="E1471" s="12"/>
-      <c r="F1471" s="12"/>
-      <c r="G1471" s="12"/>
-      <c r="H1471" s="12"/>
-      <c r="I1471" s="12"/>
-      <c r="J1471" s="14" t="s">
+    </row>
+    <row r="1482" ht="15.75" customHeight="1"/>
+    <row r="1483" ht="15.75" customHeight="1">
+      <c r="F1483" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="K1471" s="12"/>
-      <c r="L1471" s="12"/>
-      <c r="M1471" s="12"/>
-      <c r="N1471" s="12"/>
-      <c r="O1471" s="12"/>
-      <c r="P1471" s="12"/>
-      <c r="Q1471" s="12"/>
-      <c r="R1471" s="12"/>
-      <c r="S1471" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="T1471" s="12"/>
-      <c r="U1471" s="12"/>
-      <c r="V1471" s="12"/>
-      <c r="W1471" s="12"/>
-      <c r="X1471" s="12"/>
-      <c r="Y1471" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1471" s="12"/>
-      <c r="AA1471" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1471" s="12"/>
-      <c r="AC1471" s="12"/>
-      <c r="AD1471" s="26"/>
-    </row>
-    <row r="1472" ht="15.75" customHeight="1">
-      <c r="B1472" s="11" t="s">
+      <c r="J1483" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1483" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C1472" s="12"/>
-      <c r="D1472" s="12"/>
-      <c r="E1472" s="12"/>
-      <c r="F1472" s="12"/>
-      <c r="G1472" s="12"/>
-      <c r="H1472" s="12"/>
-      <c r="I1472" s="12"/>
-      <c r="J1472" s="14" t="s">
+    </row>
+    <row r="1484" ht="15.75" customHeight="1">
+      <c r="H1484" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="K1472" s="12"/>
-      <c r="L1472" s="12"/>
-      <c r="M1472" s="12"/>
-      <c r="N1472" s="12"/>
-      <c r="O1472" s="12"/>
-      <c r="P1472" s="12"/>
-      <c r="Q1472" s="12"/>
-      <c r="R1472" s="12"/>
-      <c r="S1472" s="14" t="s">
+      <c r="J1484" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1484" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="T1472" s="12"/>
-      <c r="U1472" s="12"/>
-      <c r="V1472" s="12"/>
-      <c r="W1472" s="12"/>
-      <c r="X1472" s="12"/>
-      <c r="Y1472" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1472" s="12"/>
-      <c r="AA1472" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1472" s="12"/>
-      <c r="AC1472" s="12"/>
-      <c r="AD1472" s="26"/>
-    </row>
-    <row r="1473" ht="15.75" customHeight="1">
-      <c r="B1473" s="10"/>
-      <c r="J1473" s="30" t="s">
+    </row>
+    <row r="1485" ht="15.75" customHeight="1">
+      <c r="H1485" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="J1485" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1485" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="1486" ht="15.75" customHeight="1"/>
+    <row r="1487" ht="15.75" customHeight="1">
+      <c r="E1487" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="S1473" s="15"/>
-      <c r="Y1473" s="15"/>
-      <c r="AA1473" s="15"/>
-      <c r="AD1473" s="22"/>
-    </row>
-    <row r="1474" ht="15.75" customHeight="1">
-      <c r="B1474" s="10"/>
-      <c r="J1474" s="14" t="s">
+    </row>
+    <row r="1488" ht="15.75" customHeight="1">
+      <c r="E1488" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="K1474" s="12"/>
-      <c r="L1474" s="12"/>
-      <c r="M1474" s="12"/>
-      <c r="N1474" s="12"/>
-      <c r="O1474" s="12"/>
-      <c r="P1474" s="12"/>
-      <c r="Q1474" s="12"/>
-      <c r="R1474" s="12"/>
-      <c r="S1474" s="14" t="s">
+    </row>
+    <row r="1489" ht="15.75" customHeight="1">
+      <c r="E1489" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="T1474" s="12"/>
-      <c r="U1474" s="12"/>
-      <c r="V1474" s="12"/>
-      <c r="W1474" s="12"/>
-      <c r="X1474" s="12"/>
-      <c r="Y1474" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1474" s="12"/>
-      <c r="AA1474" s="15"/>
-      <c r="AD1474" s="22"/>
-    </row>
-    <row r="1475" ht="15.75" customHeight="1">
-      <c r="B1475" s="10"/>
-      <c r="J1475" s="14" t="s">
+    </row>
+    <row r="1490" ht="15.75" customHeight="1"/>
+    <row r="1491" ht="15.75" customHeight="1">
+      <c r="F1491" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="K1475" s="12"/>
-      <c r="L1475" s="12"/>
-      <c r="M1475" s="12"/>
-      <c r="N1475" s="12"/>
-      <c r="O1475" s="12"/>
-      <c r="P1475" s="12"/>
-      <c r="Q1475" s="12"/>
-      <c r="R1475" s="12"/>
-      <c r="S1475" s="14" t="s">
+    </row>
+    <row r="1492" ht="15.75" customHeight="1">
+      <c r="H1492" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="I1492" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1492" s="6">
+        <v>1</v>
+      </c>
+      <c r="K1492" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1492" s="6">
+        <v>4</v>
+      </c>
+      <c r="M1492" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1492" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="T1475" s="12"/>
-      <c r="U1475" s="12"/>
-      <c r="V1475" s="12"/>
-      <c r="W1475" s="12"/>
-      <c r="X1475" s="12"/>
-      <c r="Y1475" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1475" s="12"/>
-      <c r="AA1475" s="15"/>
-      <c r="AD1475" s="22"/>
-    </row>
-    <row r="1476" ht="15.75" customHeight="1">
-      <c r="B1476" s="23" t="s">
+      <c r="O1492" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1492" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="C1476" s="12"/>
-      <c r="D1476" s="12"/>
-      <c r="E1476" s="12"/>
-      <c r="F1476" s="12"/>
-      <c r="G1476" s="12"/>
-      <c r="H1476" s="12"/>
-      <c r="I1476" s="12"/>
-      <c r="J1476" s="14" t="s">
+      <c r="Y1492" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1492" s="6">
+        <v>44221</v>
+      </c>
+      <c r="AC1492" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="1493" ht="15.75" customHeight="1">
+      <c r="F1493" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="K1476" s="12"/>
-      <c r="L1476" s="12"/>
-      <c r="M1476" s="12"/>
-      <c r="N1476" s="12"/>
-      <c r="O1476" s="12"/>
-      <c r="P1476" s="12"/>
-      <c r="Q1476" s="12"/>
-      <c r="R1476" s="12"/>
-      <c r="S1476" s="14" t="s">
+    </row>
+    <row r="1494" ht="15.75" customHeight="1">
+      <c r="H1494" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="T1476" s="12"/>
-      <c r="U1476" s="12"/>
-      <c r="V1476" s="12"/>
-      <c r="W1476" s="12"/>
-      <c r="X1476" s="12"/>
-      <c r="Y1476" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1476" s="12"/>
-      <c r="AA1476" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1476" s="12"/>
-      <c r="AC1476" s="12"/>
-      <c r="AD1476" s="26"/>
-    </row>
-    <row r="1477" ht="15.75" customHeight="1">
-      <c r="B1477" s="23" t="s">
+      <c r="I1494" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1494" s="6">
+        <v>1</v>
+      </c>
+      <c r="K1494" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1494" s="5">
+        <v>27</v>
+      </c>
+      <c r="N1494" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1494" s="6">
+        <v>44221</v>
+      </c>
+      <c r="Q1494" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1494" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="Y1494" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1494" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="C1477" s="12"/>
-      <c r="D1477" s="12"/>
-      <c r="E1477" s="12"/>
-      <c r="F1477" s="12"/>
-      <c r="G1477" s="12"/>
-      <c r="H1477" s="12"/>
-      <c r="I1477" s="12"/>
-      <c r="J1477" s="14" t="s">
+      <c r="AC1494" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="K1477" s="12"/>
-      <c r="L1477" s="12"/>
-      <c r="M1477" s="12"/>
-      <c r="N1477" s="12"/>
-      <c r="O1477" s="12"/>
-      <c r="P1477" s="12"/>
-      <c r="Q1477" s="12"/>
-      <c r="R1477" s="12"/>
-      <c r="S1477" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="T1477" s="12"/>
-      <c r="U1477" s="12"/>
-      <c r="V1477" s="12"/>
-      <c r="W1477" s="12"/>
-      <c r="X1477" s="12"/>
-      <c r="Y1477" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1477" s="12"/>
-      <c r="AA1477" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1477" s="12"/>
-      <c r="AC1477" s="12"/>
-      <c r="AD1477" s="26"/>
-    </row>
-    <row r="1478" ht="15.75" customHeight="1">
-      <c r="B1478" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="C1478" s="12"/>
-      <c r="D1478" s="12"/>
-      <c r="E1478" s="12"/>
-      <c r="F1478" s="12"/>
-      <c r="G1478" s="12"/>
-      <c r="H1478" s="12"/>
-      <c r="I1478" s="12"/>
-      <c r="J1478" s="14" t="s">
-        <v>589</v>
-      </c>
-      <c r="K1478" s="12"/>
-      <c r="L1478" s="12"/>
-      <c r="M1478" s="12"/>
-      <c r="N1478" s="12"/>
-      <c r="O1478" s="12"/>
-      <c r="P1478" s="12"/>
-      <c r="Q1478" s="12"/>
-      <c r="R1478" s="12"/>
-      <c r="S1478" s="14" t="s">
-        <v>590</v>
-      </c>
-      <c r="T1478" s="12"/>
-      <c r="U1478" s="12"/>
-      <c r="V1478" s="12"/>
-      <c r="W1478" s="12"/>
-      <c r="X1478" s="12"/>
-      <c r="Y1478" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1478" s="12"/>
-      <c r="AA1478" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1478" s="12"/>
-      <c r="AC1478" s="12"/>
-      <c r="AD1478" s="26"/>
-    </row>
-    <row r="1479" ht="15.75" customHeight="1">
-      <c r="B1479" s="23" t="s">
-        <v>591</v>
-      </c>
-      <c r="C1479" s="12"/>
-      <c r="D1479" s="12"/>
-      <c r="E1479" s="12"/>
-      <c r="F1479" s="12"/>
-      <c r="G1479" s="12"/>
-      <c r="H1479" s="12"/>
-      <c r="I1479" s="12"/>
-      <c r="J1479" s="14" t="s">
-        <v>592</v>
-      </c>
-      <c r="K1479" s="12"/>
-      <c r="L1479" s="12"/>
-      <c r="M1479" s="12"/>
-      <c r="N1479" s="12"/>
-      <c r="O1479" s="12"/>
-      <c r="P1479" s="12"/>
-      <c r="Q1479" s="12"/>
-      <c r="R1479" s="12"/>
-      <c r="S1479" s="14" t="s">
-        <v>581</v>
-      </c>
-      <c r="T1479" s="12"/>
-      <c r="U1479" s="12"/>
-      <c r="V1479" s="12"/>
-      <c r="W1479" s="12"/>
-      <c r="X1479" s="12"/>
-      <c r="Y1479" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1479" s="12"/>
-      <c r="AA1479" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1479" s="12"/>
-      <c r="AC1479" s="12"/>
-      <c r="AD1479" s="26"/>
-    </row>
-    <row r="1480" ht="15.75" customHeight="1">
-      <c r="B1480" s="11" t="s">
-        <v>593</v>
-      </c>
-      <c r="C1480" s="12"/>
-      <c r="D1480" s="12"/>
-      <c r="E1480" s="12"/>
-      <c r="F1480" s="12"/>
-      <c r="G1480" s="12"/>
-      <c r="H1480" s="12"/>
-      <c r="I1480" s="12"/>
-      <c r="J1480" s="14" t="s">
-        <v>594</v>
-      </c>
-      <c r="K1480" s="12"/>
-      <c r="L1480" s="12"/>
-      <c r="M1480" s="12"/>
-      <c r="N1480" s="12"/>
-      <c r="O1480" s="12"/>
-      <c r="P1480" s="12"/>
-      <c r="Q1480" s="12"/>
-      <c r="R1480" s="12"/>
-      <c r="S1480" s="14" t="s">
-        <v>579</v>
-      </c>
-      <c r="T1480" s="12"/>
-      <c r="U1480" s="12"/>
-      <c r="V1480" s="12"/>
-      <c r="W1480" s="12"/>
-      <c r="X1480" s="12"/>
-      <c r="Y1480" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1480" s="12"/>
-      <c r="AA1480" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1480" s="12"/>
-      <c r="AC1480" s="12"/>
-      <c r="AD1480" s="26"/>
-    </row>
-    <row r="1481" ht="15.75" customHeight="1">
-      <c r="B1481" s="10"/>
-      <c r="J1481" s="14" t="s">
-        <v>595</v>
-      </c>
-      <c r="K1481" s="12"/>
-      <c r="L1481" s="12"/>
-      <c r="M1481" s="12"/>
-      <c r="N1481" s="12"/>
-      <c r="O1481" s="12"/>
-      <c r="P1481" s="12"/>
-      <c r="Q1481" s="12"/>
-      <c r="R1481" s="12"/>
-      <c r="S1481" s="14" t="s">
-        <v>596</v>
-      </c>
-      <c r="T1481" s="12"/>
-      <c r="U1481" s="12"/>
-      <c r="V1481" s="12"/>
-      <c r="W1481" s="12"/>
-      <c r="X1481" s="12"/>
-      <c r="Y1481" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1481" s="12"/>
-      <c r="AA1481" s="15"/>
-      <c r="AD1481" s="22"/>
-    </row>
-    <row r="1482" ht="15.75" customHeight="1">
-      <c r="B1482" s="23" t="s">
-        <v>597</v>
-      </c>
-      <c r="C1482" s="12"/>
-      <c r="D1482" s="12"/>
-      <c r="E1482" s="12"/>
-      <c r="F1482" s="12"/>
-      <c r="G1482" s="12"/>
-      <c r="H1482" s="12"/>
-      <c r="I1482" s="12"/>
-      <c r="J1482" s="14" t="s">
-        <v>598</v>
-      </c>
-      <c r="K1482" s="12"/>
-      <c r="L1482" s="12"/>
-      <c r="M1482" s="12"/>
-      <c r="N1482" s="12"/>
-      <c r="O1482" s="12"/>
-      <c r="P1482" s="12"/>
-      <c r="Q1482" s="12"/>
-      <c r="R1482" s="12"/>
-      <c r="S1482" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="T1482" s="12"/>
-      <c r="U1482" s="12"/>
-      <c r="V1482" s="12"/>
-      <c r="W1482" s="12"/>
-      <c r="X1482" s="12"/>
-      <c r="Y1482" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z1482" s="12"/>
-      <c r="AA1482" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB1482" s="12"/>
-      <c r="AC1482" s="12"/>
-      <c r="AD1482" s="26"/>
-    </row>
-    <row r="1483" ht="15.75" customHeight="1">
-      <c r="B1483" s="8"/>
-      <c r="C1483" s="8"/>
-      <c r="D1483" s="8"/>
-      <c r="E1483" s="8"/>
-      <c r="F1483" s="8"/>
-      <c r="G1483" s="8"/>
-      <c r="H1483" s="8"/>
-      <c r="I1483" s="8"/>
-      <c r="J1483" s="8"/>
-      <c r="K1483" s="8"/>
-      <c r="L1483" s="8"/>
-      <c r="M1483" s="8"/>
-      <c r="N1483" s="8"/>
-      <c r="O1483" s="8"/>
-      <c r="P1483" s="8"/>
-      <c r="Q1483" s="8"/>
-      <c r="R1483" s="8"/>
-      <c r="S1483" s="8"/>
-      <c r="T1483" s="8"/>
-      <c r="U1483" s="8"/>
-      <c r="V1483" s="8"/>
-      <c r="W1483" s="8"/>
-      <c r="X1483" s="8"/>
-      <c r="Y1483" s="8"/>
-      <c r="Z1483" s="8"/>
-      <c r="AA1483" s="8"/>
-      <c r="AB1483" s="8"/>
-      <c r="AC1483" s="8"/>
-      <c r="AD1483" s="8"/>
-    </row>
-    <row r="1484" ht="15.75" customHeight="1">
-      <c r="C1484" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="1485" ht="15.75" customHeight="1"/>
-    <row r="1486" ht="15.75" customHeight="1">
-      <c r="D1486" s="1" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="1487" ht="15.75" customHeight="1"/>
-    <row r="1488" ht="15.75" customHeight="1">
-      <c r="E1488" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="T1488" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="1489" ht="15.75" customHeight="1"/>
-    <row r="1490" ht="15.75" customHeight="1">
-      <c r="E1490" s="2" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="1491" ht="15.75" customHeight="1">
-      <c r="E1491" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1492" ht="15.75" customHeight="1"/>
-    <row r="1493" ht="15.75" customHeight="1"/>
-    <row r="1494" ht="15.75" customHeight="1"/>
+    </row>
     <row r="1495" ht="15.75" customHeight="1"/>
     <row r="1496" ht="15.75" customHeight="1"/>
     <row r="1497" ht="15.75" customHeight="1"/>
@@ -15579,468 +16166,278 @@
     <row r="1504" ht="15.75" customHeight="1"/>
     <row r="1505" ht="15.75" customHeight="1">
       <c r="E1505" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="1506" ht="15.75" customHeight="1">
+      <c r="E1506" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="1507" ht="15.75" customHeight="1">
+      <c r="E1507" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="1508" ht="15.75" customHeight="1">
+      <c r="E1508" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="1509" ht="15.75" customHeight="1"/>
+    <row r="1510" ht="15.75" customHeight="1">
+      <c r="F1510" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="1511" ht="15.75" customHeight="1">
+      <c r="F1511" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="1512" ht="15.75" customHeight="1">
+      <c r="F1512" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="1513" ht="15.75" customHeight="1">
+      <c r="F1513" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="1514" ht="15.75" customHeight="1"/>
+    <row r="1515" ht="15.75" customHeight="1">
+      <c r="F1515" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="J1515" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1515" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="1516" ht="15.75" customHeight="1">
+      <c r="I1516" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="J1516" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1516" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="1517" ht="15.75" customHeight="1">
+      <c r="H1517" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="J1517" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1517" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="1518" ht="15.75" customHeight="1">
+      <c r="J1518" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1518" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="1519" ht="15.75" customHeight="1">
+      <c r="I1519" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="J1519" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1519" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="1520" ht="15.75" customHeight="1">
+      <c r="H1520" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J1520" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1520" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="1521" ht="15.75" customHeight="1">
+      <c r="H1521" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="J1521" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1521" s="2" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="1506" ht="15.75" customHeight="1">
-      <c r="F1506" s="2" t="s">
+    <row r="1522" ht="15.75" customHeight="1">
+      <c r="J1522" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1522" s="2" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="1507" ht="15.75" customHeight="1"/>
-    <row r="1508" ht="15.75" customHeight="1">
-      <c r="F1508" s="3" t="s">
+    <row r="1523" ht="15.75" customHeight="1">
+      <c r="H1523" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="J1523" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1523" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="J1508" s="4" t="s">
+    </row>
+    <row r="1524" ht="15.75" customHeight="1">
+      <c r="H1524" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="J1524" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K1508" s="2" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="1509" ht="15.75" customHeight="1">
-      <c r="H1509" s="3" t="s">
+      <c r="K1524" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="J1509" s="4" t="s">
+    </row>
+    <row r="1525" ht="15.75" customHeight="1">
+      <c r="J1525" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K1509" s="2" t="s">
+      <c r="K1525" s="2" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="1510" ht="15.75" customHeight="1">
-      <c r="H1510" s="3" t="s">
+    <row r="1526" ht="15.75" customHeight="1">
+      <c r="H1526" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="J1510" s="4" t="s">
+      <c r="J1526" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K1510" s="2" t="s">
+      <c r="K1526" s="2" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="1511" ht="15.75" customHeight="1">
-      <c r="H1511" s="3" t="s">
+    <row r="1527" ht="15.75" customHeight="1">
+      <c r="J1527" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1527" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="J1511" s="4" t="s">
+    </row>
+    <row r="1528" ht="15.75" customHeight="1">
+      <c r="H1528" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="J1528" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K1511" s="2" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="1512" ht="15.75" customHeight="1"/>
-    <row r="1513" ht="15.75" customHeight="1">
-      <c r="E1513" s="2" t="s">
+      <c r="K1528" s="2" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="1514" ht="15.75" customHeight="1">
-      <c r="E1514" s="2" t="s">
+    <row r="1529" ht="15.75" customHeight="1">
+      <c r="H1529" s="3" t="s">
         <v>616</v>
-      </c>
-    </row>
-    <row r="1515" ht="15.75" customHeight="1">
-      <c r="E1515" s="2" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="1516" ht="15.75" customHeight="1">
-      <c r="E1516" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="F1516" s="8"/>
-      <c r="G1516" s="8"/>
-      <c r="H1516" s="8"/>
-      <c r="I1516" s="8"/>
-      <c r="J1516" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="K1516" s="8"/>
-      <c r="L1516" s="8"/>
-      <c r="M1516" s="8"/>
-      <c r="N1516" s="8"/>
-      <c r="O1516" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="P1516" s="8"/>
-      <c r="Q1516" s="8"/>
-      <c r="R1516" s="8"/>
-      <c r="S1516" s="8"/>
-      <c r="T1516" s="8"/>
-      <c r="U1516" s="8"/>
-      <c r="V1516" s="8"/>
-      <c r="W1516" s="8"/>
-      <c r="X1516" s="8"/>
-      <c r="Y1516" s="8"/>
-      <c r="Z1516" s="8"/>
-      <c r="AA1516" s="10"/>
-    </row>
-    <row r="1517" ht="15.75" customHeight="1">
-      <c r="E1517" s="11" t="s">
-        <v>621</v>
-      </c>
-      <c r="F1517" s="12"/>
-      <c r="G1517" s="12"/>
-      <c r="H1517" s="12"/>
-      <c r="I1517" s="12"/>
-      <c r="J1517" s="14" t="s">
-        <v>622</v>
-      </c>
-      <c r="K1517" s="12"/>
-      <c r="L1517" s="12"/>
-      <c r="M1517" s="12"/>
-      <c r="N1517" s="12"/>
-      <c r="O1517" s="31">
-        <v>1000</v>
-      </c>
-      <c r="P1517" s="12"/>
-      <c r="Q1517" s="12"/>
-      <c r="R1517" s="12"/>
-      <c r="S1517" s="12"/>
-      <c r="T1517" s="12"/>
-      <c r="U1517" s="12"/>
-      <c r="V1517" s="12"/>
-      <c r="W1517" s="12"/>
-      <c r="X1517" s="12"/>
-      <c r="Y1517" s="12"/>
-      <c r="Z1517" s="12"/>
-      <c r="AA1517" s="10"/>
-    </row>
-    <row r="1518" ht="15.75" customHeight="1">
-      <c r="E1518" s="10"/>
-      <c r="J1518" s="14" t="s">
-        <v>623</v>
-      </c>
-      <c r="K1518" s="12"/>
-      <c r="L1518" s="12"/>
-      <c r="M1518" s="12"/>
-      <c r="N1518" s="12"/>
-      <c r="O1518" s="31">
-        <v>750</v>
-      </c>
-      <c r="P1518" s="12"/>
-      <c r="Q1518" s="12"/>
-      <c r="R1518" s="12"/>
-      <c r="S1518" s="12"/>
-      <c r="T1518" s="12"/>
-      <c r="U1518" s="12"/>
-      <c r="V1518" s="12"/>
-      <c r="W1518" s="12"/>
-      <c r="X1518" s="12"/>
-      <c r="Y1518" s="12"/>
-      <c r="Z1518" s="12"/>
-      <c r="AA1518" s="10"/>
-    </row>
-    <row r="1519" ht="15.75" customHeight="1">
-      <c r="E1519" s="8"/>
-      <c r="F1519" s="8"/>
-      <c r="G1519" s="8"/>
-      <c r="H1519" s="8"/>
-      <c r="I1519" s="8"/>
-      <c r="J1519" s="8"/>
-      <c r="K1519" s="8"/>
-      <c r="L1519" s="8"/>
-      <c r="M1519" s="8"/>
-      <c r="N1519" s="8"/>
-      <c r="O1519" s="8"/>
-      <c r="P1519" s="8"/>
-      <c r="Q1519" s="8"/>
-      <c r="R1519" s="8"/>
-      <c r="S1519" s="8"/>
-      <c r="T1519" s="8"/>
-      <c r="U1519" s="8"/>
-      <c r="V1519" s="8"/>
-      <c r="W1519" s="8"/>
-      <c r="X1519" s="8"/>
-      <c r="Y1519" s="8"/>
-      <c r="Z1519" s="8"/>
-    </row>
-    <row r="1520" ht="15.75" customHeight="1">
-      <c r="E1520" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="T1520" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="1521" ht="15.75" customHeight="1"/>
-    <row r="1522" ht="15.75" customHeight="1">
-      <c r="E1522" s="2" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="1523" ht="15.75" customHeight="1">
-      <c r="E1523" s="2" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="1524" ht="15.75" customHeight="1"/>
-    <row r="1525" ht="15.75" customHeight="1">
-      <c r="E1525" s="2" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="1526" ht="15.75" customHeight="1">
-      <c r="F1526" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="1527" ht="15.75" customHeight="1">
-      <c r="F1527" s="2" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="1528" ht="15.75" customHeight="1"/>
-    <row r="1529" ht="15.75" customHeight="1">
-      <c r="F1529" s="3" t="s">
-        <v>607</v>
       </c>
       <c r="J1529" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1529" s="2" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="1530" ht="15.75" customHeight="1">
-      <c r="H1530" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="J1530" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1530" s="2" t="s">
-        <v>631</v>
-      </c>
-    </row>
+        <v>617</v>
+      </c>
+    </row>
+    <row r="1530" ht="15.75" customHeight="1"/>
     <row r="1531" ht="15.75" customHeight="1">
-      <c r="H1531" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="J1531" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1531" s="2" t="s">
-        <v>633</v>
+      <c r="E1531" s="2" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="1532" ht="15.75" customHeight="1">
-      <c r="H1532" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="J1532" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1532" s="2" t="s">
-        <v>635</v>
+      <c r="E1532" s="2" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="1533" ht="15.75" customHeight="1">
-      <c r="H1533" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="J1533" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1533" s="2" t="s">
-        <v>637</v>
+      <c r="E1533" s="2" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="1534" ht="15.75" customHeight="1">
-      <c r="H1534" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="J1534" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1534" s="2" t="s">
-        <v>639</v>
+      <c r="E1534" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="1535" ht="15.75" customHeight="1">
-      <c r="H1535" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="J1535" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1535" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="1536" ht="15.75" customHeight="1">
-      <c r="H1536" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="J1536" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1536" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
+      <c r="E1535" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="1536" ht="15.75" customHeight="1"/>
     <row r="1537" ht="15.75" customHeight="1">
-      <c r="H1537" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="J1537" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1537" s="2" t="s">
-        <v>643</v>
+      <c r="E1537" s="2" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="1538" ht="15.75" customHeight="1">
-      <c r="H1538" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="J1538" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1538" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="1539" ht="15.75" customHeight="1"/>
-    <row r="1540" ht="15.75" customHeight="1">
-      <c r="E1540" s="2" t="s">
-        <v>615</v>
-      </c>
-    </row>
+      <c r="F1538" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="1539" ht="15.75" customHeight="1">
+      <c r="F1539" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="1540" ht="15.75" customHeight="1"/>
     <row r="1541" ht="15.75" customHeight="1">
       <c r="E1541" s="2" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1542" ht="15.75" customHeight="1">
-      <c r="E1542" s="2" t="s">
-        <v>645</v>
+      <c r="F1542" s="2" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="1543" ht="15.75" customHeight="1">
-      <c r="E1543" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="F1543" s="8"/>
-      <c r="G1543" s="8"/>
-      <c r="H1543" s="8"/>
-      <c r="I1543" s="8"/>
-      <c r="J1543" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="K1543" s="8"/>
-      <c r="L1543" s="8"/>
-      <c r="M1543" s="8"/>
-      <c r="N1543" s="8"/>
-      <c r="O1543" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="P1543" s="8"/>
-      <c r="Q1543" s="8"/>
-      <c r="R1543" s="8"/>
-      <c r="S1543" s="8"/>
-      <c r="T1543" s="8"/>
-      <c r="U1543" s="8"/>
-      <c r="V1543" s="8"/>
-      <c r="W1543" s="8"/>
-      <c r="X1543" s="8"/>
-      <c r="Y1543" s="8"/>
-      <c r="Z1543" s="8"/>
-      <c r="AA1543" s="10"/>
-    </row>
-    <row r="1544" ht="15.75" customHeight="1">
-      <c r="E1544" s="23" t="s">
-        <v>646</v>
-      </c>
-      <c r="F1544" s="12"/>
-      <c r="G1544" s="12"/>
-      <c r="H1544" s="12"/>
-      <c r="I1544" s="12"/>
-      <c r="J1544" s="14" t="s">
-        <v>647</v>
-      </c>
-      <c r="K1544" s="12"/>
-      <c r="L1544" s="12"/>
-      <c r="M1544" s="12"/>
-      <c r="N1544" s="12"/>
-      <c r="O1544" s="31">
-        <v>15000</v>
-      </c>
-      <c r="P1544" s="12"/>
-      <c r="Q1544" s="12"/>
-      <c r="R1544" s="12"/>
-      <c r="S1544" s="12"/>
-      <c r="T1544" s="12"/>
-      <c r="U1544" s="12"/>
-      <c r="V1544" s="12"/>
-      <c r="W1544" s="12"/>
-      <c r="X1544" s="12"/>
-      <c r="Y1544" s="12"/>
-      <c r="Z1544" s="12"/>
-      <c r="AA1544" s="10"/>
-    </row>
+      <c r="F1543" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="1544" ht="15.75" customHeight="1"/>
     <row r="1545" ht="15.75" customHeight="1">
-      <c r="E1545" s="8"/>
-      <c r="F1545" s="8"/>
-      <c r="G1545" s="8"/>
-      <c r="H1545" s="8"/>
-      <c r="I1545" s="8"/>
-      <c r="J1545" s="8"/>
-      <c r="K1545" s="8"/>
-      <c r="L1545" s="8"/>
-      <c r="M1545" s="8"/>
-      <c r="N1545" s="8"/>
-      <c r="O1545" s="8"/>
-      <c r="P1545" s="8"/>
-      <c r="Q1545" s="8"/>
-      <c r="R1545" s="8"/>
-      <c r="S1545" s="8"/>
-      <c r="T1545" s="8"/>
-      <c r="U1545" s="8"/>
-      <c r="V1545" s="8"/>
-      <c r="W1545" s="8"/>
-      <c r="X1545" s="8"/>
-      <c r="Y1545" s="8"/>
-      <c r="Z1545" s="8"/>
-    </row>
-    <row r="1546" ht="15.75" customHeight="1">
-      <c r="D1546" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="S1546" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
+      <c r="E1545" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="1546" ht="15.75" customHeight="1"/>
     <row r="1547" ht="15.75" customHeight="1"/>
-    <row r="1548" ht="15.75" customHeight="1">
-      <c r="E1548" s="2" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="1549" ht="15.75" customHeight="1">
-      <c r="E1549" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="1550" ht="15.75" customHeight="1">
-      <c r="E1550" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
+    <row r="1548" ht="15.75" customHeight="1"/>
+    <row r="1549" ht="15.75" customHeight="1"/>
+    <row r="1550" ht="15.75" customHeight="1"/>
     <row r="1551" ht="15.75" customHeight="1"/>
     <row r="1552" ht="15.75" customHeight="1">
       <c r="D1552" s="1" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1553" ht="15.75" customHeight="1"/>
     <row r="1554" ht="15.75" customHeight="1">
       <c r="B1554" s="2" t="s">
-        <v>652</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1555" ht="15.75" customHeight="1">
@@ -16054,20 +16451,20 @@
       <c r="G1555" s="8"/>
       <c r="H1555" s="8"/>
       <c r="I1555" s="8"/>
-      <c r="J1555" s="8"/>
-      <c r="K1555" s="9" t="s">
+      <c r="J1555" s="9" t="s">
         <v>357</v>
       </c>
+      <c r="K1555" s="8"/>
       <c r="L1555" s="8"/>
       <c r="M1555" s="8"/>
       <c r="N1555" s="8"/>
       <c r="O1555" s="8"/>
       <c r="P1555" s="8"/>
       <c r="Q1555" s="8"/>
-      <c r="R1555" s="9" t="s">
+      <c r="R1555" s="8"/>
+      <c r="S1555" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="S1555" s="8"/>
       <c r="T1555" s="8"/>
       <c r="U1555" s="8"/>
       <c r="V1555" s="8"/>
@@ -16085,32 +16482,30 @@
       <c r="AD1555" s="21"/>
     </row>
     <row r="1556" ht="15.75" customHeight="1">
-      <c r="B1556" s="11" t="s">
-        <v>653</v>
+      <c r="B1556" s="23" t="s">
+        <v>631</v>
       </c>
       <c r="C1556" s="12"/>
       <c r="D1556" s="12"/>
-      <c r="E1556" s="14" t="s">
-        <v>654</v>
-      </c>
+      <c r="E1556" s="12"/>
       <c r="F1556" s="12"/>
       <c r="G1556" s="12"/>
       <c r="H1556" s="12"/>
       <c r="I1556" s="12"/>
-      <c r="J1556" s="12"/>
-      <c r="K1556" s="14" t="s">
-        <v>655</v>
-      </c>
+      <c r="J1556" s="14" t="s">
+        <v>632</v>
+      </c>
+      <c r="K1556" s="12"/>
       <c r="L1556" s="12"/>
       <c r="M1556" s="12"/>
       <c r="N1556" s="12"/>
       <c r="O1556" s="12"/>
       <c r="P1556" s="12"/>
       <c r="Q1556" s="12"/>
-      <c r="R1556" s="14" t="s">
-        <v>656</v>
-      </c>
-      <c r="S1556" s="12"/>
+      <c r="R1556" s="12"/>
+      <c r="S1556" s="14" t="s">
+        <v>633</v>
+      </c>
       <c r="T1556" s="12"/>
       <c r="U1556" s="12"/>
       <c r="V1556" s="12"/>
@@ -16120,7 +16515,7 @@
         <v>363</v>
       </c>
       <c r="Z1556" s="12"/>
-      <c r="AA1556" s="13" t="s">
+      <c r="AA1556" s="14" t="s">
         <v>364</v>
       </c>
       <c r="AB1556" s="12"/>
@@ -16128,30 +16523,30 @@
       <c r="AD1556" s="26"/>
     </row>
     <row r="1557" ht="15.75" customHeight="1">
-      <c r="B1557" s="32" t="s">
-        <v>657</v>
-      </c>
-      <c r="E1557" s="14" t="s">
-        <v>658</v>
-      </c>
+      <c r="B1557" s="23" t="s">
+        <v>634</v>
+      </c>
+      <c r="C1557" s="12"/>
+      <c r="D1557" s="12"/>
+      <c r="E1557" s="12"/>
       <c r="F1557" s="12"/>
       <c r="G1557" s="12"/>
       <c r="H1557" s="12"/>
       <c r="I1557" s="12"/>
-      <c r="J1557" s="12"/>
-      <c r="K1557" s="14" t="s">
-        <v>659</v>
-      </c>
+      <c r="J1557" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="K1557" s="12"/>
       <c r="L1557" s="12"/>
       <c r="M1557" s="12"/>
       <c r="N1557" s="12"/>
       <c r="O1557" s="12"/>
       <c r="P1557" s="12"/>
       <c r="Q1557" s="12"/>
-      <c r="R1557" s="14" t="s">
-        <v>660</v>
-      </c>
-      <c r="S1557" s="12"/>
+      <c r="R1557" s="12"/>
+      <c r="S1557" s="14" t="s">
+        <v>69</v>
+      </c>
       <c r="T1557" s="12"/>
       <c r="U1557" s="12"/>
       <c r="V1557" s="12"/>
@@ -16161,34 +16556,38 @@
         <v>363</v>
       </c>
       <c r="Z1557" s="12"/>
-      <c r="AA1557" s="15"/>
-      <c r="AD1557" s="22"/>
+      <c r="AA1557" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1557" s="12"/>
+      <c r="AC1557" s="12"/>
+      <c r="AD1557" s="26"/>
     </row>
     <row r="1558" ht="15.75" customHeight="1">
-      <c r="B1558" s="32" t="s">
-        <v>661</v>
-      </c>
-      <c r="E1558" s="14" t="s">
-        <v>662</v>
-      </c>
+      <c r="B1558" s="23" t="s">
+        <v>636</v>
+      </c>
+      <c r="C1558" s="12"/>
+      <c r="D1558" s="12"/>
+      <c r="E1558" s="12"/>
       <c r="F1558" s="12"/>
       <c r="G1558" s="12"/>
       <c r="H1558" s="12"/>
       <c r="I1558" s="12"/>
-      <c r="J1558" s="12"/>
-      <c r="K1558" s="14" t="s">
-        <v>663</v>
-      </c>
+      <c r="J1558" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="K1558" s="12"/>
       <c r="L1558" s="12"/>
       <c r="M1558" s="12"/>
       <c r="N1558" s="12"/>
       <c r="O1558" s="12"/>
       <c r="P1558" s="12"/>
       <c r="Q1558" s="12"/>
-      <c r="R1558" s="14" t="s">
-        <v>664</v>
-      </c>
-      <c r="S1558" s="12"/>
+      <c r="R1558" s="12"/>
+      <c r="S1558" s="14" t="s">
+        <v>638</v>
+      </c>
       <c r="T1558" s="12"/>
       <c r="U1558" s="12"/>
       <c r="V1558" s="12"/>
@@ -16198,12 +16597,16 @@
         <v>363</v>
       </c>
       <c r="Z1558" s="12"/>
-      <c r="AA1558" s="15"/>
-      <c r="AD1558" s="22"/>
+      <c r="AA1558" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1558" s="12"/>
+      <c r="AC1558" s="12"/>
+      <c r="AD1558" s="26"/>
     </row>
     <row r="1559" ht="15.75" customHeight="1">
-      <c r="B1559" s="11" t="s">
-        <v>665</v>
+      <c r="B1559" s="23" t="s">
+        <v>639</v>
       </c>
       <c r="C1559" s="12"/>
       <c r="D1559" s="12"/>
@@ -16212,20 +16615,20 @@
       <c r="G1559" s="12"/>
       <c r="H1559" s="12"/>
       <c r="I1559" s="12"/>
-      <c r="J1559" s="12"/>
-      <c r="K1559" s="14" t="s">
-        <v>666</v>
-      </c>
+      <c r="J1559" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="K1559" s="12"/>
       <c r="L1559" s="12"/>
       <c r="M1559" s="12"/>
       <c r="N1559" s="12"/>
       <c r="O1559" s="12"/>
       <c r="P1559" s="12"/>
       <c r="Q1559" s="12"/>
-      <c r="R1559" s="14" t="s">
-        <v>667</v>
-      </c>
-      <c r="S1559" s="12"/>
+      <c r="R1559" s="12"/>
+      <c r="S1559" s="14" t="s">
+        <v>641</v>
+      </c>
       <c r="T1559" s="12"/>
       <c r="U1559" s="12"/>
       <c r="V1559" s="12"/>
@@ -16236,79 +16639,750 @@
       </c>
       <c r="Z1559" s="12"/>
       <c r="AA1559" s="14" t="s">
-        <v>364</v>
+        <v>642</v>
       </c>
       <c r="AB1559" s="12"/>
       <c r="AC1559" s="12"/>
       <c r="AD1559" s="26"/>
     </row>
     <row r="1560" ht="15.75" customHeight="1">
-      <c r="B1560" s="10"/>
-      <c r="K1560" s="15"/>
-      <c r="R1560" s="30" t="s">
+      <c r="B1560" s="23" t="s">
+        <v>643</v>
+      </c>
+      <c r="C1560" s="12"/>
+      <c r="D1560" s="12"/>
+      <c r="E1560" s="12"/>
+      <c r="F1560" s="12"/>
+      <c r="G1560" s="12"/>
+      <c r="H1560" s="12"/>
+      <c r="I1560" s="12"/>
+      <c r="J1560" s="14" t="s">
+        <v>644</v>
+      </c>
+      <c r="K1560" s="12"/>
+      <c r="L1560" s="12"/>
+      <c r="M1560" s="12"/>
+      <c r="N1560" s="12"/>
+      <c r="O1560" s="12"/>
+      <c r="P1560" s="12"/>
+      <c r="Q1560" s="12"/>
+      <c r="R1560" s="12"/>
+      <c r="S1560" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="T1560" s="12"/>
+      <c r="U1560" s="12"/>
+      <c r="V1560" s="12"/>
+      <c r="W1560" s="12"/>
+      <c r="X1560" s="12"/>
+      <c r="Y1560" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1560" s="12"/>
+      <c r="AA1560" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1560" s="12"/>
+      <c r="AC1560" s="12"/>
+      <c r="AD1560" s="26"/>
+    </row>
+    <row r="1561" ht="15.75" customHeight="1">
+      <c r="B1561" s="23" t="s">
+        <v>646</v>
+      </c>
+      <c r="C1561" s="12"/>
+      <c r="D1561" s="12"/>
+      <c r="E1561" s="12"/>
+      <c r="F1561" s="12"/>
+      <c r="G1561" s="12"/>
+      <c r="H1561" s="12"/>
+      <c r="I1561" s="12"/>
+      <c r="J1561" s="14" t="s">
+        <v>647</v>
+      </c>
+      <c r="K1561" s="12"/>
+      <c r="L1561" s="12"/>
+      <c r="M1561" s="12"/>
+      <c r="N1561" s="12"/>
+      <c r="O1561" s="12"/>
+      <c r="P1561" s="12"/>
+      <c r="Q1561" s="12"/>
+      <c r="R1561" s="12"/>
+      <c r="S1561" s="14" t="s">
+        <v>648</v>
+      </c>
+      <c r="T1561" s="12"/>
+      <c r="U1561" s="12"/>
+      <c r="V1561" s="12"/>
+      <c r="W1561" s="12"/>
+      <c r="X1561" s="12"/>
+      <c r="Y1561" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1561" s="12"/>
+      <c r="AA1561" s="29"/>
+      <c r="AB1561" s="12"/>
+      <c r="AC1561" s="12"/>
+      <c r="AD1561" s="26"/>
+    </row>
+    <row r="1562" ht="15.75" customHeight="1">
+      <c r="B1562" s="23" t="s">
+        <v>649</v>
+      </c>
+      <c r="C1562" s="12"/>
+      <c r="D1562" s="12"/>
+      <c r="E1562" s="12"/>
+      <c r="F1562" s="12"/>
+      <c r="G1562" s="12"/>
+      <c r="H1562" s="12"/>
+      <c r="I1562" s="12"/>
+      <c r="J1562" s="14" t="s">
+        <v>650</v>
+      </c>
+      <c r="K1562" s="12"/>
+      <c r="L1562" s="12"/>
+      <c r="M1562" s="12"/>
+      <c r="N1562" s="12"/>
+      <c r="O1562" s="12"/>
+      <c r="P1562" s="12"/>
+      <c r="Q1562" s="12"/>
+      <c r="R1562" s="12"/>
+      <c r="S1562" s="14" t="s">
+        <v>648</v>
+      </c>
+      <c r="T1562" s="12"/>
+      <c r="U1562" s="12"/>
+      <c r="V1562" s="12"/>
+      <c r="W1562" s="12"/>
+      <c r="X1562" s="12"/>
+      <c r="Y1562" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1562" s="12"/>
+      <c r="AA1562" s="29"/>
+      <c r="AB1562" s="12"/>
+      <c r="AC1562" s="12"/>
+      <c r="AD1562" s="26"/>
+    </row>
+    <row r="1563" ht="15.75" customHeight="1">
+      <c r="B1563" s="23" t="s">
+        <v>651</v>
+      </c>
+      <c r="C1563" s="12"/>
+      <c r="D1563" s="12"/>
+      <c r="E1563" s="12"/>
+      <c r="F1563" s="12"/>
+      <c r="G1563" s="12"/>
+      <c r="H1563" s="12"/>
+      <c r="I1563" s="12"/>
+      <c r="J1563" s="14" t="s">
+        <v>652</v>
+      </c>
+      <c r="K1563" s="12"/>
+      <c r="L1563" s="12"/>
+      <c r="M1563" s="12"/>
+      <c r="N1563" s="12"/>
+      <c r="O1563" s="12"/>
+      <c r="P1563" s="12"/>
+      <c r="Q1563" s="12"/>
+      <c r="R1563" s="12"/>
+      <c r="S1563" s="14" t="s">
+        <v>653</v>
+      </c>
+      <c r="T1563" s="12"/>
+      <c r="U1563" s="12"/>
+      <c r="V1563" s="12"/>
+      <c r="W1563" s="12"/>
+      <c r="X1563" s="12"/>
+      <c r="Y1563" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1563" s="12"/>
+      <c r="AA1563" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1563" s="12"/>
+      <c r="AC1563" s="12"/>
+      <c r="AD1563" s="26"/>
+    </row>
+    <row r="1564" ht="15.75" customHeight="1">
+      <c r="B1564" s="23" t="s">
+        <v>654</v>
+      </c>
+      <c r="C1564" s="12"/>
+      <c r="D1564" s="12"/>
+      <c r="E1564" s="12"/>
+      <c r="F1564" s="12"/>
+      <c r="G1564" s="12"/>
+      <c r="H1564" s="12"/>
+      <c r="I1564" s="12"/>
+      <c r="J1564" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="K1564" s="12"/>
+      <c r="L1564" s="12"/>
+      <c r="M1564" s="12"/>
+      <c r="N1564" s="12"/>
+      <c r="O1564" s="12"/>
+      <c r="P1564" s="12"/>
+      <c r="Q1564" s="12"/>
+      <c r="R1564" s="12"/>
+      <c r="S1564" s="14" t="s">
+        <v>656</v>
+      </c>
+      <c r="T1564" s="12"/>
+      <c r="U1564" s="12"/>
+      <c r="V1564" s="12"/>
+      <c r="W1564" s="12"/>
+      <c r="X1564" s="12"/>
+      <c r="Y1564" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1564" s="12"/>
+      <c r="AA1564" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1564" s="12"/>
+      <c r="AC1564" s="12"/>
+      <c r="AD1564" s="26"/>
+    </row>
+    <row r="1565" ht="15.75" customHeight="1">
+      <c r="B1565" s="23" t="s">
+        <v>657</v>
+      </c>
+      <c r="C1565" s="12"/>
+      <c r="D1565" s="12"/>
+      <c r="E1565" s="12"/>
+      <c r="F1565" s="12"/>
+      <c r="G1565" s="12"/>
+      <c r="H1565" s="12"/>
+      <c r="I1565" s="12"/>
+      <c r="J1565" s="14" t="s">
+        <v>658</v>
+      </c>
+      <c r="K1565" s="12"/>
+      <c r="L1565" s="12"/>
+      <c r="M1565" s="12"/>
+      <c r="N1565" s="12"/>
+      <c r="O1565" s="12"/>
+      <c r="P1565" s="12"/>
+      <c r="Q1565" s="12"/>
+      <c r="R1565" s="12"/>
+      <c r="S1565" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="T1565" s="12"/>
+      <c r="U1565" s="12"/>
+      <c r="V1565" s="12"/>
+      <c r="W1565" s="12"/>
+      <c r="X1565" s="12"/>
+      <c r="Y1565" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1565" s="12"/>
+      <c r="AA1565" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1565" s="12"/>
+      <c r="AC1565" s="12"/>
+      <c r="AD1565" s="26"/>
+    </row>
+    <row r="1566" ht="15.75" customHeight="1">
+      <c r="B1566" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="C1566" s="12"/>
+      <c r="D1566" s="12"/>
+      <c r="E1566" s="12"/>
+      <c r="F1566" s="12"/>
+      <c r="G1566" s="12"/>
+      <c r="H1566" s="12"/>
+      <c r="I1566" s="12"/>
+      <c r="J1566" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1566" s="12"/>
+      <c r="L1566" s="12"/>
+      <c r="M1566" s="12"/>
+      <c r="N1566" s="12"/>
+      <c r="O1566" s="12"/>
+      <c r="P1566" s="12"/>
+      <c r="Q1566" s="12"/>
+      <c r="R1566" s="12"/>
+      <c r="S1566" s="14" t="s">
+        <v>661</v>
+      </c>
+      <c r="T1566" s="12"/>
+      <c r="U1566" s="12"/>
+      <c r="V1566" s="12"/>
+      <c r="W1566" s="12"/>
+      <c r="X1566" s="12"/>
+      <c r="Y1566" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1566" s="12"/>
+      <c r="AA1566" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1566" s="12"/>
+      <c r="AC1566" s="12"/>
+      <c r="AD1566" s="26"/>
+    </row>
+    <row r="1567" ht="15.75" customHeight="1">
+      <c r="B1567" s="10"/>
+      <c r="J1567" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="S1567" s="15"/>
+      <c r="Y1567" s="15"/>
+      <c r="AA1567" s="15"/>
+      <c r="AD1567" s="22"/>
+    </row>
+    <row r="1568" ht="15.75" customHeight="1">
+      <c r="B1568" s="10"/>
+      <c r="J1568" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="K1568" s="12"/>
+      <c r="L1568" s="12"/>
+      <c r="M1568" s="12"/>
+      <c r="N1568" s="12"/>
+      <c r="O1568" s="12"/>
+      <c r="P1568" s="12"/>
+      <c r="Q1568" s="12"/>
+      <c r="R1568" s="12"/>
+      <c r="S1568" s="14" t="s">
+        <v>664</v>
+      </c>
+      <c r="T1568" s="12"/>
+      <c r="U1568" s="12"/>
+      <c r="V1568" s="12"/>
+      <c r="W1568" s="12"/>
+      <c r="X1568" s="12"/>
+      <c r="Y1568" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1568" s="12"/>
+      <c r="AA1568" s="15"/>
+      <c r="AD1568" s="22"/>
+    </row>
+    <row r="1569" ht="15.75" customHeight="1">
+      <c r="B1569" s="10"/>
+      <c r="J1569" s="14" t="s">
+        <v>665</v>
+      </c>
+      <c r="K1569" s="12"/>
+      <c r="L1569" s="12"/>
+      <c r="M1569" s="12"/>
+      <c r="N1569" s="12"/>
+      <c r="O1569" s="12"/>
+      <c r="P1569" s="12"/>
+      <c r="Q1569" s="12"/>
+      <c r="R1569" s="12"/>
+      <c r="S1569" s="14" t="s">
+        <v>666</v>
+      </c>
+      <c r="T1569" s="12"/>
+      <c r="U1569" s="12"/>
+      <c r="V1569" s="12"/>
+      <c r="W1569" s="12"/>
+      <c r="X1569" s="12"/>
+      <c r="Y1569" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1569" s="12"/>
+      <c r="AA1569" s="15"/>
+      <c r="AD1569" s="22"/>
+    </row>
+    <row r="1570" ht="15.75" customHeight="1">
+      <c r="B1570" s="23" t="s">
+        <v>667</v>
+      </c>
+      <c r="C1570" s="12"/>
+      <c r="D1570" s="12"/>
+      <c r="E1570" s="12"/>
+      <c r="F1570" s="12"/>
+      <c r="G1570" s="12"/>
+      <c r="H1570" s="12"/>
+      <c r="I1570" s="12"/>
+      <c r="J1570" s="14" t="s">
         <v>668</v>
       </c>
-      <c r="Y1560" s="15"/>
-      <c r="AA1560" s="15"/>
-      <c r="AD1560" s="22"/>
-    </row>
-    <row r="1561" ht="15.75" customHeight="1">
-      <c r="B1561" s="8"/>
-      <c r="C1561" s="8"/>
-      <c r="D1561" s="8"/>
-      <c r="E1561" s="8"/>
-      <c r="F1561" s="8"/>
-      <c r="G1561" s="8"/>
-      <c r="H1561" s="8"/>
-      <c r="I1561" s="8"/>
-      <c r="J1561" s="8"/>
-      <c r="K1561" s="8"/>
-      <c r="L1561" s="8"/>
-      <c r="M1561" s="8"/>
-      <c r="N1561" s="8"/>
-      <c r="O1561" s="8"/>
-      <c r="P1561" s="8"/>
-      <c r="Q1561" s="8"/>
-      <c r="R1561" s="8"/>
-      <c r="S1561" s="8"/>
-      <c r="T1561" s="8"/>
-      <c r="U1561" s="8"/>
-      <c r="V1561" s="8"/>
-      <c r="W1561" s="8"/>
-      <c r="X1561" s="8"/>
-      <c r="Y1561" s="8"/>
-      <c r="Z1561" s="8"/>
-      <c r="AA1561" s="8"/>
-      <c r="AB1561" s="8"/>
-      <c r="AC1561" s="8"/>
-      <c r="AD1561" s="8"/>
-    </row>
-    <row r="1562" ht="15.75" customHeight="1"/>
-    <row r="1563" ht="15.75" customHeight="1"/>
-    <row r="1564" ht="15.75" customHeight="1"/>
-    <row r="1565" ht="15.75" customHeight="1"/>
-    <row r="1566" ht="15.75" customHeight="1"/>
-    <row r="1567" ht="15.75" customHeight="1"/>
-    <row r="1568" ht="15.75" customHeight="1"/>
-    <row r="1569" ht="15.75" customHeight="1"/>
-    <row r="1570" ht="15.75" customHeight="1"/>
-    <row r="1571" ht="15.75" customHeight="1"/>
-    <row r="1572" ht="15.75" customHeight="1"/>
-    <row r="1573" ht="15.75" customHeight="1"/>
-    <row r="1574" ht="15.75" customHeight="1"/>
-    <row r="1575" ht="15.75" customHeight="1"/>
-    <row r="1576" ht="15.75" customHeight="1"/>
-    <row r="1577" ht="15.75" customHeight="1"/>
-    <row r="1578" ht="15.75" customHeight="1"/>
-    <row r="1579" ht="15.75" customHeight="1"/>
-    <row r="1580" ht="15.75" customHeight="1"/>
+      <c r="K1570" s="12"/>
+      <c r="L1570" s="12"/>
+      <c r="M1570" s="12"/>
+      <c r="N1570" s="12"/>
+      <c r="O1570" s="12"/>
+      <c r="P1570" s="12"/>
+      <c r="Q1570" s="12"/>
+      <c r="R1570" s="12"/>
+      <c r="S1570" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="T1570" s="12"/>
+      <c r="U1570" s="12"/>
+      <c r="V1570" s="12"/>
+      <c r="W1570" s="12"/>
+      <c r="X1570" s="12"/>
+      <c r="Y1570" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1570" s="12"/>
+      <c r="AA1570" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1570" s="12"/>
+      <c r="AC1570" s="12"/>
+      <c r="AD1570" s="26"/>
+    </row>
+    <row r="1571" ht="15.75" customHeight="1">
+      <c r="B1571" s="23" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1571" s="12"/>
+      <c r="D1571" s="12"/>
+      <c r="E1571" s="12"/>
+      <c r="F1571" s="12"/>
+      <c r="G1571" s="12"/>
+      <c r="H1571" s="12"/>
+      <c r="I1571" s="12"/>
+      <c r="J1571" s="14" t="s">
+        <v>671</v>
+      </c>
+      <c r="K1571" s="12"/>
+      <c r="L1571" s="12"/>
+      <c r="M1571" s="12"/>
+      <c r="N1571" s="12"/>
+      <c r="O1571" s="12"/>
+      <c r="P1571" s="12"/>
+      <c r="Q1571" s="12"/>
+      <c r="R1571" s="12"/>
+      <c r="S1571" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="T1571" s="12"/>
+      <c r="U1571" s="12"/>
+      <c r="V1571" s="12"/>
+      <c r="W1571" s="12"/>
+      <c r="X1571" s="12"/>
+      <c r="Y1571" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1571" s="12"/>
+      <c r="AA1571" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1571" s="12"/>
+      <c r="AC1571" s="12"/>
+      <c r="AD1571" s="26"/>
+    </row>
+    <row r="1572" ht="15.75" customHeight="1">
+      <c r="B1572" s="23" t="s">
+        <v>673</v>
+      </c>
+      <c r="C1572" s="12"/>
+      <c r="D1572" s="12"/>
+      <c r="E1572" s="12"/>
+      <c r="F1572" s="12"/>
+      <c r="G1572" s="12"/>
+      <c r="H1572" s="12"/>
+      <c r="I1572" s="12"/>
+      <c r="J1572" s="14" t="s">
+        <v>674</v>
+      </c>
+      <c r="K1572" s="12"/>
+      <c r="L1572" s="12"/>
+      <c r="M1572" s="12"/>
+      <c r="N1572" s="12"/>
+      <c r="O1572" s="12"/>
+      <c r="P1572" s="12"/>
+      <c r="Q1572" s="12"/>
+      <c r="R1572" s="12"/>
+      <c r="S1572" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="T1572" s="12"/>
+      <c r="U1572" s="12"/>
+      <c r="V1572" s="12"/>
+      <c r="W1572" s="12"/>
+      <c r="X1572" s="12"/>
+      <c r="Y1572" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1572" s="12"/>
+      <c r="AA1572" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1572" s="12"/>
+      <c r="AC1572" s="12"/>
+      <c r="AD1572" s="26"/>
+    </row>
+    <row r="1573" ht="15.75" customHeight="1">
+      <c r="B1573" s="23" t="s">
+        <v>676</v>
+      </c>
+      <c r="C1573" s="12"/>
+      <c r="D1573" s="12"/>
+      <c r="E1573" s="12"/>
+      <c r="F1573" s="12"/>
+      <c r="G1573" s="12"/>
+      <c r="H1573" s="12"/>
+      <c r="I1573" s="12"/>
+      <c r="J1573" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="K1573" s="12"/>
+      <c r="L1573" s="12"/>
+      <c r="M1573" s="12"/>
+      <c r="N1573" s="12"/>
+      <c r="O1573" s="12"/>
+      <c r="P1573" s="12"/>
+      <c r="Q1573" s="12"/>
+      <c r="R1573" s="12"/>
+      <c r="S1573" s="14" t="s">
+        <v>666</v>
+      </c>
+      <c r="T1573" s="12"/>
+      <c r="U1573" s="12"/>
+      <c r="V1573" s="12"/>
+      <c r="W1573" s="12"/>
+      <c r="X1573" s="12"/>
+      <c r="Y1573" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1573" s="12"/>
+      <c r="AA1573" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1573" s="12"/>
+      <c r="AC1573" s="12"/>
+      <c r="AD1573" s="26"/>
+    </row>
+    <row r="1574" ht="15.75" customHeight="1">
+      <c r="B1574" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="C1574" s="12"/>
+      <c r="D1574" s="12"/>
+      <c r="E1574" s="12"/>
+      <c r="F1574" s="12"/>
+      <c r="G1574" s="12"/>
+      <c r="H1574" s="12"/>
+      <c r="I1574" s="12"/>
+      <c r="J1574" s="14" t="s">
+        <v>679</v>
+      </c>
+      <c r="K1574" s="12"/>
+      <c r="L1574" s="12"/>
+      <c r="M1574" s="12"/>
+      <c r="N1574" s="12"/>
+      <c r="O1574" s="12"/>
+      <c r="P1574" s="12"/>
+      <c r="Q1574" s="12"/>
+      <c r="R1574" s="12"/>
+      <c r="S1574" s="14" t="s">
+        <v>664</v>
+      </c>
+      <c r="T1574" s="12"/>
+      <c r="U1574" s="12"/>
+      <c r="V1574" s="12"/>
+      <c r="W1574" s="12"/>
+      <c r="X1574" s="12"/>
+      <c r="Y1574" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1574" s="12"/>
+      <c r="AA1574" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1574" s="12"/>
+      <c r="AC1574" s="12"/>
+      <c r="AD1574" s="26"/>
+    </row>
+    <row r="1575" ht="15.75" customHeight="1">
+      <c r="B1575" s="10"/>
+      <c r="J1575" s="14" t="s">
+        <v>680</v>
+      </c>
+      <c r="K1575" s="12"/>
+      <c r="L1575" s="12"/>
+      <c r="M1575" s="12"/>
+      <c r="N1575" s="12"/>
+      <c r="O1575" s="12"/>
+      <c r="P1575" s="12"/>
+      <c r="Q1575" s="12"/>
+      <c r="R1575" s="12"/>
+      <c r="S1575" s="14" t="s">
+        <v>681</v>
+      </c>
+      <c r="T1575" s="12"/>
+      <c r="U1575" s="12"/>
+      <c r="V1575" s="12"/>
+      <c r="W1575" s="12"/>
+      <c r="X1575" s="12"/>
+      <c r="Y1575" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1575" s="12"/>
+      <c r="AA1575" s="15"/>
+      <c r="AD1575" s="22"/>
+    </row>
+    <row r="1576" ht="15.75" customHeight="1">
+      <c r="B1576" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="C1576" s="12"/>
+      <c r="D1576" s="12"/>
+      <c r="E1576" s="12"/>
+      <c r="F1576" s="12"/>
+      <c r="G1576" s="12"/>
+      <c r="H1576" s="12"/>
+      <c r="I1576" s="12"/>
+      <c r="J1576" s="14" t="s">
+        <v>683</v>
+      </c>
+      <c r="K1576" s="12"/>
+      <c r="L1576" s="12"/>
+      <c r="M1576" s="12"/>
+      <c r="N1576" s="12"/>
+      <c r="O1576" s="12"/>
+      <c r="P1576" s="12"/>
+      <c r="Q1576" s="12"/>
+      <c r="R1576" s="12"/>
+      <c r="S1576" s="14" t="s">
+        <v>684</v>
+      </c>
+      <c r="T1576" s="12"/>
+      <c r="U1576" s="12"/>
+      <c r="V1576" s="12"/>
+      <c r="W1576" s="12"/>
+      <c r="X1576" s="12"/>
+      <c r="Y1576" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1576" s="12"/>
+      <c r="AA1576" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1576" s="12"/>
+      <c r="AC1576" s="12"/>
+      <c r="AD1576" s="26"/>
+    </row>
+    <row r="1577" ht="15.75" customHeight="1">
+      <c r="B1577" s="23" t="s">
+        <v>685</v>
+      </c>
+      <c r="C1577" s="12"/>
+      <c r="D1577" s="12"/>
+      <c r="E1577" s="12"/>
+      <c r="F1577" s="12"/>
+      <c r="G1577" s="12"/>
+      <c r="H1577" s="12"/>
+      <c r="I1577" s="12"/>
+      <c r="J1577" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="K1577" s="12"/>
+      <c r="L1577" s="12"/>
+      <c r="M1577" s="12"/>
+      <c r="N1577" s="12"/>
+      <c r="O1577" s="12"/>
+      <c r="P1577" s="12"/>
+      <c r="Q1577" s="12"/>
+      <c r="R1577" s="12"/>
+      <c r="S1577" s="14" t="s">
+        <v>687</v>
+      </c>
+      <c r="T1577" s="12"/>
+      <c r="U1577" s="12"/>
+      <c r="V1577" s="12"/>
+      <c r="W1577" s="12"/>
+      <c r="X1577" s="12"/>
+      <c r="Y1577" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1577" s="12"/>
+      <c r="AA1577" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="AB1577" s="12"/>
+      <c r="AC1577" s="12"/>
+      <c r="AD1577" s="26"/>
+    </row>
+    <row r="1578" ht="15.75" customHeight="1">
+      <c r="B1578" s="31" t="s">
+        <v>689</v>
+      </c>
+      <c r="J1578" s="15"/>
+      <c r="S1578" s="30" t="s">
+        <v>690</v>
+      </c>
+      <c r="Y1578" s="15"/>
+      <c r="AA1578" s="15"/>
+      <c r="AD1578" s="22"/>
+    </row>
+    <row r="1579" ht="15.75" customHeight="1">
+      <c r="B1579" s="8"/>
+      <c r="C1579" s="8"/>
+      <c r="D1579" s="8"/>
+      <c r="E1579" s="8"/>
+      <c r="F1579" s="8"/>
+      <c r="G1579" s="8"/>
+      <c r="H1579" s="8"/>
+      <c r="I1579" s="8"/>
+      <c r="J1579" s="8"/>
+      <c r="K1579" s="8"/>
+      <c r="L1579" s="8"/>
+      <c r="M1579" s="8"/>
+      <c r="N1579" s="8"/>
+      <c r="O1579" s="8"/>
+      <c r="P1579" s="8"/>
+      <c r="Q1579" s="8"/>
+      <c r="R1579" s="8"/>
+      <c r="S1579" s="8"/>
+      <c r="T1579" s="8"/>
+      <c r="U1579" s="8"/>
+      <c r="V1579" s="8"/>
+      <c r="W1579" s="8"/>
+      <c r="X1579" s="8"/>
+      <c r="Y1579" s="8"/>
+      <c r="Z1579" s="8"/>
+      <c r="AA1579" s="8"/>
+      <c r="AB1579" s="8"/>
+      <c r="AC1579" s="8"/>
+      <c r="AD1579" s="8"/>
+    </row>
+    <row r="1580" ht="15.75" customHeight="1">
+      <c r="C1580" s="1" t="s">
+        <v>691</v>
+      </c>
+    </row>
     <row r="1581" ht="15.75" customHeight="1"/>
-    <row r="1582" ht="15.75" customHeight="1"/>
+    <row r="1582" ht="15.75" customHeight="1">
+      <c r="D1582" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
     <row r="1583" ht="15.75" customHeight="1"/>
-    <row r="1584" ht="15.75" customHeight="1"/>
+    <row r="1584" ht="15.75" customHeight="1">
+      <c r="E1584" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="T1584" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
     <row r="1585" ht="15.75" customHeight="1"/>
-    <row r="1586" ht="15.75" customHeight="1"/>
-    <row r="1587" ht="15.75" customHeight="1"/>
+    <row r="1586" ht="15.75" customHeight="1">
+      <c r="E1586" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="1587" ht="15.75" customHeight="1">
+      <c r="E1587" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
     <row r="1588" ht="15.75" customHeight="1"/>
     <row r="1589" ht="15.75" customHeight="1"/>
     <row r="1590" ht="15.75" customHeight="1"/>
@@ -16320,8 +17394,751 @@
     <row r="1596" ht="15.75" customHeight="1"/>
     <row r="1597" ht="15.75" customHeight="1"/>
     <row r="1598" ht="15.75" customHeight="1"/>
+    <row r="1599" ht="15.75" customHeight="1">
+      <c r="E1599" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="1600" ht="15.75" customHeight="1">
+      <c r="F1600" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="1601" ht="15.75" customHeight="1"/>
+    <row r="1602" ht="15.75" customHeight="1">
+      <c r="F1602" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="J1602" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1602" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="1603" ht="15.75" customHeight="1">
+      <c r="H1603" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="J1603" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1603" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="1604" ht="15.75" customHeight="1">
+      <c r="H1604" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="J1604" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1604" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="1605" ht="15.75" customHeight="1">
+      <c r="H1605" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="J1605" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1605" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="1606" ht="15.75" customHeight="1"/>
+    <row r="1607" ht="15.75" customHeight="1">
+      <c r="E1607" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="1608" ht="15.75" customHeight="1">
+      <c r="E1608" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="1609" ht="15.75" customHeight="1">
+      <c r="E1609" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="1610" ht="15.75" customHeight="1">
+      <c r="E1610" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="F1610" s="8"/>
+      <c r="G1610" s="8"/>
+      <c r="H1610" s="8"/>
+      <c r="I1610" s="8"/>
+      <c r="J1610" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="K1610" s="8"/>
+      <c r="L1610" s="8"/>
+      <c r="M1610" s="8"/>
+      <c r="N1610" s="8"/>
+      <c r="O1610" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="P1610" s="8"/>
+      <c r="Q1610" s="8"/>
+      <c r="R1610" s="8"/>
+      <c r="S1610" s="8"/>
+      <c r="T1610" s="8"/>
+      <c r="U1610" s="8"/>
+      <c r="V1610" s="8"/>
+      <c r="W1610" s="8"/>
+      <c r="X1610" s="8"/>
+      <c r="Y1610" s="8"/>
+      <c r="Z1610" s="8"/>
+      <c r="AA1610" s="10"/>
+    </row>
+    <row r="1611" ht="15.75" customHeight="1">
+      <c r="E1611" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="F1611" s="12"/>
+      <c r="G1611" s="12"/>
+      <c r="H1611" s="12"/>
+      <c r="I1611" s="12"/>
+      <c r="J1611" s="14" t="s">
+        <v>713</v>
+      </c>
+      <c r="K1611" s="12"/>
+      <c r="L1611" s="12"/>
+      <c r="M1611" s="12"/>
+      <c r="N1611" s="12"/>
+      <c r="O1611" s="32">
+        <v>1000</v>
+      </c>
+      <c r="P1611" s="12"/>
+      <c r="Q1611" s="12"/>
+      <c r="R1611" s="12"/>
+      <c r="S1611" s="12"/>
+      <c r="T1611" s="12"/>
+      <c r="U1611" s="12"/>
+      <c r="V1611" s="12"/>
+      <c r="W1611" s="12"/>
+      <c r="X1611" s="12"/>
+      <c r="Y1611" s="12"/>
+      <c r="Z1611" s="12"/>
+      <c r="AA1611" s="10"/>
+    </row>
+    <row r="1612" ht="15.75" customHeight="1">
+      <c r="E1612" s="10"/>
+      <c r="J1612" s="14" t="s">
+        <v>714</v>
+      </c>
+      <c r="K1612" s="12"/>
+      <c r="L1612" s="12"/>
+      <c r="M1612" s="12"/>
+      <c r="N1612" s="12"/>
+      <c r="O1612" s="32">
+        <v>750</v>
+      </c>
+      <c r="P1612" s="12"/>
+      <c r="Q1612" s="12"/>
+      <c r="R1612" s="12"/>
+      <c r="S1612" s="12"/>
+      <c r="T1612" s="12"/>
+      <c r="U1612" s="12"/>
+      <c r="V1612" s="12"/>
+      <c r="W1612" s="12"/>
+      <c r="X1612" s="12"/>
+      <c r="Y1612" s="12"/>
+      <c r="Z1612" s="12"/>
+      <c r="AA1612" s="10"/>
+    </row>
+    <row r="1613" ht="15.75" customHeight="1">
+      <c r="E1613" s="8"/>
+      <c r="F1613" s="8"/>
+      <c r="G1613" s="8"/>
+      <c r="H1613" s="8"/>
+      <c r="I1613" s="8"/>
+      <c r="J1613" s="8"/>
+      <c r="K1613" s="8"/>
+      <c r="L1613" s="8"/>
+      <c r="M1613" s="8"/>
+      <c r="N1613" s="8"/>
+      <c r="O1613" s="8"/>
+      <c r="P1613" s="8"/>
+      <c r="Q1613" s="8"/>
+      <c r="R1613" s="8"/>
+      <c r="S1613" s="8"/>
+      <c r="T1613" s="8"/>
+      <c r="U1613" s="8"/>
+      <c r="V1613" s="8"/>
+      <c r="W1613" s="8"/>
+      <c r="X1613" s="8"/>
+      <c r="Y1613" s="8"/>
+      <c r="Z1613" s="8"/>
+    </row>
+    <row r="1614" ht="15.75" customHeight="1">
+      <c r="E1614" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="T1614" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="1615" ht="15.75" customHeight="1"/>
+    <row r="1616" ht="15.75" customHeight="1">
+      <c r="E1616" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="1617" ht="15.75" customHeight="1">
+      <c r="E1617" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="1618" ht="15.75" customHeight="1"/>
+    <row r="1619" ht="15.75" customHeight="1">
+      <c r="E1619" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="1620" ht="15.75" customHeight="1">
+      <c r="F1620" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1621" ht="15.75" customHeight="1">
+      <c r="F1621" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="1622" ht="15.75" customHeight="1"/>
+    <row r="1623" ht="15.75" customHeight="1">
+      <c r="F1623" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="J1623" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1623" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="1624" ht="15.75" customHeight="1">
+      <c r="H1624" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="J1624" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1624" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="1625" ht="15.75" customHeight="1">
+      <c r="H1625" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="J1625" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1625" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="1626" ht="15.75" customHeight="1">
+      <c r="H1626" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="J1626" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1626" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="1627" ht="15.75" customHeight="1">
+      <c r="H1627" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="J1627" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1627" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="1628" ht="15.75" customHeight="1">
+      <c r="H1628" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="J1628" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1628" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="1629" ht="15.75" customHeight="1">
+      <c r="H1629" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="J1629" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1629" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="1630" ht="15.75" customHeight="1">
+      <c r="H1630" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="J1630" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1630" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="1631" ht="15.75" customHeight="1">
+      <c r="H1631" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="J1631" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1631" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="1632" ht="15.75" customHeight="1">
+      <c r="H1632" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="J1632" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1632" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="1633" ht="15.75" customHeight="1"/>
+    <row r="1634" ht="15.75" customHeight="1">
+      <c r="E1634" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="1635" ht="15.75" customHeight="1">
+      <c r="E1635" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="1636" ht="15.75" customHeight="1">
+      <c r="E1636" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="1637" ht="15.75" customHeight="1">
+      <c r="E1637" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="F1637" s="8"/>
+      <c r="G1637" s="8"/>
+      <c r="H1637" s="8"/>
+      <c r="I1637" s="8"/>
+      <c r="J1637" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="K1637" s="8"/>
+      <c r="L1637" s="8"/>
+      <c r="M1637" s="8"/>
+      <c r="N1637" s="8"/>
+      <c r="O1637" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="P1637" s="8"/>
+      <c r="Q1637" s="8"/>
+      <c r="R1637" s="8"/>
+      <c r="S1637" s="8"/>
+      <c r="T1637" s="8"/>
+      <c r="U1637" s="8"/>
+      <c r="V1637" s="8"/>
+      <c r="W1637" s="8"/>
+      <c r="X1637" s="8"/>
+      <c r="Y1637" s="8"/>
+      <c r="Z1637" s="8"/>
+      <c r="AA1637" s="10"/>
+    </row>
+    <row r="1638" ht="15.75" customHeight="1">
+      <c r="E1638" s="23" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1638" s="12"/>
+      <c r="G1638" s="12"/>
+      <c r="H1638" s="12"/>
+      <c r="I1638" s="12"/>
+      <c r="J1638" s="14" t="s">
+        <v>738</v>
+      </c>
+      <c r="K1638" s="12"/>
+      <c r="L1638" s="12"/>
+      <c r="M1638" s="12"/>
+      <c r="N1638" s="12"/>
+      <c r="O1638" s="32">
+        <v>15000</v>
+      </c>
+      <c r="P1638" s="12"/>
+      <c r="Q1638" s="12"/>
+      <c r="R1638" s="12"/>
+      <c r="S1638" s="12"/>
+      <c r="T1638" s="12"/>
+      <c r="U1638" s="12"/>
+      <c r="V1638" s="12"/>
+      <c r="W1638" s="12"/>
+      <c r="X1638" s="12"/>
+      <c r="Y1638" s="12"/>
+      <c r="Z1638" s="12"/>
+      <c r="AA1638" s="10"/>
+    </row>
+    <row r="1639" ht="15.75" customHeight="1">
+      <c r="E1639" s="8"/>
+      <c r="F1639" s="8"/>
+      <c r="G1639" s="8"/>
+      <c r="H1639" s="8"/>
+      <c r="I1639" s="8"/>
+      <c r="J1639" s="8"/>
+      <c r="K1639" s="8"/>
+      <c r="L1639" s="8"/>
+      <c r="M1639" s="8"/>
+      <c r="N1639" s="8"/>
+      <c r="O1639" s="8"/>
+      <c r="P1639" s="8"/>
+      <c r="Q1639" s="8"/>
+      <c r="R1639" s="8"/>
+      <c r="S1639" s="8"/>
+      <c r="T1639" s="8"/>
+      <c r="U1639" s="8"/>
+      <c r="V1639" s="8"/>
+      <c r="W1639" s="8"/>
+      <c r="X1639" s="8"/>
+      <c r="Y1639" s="8"/>
+      <c r="Z1639" s="8"/>
+    </row>
+    <row r="1640" ht="15.75" customHeight="1">
+      <c r="D1640" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="S1640" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="1641" ht="15.75" customHeight="1"/>
+    <row r="1642" ht="15.75" customHeight="1">
+      <c r="E1642" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="1643" ht="15.75" customHeight="1">
+      <c r="E1643" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="1644" ht="15.75" customHeight="1">
+      <c r="E1644" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1645" ht="15.75" customHeight="1"/>
+    <row r="1646" ht="15.75" customHeight="1">
+      <c r="D1646" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="1647" ht="15.75" customHeight="1"/>
+    <row r="1648" ht="15.75" customHeight="1">
+      <c r="B1648" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="1649" ht="15.75" customHeight="1">
+      <c r="B1649" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C1649" s="8"/>
+      <c r="D1649" s="8"/>
+      <c r="E1649" s="8"/>
+      <c r="F1649" s="8"/>
+      <c r="G1649" s="8"/>
+      <c r="H1649" s="8"/>
+      <c r="I1649" s="8"/>
+      <c r="J1649" s="8"/>
+      <c r="K1649" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L1649" s="8"/>
+      <c r="M1649" s="8"/>
+      <c r="N1649" s="8"/>
+      <c r="O1649" s="8"/>
+      <c r="P1649" s="8"/>
+      <c r="Q1649" s="8"/>
+      <c r="R1649" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="S1649" s="8"/>
+      <c r="T1649" s="8"/>
+      <c r="U1649" s="8"/>
+      <c r="V1649" s="8"/>
+      <c r="W1649" s="8"/>
+      <c r="X1649" s="8"/>
+      <c r="Y1649" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="Z1649" s="8"/>
+      <c r="AA1649" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB1649" s="8"/>
+      <c r="AC1649" s="8"/>
+      <c r="AD1649" s="21"/>
+    </row>
+    <row r="1650" ht="15.75" customHeight="1">
+      <c r="B1650" s="11" t="s">
+        <v>744</v>
+      </c>
+      <c r="C1650" s="12"/>
+      <c r="D1650" s="12"/>
+      <c r="E1650" s="14" t="s">
+        <v>745</v>
+      </c>
+      <c r="F1650" s="12"/>
+      <c r="G1650" s="12"/>
+      <c r="H1650" s="12"/>
+      <c r="I1650" s="12"/>
+      <c r="J1650" s="12"/>
+      <c r="K1650" s="14" t="s">
+        <v>746</v>
+      </c>
+      <c r="L1650" s="12"/>
+      <c r="M1650" s="12"/>
+      <c r="N1650" s="12"/>
+      <c r="O1650" s="12"/>
+      <c r="P1650" s="12"/>
+      <c r="Q1650" s="12"/>
+      <c r="R1650" s="14" t="s">
+        <v>747</v>
+      </c>
+      <c r="S1650" s="12"/>
+      <c r="T1650" s="12"/>
+      <c r="U1650" s="12"/>
+      <c r="V1650" s="12"/>
+      <c r="W1650" s="12"/>
+      <c r="X1650" s="12"/>
+      <c r="Y1650" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1650" s="12"/>
+      <c r="AA1650" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1650" s="12"/>
+      <c r="AC1650" s="12"/>
+      <c r="AD1650" s="26"/>
+    </row>
+    <row r="1651" ht="15.75" customHeight="1">
+      <c r="B1651" s="33" t="s">
+        <v>748</v>
+      </c>
+      <c r="E1651" s="14" t="s">
+        <v>749</v>
+      </c>
+      <c r="F1651" s="12"/>
+      <c r="G1651" s="12"/>
+      <c r="H1651" s="12"/>
+      <c r="I1651" s="12"/>
+      <c r="J1651" s="12"/>
+      <c r="K1651" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="L1651" s="12"/>
+      <c r="M1651" s="12"/>
+      <c r="N1651" s="12"/>
+      <c r="O1651" s="12"/>
+      <c r="P1651" s="12"/>
+      <c r="Q1651" s="12"/>
+      <c r="R1651" s="14" t="s">
+        <v>751</v>
+      </c>
+      <c r="S1651" s="12"/>
+      <c r="T1651" s="12"/>
+      <c r="U1651" s="12"/>
+      <c r="V1651" s="12"/>
+      <c r="W1651" s="12"/>
+      <c r="X1651" s="12"/>
+      <c r="Y1651" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1651" s="12"/>
+      <c r="AA1651" s="15"/>
+      <c r="AD1651" s="22"/>
+    </row>
+    <row r="1652" ht="15.75" customHeight="1">
+      <c r="B1652" s="33" t="s">
+        <v>752</v>
+      </c>
+      <c r="E1652" s="14" t="s">
+        <v>753</v>
+      </c>
+      <c r="F1652" s="12"/>
+      <c r="G1652" s="12"/>
+      <c r="H1652" s="12"/>
+      <c r="I1652" s="12"/>
+      <c r="J1652" s="12"/>
+      <c r="K1652" s="14" t="s">
+        <v>754</v>
+      </c>
+      <c r="L1652" s="12"/>
+      <c r="M1652" s="12"/>
+      <c r="N1652" s="12"/>
+      <c r="O1652" s="12"/>
+      <c r="P1652" s="12"/>
+      <c r="Q1652" s="12"/>
+      <c r="R1652" s="14" t="s">
+        <v>755</v>
+      </c>
+      <c r="S1652" s="12"/>
+      <c r="T1652" s="12"/>
+      <c r="U1652" s="12"/>
+      <c r="V1652" s="12"/>
+      <c r="W1652" s="12"/>
+      <c r="X1652" s="12"/>
+      <c r="Y1652" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1652" s="12"/>
+      <c r="AA1652" s="15"/>
+      <c r="AD1652" s="22"/>
+    </row>
+    <row r="1653" ht="15.75" customHeight="1">
+      <c r="B1653" s="11" t="s">
+        <v>756</v>
+      </c>
+      <c r="C1653" s="12"/>
+      <c r="D1653" s="12"/>
+      <c r="E1653" s="12"/>
+      <c r="F1653" s="12"/>
+      <c r="G1653" s="12"/>
+      <c r="H1653" s="12"/>
+      <c r="I1653" s="12"/>
+      <c r="J1653" s="12"/>
+      <c r="K1653" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="L1653" s="12"/>
+      <c r="M1653" s="12"/>
+      <c r="N1653" s="12"/>
+      <c r="O1653" s="12"/>
+      <c r="P1653" s="12"/>
+      <c r="Q1653" s="12"/>
+      <c r="R1653" s="14" t="s">
+        <v>758</v>
+      </c>
+      <c r="S1653" s="12"/>
+      <c r="T1653" s="12"/>
+      <c r="U1653" s="12"/>
+      <c r="V1653" s="12"/>
+      <c r="W1653" s="12"/>
+      <c r="X1653" s="12"/>
+      <c r="Y1653" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z1653" s="12"/>
+      <c r="AA1653" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB1653" s="12"/>
+      <c r="AC1653" s="12"/>
+      <c r="AD1653" s="26"/>
+    </row>
+    <row r="1654" ht="15.75" customHeight="1">
+      <c r="B1654" s="10"/>
+      <c r="K1654" s="15"/>
+      <c r="R1654" s="30" t="s">
+        <v>759</v>
+      </c>
+      <c r="Y1654" s="15"/>
+      <c r="AA1654" s="15"/>
+      <c r="AD1654" s="22"/>
+    </row>
+    <row r="1655" ht="15.75" customHeight="1">
+      <c r="B1655" s="8"/>
+      <c r="C1655" s="8"/>
+      <c r="D1655" s="8"/>
+      <c r="E1655" s="8"/>
+      <c r="F1655" s="8"/>
+      <c r="G1655" s="8"/>
+      <c r="H1655" s="8"/>
+      <c r="I1655" s="8"/>
+      <c r="J1655" s="8"/>
+      <c r="K1655" s="8"/>
+      <c r="L1655" s="8"/>
+      <c r="M1655" s="8"/>
+      <c r="N1655" s="8"/>
+      <c r="O1655" s="8"/>
+      <c r="P1655" s="8"/>
+      <c r="Q1655" s="8"/>
+      <c r="R1655" s="8"/>
+      <c r="S1655" s="8"/>
+      <c r="T1655" s="8"/>
+      <c r="U1655" s="8"/>
+      <c r="V1655" s="8"/>
+      <c r="W1655" s="8"/>
+      <c r="X1655" s="8"/>
+      <c r="Y1655" s="8"/>
+      <c r="Z1655" s="8"/>
+      <c r="AA1655" s="8"/>
+      <c r="AB1655" s="8"/>
+      <c r="AC1655" s="8"/>
+      <c r="AD1655" s="8"/>
+    </row>
+    <row r="1656" ht="15.75" customHeight="1"/>
+    <row r="1657" ht="15.75" customHeight="1"/>
+    <row r="1658" ht="15.75" customHeight="1"/>
+    <row r="1659" ht="15.75" customHeight="1"/>
+    <row r="1660" ht="15.75" customHeight="1"/>
+    <row r="1661" ht="15.75" customHeight="1"/>
+    <row r="1662" ht="15.75" customHeight="1"/>
+    <row r="1663" ht="15.75" customHeight="1"/>
+    <row r="1664" ht="15.75" customHeight="1"/>
+    <row r="1665" ht="15.75" customHeight="1"/>
+    <row r="1666" ht="15.75" customHeight="1"/>
+    <row r="1667" ht="15.75" customHeight="1"/>
+    <row r="1668" ht="15.75" customHeight="1"/>
+    <row r="1669" ht="15.75" customHeight="1"/>
+    <row r="1670" ht="15.75" customHeight="1"/>
+    <row r="1671" ht="15.75" customHeight="1"/>
+    <row r="1672" ht="15.75" customHeight="1"/>
+    <row r="1673" ht="15.75" customHeight="1"/>
+    <row r="1674" ht="15.75" customHeight="1"/>
+    <row r="1675" ht="15.75" customHeight="1"/>
+    <row r="1676" ht="15.75" customHeight="1"/>
+    <row r="1677" ht="15.75" customHeight="1"/>
+    <row r="1678" ht="15.75" customHeight="1"/>
+    <row r="1679" ht="15.75" customHeight="1"/>
+    <row r="1680" ht="15.75" customHeight="1"/>
+    <row r="1681" ht="15.75" customHeight="1"/>
+    <row r="1682" ht="15.75" customHeight="1"/>
+    <row r="1683" ht="15.75" customHeight="1"/>
+    <row r="1684" ht="15.75" customHeight="1"/>
+    <row r="1685" ht="15.75" customHeight="1"/>
+    <row r="1686" ht="15.75" customHeight="1"/>
+    <row r="1687" ht="15.75" customHeight="1"/>
+    <row r="1688" ht="15.75" customHeight="1"/>
+    <row r="1689" ht="15.75" customHeight="1"/>
+    <row r="1690" ht="15.75" customHeight="1"/>
+    <row r="1691" ht="15.75" customHeight="1"/>
+    <row r="1692" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1437">
+  <mergeCells count="1534">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="C5:E5"/>
@@ -17560,210 +19377,307 @@
     <mergeCell ref="F1442:P1442"/>
     <mergeCell ref="E1444:AD1444"/>
     <mergeCell ref="E1445:AB1445"/>
-    <mergeCell ref="E1446:P1446"/>
-    <mergeCell ref="E1447:X1447"/>
-    <mergeCell ref="D1458:I1458"/>
-    <mergeCell ref="B1460:H1460"/>
-    <mergeCell ref="B1461:I1461"/>
-    <mergeCell ref="J1461:R1461"/>
-    <mergeCell ref="S1461:X1461"/>
-    <mergeCell ref="Y1461:Z1461"/>
-    <mergeCell ref="AA1461:AD1461"/>
-    <mergeCell ref="B1462:I1462"/>
-    <mergeCell ref="J1462:R1462"/>
-    <mergeCell ref="S1462:X1462"/>
-    <mergeCell ref="Y1462:Z1462"/>
-    <mergeCell ref="AA1462:AD1462"/>
-    <mergeCell ref="B1463:I1463"/>
-    <mergeCell ref="J1463:R1463"/>
-    <mergeCell ref="S1463:X1463"/>
-    <mergeCell ref="Y1463:Z1463"/>
-    <mergeCell ref="AA1463:AD1463"/>
-    <mergeCell ref="B1464:I1464"/>
-    <mergeCell ref="J1464:R1464"/>
-    <mergeCell ref="S1464:X1464"/>
-    <mergeCell ref="Y1464:Z1464"/>
-    <mergeCell ref="AA1464:AD1464"/>
-    <mergeCell ref="B1465:I1465"/>
-    <mergeCell ref="J1465:R1465"/>
-    <mergeCell ref="S1465:X1465"/>
-    <mergeCell ref="Y1465:Z1465"/>
-    <mergeCell ref="AA1465:AD1465"/>
-    <mergeCell ref="B1466:I1466"/>
-    <mergeCell ref="J1466:R1466"/>
-    <mergeCell ref="S1466:X1466"/>
-    <mergeCell ref="Y1466:Z1466"/>
-    <mergeCell ref="AA1466:AD1466"/>
-    <mergeCell ref="B1467:I1467"/>
-    <mergeCell ref="J1467:R1467"/>
-    <mergeCell ref="S1467:X1467"/>
-    <mergeCell ref="Y1467:Z1467"/>
-    <mergeCell ref="B1468:I1468"/>
-    <mergeCell ref="J1468:R1468"/>
-    <mergeCell ref="S1468:X1468"/>
-    <mergeCell ref="Y1468:Z1468"/>
-    <mergeCell ref="B1469:I1469"/>
-    <mergeCell ref="J1469:R1469"/>
-    <mergeCell ref="S1469:X1469"/>
-    <mergeCell ref="Y1469:Z1469"/>
-    <mergeCell ref="AA1469:AD1469"/>
-    <mergeCell ref="B1470:I1470"/>
-    <mergeCell ref="J1470:R1470"/>
-    <mergeCell ref="S1470:X1470"/>
-    <mergeCell ref="Y1470:Z1470"/>
-    <mergeCell ref="AA1470:AD1470"/>
-    <mergeCell ref="B1471:I1471"/>
-    <mergeCell ref="J1471:R1471"/>
-    <mergeCell ref="S1471:X1471"/>
-    <mergeCell ref="Y1471:Z1471"/>
-    <mergeCell ref="AA1471:AD1471"/>
-    <mergeCell ref="B1472:I1475"/>
-    <mergeCell ref="J1472:Q1472"/>
-    <mergeCell ref="S1472:X1473"/>
-    <mergeCell ref="Y1472:Z1473"/>
-    <mergeCell ref="AA1472:AD1475"/>
-    <mergeCell ref="J1473:N1473"/>
-    <mergeCell ref="J1474:R1474"/>
-    <mergeCell ref="S1474:X1474"/>
-    <mergeCell ref="Y1474:Z1474"/>
-    <mergeCell ref="J1475:R1475"/>
-    <mergeCell ref="S1475:X1475"/>
-    <mergeCell ref="Y1475:Z1475"/>
-    <mergeCell ref="B1476:I1476"/>
-    <mergeCell ref="J1476:R1476"/>
-    <mergeCell ref="S1476:X1476"/>
-    <mergeCell ref="Y1476:Z1476"/>
-    <mergeCell ref="AA1476:AD1476"/>
-    <mergeCell ref="B1477:I1477"/>
-    <mergeCell ref="J1477:R1477"/>
-    <mergeCell ref="S1477:X1477"/>
-    <mergeCell ref="Y1477:Z1477"/>
-    <mergeCell ref="AA1477:AD1477"/>
-    <mergeCell ref="B1478:I1478"/>
-    <mergeCell ref="J1478:R1478"/>
-    <mergeCell ref="S1478:X1478"/>
-    <mergeCell ref="Y1478:Z1478"/>
-    <mergeCell ref="AA1478:AD1478"/>
-    <mergeCell ref="B1479:I1479"/>
-    <mergeCell ref="J1479:R1479"/>
-    <mergeCell ref="S1479:X1479"/>
-    <mergeCell ref="Y1479:Z1479"/>
-    <mergeCell ref="AA1479:AD1479"/>
-    <mergeCell ref="B1480:I1481"/>
-    <mergeCell ref="J1480:R1480"/>
-    <mergeCell ref="S1480:X1480"/>
-    <mergeCell ref="Y1480:Z1480"/>
-    <mergeCell ref="AA1480:AD1481"/>
-    <mergeCell ref="J1481:R1481"/>
-    <mergeCell ref="S1481:X1481"/>
-    <mergeCell ref="Y1481:Z1481"/>
-    <mergeCell ref="B1482:I1482"/>
-    <mergeCell ref="J1482:R1482"/>
-    <mergeCell ref="S1482:X1482"/>
-    <mergeCell ref="Y1482:Z1482"/>
-    <mergeCell ref="AA1482:AD1482"/>
-    <mergeCell ref="C1484:I1484"/>
-    <mergeCell ref="D1486:O1486"/>
-    <mergeCell ref="E1488:S1488"/>
-    <mergeCell ref="T1488:AB1488"/>
-    <mergeCell ref="E1490:AC1490"/>
-    <mergeCell ref="E1491:F1491"/>
-    <mergeCell ref="E1505:AC1505"/>
-    <mergeCell ref="F1506:Z1506"/>
-    <mergeCell ref="F1508:I1508"/>
-    <mergeCell ref="K1508:O1508"/>
-    <mergeCell ref="H1509:I1509"/>
-    <mergeCell ref="K1509:R1509"/>
-    <mergeCell ref="H1510:I1510"/>
-    <mergeCell ref="K1510:AD1510"/>
-    <mergeCell ref="H1511:I1511"/>
-    <mergeCell ref="K1511:AC1511"/>
-    <mergeCell ref="E1513:AD1513"/>
-    <mergeCell ref="E1514:W1514"/>
-    <mergeCell ref="E1515:AD1515"/>
-    <mergeCell ref="E1516:I1516"/>
-    <mergeCell ref="J1516:N1516"/>
-    <mergeCell ref="O1516:Z1516"/>
-    <mergeCell ref="E1517:I1518"/>
-    <mergeCell ref="J1517:N1517"/>
-    <mergeCell ref="O1517:Z1517"/>
-    <mergeCell ref="J1518:N1518"/>
-    <mergeCell ref="O1518:Z1518"/>
-    <mergeCell ref="E1520:S1520"/>
-    <mergeCell ref="T1520:AB1520"/>
-    <mergeCell ref="E1522:AD1522"/>
-    <mergeCell ref="E1523:Q1523"/>
-    <mergeCell ref="E1525:AC1525"/>
-    <mergeCell ref="F1526:Z1526"/>
-    <mergeCell ref="F1527:P1527"/>
-    <mergeCell ref="F1529:I1529"/>
-    <mergeCell ref="K1529:O1529"/>
-    <mergeCell ref="H1530:I1530"/>
-    <mergeCell ref="K1530:U1530"/>
-    <mergeCell ref="H1531:I1531"/>
-    <mergeCell ref="K1531:AC1531"/>
-    <mergeCell ref="H1532:I1532"/>
-    <mergeCell ref="K1532:AD1532"/>
-    <mergeCell ref="H1533:I1533"/>
-    <mergeCell ref="K1533:AC1533"/>
-    <mergeCell ref="H1534:I1534"/>
-    <mergeCell ref="K1534:Z1534"/>
-    <mergeCell ref="H1535:I1535"/>
-    <mergeCell ref="K1535:U1535"/>
-    <mergeCell ref="H1536:I1536"/>
-    <mergeCell ref="K1536:R1536"/>
-    <mergeCell ref="H1537:I1537"/>
-    <mergeCell ref="K1537:Q1537"/>
-    <mergeCell ref="H1538:I1538"/>
-    <mergeCell ref="K1538:AB1538"/>
-    <mergeCell ref="E1540:AD1540"/>
-    <mergeCell ref="E1541:W1541"/>
-    <mergeCell ref="E1542:AD1542"/>
-    <mergeCell ref="E1543:I1543"/>
-    <mergeCell ref="J1543:N1543"/>
-    <mergeCell ref="O1543:Z1543"/>
-    <mergeCell ref="E1544:I1544"/>
-    <mergeCell ref="J1544:N1544"/>
-    <mergeCell ref="O1544:Z1544"/>
-    <mergeCell ref="D1546:M1546"/>
-    <mergeCell ref="S1546:AA1546"/>
-    <mergeCell ref="E1548:AB1548"/>
-    <mergeCell ref="E1549:AD1549"/>
-    <mergeCell ref="E1550:F1550"/>
+    <mergeCell ref="E1446:AD1446"/>
+    <mergeCell ref="E1447:H1447"/>
+    <mergeCell ref="E1448:X1448"/>
+    <mergeCell ref="E1450:P1450"/>
+    <mergeCell ref="E1452:AD1452"/>
+    <mergeCell ref="E1453:AD1453"/>
+    <mergeCell ref="E1454:AC1454"/>
+    <mergeCell ref="E1458:M1458"/>
+    <mergeCell ref="E1459:AD1459"/>
+    <mergeCell ref="E1460:G1460"/>
+    <mergeCell ref="F1462:W1462"/>
+    <mergeCell ref="F1463:P1463"/>
+    <mergeCell ref="E1465:I1465"/>
+    <mergeCell ref="K1465:W1465"/>
+    <mergeCell ref="K1466:R1466"/>
+    <mergeCell ref="H1467:I1467"/>
+    <mergeCell ref="K1467:Q1467"/>
+    <mergeCell ref="H1468:I1468"/>
+    <mergeCell ref="K1468:Q1468"/>
+    <mergeCell ref="K1469:Q1469"/>
+    <mergeCell ref="K1470:O1470"/>
+    <mergeCell ref="H1471:I1471"/>
+    <mergeCell ref="K1471:V1471"/>
+    <mergeCell ref="F1473:S1473"/>
+    <mergeCell ref="F1474:Z1474"/>
+    <mergeCell ref="G1475:O1475"/>
+    <mergeCell ref="E1477:M1477"/>
+    <mergeCell ref="E1478:Y1478"/>
+    <mergeCell ref="F1480:U1480"/>
+    <mergeCell ref="F1481:P1481"/>
+    <mergeCell ref="F1483:I1483"/>
+    <mergeCell ref="K1483:U1483"/>
+    <mergeCell ref="H1484:I1484"/>
+    <mergeCell ref="K1484:Q1484"/>
+    <mergeCell ref="H1485:I1485"/>
+    <mergeCell ref="K1485:V1485"/>
+    <mergeCell ref="E1487:AD1487"/>
+    <mergeCell ref="E1488:AD1488"/>
+    <mergeCell ref="E1489:U1489"/>
+    <mergeCell ref="F1491:Z1491"/>
+    <mergeCell ref="P1492:T1492"/>
+    <mergeCell ref="Z1492:AA1492"/>
+    <mergeCell ref="AC1492:AD1492"/>
+    <mergeCell ref="F1493:P1493"/>
+    <mergeCell ref="L1494:M1494"/>
+    <mergeCell ref="O1494:P1494"/>
+    <mergeCell ref="R1494:S1494"/>
+    <mergeCell ref="Z1494:AA1494"/>
+    <mergeCell ref="E1505:J1505"/>
+    <mergeCell ref="E1506:AD1506"/>
+    <mergeCell ref="E1507:AD1507"/>
+    <mergeCell ref="E1508:R1508"/>
+    <mergeCell ref="F1510:X1510"/>
+    <mergeCell ref="F1511:P1511"/>
+    <mergeCell ref="F1512:Y1512"/>
+    <mergeCell ref="F1513:P1513"/>
+    <mergeCell ref="F1515:I1515"/>
+    <mergeCell ref="K1515:Q1515"/>
+    <mergeCell ref="K1516:S1516"/>
+    <mergeCell ref="H1517:I1517"/>
+    <mergeCell ref="K1517:Y1517"/>
+    <mergeCell ref="K1518:U1518"/>
+    <mergeCell ref="K1519:R1519"/>
+    <mergeCell ref="H1520:I1520"/>
+    <mergeCell ref="K1520:S1520"/>
+    <mergeCell ref="H1521:I1521"/>
+    <mergeCell ref="K1521:W1521"/>
+    <mergeCell ref="K1522:O1522"/>
+    <mergeCell ref="H1523:I1523"/>
+    <mergeCell ref="K1523:U1523"/>
+    <mergeCell ref="H1524:I1524"/>
+    <mergeCell ref="K1524:X1524"/>
+    <mergeCell ref="K1525:X1525"/>
+    <mergeCell ref="H1526:I1526"/>
+    <mergeCell ref="K1526:X1526"/>
+    <mergeCell ref="K1527:W1527"/>
+    <mergeCell ref="H1528:I1528"/>
+    <mergeCell ref="K1528:P1528"/>
+    <mergeCell ref="H1529:I1529"/>
+    <mergeCell ref="K1529:Q1529"/>
+    <mergeCell ref="E1531:AD1531"/>
+    <mergeCell ref="E1532:AD1532"/>
+    <mergeCell ref="E1533:AD1533"/>
+    <mergeCell ref="E1534:AD1534"/>
+    <mergeCell ref="E1535:AD1535"/>
+    <mergeCell ref="E1537:Q1537"/>
+    <mergeCell ref="F1538:AA1538"/>
+    <mergeCell ref="F1539:P1539"/>
+    <mergeCell ref="E1541:Q1541"/>
+    <mergeCell ref="F1542:AD1542"/>
+    <mergeCell ref="F1543:P1543"/>
+    <mergeCell ref="E1545:AC1545"/>
     <mergeCell ref="D1552:I1552"/>
     <mergeCell ref="B1554:H1554"/>
-    <mergeCell ref="B1555:J1555"/>
-    <mergeCell ref="K1555:Q1555"/>
-    <mergeCell ref="R1555:X1555"/>
+    <mergeCell ref="B1555:I1555"/>
+    <mergeCell ref="J1555:R1555"/>
+    <mergeCell ref="S1555:X1555"/>
     <mergeCell ref="Y1555:Z1555"/>
     <mergeCell ref="AA1555:AD1555"/>
-    <mergeCell ref="B1556:D1556"/>
-    <mergeCell ref="E1556:J1556"/>
-    <mergeCell ref="K1556:Q1556"/>
-    <mergeCell ref="R1556:X1556"/>
+    <mergeCell ref="B1556:I1556"/>
+    <mergeCell ref="J1556:R1556"/>
+    <mergeCell ref="S1556:X1556"/>
     <mergeCell ref="Y1556:Z1556"/>
-    <mergeCell ref="AA1556:AD1558"/>
-    <mergeCell ref="B1557:D1557"/>
-    <mergeCell ref="E1557:J1557"/>
-    <mergeCell ref="K1557:Q1557"/>
-    <mergeCell ref="R1557:X1557"/>
+    <mergeCell ref="AA1556:AD1556"/>
+    <mergeCell ref="B1557:I1557"/>
+    <mergeCell ref="J1557:R1557"/>
+    <mergeCell ref="S1557:X1557"/>
     <mergeCell ref="Y1557:Z1557"/>
-    <mergeCell ref="B1558:D1558"/>
-    <mergeCell ref="E1558:J1558"/>
-    <mergeCell ref="K1558:Q1558"/>
-    <mergeCell ref="R1558:X1558"/>
+    <mergeCell ref="AA1557:AD1557"/>
+    <mergeCell ref="B1558:I1558"/>
+    <mergeCell ref="J1558:R1558"/>
+    <mergeCell ref="S1558:X1558"/>
     <mergeCell ref="Y1558:Z1558"/>
-    <mergeCell ref="B1559:J1560"/>
-    <mergeCell ref="K1559:Q1560"/>
-    <mergeCell ref="R1559:V1559"/>
-    <mergeCell ref="Y1559:Z1560"/>
-    <mergeCell ref="AA1559:AD1560"/>
-    <mergeCell ref="R1560:V1560"/>
+    <mergeCell ref="AA1558:AD1558"/>
+    <mergeCell ref="B1559:I1559"/>
+    <mergeCell ref="J1559:R1559"/>
+    <mergeCell ref="S1559:X1559"/>
+    <mergeCell ref="Y1559:Z1559"/>
+    <mergeCell ref="AA1559:AD1559"/>
+    <mergeCell ref="B1560:I1560"/>
+    <mergeCell ref="J1560:R1560"/>
+    <mergeCell ref="S1560:X1560"/>
+    <mergeCell ref="Y1560:Z1560"/>
+    <mergeCell ref="AA1560:AD1560"/>
+    <mergeCell ref="B1561:I1561"/>
+    <mergeCell ref="J1561:R1561"/>
+    <mergeCell ref="S1561:X1561"/>
+    <mergeCell ref="Y1561:Z1561"/>
+    <mergeCell ref="B1562:I1562"/>
+    <mergeCell ref="J1562:R1562"/>
+    <mergeCell ref="S1562:X1562"/>
+    <mergeCell ref="Y1562:Z1562"/>
+    <mergeCell ref="B1563:I1563"/>
+    <mergeCell ref="J1563:R1563"/>
+    <mergeCell ref="S1563:X1563"/>
+    <mergeCell ref="Y1563:Z1563"/>
+    <mergeCell ref="AA1563:AD1563"/>
+    <mergeCell ref="B1564:I1564"/>
+    <mergeCell ref="J1564:R1564"/>
+    <mergeCell ref="S1564:X1564"/>
+    <mergeCell ref="Y1564:Z1564"/>
+    <mergeCell ref="AA1564:AD1564"/>
+    <mergeCell ref="B1565:I1565"/>
+    <mergeCell ref="J1565:R1565"/>
+    <mergeCell ref="S1565:X1565"/>
+    <mergeCell ref="Y1565:Z1565"/>
+    <mergeCell ref="AA1565:AD1565"/>
+    <mergeCell ref="B1566:I1569"/>
+    <mergeCell ref="J1566:Q1566"/>
+    <mergeCell ref="S1566:X1567"/>
+    <mergeCell ref="Y1566:Z1567"/>
+    <mergeCell ref="AA1566:AD1569"/>
+    <mergeCell ref="J1567:N1567"/>
+    <mergeCell ref="J1568:R1568"/>
+    <mergeCell ref="S1568:X1568"/>
+    <mergeCell ref="Y1568:Z1568"/>
+    <mergeCell ref="J1569:R1569"/>
+    <mergeCell ref="S1569:X1569"/>
+    <mergeCell ref="Y1569:Z1569"/>
+    <mergeCell ref="B1570:I1570"/>
+    <mergeCell ref="J1570:R1570"/>
+    <mergeCell ref="S1570:X1570"/>
+    <mergeCell ref="Y1570:Z1570"/>
+    <mergeCell ref="AA1570:AD1570"/>
+    <mergeCell ref="B1571:I1571"/>
+    <mergeCell ref="J1571:R1571"/>
+    <mergeCell ref="S1571:X1571"/>
+    <mergeCell ref="Y1571:Z1571"/>
+    <mergeCell ref="AA1571:AD1571"/>
+    <mergeCell ref="B1572:I1572"/>
+    <mergeCell ref="J1572:R1572"/>
+    <mergeCell ref="S1572:X1572"/>
+    <mergeCell ref="Y1572:Z1572"/>
+    <mergeCell ref="AA1572:AD1572"/>
+    <mergeCell ref="B1573:I1573"/>
+    <mergeCell ref="J1573:R1573"/>
+    <mergeCell ref="S1573:X1573"/>
+    <mergeCell ref="Y1573:Z1573"/>
+    <mergeCell ref="AA1573:AD1573"/>
+    <mergeCell ref="B1574:I1575"/>
+    <mergeCell ref="J1574:R1574"/>
+    <mergeCell ref="S1574:X1574"/>
+    <mergeCell ref="Y1574:Z1574"/>
+    <mergeCell ref="AA1574:AD1575"/>
+    <mergeCell ref="J1575:R1575"/>
+    <mergeCell ref="S1575:X1575"/>
+    <mergeCell ref="Y1575:Z1575"/>
+    <mergeCell ref="B1576:I1576"/>
+    <mergeCell ref="J1576:R1576"/>
+    <mergeCell ref="S1576:X1576"/>
+    <mergeCell ref="Y1576:Z1576"/>
+    <mergeCell ref="AA1576:AD1576"/>
+    <mergeCell ref="B1577:H1577"/>
+    <mergeCell ref="J1577:R1578"/>
+    <mergeCell ref="S1577:V1577"/>
+    <mergeCell ref="Y1577:Z1578"/>
+    <mergeCell ref="AA1577:AD1578"/>
+    <mergeCell ref="B1578:F1578"/>
+    <mergeCell ref="S1578:V1578"/>
+    <mergeCell ref="C1580:I1580"/>
+    <mergeCell ref="D1582:O1582"/>
+    <mergeCell ref="E1584:S1584"/>
+    <mergeCell ref="T1584:AB1584"/>
+    <mergeCell ref="E1586:AC1586"/>
+    <mergeCell ref="E1587:F1587"/>
+    <mergeCell ref="E1599:AC1599"/>
+    <mergeCell ref="F1600:Z1600"/>
+    <mergeCell ref="F1602:I1602"/>
+    <mergeCell ref="K1602:O1602"/>
+    <mergeCell ref="H1603:I1603"/>
+    <mergeCell ref="K1603:R1603"/>
+    <mergeCell ref="H1604:I1604"/>
+    <mergeCell ref="K1604:AD1604"/>
+    <mergeCell ref="H1605:I1605"/>
+    <mergeCell ref="K1605:AC1605"/>
+    <mergeCell ref="E1607:AD1607"/>
+    <mergeCell ref="E1608:W1608"/>
+    <mergeCell ref="E1609:AD1609"/>
+    <mergeCell ref="E1610:I1610"/>
+    <mergeCell ref="J1610:N1610"/>
+    <mergeCell ref="O1610:Z1610"/>
+    <mergeCell ref="E1611:I1612"/>
+    <mergeCell ref="J1611:N1611"/>
+    <mergeCell ref="O1611:Z1611"/>
+    <mergeCell ref="J1612:N1612"/>
+    <mergeCell ref="O1612:Z1612"/>
+    <mergeCell ref="E1614:S1614"/>
+    <mergeCell ref="T1614:AB1614"/>
+    <mergeCell ref="E1616:AD1616"/>
+    <mergeCell ref="E1617:Q1617"/>
+    <mergeCell ref="E1619:AC1619"/>
+    <mergeCell ref="F1620:Z1620"/>
+    <mergeCell ref="F1621:P1621"/>
+    <mergeCell ref="F1623:I1623"/>
+    <mergeCell ref="K1623:O1623"/>
+    <mergeCell ref="H1624:I1624"/>
+    <mergeCell ref="K1624:U1624"/>
+    <mergeCell ref="H1625:I1625"/>
+    <mergeCell ref="K1625:AC1625"/>
+    <mergeCell ref="H1626:I1626"/>
+    <mergeCell ref="K1626:AD1626"/>
+    <mergeCell ref="H1627:I1627"/>
+    <mergeCell ref="K1627:AC1627"/>
+    <mergeCell ref="H1628:I1628"/>
+    <mergeCell ref="K1628:Z1628"/>
+    <mergeCell ref="H1629:I1629"/>
+    <mergeCell ref="K1629:U1629"/>
+    <mergeCell ref="H1630:I1630"/>
+    <mergeCell ref="K1630:R1630"/>
+    <mergeCell ref="H1631:I1631"/>
+    <mergeCell ref="K1631:Q1631"/>
+    <mergeCell ref="H1632:I1632"/>
+    <mergeCell ref="K1632:AB1632"/>
+    <mergeCell ref="E1634:AD1634"/>
+    <mergeCell ref="E1635:W1635"/>
+    <mergeCell ref="E1636:AD1636"/>
+    <mergeCell ref="E1637:I1637"/>
+    <mergeCell ref="J1637:N1637"/>
+    <mergeCell ref="O1637:Z1637"/>
+    <mergeCell ref="E1638:I1638"/>
+    <mergeCell ref="J1638:N1638"/>
+    <mergeCell ref="O1638:Z1638"/>
+    <mergeCell ref="D1640:M1640"/>
+    <mergeCell ref="S1640:AA1640"/>
+    <mergeCell ref="E1642:AB1642"/>
+    <mergeCell ref="E1643:AD1643"/>
+    <mergeCell ref="E1644:F1644"/>
+    <mergeCell ref="D1646:I1646"/>
+    <mergeCell ref="B1648:H1648"/>
+    <mergeCell ref="B1649:J1649"/>
+    <mergeCell ref="K1649:Q1649"/>
+    <mergeCell ref="R1649:X1649"/>
+    <mergeCell ref="Y1649:Z1649"/>
+    <mergeCell ref="AA1649:AD1649"/>
+    <mergeCell ref="B1650:D1650"/>
+    <mergeCell ref="E1650:J1650"/>
+    <mergeCell ref="K1650:Q1650"/>
+    <mergeCell ref="R1650:X1650"/>
+    <mergeCell ref="Y1650:Z1650"/>
+    <mergeCell ref="AA1650:AD1652"/>
+    <mergeCell ref="B1651:D1651"/>
+    <mergeCell ref="E1651:J1651"/>
+    <mergeCell ref="K1651:Q1651"/>
+    <mergeCell ref="R1651:X1651"/>
+    <mergeCell ref="Y1651:Z1651"/>
+    <mergeCell ref="B1652:D1652"/>
+    <mergeCell ref="E1652:J1652"/>
+    <mergeCell ref="K1652:Q1652"/>
+    <mergeCell ref="R1652:X1652"/>
+    <mergeCell ref="Y1652:Z1652"/>
+    <mergeCell ref="B1653:J1654"/>
+    <mergeCell ref="K1653:Q1654"/>
+    <mergeCell ref="R1653:V1653"/>
+    <mergeCell ref="Y1653:Z1654"/>
+    <mergeCell ref="AA1653:AD1654"/>
+    <mergeCell ref="R1654:V1654"/>
   </mergeCells>
   <printOptions gridLines="0"/>
   <pageMargins left="0.706666667" right="0.758333333" top="0.758305556" bottom="0.706388889" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="1" orientation="portrait" useFirstPageNumber="1"/>
-  <rowBreaks count="33" manualBreakCount="33">
+  <rowBreaks count="35" manualBreakCount="35">
     <brk id="47" max="16383" man="1"/>
     <brk id="94" max="16383" man="1"/>
     <brk id="141" max="16383" man="1"/>
@@ -17797,6 +19711,8 @@
     <brk id="1457" max="16383" man="1"/>
     <brk id="1504" max="16383" man="1"/>
     <brk id="1551" max="16383" man="1"/>
+    <brk id="1598" max="16383" man="1"/>
+    <brk id="1645" max="16383" man="1"/>
   </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
+++ b/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="761">
   <si>
     <t>§4. 照査の前提</t>
   </si>
@@ -2042,106 +2042,103 @@
     <t>0.482 %</t>
   </si>
   <si>
-    <t>照査は、フーチングの断面照査で地震時以外の照査を行うときに「最小鉄筋量及び最大鉄筋</t>
-  </si>
-  <si>
-    <t>量」で確かめる。</t>
-  </si>
-  <si>
-    <t>照査は、フーチングの断面照査で地震時以外の照査を行うときに「耐久性の照査」で確かめ</t>
+    <t>照査は「12.5 最小鉄筋量及び最大鉄筋量」に示す。</t>
+  </si>
+  <si>
+    <t>照査は「12.3 耐久性の照査」に示す。</t>
+  </si>
+  <si>
+    <t>150.0 − 32 = 118.0 mm</t>
+  </si>
+  <si>
+    <t>フーチング（上側）</t>
+  </si>
+  <si>
+    <t>軸方向鉄筋のあき 118.0</t>
+  </si>
+  <si>
+    <t>≧ 40.0 × 4/3 = 53.3 mm</t>
+  </si>
+  <si>
+    <t>フーチング（下側）</t>
+  </si>
+  <si>
+    <t>スターラップ　D25 − 2.22 本/m　ctc 300.0</t>
+  </si>
+  <si>
+    <t>(1000 × 300.0)</t>
+  </si>
+  <si>
+    <t>0.375 %</t>
+  </si>
+  <si>
+    <t>一般部：上記最小間隔は300mmに対して計算上の配置間隔は300.0mmより満足する。</t>
+  </si>
+  <si>
+    <t>0.021 × 1.15 × 0.375 ＋ 0.013 = 0.022 ≦ 0.040　・・・・・・ OK</t>
+  </si>
+  <si>
+    <t>せん断補強鉄筋比 (= 0.375 %)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve">コンクリートの設計基準強度 (= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>27.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t xml:space="preserve"> N/mm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Mincho"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>0.00375 × 390 / (27.0 / 1.3) = 0.070 ≦ 0.10</t>
+  </si>
+  <si>
+    <t>10) 配力鉄筋及び圧縮鉄筋</t>
+  </si>
+  <si>
+    <t>【RC標準13.6.4】</t>
+  </si>
+  <si>
+    <t>・配力鉄筋として、引張鉄筋の単位幅当りの断面積の1/6以上を単位幅当りに対して配置す</t>
   </si>
   <si>
     <t>る。</t>
   </si>
   <si>
-    <t>150.0 − 32 = 118.0 mm</t>
-  </si>
-  <si>
-    <t>フーチング（上側）</t>
-  </si>
-  <si>
-    <t>軸方向鉄筋のあき 118.0</t>
-  </si>
-  <si>
-    <t>≧ 40.0 × 4/3 = 53.3 mm</t>
-  </si>
-  <si>
-    <t>フーチング（下側）</t>
-  </si>
-  <si>
-    <t>スターラップ　D25 − 2.22 本/m　ctc 300.0</t>
-  </si>
-  <si>
-    <t>(1000 × 300.0)</t>
-  </si>
-  <si>
-    <t>0.375 %</t>
-  </si>
-  <si>
-    <t>一般部：上記最小間隔は300mmに対して計算上の配置間隔は300.0mmより満足する。</t>
-  </si>
-  <si>
-    <t>0.021 × 1.15 × 0.375 ＋ 0.013 = 0.022 ≦ 0.040　・・・・・・ OK</t>
-  </si>
-  <si>
-    <t>せん断補強鉄筋比 (= 0.375 %)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="MS Mincho"/>
-      </rPr>
-      <t xml:space="preserve">コンクリートの設計基準強度 (= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="MS Mincho"/>
-      </rPr>
-      <t>27.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="MS Mincho"/>
-      </rPr>
-      <t xml:space="preserve"> N/mm</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="MS Mincho"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="MS Mincho"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>0.00375 × 390 / (27.0 / 1.3) = 0.070 ≦ 0.10</t>
-  </si>
-  <si>
-    <t>10) 配力鉄筋及び圧縮鉄筋</t>
-  </si>
-  <si>
-    <t>【RC標準13.6.4】</t>
-  </si>
-  <si>
-    <t>・配力鉄筋として、引張鉄筋の単位幅当りの断面積の1/6以上を単位幅当りに対して配置す</t>
-  </si>
-  <si>
     <t>・圧縮鉄筋として、引張鉄筋の単位幅当りの断面積の1/6以上を単位幅当りに対して配置す</t>
   </si>
   <si>
@@ -2176,6 +2173,12 @@
   </si>
   <si>
     <t>下側</t>
+  </si>
+  <si>
+    <t>照査は「12.9 最小鉄筋量及び最大鉄筋量」に示す。</t>
+  </si>
+  <si>
+    <t>照査は「12.7 耐久性の照査」に示す。</t>
   </si>
   <si>
     <t>4.5 杭の構造細目</t>
@@ -10886,63 +10889,51 @@
         <v>259</v>
       </c>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
-      <c r="E736" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1">
-      <c r="E738" s="1" t="s">
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1">
+      <c r="E737" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1">
+      <c r="E739" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="740" ht="15.75" customHeight="1">
       <c r="E740" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="741" ht="15.75" customHeight="1">
       <c r="E741" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="742" ht="15.75" customHeight="1">
-      <c r="E742" s="2" t="s">
         <v>259</v>
       </c>
     </row>
+    <row r="742" ht="15.75" customHeight="1"/>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="E743" s="2" t="s">
-        <v>260</v>
+      <c r="D743" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S743" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="744" ht="15.75" customHeight="1"/>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="D745" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S745" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1">
-      <c r="E747" s="2" t="s">
+      <c r="E745" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
-      <c r="E748" s="2" t="s">
+    <row r="746" ht="15.75" customHeight="1">
+      <c r="E746" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
-      <c r="E749" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
     <row r="750" ht="15.75" customHeight="1"/>
     <row r="751" ht="15.75" customHeight="1"/>
     <row r="752" ht="15.75" customHeight="1"/>
@@ -11022,168 +11013,180 @@
     </row>
     <row r="767" ht="15.75" customHeight="1">
       <c r="E767" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="768" ht="15.75" customHeight="1">
-      <c r="E768" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1">
-      <c r="D770" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1">
+      <c r="D769" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S770" s="1" t="s">
+      <c r="S769" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1">
+      <c r="E771" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
     <row r="772" ht="15.75" customHeight="1">
       <c r="E772" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="773" ht="15.75" customHeight="1">
       <c r="E773" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="774" ht="15.75" customHeight="1">
-      <c r="E774" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1">
+      <c r="J775" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="R775" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S775" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="J776" s="3" t="s">
-        <v>223</v>
+      <c r="M776" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="R776" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S776" s="2" t="s">
-        <v>65</v>
+        <v>226</v>
       </c>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="M777" s="3" t="s">
-        <v>225</v>
+      <c r="J777" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="R777" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S777" s="2" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
     </row>
     <row r="778" ht="15.75" customHeight="1">
       <c r="J778" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R778" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S778" s="2" t="s">
-        <v>263</v>
+        <v>65</v>
       </c>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="J779" s="3" t="s">
-        <v>229</v>
+      <c r="M779" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="R779" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S779" s="2" t="s">
-        <v>65</v>
+        <v>226</v>
       </c>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="M780" s="3" t="s">
-        <v>231</v>
+      <c r="J780" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="R780" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S780" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="781" ht="15.75" customHeight="1">
-      <c r="J781" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="R781" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S781" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1">
+      <c r="E782" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="783" ht="15.75" customHeight="1">
+      <c r="E783" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F783" s="8"/>
+      <c r="G783" s="8"/>
+      <c r="H783" s="8"/>
+      <c r="I783" s="8"/>
+      <c r="J783" s="8"/>
+      <c r="K783" s="8"/>
+      <c r="L783" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M783" s="8"/>
+      <c r="N783" s="8"/>
+      <c r="O783" s="8"/>
+      <c r="P783" s="8"/>
+      <c r="Q783" s="8"/>
+      <c r="R783" s="8"/>
+      <c r="S783" s="8"/>
+      <c r="T783" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U783" s="8"/>
+      <c r="V783" s="8"/>
+      <c r="W783" s="8"/>
+      <c r="X783" s="8"/>
+      <c r="Y783" s="8"/>
+      <c r="Z783" s="8"/>
+      <c r="AA783" s="8"/>
+      <c r="AB783" s="8"/>
+      <c r="AC783" s="8"/>
+      <c r="AD783" s="10"/>
+    </row>
+    <row r="784" ht="15.75" customHeight="1">
+      <c r="E784" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="F784" s="12"/>
+      <c r="G784" s="12"/>
+      <c r="H784" s="12"/>
+      <c r="I784" s="12"/>
+      <c r="J784" s="12"/>
+      <c r="K784" s="12"/>
+      <c r="L784" s="13" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1">
-      <c r="E783" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="784" ht="15.75" customHeight="1">
-      <c r="E784" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F784" s="8"/>
-      <c r="G784" s="8"/>
-      <c r="H784" s="8"/>
-      <c r="I784" s="8"/>
-      <c r="J784" s="8"/>
-      <c r="K784" s="8"/>
-      <c r="L784" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="M784" s="8"/>
-      <c r="N784" s="8"/>
-      <c r="O784" s="8"/>
-      <c r="P784" s="8"/>
-      <c r="Q784" s="8"/>
-      <c r="R784" s="8"/>
-      <c r="S784" s="8"/>
-      <c r="T784" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="U784" s="8"/>
-      <c r="V784" s="8"/>
-      <c r="W784" s="8"/>
-      <c r="X784" s="8"/>
-      <c r="Y784" s="8"/>
-      <c r="Z784" s="8"/>
-      <c r="AA784" s="8"/>
-      <c r="AB784" s="8"/>
-      <c r="AC784" s="8"/>
+      <c r="M784" s="12"/>
+      <c r="N784" s="12"/>
+      <c r="O784" s="12"/>
+      <c r="P784" s="12"/>
+      <c r="Q784" s="12"/>
+      <c r="R784" s="12"/>
+      <c r="S784" s="12"/>
+      <c r="T784" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="U784" s="12"/>
+      <c r="V784" s="12"/>
+      <c r="W784" s="12"/>
+      <c r="X784" s="12"/>
+      <c r="Y784" s="12"/>
+      <c r="Z784" s="12"/>
+      <c r="AA784" s="12"/>
+      <c r="AB784" s="12"/>
+      <c r="AC784" s="12"/>
       <c r="AD784" s="10"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="E785" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="F785" s="12"/>
-      <c r="G785" s="12"/>
-      <c r="H785" s="12"/>
-      <c r="I785" s="12"/>
-      <c r="J785" s="12"/>
-      <c r="K785" s="12"/>
-      <c r="L785" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="M785" s="12"/>
-      <c r="N785" s="12"/>
-      <c r="O785" s="12"/>
-      <c r="P785" s="12"/>
-      <c r="Q785" s="12"/>
-      <c r="R785" s="12"/>
-      <c r="S785" s="12"/>
+      <c r="E785" s="10"/>
+      <c r="L785" s="15"/>
       <c r="T785" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="U785" s="12"/>
       <c r="V785" s="12"/>
@@ -11200,7 +11203,7 @@
       <c r="E786" s="10"/>
       <c r="L786" s="15"/>
       <c r="T786" s="14" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="U786" s="12"/>
       <c r="V786" s="12"/>
@@ -11214,10 +11217,27 @@
       <c r="AD786" s="10"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="E787" s="10"/>
-      <c r="L787" s="15"/>
+      <c r="E787" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="F787" s="12"/>
+      <c r="G787" s="12"/>
+      <c r="H787" s="12"/>
+      <c r="I787" s="12"/>
+      <c r="J787" s="12"/>
+      <c r="K787" s="12"/>
+      <c r="L787" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="M787" s="12"/>
+      <c r="N787" s="12"/>
+      <c r="O787" s="12"/>
+      <c r="P787" s="12"/>
+      <c r="Q787" s="12"/>
+      <c r="R787" s="12"/>
+      <c r="S787" s="12"/>
       <c r="T787" s="14" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="U787" s="12"/>
       <c r="V787" s="12"/>
@@ -11231,27 +11251,10 @@
       <c r="AD787" s="10"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="E788" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="F788" s="12"/>
-      <c r="G788" s="12"/>
-      <c r="H788" s="12"/>
-      <c r="I788" s="12"/>
-      <c r="J788" s="12"/>
-      <c r="K788" s="12"/>
-      <c r="L788" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="M788" s="12"/>
-      <c r="N788" s="12"/>
-      <c r="O788" s="12"/>
-      <c r="P788" s="12"/>
-      <c r="Q788" s="12"/>
-      <c r="R788" s="12"/>
-      <c r="S788" s="12"/>
+      <c r="E788" s="10"/>
+      <c r="L788" s="15"/>
       <c r="T788" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="U788" s="12"/>
       <c r="V788" s="12"/>
@@ -11268,7 +11271,7 @@
       <c r="E789" s="10"/>
       <c r="L789" s="15"/>
       <c r="T789" s="14" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="U789" s="12"/>
       <c r="V789" s="12"/>
@@ -11282,54 +11285,38 @@
       <c r="AD789" s="10"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="E790" s="10"/>
-      <c r="L790" s="15"/>
-      <c r="T790" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="U790" s="12"/>
-      <c r="V790" s="12"/>
-      <c r="W790" s="12"/>
-      <c r="X790" s="12"/>
-      <c r="Y790" s="12"/>
-      <c r="Z790" s="12"/>
-      <c r="AA790" s="12"/>
-      <c r="AB790" s="12"/>
-      <c r="AC790" s="12"/>
-      <c r="AD790" s="10"/>
+      <c r="E790" s="8"/>
+      <c r="F790" s="8"/>
+      <c r="G790" s="8"/>
+      <c r="H790" s="8"/>
+      <c r="I790" s="8"/>
+      <c r="J790" s="8"/>
+      <c r="K790" s="8"/>
+      <c r="L790" s="8"/>
+      <c r="M790" s="8"/>
+      <c r="N790" s="8"/>
+      <c r="O790" s="8"/>
+      <c r="P790" s="8"/>
+      <c r="Q790" s="8"/>
+      <c r="R790" s="8"/>
+      <c r="S790" s="8"/>
+      <c r="T790" s="8"/>
+      <c r="U790" s="8"/>
+      <c r="V790" s="8"/>
+      <c r="W790" s="8"/>
+      <c r="X790" s="8"/>
+      <c r="Y790" s="8"/>
+      <c r="Z790" s="8"/>
+      <c r="AA790" s="8"/>
+      <c r="AB790" s="8"/>
+      <c r="AC790" s="8"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="E791" s="8"/>
-      <c r="F791" s="8"/>
-      <c r="G791" s="8"/>
-      <c r="H791" s="8"/>
-      <c r="I791" s="8"/>
-      <c r="J791" s="8"/>
-      <c r="K791" s="8"/>
-      <c r="L791" s="8"/>
-      <c r="M791" s="8"/>
-      <c r="N791" s="8"/>
-      <c r="O791" s="8"/>
-      <c r="P791" s="8"/>
-      <c r="Q791" s="8"/>
-      <c r="R791" s="8"/>
-      <c r="S791" s="8"/>
-      <c r="T791" s="8"/>
-      <c r="U791" s="8"/>
-      <c r="V791" s="8"/>
-      <c r="W791" s="8"/>
-      <c r="X791" s="8"/>
-      <c r="Y791" s="8"/>
-      <c r="Z791" s="8"/>
-      <c r="AA791" s="8"/>
-      <c r="AB791" s="8"/>
-      <c r="AC791" s="8"/>
-    </row>
-    <row r="792" ht="15.75" customHeight="1">
-      <c r="E792" s="2" t="s">
+      <c r="E791" s="2" t="s">
         <v>82</v>
       </c>
     </row>
+    <row r="792" ht="15.75" customHeight="1"/>
     <row r="793" ht="15.75" customHeight="1"/>
     <row r="794" ht="15.75" customHeight="1"/>
     <row r="795" ht="15.75" customHeight="1"/>
@@ -11359,7 +11346,7 @@
     <row r="804" ht="15.75" customHeight="1"/>
     <row r="805" ht="15.75" customHeight="1">
       <c r="F805" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="806" ht="15.75" customHeight="1">
@@ -11382,7 +11369,7 @@
         <v>27</v>
       </c>
       <c r="P806" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="U806" s="4" t="s">
         <v>28</v>
@@ -11396,7 +11383,7 @@
         <v>26</v>
       </c>
       <c r="J807" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M807" s="3" t="s">
         <v>30</v>
@@ -11589,7 +11576,7 @@
     <row r="828" ht="15.75" customHeight="1"/>
     <row r="829" ht="15.75" customHeight="1">
       <c r="F829" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="830" ht="15.75" customHeight="1"/>
@@ -11650,7 +11637,7 @@
         <v>27</v>
       </c>
       <c r="N839" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="S839" s="4" t="s">
         <v>28</v>
@@ -11670,7 +11657,7 @@
     </row>
     <row r="840" ht="15.75" customHeight="1">
       <c r="F840" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="841" ht="15.75" customHeight="1"/>
@@ -11707,7 +11694,7 @@
         <v>15</v>
       </c>
       <c r="K852" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="853" ht="15.75" customHeight="1">
@@ -11773,7 +11760,7 @@
         <v>15</v>
       </c>
       <c r="K858" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="859" ht="15.75" customHeight="1">
@@ -11790,37 +11777,37 @@
     <row r="860" ht="15.75" customHeight="1"/>
     <row r="861" ht="15.75" customHeight="1">
       <c r="F861" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="862" ht="15.75" customHeight="1"/>
     <row r="863" ht="15.75" customHeight="1">
       <c r="D863" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="S863" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="864" ht="15.75" customHeight="1"/>
     <row r="865" ht="15.75" customHeight="1">
       <c r="E865" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="866" ht="15.75" customHeight="1">
       <c r="E866" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="867" ht="15.75" customHeight="1">
       <c r="E867" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="868" ht="15.75" customHeight="1">
       <c r="E868" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="869" ht="15.75" customHeight="1"/>
@@ -11829,7 +11816,7 @@
       <c r="C870" s="8"/>
       <c r="D870" s="8"/>
       <c r="E870" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F870" s="8"/>
       <c r="G870" s="8"/>
@@ -11838,18 +11825,18 @@
       <c r="J870" s="8"/>
       <c r="K870" s="19"/>
       <c r="L870" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M870" s="8"/>
       <c r="N870" s="8"/>
       <c r="O870" s="19"/>
       <c r="P870" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q870" s="8"/>
       <c r="R870" s="8"/>
       <c r="S870" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T870" s="8"/>
       <c r="U870" s="8"/>
@@ -11857,7 +11844,7 @@
       <c r="W870" s="8"/>
       <c r="X870" s="8"/>
       <c r="Y870" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Z870" s="8"/>
       <c r="AA870" s="8"/>
@@ -11870,30 +11857,30 @@
       <c r="E871" s="15"/>
       <c r="K871" s="15"/>
       <c r="L871" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O871" s="15"/>
       <c r="P871" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="S871" s="15"/>
       <c r="T871" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Y871" s="15"/>
       <c r="Z871" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AD871" s="22"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
       <c r="B872" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C872" s="12"/>
       <c r="D872" s="12"/>
       <c r="E872" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F872" s="12"/>
       <c r="G872" s="12"/>
@@ -11913,7 +11900,7 @@
       <c r="Q872" s="12"/>
       <c r="R872" s="12"/>
       <c r="S872" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T872" s="12"/>
       <c r="U872" s="12"/>
@@ -11921,7 +11908,7 @@
       <c r="W872" s="12"/>
       <c r="X872" s="12"/>
       <c r="Y872" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Z872" s="12"/>
       <c r="AA872" s="12"/>
@@ -11931,12 +11918,12 @@
     </row>
     <row r="873" ht="15.75" customHeight="1">
       <c r="B873" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C873" s="12"/>
       <c r="D873" s="12"/>
       <c r="E873" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F873" s="12"/>
       <c r="G873" s="12"/>
@@ -11956,7 +11943,7 @@
       <c r="Q873" s="12"/>
       <c r="R873" s="12"/>
       <c r="S873" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T873" s="12"/>
       <c r="U873" s="12"/>
@@ -11964,7 +11951,7 @@
       <c r="W873" s="12"/>
       <c r="X873" s="12"/>
       <c r="Y873" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Z873" s="12"/>
       <c r="AA873" s="12"/>
@@ -12189,66 +12176,54 @@
     </row>
     <row r="921" ht="15.75" customHeight="1">
       <c r="E921" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="922" ht="15.75" customHeight="1">
-      <c r="E922" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1">
-      <c r="E924" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1">
+      <c r="E923" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1">
+      <c r="E925" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="926" ht="15.75" customHeight="1">
       <c r="E926" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="927" ht="15.75" customHeight="1">
       <c r="E927" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="928" ht="15.75" customHeight="1">
-      <c r="E928" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="928" ht="15.75" customHeight="1"/>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="E929" s="2" t="s">
-        <v>260</v>
+      <c r="D929" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S929" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="930" ht="15.75" customHeight="1"/>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="D931" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S931" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1">
-      <c r="E933" s="2" t="s">
+      <c r="E931" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
-      <c r="E934" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="935" ht="15.75" customHeight="1">
-      <c r="E935" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
+    <row r="932" ht="15.75" customHeight="1">
+      <c r="E932" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
     <row r="936" ht="15.75" customHeight="1"/>
     <row r="937" ht="15.75" customHeight="1"/>
     <row r="938" ht="15.75" customHeight="1"/>
@@ -12330,168 +12305,180 @@
     </row>
     <row r="955" ht="15.75" customHeight="1">
       <c r="E955" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="956" ht="15.75" customHeight="1">
-      <c r="E956" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1">
-      <c r="D958" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1">
+      <c r="D957" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S958" s="1" t="s">
+      <c r="S957" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1">
+      <c r="E959" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
     <row r="960" ht="15.75" customHeight="1">
       <c r="E960" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="961" ht="15.75" customHeight="1">
       <c r="E961" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="962" ht="15.75" customHeight="1">
-      <c r="E962" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1">
+      <c r="J963" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="R963" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S963" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="J964" s="3" t="s">
-        <v>223</v>
+      <c r="M964" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="R964" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S964" s="2" t="s">
-        <v>65</v>
+        <v>226</v>
       </c>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="M965" s="3" t="s">
-        <v>225</v>
+      <c r="J965" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="R965" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S965" s="2" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
     </row>
     <row r="966" ht="15.75" customHeight="1">
       <c r="J966" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R966" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S966" s="2" t="s">
-        <v>263</v>
+        <v>65</v>
       </c>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="J967" s="3" t="s">
-        <v>229</v>
+      <c r="M967" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="R967" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S967" s="2" t="s">
-        <v>65</v>
+        <v>226</v>
       </c>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="M968" s="3" t="s">
-        <v>231</v>
+      <c r="J968" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="R968" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S968" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="969" ht="15.75" customHeight="1">
-      <c r="J969" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="R969" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S969" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1">
+      <c r="E970" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="971" ht="15.75" customHeight="1">
+      <c r="E971" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F971" s="8"/>
+      <c r="G971" s="8"/>
+      <c r="H971" s="8"/>
+      <c r="I971" s="8"/>
+      <c r="J971" s="8"/>
+      <c r="K971" s="8"/>
+      <c r="L971" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M971" s="8"/>
+      <c r="N971" s="8"/>
+      <c r="O971" s="8"/>
+      <c r="P971" s="8"/>
+      <c r="Q971" s="8"/>
+      <c r="R971" s="8"/>
+      <c r="S971" s="8"/>
+      <c r="T971" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U971" s="8"/>
+      <c r="V971" s="8"/>
+      <c r="W971" s="8"/>
+      <c r="X971" s="8"/>
+      <c r="Y971" s="8"/>
+      <c r="Z971" s="8"/>
+      <c r="AA971" s="8"/>
+      <c r="AB971" s="8"/>
+      <c r="AC971" s="8"/>
+      <c r="AD971" s="10"/>
+    </row>
+    <row r="972" ht="15.75" customHeight="1">
+      <c r="E972" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="F972" s="12"/>
+      <c r="G972" s="12"/>
+      <c r="H972" s="12"/>
+      <c r="I972" s="12"/>
+      <c r="J972" s="12"/>
+      <c r="K972" s="12"/>
+      <c r="L972" s="13" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1">
-      <c r="E971" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="E972" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F972" s="8"/>
-      <c r="G972" s="8"/>
-      <c r="H972" s="8"/>
-      <c r="I972" s="8"/>
-      <c r="J972" s="8"/>
-      <c r="K972" s="8"/>
-      <c r="L972" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="M972" s="8"/>
-      <c r="N972" s="8"/>
-      <c r="O972" s="8"/>
-      <c r="P972" s="8"/>
-      <c r="Q972" s="8"/>
-      <c r="R972" s="8"/>
-      <c r="S972" s="8"/>
-      <c r="T972" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="U972" s="8"/>
-      <c r="V972" s="8"/>
-      <c r="W972" s="8"/>
-      <c r="X972" s="8"/>
-      <c r="Y972" s="8"/>
-      <c r="Z972" s="8"/>
-      <c r="AA972" s="8"/>
-      <c r="AB972" s="8"/>
-      <c r="AC972" s="8"/>
+      <c r="M972" s="12"/>
+      <c r="N972" s="12"/>
+      <c r="O972" s="12"/>
+      <c r="P972" s="12"/>
+      <c r="Q972" s="12"/>
+      <c r="R972" s="12"/>
+      <c r="S972" s="12"/>
+      <c r="T972" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="U972" s="12"/>
+      <c r="V972" s="12"/>
+      <c r="W972" s="12"/>
+      <c r="X972" s="12"/>
+      <c r="Y972" s="12"/>
+      <c r="Z972" s="12"/>
+      <c r="AA972" s="12"/>
+      <c r="AB972" s="12"/>
+      <c r="AC972" s="12"/>
       <c r="AD972" s="10"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="E973" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="F973" s="12"/>
-      <c r="G973" s="12"/>
-      <c r="H973" s="12"/>
-      <c r="I973" s="12"/>
-      <c r="J973" s="12"/>
-      <c r="K973" s="12"/>
-      <c r="L973" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="M973" s="12"/>
-      <c r="N973" s="12"/>
-      <c r="O973" s="12"/>
-      <c r="P973" s="12"/>
-      <c r="Q973" s="12"/>
-      <c r="R973" s="12"/>
-      <c r="S973" s="12"/>
+      <c r="E973" s="10"/>
+      <c r="L973" s="15"/>
       <c r="T973" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="U973" s="12"/>
       <c r="V973" s="12"/>
@@ -12508,7 +12495,7 @@
       <c r="E974" s="10"/>
       <c r="L974" s="15"/>
       <c r="T974" s="14" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="U974" s="12"/>
       <c r="V974" s="12"/>
@@ -12522,10 +12509,27 @@
       <c r="AD974" s="10"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="E975" s="10"/>
-      <c r="L975" s="15"/>
+      <c r="E975" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="F975" s="12"/>
+      <c r="G975" s="12"/>
+      <c r="H975" s="12"/>
+      <c r="I975" s="12"/>
+      <c r="J975" s="12"/>
+      <c r="K975" s="12"/>
+      <c r="L975" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="M975" s="12"/>
+      <c r="N975" s="12"/>
+      <c r="O975" s="12"/>
+      <c r="P975" s="12"/>
+      <c r="Q975" s="12"/>
+      <c r="R975" s="12"/>
+      <c r="S975" s="12"/>
       <c r="T975" s="14" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="U975" s="12"/>
       <c r="V975" s="12"/>
@@ -12539,27 +12543,10 @@
       <c r="AD975" s="10"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="E976" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="F976" s="12"/>
-      <c r="G976" s="12"/>
-      <c r="H976" s="12"/>
-      <c r="I976" s="12"/>
-      <c r="J976" s="12"/>
-      <c r="K976" s="12"/>
-      <c r="L976" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="M976" s="12"/>
-      <c r="N976" s="12"/>
-      <c r="O976" s="12"/>
-      <c r="P976" s="12"/>
-      <c r="Q976" s="12"/>
-      <c r="R976" s="12"/>
-      <c r="S976" s="12"/>
+      <c r="E976" s="10"/>
+      <c r="L976" s="15"/>
       <c r="T976" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="U976" s="12"/>
       <c r="V976" s="12"/>
@@ -12576,7 +12563,7 @@
       <c r="E977" s="10"/>
       <c r="L977" s="15"/>
       <c r="T977" s="14" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="U977" s="12"/>
       <c r="V977" s="12"/>
@@ -12590,54 +12577,38 @@
       <c r="AD977" s="10"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="E978" s="10"/>
-      <c r="L978" s="15"/>
-      <c r="T978" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="U978" s="12"/>
-      <c r="V978" s="12"/>
-      <c r="W978" s="12"/>
-      <c r="X978" s="12"/>
-      <c r="Y978" s="12"/>
-      <c r="Z978" s="12"/>
-      <c r="AA978" s="12"/>
-      <c r="AB978" s="12"/>
-      <c r="AC978" s="12"/>
-      <c r="AD978" s="10"/>
+      <c r="E978" s="8"/>
+      <c r="F978" s="8"/>
+      <c r="G978" s="8"/>
+      <c r="H978" s="8"/>
+      <c r="I978" s="8"/>
+      <c r="J978" s="8"/>
+      <c r="K978" s="8"/>
+      <c r="L978" s="8"/>
+      <c r="M978" s="8"/>
+      <c r="N978" s="8"/>
+      <c r="O978" s="8"/>
+      <c r="P978" s="8"/>
+      <c r="Q978" s="8"/>
+      <c r="R978" s="8"/>
+      <c r="S978" s="8"/>
+      <c r="T978" s="8"/>
+      <c r="U978" s="8"/>
+      <c r="V978" s="8"/>
+      <c r="W978" s="8"/>
+      <c r="X978" s="8"/>
+      <c r="Y978" s="8"/>
+      <c r="Z978" s="8"/>
+      <c r="AA978" s="8"/>
+      <c r="AB978" s="8"/>
+      <c r="AC978" s="8"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="E979" s="8"/>
-      <c r="F979" s="8"/>
-      <c r="G979" s="8"/>
-      <c r="H979" s="8"/>
-      <c r="I979" s="8"/>
-      <c r="J979" s="8"/>
-      <c r="K979" s="8"/>
-      <c r="L979" s="8"/>
-      <c r="M979" s="8"/>
-      <c r="N979" s="8"/>
-      <c r="O979" s="8"/>
-      <c r="P979" s="8"/>
-      <c r="Q979" s="8"/>
-      <c r="R979" s="8"/>
-      <c r="S979" s="8"/>
-      <c r="T979" s="8"/>
-      <c r="U979" s="8"/>
-      <c r="V979" s="8"/>
-      <c r="W979" s="8"/>
-      <c r="X979" s="8"/>
-      <c r="Y979" s="8"/>
-      <c r="Z979" s="8"/>
-      <c r="AA979" s="8"/>
-      <c r="AB979" s="8"/>
-      <c r="AC979" s="8"/>
-    </row>
-    <row r="980" ht="15.75" customHeight="1">
-      <c r="E980" s="2" t="s">
+      <c r="E979" s="2" t="s">
         <v>82</v>
       </c>
     </row>
+    <row r="980" ht="15.75" customHeight="1"/>
     <row r="981" ht="15.75" customHeight="1"/>
     <row r="982" ht="15.75" customHeight="1"/>
     <row r="983" ht="15.75" customHeight="1"/>
@@ -12667,7 +12638,7 @@
     <row r="992" ht="15.75" customHeight="1"/>
     <row r="993" ht="15.75" customHeight="1">
       <c r="F993" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="994" ht="15.75" customHeight="1">
@@ -12690,7 +12661,7 @@
         <v>27</v>
       </c>
       <c r="P994" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="U994" s="4" t="s">
         <v>28</v>
@@ -12704,7 +12675,7 @@
         <v>26</v>
       </c>
       <c r="J995" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M995" s="3" t="s">
         <v>30</v>
@@ -12897,7 +12868,7 @@
     <row r="1016" ht="15.75" customHeight="1"/>
     <row r="1017" ht="15.75" customHeight="1">
       <c r="F1017" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="1018" ht="15.75" customHeight="1"/>
@@ -12958,7 +12929,7 @@
         <v>27</v>
       </c>
       <c r="N1027" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="S1027" s="4" t="s">
         <v>28</v>
@@ -12978,7 +12949,7 @@
     </row>
     <row r="1028" ht="15.75" customHeight="1">
       <c r="F1028" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="1029" ht="15.75" customHeight="1"/>
@@ -13015,7 +12986,7 @@
         <v>15</v>
       </c>
       <c r="K1040" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="1041" ht="15.75" customHeight="1">
@@ -13081,7 +13052,7 @@
         <v>15</v>
       </c>
       <c r="K1046" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="1047" ht="15.75" customHeight="1">
@@ -13098,37 +13069,37 @@
     <row r="1048" ht="15.75" customHeight="1"/>
     <row r="1049" ht="15.75" customHeight="1">
       <c r="F1049" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1050" ht="15.75" customHeight="1"/>
     <row r="1051" ht="15.75" customHeight="1">
       <c r="D1051" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="S1051" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="1052" ht="15.75" customHeight="1"/>
     <row r="1053" ht="15.75" customHeight="1">
       <c r="E1053" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1054" ht="15.75" customHeight="1">
       <c r="E1054" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1055" ht="15.75" customHeight="1">
       <c r="E1055" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="1056" ht="15.75" customHeight="1">
       <c r="E1056" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1057" ht="15.75" customHeight="1"/>
@@ -13137,7 +13108,7 @@
       <c r="C1058" s="8"/>
       <c r="D1058" s="8"/>
       <c r="E1058" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F1058" s="8"/>
       <c r="G1058" s="8"/>
@@ -13146,18 +13117,18 @@
       <c r="J1058" s="8"/>
       <c r="K1058" s="19"/>
       <c r="L1058" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M1058" s="8"/>
       <c r="N1058" s="8"/>
       <c r="O1058" s="19"/>
       <c r="P1058" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q1058" s="8"/>
       <c r="R1058" s="8"/>
       <c r="S1058" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T1058" s="8"/>
       <c r="U1058" s="8"/>
@@ -13165,7 +13136,7 @@
       <c r="W1058" s="8"/>
       <c r="X1058" s="8"/>
       <c r="Y1058" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Z1058" s="8"/>
       <c r="AA1058" s="8"/>
@@ -13178,30 +13149,30 @@
       <c r="E1059" s="15"/>
       <c r="K1059" s="15"/>
       <c r="L1059" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O1059" s="15"/>
       <c r="P1059" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="S1059" s="15"/>
       <c r="T1059" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Y1059" s="15"/>
       <c r="Z1059" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AD1059" s="22"/>
     </row>
     <row r="1060" ht="15.75" customHeight="1">
       <c r="B1060" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C1060" s="12"/>
       <c r="D1060" s="12"/>
       <c r="E1060" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F1060" s="12"/>
       <c r="G1060" s="12"/>
@@ -13221,7 +13192,7 @@
       <c r="Q1060" s="12"/>
       <c r="R1060" s="12"/>
       <c r="S1060" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T1060" s="12"/>
       <c r="U1060" s="12"/>
@@ -13229,7 +13200,7 @@
       <c r="W1060" s="12"/>
       <c r="X1060" s="12"/>
       <c r="Y1060" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Z1060" s="12"/>
       <c r="AA1060" s="12"/>
@@ -13239,12 +13210,12 @@
     </row>
     <row r="1061" ht="15.75" customHeight="1">
       <c r="B1061" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1061" s="12"/>
       <c r="D1061" s="12"/>
       <c r="E1061" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F1061" s="12"/>
       <c r="G1061" s="12"/>
@@ -13264,7 +13235,7 @@
       <c r="Q1061" s="12"/>
       <c r="R1061" s="12"/>
       <c r="S1061" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T1061" s="12"/>
       <c r="U1061" s="12"/>
@@ -13272,7 +13243,7 @@
       <c r="W1061" s="12"/>
       <c r="X1061" s="12"/>
       <c r="Y1061" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Z1061" s="12"/>
       <c r="AA1061" s="12"/>
@@ -13332,193 +13303,193 @@
     <row r="1081" ht="15.75" customHeight="1"/>
     <row r="1082" ht="15.75" customHeight="1">
       <c r="B1082" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="1083" ht="15.75" customHeight="1"/>
     <row r="1084" ht="15.75" customHeight="1">
       <c r="C1084" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="1085" ht="15.75" customHeight="1"/>
     <row r="1086" ht="15.75" customHeight="1">
       <c r="D1086" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S1086" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="1087" ht="15.75" customHeight="1"/>
     <row r="1088" ht="15.75" customHeight="1">
       <c r="E1088" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1089" ht="15.75" customHeight="1">
       <c r="E1089" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1090" ht="15.75" customHeight="1"/>
     <row r="1091" ht="15.75" customHeight="1">
       <c r="D1091" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S1091" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="1092" ht="15.75" customHeight="1"/>
     <row r="1093" ht="15.75" customHeight="1">
       <c r="E1093" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1094" ht="15.75" customHeight="1"/>
     <row r="1095" ht="15.75" customHeight="1">
       <c r="N1095" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R1095" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1095" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1096" ht="15.75" customHeight="1">
       <c r="K1096" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R1096" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1096" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="1097" ht="15.75" customHeight="1"/>
     <row r="1098" ht="15.75" customHeight="1">
       <c r="F1098" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1099" ht="15.75" customHeight="1"/>
     <row r="1100" ht="15.75" customHeight="1">
       <c r="E1100" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="1101" ht="15.75" customHeight="1">
       <c r="E1101" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="1102" ht="15.75" customHeight="1">
       <c r="E1102" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="1103" ht="15.75" customHeight="1"/>
     <row r="1104" ht="15.75" customHeight="1">
       <c r="N1104" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R1104" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1104" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1105" ht="15.75" customHeight="1">
       <c r="L1105" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R1105" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1105" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="1106" ht="15.75" customHeight="1"/>
     <row r="1107" ht="15.75" customHeight="1">
       <c r="F1107" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="1108" ht="15.75" customHeight="1"/>
     <row r="1109" ht="15.75" customHeight="1">
       <c r="E1109" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="1110" ht="15.75" customHeight="1"/>
     <row r="1111" ht="15.75" customHeight="1">
       <c r="D1111" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S1111" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1112" ht="15.75" customHeight="1"/>
     <row r="1113" ht="15.75" customHeight="1">
       <c r="E1113" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1114" ht="15.75" customHeight="1">
       <c r="E1114" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1115" ht="15.75" customHeight="1">
       <c r="E1115" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1116" ht="15.75" customHeight="1">
       <c r="E1116" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1117" ht="15.75" customHeight="1">
       <c r="E1117" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1118" ht="15.75" customHeight="1">
       <c r="E1118" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1119" ht="15.75" customHeight="1">
       <c r="E1119" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="1120" ht="15.75" customHeight="1">
       <c r="E1120" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="1121" ht="15.75" customHeight="1">
       <c r="E1121" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1122" ht="15.75" customHeight="1">
       <c r="E1122" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="1123" ht="15.75" customHeight="1">
       <c r="E1123" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1124" ht="15.75" customHeight="1"/>
@@ -13528,71 +13499,71 @@
     <row r="1128" ht="15.75" customHeight="1"/>
     <row r="1129" ht="15.75" customHeight="1">
       <c r="D1129" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1130" ht="15.75" customHeight="1"/>
     <row r="1131" ht="15.75" customHeight="1">
       <c r="E1131" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S1131" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1132" ht="15.75" customHeight="1"/>
     <row r="1133" ht="15.75" customHeight="1">
       <c r="E1133" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1134" ht="15.75" customHeight="1">
       <c r="E1134" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="1135" ht="15.75" customHeight="1">
       <c r="E1135" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1136" ht="15.75" customHeight="1">
       <c r="E1136" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1137" ht="15.75" customHeight="1">
       <c r="E1137" s="18"/>
       <c r="F1137" s="20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G1137" s="8"/>
       <c r="H1137" s="8"/>
       <c r="I1137" s="8"/>
       <c r="J1137" s="19"/>
       <c r="K1137" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L1137" s="8"/>
       <c r="M1137" s="8"/>
       <c r="N1137" s="8"/>
       <c r="O1137" s="19"/>
       <c r="P1137" s="20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q1137" s="8"/>
       <c r="R1137" s="8"/>
       <c r="S1137" s="8"/>
       <c r="T1137" s="19"/>
       <c r="U1137" s="20" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="V1137" s="8"/>
       <c r="W1137" s="8"/>
       <c r="X1137" s="8"/>
       <c r="Y1137" s="19"/>
       <c r="Z1137" s="20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA1137" s="8"/>
       <c r="AB1137" s="8"/>
@@ -13602,23 +13573,23 @@
     <row r="1138" ht="15.75" customHeight="1">
       <c r="E1138" s="10"/>
       <c r="F1138" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J1138" s="15"/>
       <c r="K1138" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O1138" s="15"/>
       <c r="P1138" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T1138" s="15"/>
       <c r="U1138" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Y1138" s="15"/>
       <c r="Z1138" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AD1138" s="10"/>
     </row>
@@ -13841,93 +13812,93 @@
     </row>
     <row r="1145" ht="15.75" customHeight="1">
       <c r="E1145" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="1146" ht="15.75" customHeight="1">
       <c r="E1146" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="1147" ht="15.75" customHeight="1"/>
     <row r="1148" ht="15.75" customHeight="1">
       <c r="E1148" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S1148" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1149" ht="15.75" customHeight="1"/>
     <row r="1150" ht="15.75" customHeight="1">
       <c r="E1150" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="1151" ht="15.75" customHeight="1"/>
     <row r="1152" ht="15.75" customHeight="1">
       <c r="F1152" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="1153" ht="15.75" customHeight="1"/>
     <row r="1154" ht="15.75" customHeight="1">
       <c r="E1154" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="1155" ht="15.75" customHeight="1"/>
     <row r="1156" ht="15.75" customHeight="1">
       <c r="E1156" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S1156" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1157" ht="15.75" customHeight="1"/>
     <row r="1158" ht="15.75" customHeight="1">
       <c r="E1158" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1159" ht="15.75" customHeight="1"/>
     <row r="1160" ht="15.75" customHeight="1">
       <c r="F1160" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1161" ht="15.75" customHeight="1"/>
     <row r="1162" ht="15.75" customHeight="1">
       <c r="E1162" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1163" ht="15.75" customHeight="1"/>
     <row r="1164" ht="15.75" customHeight="1">
       <c r="E1164" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S1164" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1165" ht="15.75" customHeight="1"/>
     <row r="1166" ht="15.75" customHeight="1">
       <c r="E1166" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="1167" ht="15.75" customHeight="1"/>
     <row r="1168" ht="15.75" customHeight="1">
       <c r="F1168" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1169" ht="15.75" customHeight="1"/>
     <row r="1170" ht="15.75" customHeight="1">
       <c r="E1170" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="1171" ht="15.75" customHeight="1"/>
@@ -13937,18 +13908,18 @@
     <row r="1175" ht="15.75" customHeight="1"/>
     <row r="1176" ht="15.75" customHeight="1">
       <c r="D1176" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1177" ht="15.75" customHeight="1"/>
     <row r="1178" ht="15.75" customHeight="1">
       <c r="B1178" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1179" ht="15.75" customHeight="1">
       <c r="B1179" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1179" s="8"/>
       <c r="D1179" s="8"/>
@@ -13958,7 +13929,7 @@
       <c r="H1179" s="8"/>
       <c r="I1179" s="8"/>
       <c r="J1179" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K1179" s="8"/>
       <c r="L1179" s="8"/>
@@ -13969,7 +13940,7 @@
       <c r="Q1179" s="8"/>
       <c r="R1179" s="8"/>
       <c r="S1179" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="T1179" s="8"/>
       <c r="U1179" s="8"/>
@@ -13977,7 +13948,7 @@
       <c r="W1179" s="8"/>
       <c r="X1179" s="8"/>
       <c r="Y1179" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z1179" s="8"/>
       <c r="AA1179" s="9" t="s">
@@ -13989,7 +13960,7 @@
     </row>
     <row r="1180" ht="15.75" customHeight="1">
       <c r="B1180" s="23" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1180" s="12"/>
       <c r="D1180" s="12"/>
@@ -13999,7 +13970,7 @@
       <c r="H1180" s="12"/>
       <c r="I1180" s="12"/>
       <c r="J1180" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K1180" s="12"/>
       <c r="L1180" s="12"/>
@@ -14010,7 +13981,7 @@
       <c r="Q1180" s="12"/>
       <c r="R1180" s="12"/>
       <c r="S1180" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T1180" s="12"/>
       <c r="U1180" s="12"/>
@@ -14018,11 +13989,11 @@
       <c r="W1180" s="12"/>
       <c r="X1180" s="12"/>
       <c r="Y1180" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1180" s="12"/>
       <c r="AA1180" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1180" s="12"/>
       <c r="AC1180" s="12"/>
@@ -14030,7 +14001,7 @@
     </row>
     <row r="1181" ht="15.75" customHeight="1">
       <c r="B1181" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C1181" s="12"/>
       <c r="D1181" s="12"/>
@@ -14040,7 +14011,7 @@
       <c r="H1181" s="12"/>
       <c r="I1181" s="12"/>
       <c r="J1181" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K1181" s="12"/>
       <c r="L1181" s="12"/>
@@ -14051,7 +14022,7 @@
       <c r="Q1181" s="12"/>
       <c r="R1181" s="12"/>
       <c r="S1181" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T1181" s="12"/>
       <c r="U1181" s="12"/>
@@ -14059,11 +14030,11 @@
       <c r="W1181" s="12"/>
       <c r="X1181" s="12"/>
       <c r="Y1181" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1181" s="12"/>
       <c r="AA1181" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1181" s="12"/>
       <c r="AC1181" s="12"/>
@@ -14072,7 +14043,7 @@
     <row r="1182" ht="15.75" customHeight="1">
       <c r="B1182" s="10"/>
       <c r="J1182" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K1182" s="12"/>
       <c r="L1182" s="12"/>
@@ -14083,7 +14054,7 @@
       <c r="Q1182" s="12"/>
       <c r="R1182" s="12"/>
       <c r="S1182" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="T1182" s="12"/>
       <c r="U1182" s="12"/>
@@ -14091,7 +14062,7 @@
       <c r="W1182" s="12"/>
       <c r="X1182" s="12"/>
       <c r="Y1182" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1182" s="12"/>
       <c r="AA1182" s="15"/>
@@ -14099,7 +14070,7 @@
     </row>
     <row r="1183" ht="15.75" customHeight="1">
       <c r="B1183" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C1183" s="12"/>
       <c r="D1183" s="12"/>
@@ -14109,7 +14080,7 @@
       <c r="H1183" s="12"/>
       <c r="I1183" s="12"/>
       <c r="J1183" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K1183" s="12"/>
       <c r="L1183" s="12"/>
@@ -14120,7 +14091,7 @@
       <c r="Q1183" s="12"/>
       <c r="R1183" s="12"/>
       <c r="S1183" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="T1183" s="12"/>
       <c r="U1183" s="12"/>
@@ -14128,11 +14099,11 @@
       <c r="W1183" s="12"/>
       <c r="X1183" s="12"/>
       <c r="Y1183" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1183" s="12"/>
       <c r="AA1183" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1183" s="12"/>
       <c r="AC1183" s="12"/>
@@ -14141,7 +14112,7 @@
     <row r="1184" ht="15.75" customHeight="1">
       <c r="B1184" s="10"/>
       <c r="J1184" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K1184" s="12"/>
       <c r="L1184" s="12"/>
@@ -14152,7 +14123,7 @@
       <c r="Q1184" s="12"/>
       <c r="R1184" s="12"/>
       <c r="S1184" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T1184" s="12"/>
       <c r="U1184" s="12"/>
@@ -14160,7 +14131,7 @@
       <c r="W1184" s="12"/>
       <c r="X1184" s="12"/>
       <c r="Y1184" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1184" s="12"/>
       <c r="AA1184" s="15"/>
@@ -14168,7 +14139,7 @@
     </row>
     <row r="1185" ht="15.75" customHeight="1">
       <c r="B1185" s="23" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C1185" s="12"/>
       <c r="D1185" s="12"/>
@@ -14178,7 +14149,7 @@
       <c r="H1185" s="12"/>
       <c r="I1185" s="12"/>
       <c r="J1185" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K1185" s="12"/>
       <c r="L1185" s="12"/>
@@ -14189,7 +14160,7 @@
       <c r="Q1185" s="12"/>
       <c r="R1185" s="12"/>
       <c r="S1185" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="T1185" s="12"/>
       <c r="U1185" s="12"/>
@@ -14197,11 +14168,11 @@
       <c r="W1185" s="12"/>
       <c r="X1185" s="12"/>
       <c r="Y1185" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1185" s="12"/>
       <c r="AA1185" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1185" s="12"/>
       <c r="AC1185" s="12"/>
@@ -14209,7 +14180,7 @@
     </row>
     <row r="1186" ht="15.75" customHeight="1">
       <c r="B1186" s="23" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C1186" s="12"/>
       <c r="D1186" s="12"/>
@@ -14219,7 +14190,7 @@
       <c r="H1186" s="12"/>
       <c r="I1186" s="12"/>
       <c r="J1186" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K1186" s="12"/>
       <c r="L1186" s="12"/>
@@ -14230,7 +14201,7 @@
       <c r="Q1186" s="12"/>
       <c r="R1186" s="12"/>
       <c r="S1186" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="T1186" s="12"/>
       <c r="U1186" s="12"/>
@@ -14238,11 +14209,11 @@
       <c r="W1186" s="12"/>
       <c r="X1186" s="12"/>
       <c r="Y1186" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1186" s="12"/>
       <c r="AA1186" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1186" s="12"/>
       <c r="AC1186" s="12"/>
@@ -14250,7 +14221,7 @@
     </row>
     <row r="1187" ht="15.75" customHeight="1">
       <c r="B1187" s="23" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C1187" s="12"/>
       <c r="D1187" s="12"/>
@@ -14260,7 +14231,7 @@
       <c r="H1187" s="12"/>
       <c r="I1187" s="12"/>
       <c r="J1187" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K1187" s="12"/>
       <c r="L1187" s="12"/>
@@ -14271,7 +14242,7 @@
       <c r="Q1187" s="12"/>
       <c r="R1187" s="12"/>
       <c r="S1187" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="T1187" s="12"/>
       <c r="U1187" s="12"/>
@@ -14279,11 +14250,11 @@
       <c r="W1187" s="12"/>
       <c r="X1187" s="12"/>
       <c r="Y1187" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1187" s="12"/>
       <c r="AA1187" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1187" s="12"/>
       <c r="AC1187" s="12"/>
@@ -14291,7 +14262,7 @@
     </row>
     <row r="1188" ht="15.75" customHeight="1">
       <c r="B1188" s="23" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C1188" s="12"/>
       <c r="D1188" s="12"/>
@@ -14301,7 +14272,7 @@
       <c r="H1188" s="12"/>
       <c r="I1188" s="12"/>
       <c r="J1188" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K1188" s="12"/>
       <c r="L1188" s="12"/>
@@ -14312,7 +14283,7 @@
       <c r="Q1188" s="12"/>
       <c r="R1188" s="12"/>
       <c r="S1188" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="T1188" s="12"/>
       <c r="U1188" s="12"/>
@@ -14320,11 +14291,11 @@
       <c r="W1188" s="12"/>
       <c r="X1188" s="12"/>
       <c r="Y1188" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1188" s="12"/>
       <c r="AA1188" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1188" s="12"/>
       <c r="AC1188" s="12"/>
@@ -14363,69 +14334,69 @@
     </row>
     <row r="1190" ht="15.75" customHeight="1">
       <c r="C1190" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="1191" ht="15.75" customHeight="1"/>
     <row r="1192" ht="15.75" customHeight="1">
       <c r="D1192" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="S1192" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="1193" ht="15.75" customHeight="1"/>
     <row r="1194" ht="15.75" customHeight="1">
       <c r="E1194" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="1195" ht="15.75" customHeight="1">
       <c r="E1195" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="1196" ht="15.75" customHeight="1">
       <c r="E1196" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="1197" ht="15.75" customHeight="1"/>
     <row r="1198" ht="15.75" customHeight="1">
       <c r="D1198" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="S1198" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="1199" ht="15.75" customHeight="1"/>
     <row r="1200" ht="15.75" customHeight="1">
       <c r="E1200" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="1201" ht="15.75" customHeight="1"/>
     <row r="1202" ht="15.75" customHeight="1">
       <c r="E1202" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="1203" ht="15.75" customHeight="1">
       <c r="E1203" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="1204" ht="15.75" customHeight="1">
       <c r="F1204" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="1205" ht="15.75" customHeight="1"/>
     <row r="1206" ht="15.75" customHeight="1">
       <c r="E1206" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="1207" ht="15.75" customHeight="1"/>
@@ -14446,27 +14417,27 @@
     <row r="1222" ht="15.75" customHeight="1"/>
     <row r="1223" ht="15.75" customHeight="1">
       <c r="D1223" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="S1223" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1224" ht="15.75" customHeight="1"/>
     <row r="1225" ht="15.75" customHeight="1">
       <c r="E1225" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="1226" ht="15.75" customHeight="1">
       <c r="E1226" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="1227" ht="15.75" customHeight="1"/>
     <row r="1228" ht="15.75" customHeight="1">
       <c r="F1228" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1229" ht="15.75" customHeight="1"/>
@@ -14478,18 +14449,18 @@
         <v>15</v>
       </c>
       <c r="S1230" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="1231" ht="15.75" customHeight="1">
       <c r="M1231" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R1231" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1231" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="1232" ht="15.75" customHeight="1">
@@ -14500,7 +14471,7 @@
         <v>15</v>
       </c>
       <c r="S1232" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="1233" ht="15.75" customHeight="1"/>
@@ -14530,7 +14501,7 @@
       <c r="R1235" s="8"/>
       <c r="S1235" s="8"/>
       <c r="T1235" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U1235" s="8"/>
       <c r="V1235" s="8"/>
@@ -14545,7 +14516,7 @@
     </row>
     <row r="1236" ht="15.75" customHeight="1">
       <c r="E1236" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F1236" s="12"/>
       <c r="G1236" s="12"/>
@@ -14554,7 +14525,7 @@
       <c r="J1236" s="12"/>
       <c r="K1236" s="12"/>
       <c r="L1236" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M1236" s="12"/>
       <c r="N1236" s="12"/>
@@ -14581,7 +14552,7 @@
       <c r="E1237" s="10"/>
       <c r="L1237" s="15"/>
       <c r="T1237" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U1237" s="12"/>
       <c r="V1237" s="12"/>
@@ -14598,7 +14569,7 @@
       <c r="E1238" s="10"/>
       <c r="L1238" s="15"/>
       <c r="T1238" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U1238" s="12"/>
       <c r="V1238" s="12"/>
@@ -14640,84 +14611,84 @@
     </row>
     <row r="1240" ht="15.75" customHeight="1">
       <c r="E1240" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1241" ht="15.75" customHeight="1">
       <c r="E1241" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="1242" ht="15.75" customHeight="1"/>
     <row r="1243" ht="15.75" customHeight="1">
       <c r="E1243" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="1244" ht="15.75" customHeight="1">
       <c r="F1244" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="1245" ht="15.75" customHeight="1"/>
     <row r="1246" ht="15.75" customHeight="1">
       <c r="E1246" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1247" ht="15.75" customHeight="1"/>
     <row r="1248" ht="15.75" customHeight="1">
       <c r="D1248" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="S1248" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1249" ht="15.75" customHeight="1"/>
     <row r="1250" ht="15.75" customHeight="1">
       <c r="E1250" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1251" ht="15.75" customHeight="1"/>
     <row r="1252" ht="15.75" customHeight="1">
       <c r="E1252" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="1253" ht="15.75" customHeight="1">
       <c r="F1253" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="1254" ht="15.75" customHeight="1"/>
     <row r="1255" ht="15.75" customHeight="1">
       <c r="F1255" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J1255" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1255" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="1256" ht="15.75" customHeight="1">
       <c r="I1256" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J1256" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1256" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="1257" ht="15.75" customHeight="1"/>
     <row r="1258" ht="15.75" customHeight="1">
       <c r="H1258" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I1258" s="4" t="s">
         <v>26</v>
@@ -14729,7 +14700,7 @@
         <v>27</v>
       </c>
       <c r="N1258" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="T1258" s="4" t="s">
         <v>28</v>
@@ -14749,28 +14720,28 @@
     </row>
     <row r="1259" ht="15.75" customHeight="1">
       <c r="F1259" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="1260" ht="15.75" customHeight="1"/>
     <row r="1261" ht="15.75" customHeight="1">
       <c r="E1261" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1262" ht="15.75" customHeight="1"/>
     <row r="1263" ht="15.75" customHeight="1">
       <c r="D1263" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S1263" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1264" ht="15.75" customHeight="1"/>
     <row r="1265" ht="15.75" customHeight="1">
       <c r="E1265" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1266" ht="15.75" customHeight="1"/>
@@ -14779,12 +14750,12 @@
     <row r="1269" ht="15.75" customHeight="1"/>
     <row r="1270" ht="15.75" customHeight="1">
       <c r="E1270" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="1271" ht="15.75" customHeight="1">
       <c r="H1271" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I1271" s="4" t="s">
         <v>26</v>
@@ -14796,7 +14767,7 @@
         <v>27</v>
       </c>
       <c r="N1271" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="T1271" s="4" t="s">
         <v>28</v>
@@ -14816,62 +14787,62 @@
     </row>
     <row r="1272" ht="15.75" customHeight="1">
       <c r="F1272" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="1273" ht="15.75" customHeight="1"/>
     <row r="1274" ht="15.75" customHeight="1">
       <c r="E1274" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1275" ht="15.75" customHeight="1"/>
     <row r="1276" ht="15.75" customHeight="1">
       <c r="D1276" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1277" ht="15.75" customHeight="1"/>
     <row r="1278" ht="15.75" customHeight="1">
       <c r="E1278" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="T1278" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="1279" ht="15.75" customHeight="1"/>
     <row r="1280" ht="15.75" customHeight="1">
       <c r="E1280" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="1281" ht="15.75" customHeight="1">
       <c r="F1281" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1282" ht="15.75" customHeight="1"/>
     <row r="1283" ht="15.75" customHeight="1">
       <c r="E1283" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J1283" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1283" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="1284" ht="15.75" customHeight="1">
       <c r="H1284" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J1284" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1284" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="1285" ht="15.75" customHeight="1">
@@ -14882,7 +14853,7 @@
         <v>15</v>
       </c>
       <c r="K1285" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1286" ht="15.75" customHeight="1">
@@ -14893,51 +14864,51 @@
         <v>15</v>
       </c>
       <c r="K1286" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1287" ht="15.75" customHeight="1">
       <c r="H1287" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J1287" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1287" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1288" ht="15.75" customHeight="1">
       <c r="H1288" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J1288" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1288" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1289" ht="15.75" customHeight="1">
       <c r="H1289" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J1289" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1289" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1290" ht="15.75" customHeight="1">
       <c r="H1290" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J1290" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1290" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1291" ht="15.75" customHeight="1"/>
@@ -14964,12 +14935,12 @@
         <v>20.8</v>
       </c>
       <c r="AC1292" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1293" ht="15.75" customHeight="1">
       <c r="H1293" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I1293" s="4" t="s">
         <v>26</v>
@@ -14978,7 +14949,7 @@
         <v>1</v>
       </c>
       <c r="K1293" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L1293" s="5">
         <v>0.5</v>
@@ -15004,7 +14975,7 @@
     </row>
     <row r="1294" ht="15.75" customHeight="1">
       <c r="G1294" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I1294" s="4" t="s">
         <v>26</v>
@@ -15016,7 +14987,7 @@
         <v>28</v>
       </c>
       <c r="M1294" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U1294" s="4" t="s">
         <v>28</v>
@@ -15037,130 +15008,130 @@
     <row r="1295" ht="15.75" customHeight="1"/>
     <row r="1296" ht="15.75" customHeight="1">
       <c r="E1296" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1297" ht="15.75" customHeight="1">
       <c r="E1297" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="1298" ht="15.75" customHeight="1"/>
     <row r="1299" ht="15.75" customHeight="1">
       <c r="F1299" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1300" ht="15.75" customHeight="1"/>
     <row r="1301" ht="15.75" customHeight="1">
       <c r="E1301" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1302" ht="15.75" customHeight="1"/>
     <row r="1303" ht="15.75" customHeight="1">
       <c r="F1303" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1304" ht="15.75" customHeight="1"/>
     <row r="1305" ht="15.75" customHeight="1">
       <c r="E1305" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="S1305" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1306" ht="15.75" customHeight="1"/>
     <row r="1307" ht="15.75" customHeight="1">
       <c r="E1307" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1308" ht="15.75" customHeight="1">
       <c r="E1308" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1309" ht="15.75" customHeight="1"/>
     <row r="1310" ht="15.75" customHeight="1">
       <c r="F1310" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="1311" ht="15.75" customHeight="1"/>
     <row r="1312" ht="15.75" customHeight="1">
       <c r="F1312" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J1312" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1312" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1313" ht="15.75" customHeight="1">
       <c r="H1313" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J1313" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1313" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1314" ht="15.75" customHeight="1"/>
     <row r="1315" ht="15.75" customHeight="1">
       <c r="F1315" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1316" ht="15.75" customHeight="1">
       <c r="F1316" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1317" ht="15.75" customHeight="1">
       <c r="E1317" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="S1317" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1318" ht="15.75" customHeight="1"/>
     <row r="1319" ht="15.75" customHeight="1">
       <c r="E1319" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1320" ht="15.75" customHeight="1">
       <c r="E1320" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1321" ht="15.75" customHeight="1">
       <c r="E1321" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1322" ht="15.75" customHeight="1"/>
     <row r="1323" ht="15.75" customHeight="1">
       <c r="F1323" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1324" ht="15.75" customHeight="1">
       <c r="F1324" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1325" ht="15.75" customHeight="1">
       <c r="G1325" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I1325" s="4" t="s">
         <v>26</v>
@@ -15178,7 +15149,7 @@
         <v>27</v>
       </c>
       <c r="P1325" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="T1325" s="4" t="s">
         <v>28</v>
@@ -15198,7 +15169,7 @@
     </row>
     <row r="1326" ht="15.75" customHeight="1">
       <c r="H1326" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I1326" s="4" t="s">
         <v>26</v>
@@ -15207,7 +15178,7 @@
         <v>100</v>
       </c>
       <c r="L1326" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M1326" s="6">
         <v>1170</v>
@@ -15225,92 +15196,92 @@
     <row r="1327" ht="15.75" customHeight="1"/>
     <row r="1328" ht="15.75" customHeight="1">
       <c r="D1328" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="S1328" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1329" ht="15.75" customHeight="1"/>
     <row r="1330" ht="15.75" customHeight="1">
       <c r="E1330" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1331" ht="15.75" customHeight="1">
       <c r="E1331" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1332" ht="15.75" customHeight="1">
       <c r="E1332" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1333" ht="15.75" customHeight="1"/>
     <row r="1334" ht="15.75" customHeight="1">
       <c r="F1334" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1335" ht="15.75" customHeight="1"/>
     <row r="1336" ht="15.75" customHeight="1">
       <c r="F1336" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J1336" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1336" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1337" ht="15.75" customHeight="1"/>
     <row r="1338" ht="15.75" customHeight="1">
       <c r="F1338" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1339" ht="15.75" customHeight="1">
       <c r="F1339" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1340" ht="15.75" customHeight="1">
       <c r="F1340" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1341" ht="15.75" customHeight="1"/>
     <row r="1342" ht="15.75" customHeight="1">
       <c r="D1342" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1343" ht="15.75" customHeight="1"/>
     <row r="1344" ht="15.75" customHeight="1">
       <c r="E1344" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="S1344" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1345" ht="15.75" customHeight="1"/>
     <row r="1346" ht="15.75" customHeight="1">
       <c r="E1346" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1347" ht="15.75" customHeight="1">
       <c r="E1347" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1348" ht="15.75" customHeight="1"/>
     <row r="1349" ht="15.75" customHeight="1">
       <c r="L1349" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="R1349" s="4" t="s">
         <v>15</v>
@@ -15321,24 +15292,24 @@
     </row>
     <row r="1350" ht="15.75" customHeight="1">
       <c r="N1350" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R1350" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1350" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1351" ht="15.75" customHeight="1"/>
     <row r="1352" ht="15.75" customHeight="1">
       <c r="E1352" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1353" ht="15.75" customHeight="1">
       <c r="E1353" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1354" ht="15.75" customHeight="1"/>
@@ -15353,36 +15324,36 @@
     <row r="1363" ht="15.75" customHeight="1"/>
     <row r="1364" ht="15.75" customHeight="1">
       <c r="E1364" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="S1364" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1365" ht="15.75" customHeight="1"/>
     <row r="1366" ht="15.75" customHeight="1">
       <c r="E1366" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1367" ht="15.75" customHeight="1">
       <c r="E1367" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1368" ht="15.75" customHeight="1">
       <c r="E1368" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1369" ht="15.75" customHeight="1">
       <c r="E1369" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1370" ht="15.75" customHeight="1">
       <c r="E1370" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F1370" s="8"/>
       <c r="G1370" s="8"/>
@@ -15399,14 +15370,14 @@
       <c r="R1370" s="8"/>
       <c r="S1370" s="8"/>
       <c r="T1370" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="U1370" s="8"/>
       <c r="V1370" s="8"/>
       <c r="W1370" s="8"/>
       <c r="X1370" s="8"/>
       <c r="Y1370" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Z1370" s="8"/>
       <c r="AA1370" s="8"/>
@@ -15416,14 +15387,14 @@
     </row>
     <row r="1371" ht="15.75" customHeight="1">
       <c r="E1371" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F1371" s="12"/>
       <c r="G1371" s="12"/>
       <c r="H1371" s="12"/>
       <c r="I1371" s="12"/>
       <c r="J1371" s="14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K1371" s="12"/>
       <c r="L1371" s="12"/>
@@ -15435,14 +15406,14 @@
       <c r="R1371" s="12"/>
       <c r="S1371" s="12"/>
       <c r="T1371" s="14" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="U1371" s="12"/>
       <c r="V1371" s="12"/>
       <c r="W1371" s="12"/>
       <c r="X1371" s="12"/>
       <c r="Y1371" s="14" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="Z1371" s="12"/>
       <c r="AA1371" s="12"/>
@@ -15453,7 +15424,7 @@
     <row r="1372" ht="15.75" customHeight="1">
       <c r="E1372" s="10"/>
       <c r="J1372" s="14" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K1372" s="12"/>
       <c r="L1372" s="12"/>
@@ -15465,14 +15436,14 @@
       <c r="R1372" s="12"/>
       <c r="S1372" s="12"/>
       <c r="T1372" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="U1372" s="12"/>
       <c r="V1372" s="12"/>
       <c r="W1372" s="12"/>
       <c r="X1372" s="12"/>
       <c r="Y1372" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z1372" s="12"/>
       <c r="AA1372" s="12"/>
@@ -15482,14 +15453,14 @@
     </row>
     <row r="1373" ht="15.75" customHeight="1">
       <c r="E1373" s="23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F1373" s="12"/>
       <c r="G1373" s="12"/>
       <c r="H1373" s="12"/>
       <c r="I1373" s="12"/>
       <c r="J1373" s="14" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K1373" s="12"/>
       <c r="L1373" s="12"/>
@@ -15501,7 +15472,7 @@
       <c r="R1373" s="12"/>
       <c r="S1373" s="12"/>
       <c r="T1373" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="U1373" s="12"/>
       <c r="V1373" s="12"/>
@@ -15543,23 +15514,23 @@
     </row>
     <row r="1375" ht="15.75" customHeight="1">
       <c r="F1375" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1376" ht="15.75" customHeight="1">
       <c r="F1376" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1377" ht="15.75" customHeight="1">
       <c r="F1377" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1378" ht="15.75" customHeight="1"/>
     <row r="1379" ht="15.75" customHeight="1">
       <c r="E1379" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1380" ht="15.75" customHeight="1"/>
@@ -15595,110 +15566,110 @@
     <row r="1410" ht="15.75" customHeight="1"/>
     <row r="1411" ht="15.75" customHeight="1">
       <c r="D1411" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1412" ht="15.75" customHeight="1"/>
     <row r="1413" ht="15.75" customHeight="1">
       <c r="E1413" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="S1413" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="1414" ht="15.75" customHeight="1"/>
     <row r="1415" ht="15.75" customHeight="1">
       <c r="E1415" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1416" ht="15.75" customHeight="1">
       <c r="E1416" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1417" ht="15.75" customHeight="1">
       <c r="E1417" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1418" ht="15.75" customHeight="1"/>
     <row r="1419" ht="15.75" customHeight="1">
       <c r="L1419" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R1419" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1419" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="1420" ht="15.75" customHeight="1">
       <c r="L1420" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="R1420" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1420" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1421" ht="15.75" customHeight="1"/>
     <row r="1422" ht="15.75" customHeight="1">
       <c r="E1422" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1423" ht="15.75" customHeight="1">
       <c r="E1423" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1424" ht="15.75" customHeight="1"/>
     <row r="1425" ht="15.75" customHeight="1">
       <c r="J1425" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R1425" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1425" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1426" ht="15.75" customHeight="1">
       <c r="M1426" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="R1426" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1426" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1427" ht="15.75" customHeight="1"/>
     <row r="1428" ht="15.75" customHeight="1">
       <c r="E1428" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1429" ht="15.75" customHeight="1">
       <c r="E1429" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1430" ht="15.75" customHeight="1">
       <c r="E1430" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1431" ht="15.75" customHeight="1">
       <c r="E1431" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F1431" s="8"/>
       <c r="G1431" s="8"/>
@@ -15706,25 +15677,25 @@
       <c r="I1431" s="8"/>
       <c r="J1431" s="8"/>
       <c r="K1431" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L1431" s="8"/>
       <c r="M1431" s="8"/>
       <c r="N1431" s="8"/>
       <c r="O1431" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P1431" s="8"/>
       <c r="Q1431" s="8"/>
       <c r="R1431" s="8"/>
       <c r="S1431" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="T1431" s="8"/>
       <c r="U1431" s="8"/>
       <c r="V1431" s="8"/>
       <c r="W1431" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="X1431" s="8"/>
       <c r="Y1431" s="8"/>
@@ -15733,7 +15704,7 @@
     </row>
     <row r="1432" ht="15.75" customHeight="1">
       <c r="E1432" s="23" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F1432" s="12"/>
       <c r="G1432" s="12"/>
@@ -15792,87 +15763,87 @@
     </row>
     <row r="1434" ht="15.75" customHeight="1">
       <c r="F1434" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1435" ht="15.75" customHeight="1"/>
     <row r="1436" ht="15.75" customHeight="1">
       <c r="E1436" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1437" ht="15.75" customHeight="1">
       <c r="E1437" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1438" ht="15.75" customHeight="1">
       <c r="E1438" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="1439" ht="15.75" customHeight="1">
       <c r="E1439" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1440" ht="15.75" customHeight="1"/>
     <row r="1441" ht="15.75" customHeight="1">
       <c r="F1441" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1442" ht="15.75" customHeight="1">
       <c r="F1442" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1443" ht="15.75" customHeight="1"/>
     <row r="1444" ht="15.75" customHeight="1">
       <c r="E1444" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1445" ht="15.75" customHeight="1">
       <c r="E1445" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1446" ht="15.75" customHeight="1">
       <c r="E1446" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1447" ht="15.75" customHeight="1">
       <c r="E1447" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1448" ht="15.75" customHeight="1">
       <c r="E1448" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1449" ht="15.75" customHeight="1"/>
     <row r="1450" ht="15.75" customHeight="1">
       <c r="E1450" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1451" ht="15.75" customHeight="1"/>
     <row r="1452" ht="15.75" customHeight="1">
       <c r="E1452" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1453" ht="15.75" customHeight="1">
       <c r="E1453" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1454" ht="15.75" customHeight="1">
       <c r="E1454" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1455" ht="15.75" customHeight="1"/>
@@ -15880,40 +15851,40 @@
     <row r="1457" ht="15.75" customHeight="1"/>
     <row r="1458" ht="15.75" customHeight="1">
       <c r="E1458" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1459" ht="15.75" customHeight="1">
       <c r="E1459" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1460" ht="15.75" customHeight="1">
       <c r="E1460" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1461" ht="15.75" customHeight="1"/>
     <row r="1462" ht="15.75" customHeight="1">
       <c r="F1462" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1463" ht="15.75" customHeight="1">
       <c r="F1463" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="1464" ht="15.75" customHeight="1"/>
     <row r="1465" ht="15.75" customHeight="1">
       <c r="E1465" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J1465" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1465" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="1466" ht="15.75" customHeight="1">
@@ -15921,161 +15892,161 @@
         <v>15</v>
       </c>
       <c r="K1466" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="1467" ht="15.75" customHeight="1">
       <c r="H1467" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J1467" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1467" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="1468" ht="15.75" customHeight="1">
       <c r="H1468" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J1468" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1468" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="1469" ht="15.75" customHeight="1">
       <c r="I1469" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J1469" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1469" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="1470" ht="15.75" customHeight="1">
       <c r="I1470" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J1470" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1470" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="1471" ht="15.75" customHeight="1">
       <c r="H1471" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J1471" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1471" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="1472" ht="15.75" customHeight="1"/>
     <row r="1473" ht="15.75" customHeight="1">
       <c r="F1473" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="1474" ht="15.75" customHeight="1">
       <c r="F1474" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="1475" ht="15.75" customHeight="1">
       <c r="G1475" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="1476" ht="15.75" customHeight="1"/>
     <row r="1477" ht="15.75" customHeight="1">
       <c r="E1477" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="1478" ht="15.75" customHeight="1">
       <c r="E1478" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1479" ht="15.75" customHeight="1"/>
     <row r="1480" ht="15.75" customHeight="1">
       <c r="F1480" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="1481" ht="15.75" customHeight="1">
       <c r="F1481" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1482" ht="15.75" customHeight="1"/>
     <row r="1483" ht="15.75" customHeight="1">
       <c r="F1483" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J1483" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1483" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1484" ht="15.75" customHeight="1">
       <c r="H1484" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J1484" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1484" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1485" ht="15.75" customHeight="1">
       <c r="H1485" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J1485" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1485" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="1486" ht="15.75" customHeight="1"/>
     <row r="1487" ht="15.75" customHeight="1">
       <c r="E1487" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="1488" ht="15.75" customHeight="1">
       <c r="E1488" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1489" ht="15.75" customHeight="1">
       <c r="E1489" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1490" ht="15.75" customHeight="1"/>
     <row r="1491" ht="15.75" customHeight="1">
       <c r="F1491" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1492" ht="15.75" customHeight="1">
       <c r="H1492" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I1492" s="4" t="s">
         <v>26</v>
@@ -16093,13 +16064,13 @@
         <v>28</v>
       </c>
       <c r="N1492" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O1492" s="4" t="s">
         <v>28</v>
       </c>
       <c r="P1492" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Y1492" s="4" t="s">
         <v>26</v>
@@ -16113,12 +16084,12 @@
     </row>
     <row r="1493" ht="15.75" customHeight="1">
       <c r="F1493" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1494" ht="15.75" customHeight="1">
       <c r="H1494" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I1494" s="4" t="s">
         <v>26</v>
@@ -16148,10 +16119,10 @@
         <v>26</v>
       </c>
       <c r="Z1494" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AC1494" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1495" ht="15.75" customHeight="1"/>
@@ -16166,77 +16137,77 @@
     <row r="1504" ht="15.75" customHeight="1"/>
     <row r="1505" ht="15.75" customHeight="1">
       <c r="E1505" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1506" ht="15.75" customHeight="1">
       <c r="E1506" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1507" ht="15.75" customHeight="1">
       <c r="E1507" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1508" ht="15.75" customHeight="1">
       <c r="E1508" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1509" ht="15.75" customHeight="1"/>
     <row r="1510" ht="15.75" customHeight="1">
       <c r="F1510" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1511" ht="15.75" customHeight="1">
       <c r="F1511" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1512" ht="15.75" customHeight="1">
       <c r="F1512" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1513" ht="15.75" customHeight="1">
       <c r="F1513" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1514" ht="15.75" customHeight="1"/>
     <row r="1515" ht="15.75" customHeight="1">
       <c r="F1515" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J1515" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1515" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1516" ht="15.75" customHeight="1">
       <c r="I1516" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J1516" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1516" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1517" ht="15.75" customHeight="1">
       <c r="H1517" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J1517" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1517" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1518" ht="15.75" customHeight="1">
@@ -16244,40 +16215,40 @@
         <v>15</v>
       </c>
       <c r="K1518" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1519" ht="15.75" customHeight="1">
       <c r="I1519" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J1519" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1519" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1520" ht="15.75" customHeight="1">
       <c r="H1520" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J1520" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1520" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1521" ht="15.75" customHeight="1">
       <c r="H1521" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J1521" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1521" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1522" ht="15.75" customHeight="1">
@@ -16285,29 +16256,29 @@
         <v>15</v>
       </c>
       <c r="K1522" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1523" ht="15.75" customHeight="1">
       <c r="H1523" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J1523" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1523" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1524" ht="15.75" customHeight="1">
       <c r="H1524" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J1524" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1524" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="1525" ht="15.75" customHeight="1">
@@ -16315,18 +16286,18 @@
         <v>15</v>
       </c>
       <c r="K1525" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="1526" ht="15.75" customHeight="1">
       <c r="H1526" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J1526" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1526" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="1527" ht="15.75" customHeight="1">
@@ -16334,93 +16305,93 @@
         <v>15</v>
       </c>
       <c r="K1527" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="1528" ht="15.75" customHeight="1">
       <c r="H1528" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J1528" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1528" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1529" ht="15.75" customHeight="1">
       <c r="H1529" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="J1529" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1529" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="1530" ht="15.75" customHeight="1"/>
     <row r="1531" ht="15.75" customHeight="1">
       <c r="E1531" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1532" ht="15.75" customHeight="1">
       <c r="E1532" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="1533" ht="15.75" customHeight="1">
       <c r="E1533" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="1534" ht="15.75" customHeight="1">
       <c r="E1534" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="1535" ht="15.75" customHeight="1">
       <c r="E1535" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="1536" ht="15.75" customHeight="1"/>
     <row r="1537" ht="15.75" customHeight="1">
       <c r="E1537" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1538" ht="15.75" customHeight="1">
       <c r="F1538" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1539" ht="15.75" customHeight="1">
       <c r="F1539" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1540" ht="15.75" customHeight="1"/>
     <row r="1541" ht="15.75" customHeight="1">
       <c r="E1541" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1542" ht="15.75" customHeight="1">
       <c r="F1542" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="1543" ht="15.75" customHeight="1">
       <c r="F1543" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1544" ht="15.75" customHeight="1"/>
     <row r="1545" ht="15.75" customHeight="1">
       <c r="E1545" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1546" ht="15.75" customHeight="1"/>
@@ -16431,18 +16402,18 @@
     <row r="1551" ht="15.75" customHeight="1"/>
     <row r="1552" ht="15.75" customHeight="1">
       <c r="D1552" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1553" ht="15.75" customHeight="1"/>
     <row r="1554" ht="15.75" customHeight="1">
       <c r="B1554" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1555" ht="15.75" customHeight="1">
       <c r="B1555" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1555" s="8"/>
       <c r="D1555" s="8"/>
@@ -16452,7 +16423,7 @@
       <c r="H1555" s="8"/>
       <c r="I1555" s="8"/>
       <c r="J1555" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K1555" s="8"/>
       <c r="L1555" s="8"/>
@@ -16463,7 +16434,7 @@
       <c r="Q1555" s="8"/>
       <c r="R1555" s="8"/>
       <c r="S1555" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="T1555" s="8"/>
       <c r="U1555" s="8"/>
@@ -16471,7 +16442,7 @@
       <c r="W1555" s="8"/>
       <c r="X1555" s="8"/>
       <c r="Y1555" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z1555" s="8"/>
       <c r="AA1555" s="9" t="s">
@@ -16483,7 +16454,7 @@
     </row>
     <row r="1556" ht="15.75" customHeight="1">
       <c r="B1556" s="23" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C1556" s="12"/>
       <c r="D1556" s="12"/>
@@ -16493,7 +16464,7 @@
       <c r="H1556" s="12"/>
       <c r="I1556" s="12"/>
       <c r="J1556" s="14" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K1556" s="12"/>
       <c r="L1556" s="12"/>
@@ -16504,7 +16475,7 @@
       <c r="Q1556" s="12"/>
       <c r="R1556" s="12"/>
       <c r="S1556" s="14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="T1556" s="12"/>
       <c r="U1556" s="12"/>
@@ -16512,11 +16483,11 @@
       <c r="W1556" s="12"/>
       <c r="X1556" s="12"/>
       <c r="Y1556" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1556" s="12"/>
       <c r="AA1556" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1556" s="12"/>
       <c r="AC1556" s="12"/>
@@ -16524,7 +16495,7 @@
     </row>
     <row r="1557" ht="15.75" customHeight="1">
       <c r="B1557" s="23" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C1557" s="12"/>
       <c r="D1557" s="12"/>
@@ -16534,7 +16505,7 @@
       <c r="H1557" s="12"/>
       <c r="I1557" s="12"/>
       <c r="J1557" s="14" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K1557" s="12"/>
       <c r="L1557" s="12"/>
@@ -16553,11 +16524,11 @@
       <c r="W1557" s="12"/>
       <c r="X1557" s="12"/>
       <c r="Y1557" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1557" s="12"/>
       <c r="AA1557" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1557" s="12"/>
       <c r="AC1557" s="12"/>
@@ -16565,7 +16536,7 @@
     </row>
     <row r="1558" ht="15.75" customHeight="1">
       <c r="B1558" s="23" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C1558" s="12"/>
       <c r="D1558" s="12"/>
@@ -16575,7 +16546,7 @@
       <c r="H1558" s="12"/>
       <c r="I1558" s="12"/>
       <c r="J1558" s="14" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K1558" s="12"/>
       <c r="L1558" s="12"/>
@@ -16586,7 +16557,7 @@
       <c r="Q1558" s="12"/>
       <c r="R1558" s="12"/>
       <c r="S1558" s="14" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="T1558" s="12"/>
       <c r="U1558" s="12"/>
@@ -16594,11 +16565,11 @@
       <c r="W1558" s="12"/>
       <c r="X1558" s="12"/>
       <c r="Y1558" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1558" s="12"/>
       <c r="AA1558" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1558" s="12"/>
       <c r="AC1558" s="12"/>
@@ -16606,7 +16577,7 @@
     </row>
     <row r="1559" ht="15.75" customHeight="1">
       <c r="B1559" s="23" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C1559" s="12"/>
       <c r="D1559" s="12"/>
@@ -16616,7 +16587,7 @@
       <c r="H1559" s="12"/>
       <c r="I1559" s="12"/>
       <c r="J1559" s="14" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K1559" s="12"/>
       <c r="L1559" s="12"/>
@@ -16627,7 +16598,7 @@
       <c r="Q1559" s="12"/>
       <c r="R1559" s="12"/>
       <c r="S1559" s="14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="T1559" s="12"/>
       <c r="U1559" s="12"/>
@@ -16635,11 +16606,11 @@
       <c r="W1559" s="12"/>
       <c r="X1559" s="12"/>
       <c r="Y1559" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1559" s="12"/>
       <c r="AA1559" s="14" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AB1559" s="12"/>
       <c r="AC1559" s="12"/>
@@ -16647,7 +16618,7 @@
     </row>
     <row r="1560" ht="15.75" customHeight="1">
       <c r="B1560" s="23" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C1560" s="12"/>
       <c r="D1560" s="12"/>
@@ -16657,7 +16628,7 @@
       <c r="H1560" s="12"/>
       <c r="I1560" s="12"/>
       <c r="J1560" s="14" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="K1560" s="12"/>
       <c r="L1560" s="12"/>
@@ -16668,7 +16639,7 @@
       <c r="Q1560" s="12"/>
       <c r="R1560" s="12"/>
       <c r="S1560" s="14" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="T1560" s="12"/>
       <c r="U1560" s="12"/>
@@ -16676,11 +16647,11 @@
       <c r="W1560" s="12"/>
       <c r="X1560" s="12"/>
       <c r="Y1560" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1560" s="12"/>
       <c r="AA1560" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1560" s="12"/>
       <c r="AC1560" s="12"/>
@@ -16688,7 +16659,7 @@
     </row>
     <row r="1561" ht="15.75" customHeight="1">
       <c r="B1561" s="23" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C1561" s="12"/>
       <c r="D1561" s="12"/>
@@ -16698,7 +16669,7 @@
       <c r="H1561" s="12"/>
       <c r="I1561" s="12"/>
       <c r="J1561" s="14" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K1561" s="12"/>
       <c r="L1561" s="12"/>
@@ -16709,7 +16680,7 @@
       <c r="Q1561" s="12"/>
       <c r="R1561" s="12"/>
       <c r="S1561" s="14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="T1561" s="12"/>
       <c r="U1561" s="12"/>
@@ -16717,7 +16688,7 @@
       <c r="W1561" s="12"/>
       <c r="X1561" s="12"/>
       <c r="Y1561" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1561" s="12"/>
       <c r="AA1561" s="29"/>
@@ -16727,7 +16698,7 @@
     </row>
     <row r="1562" ht="15.75" customHeight="1">
       <c r="B1562" s="23" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C1562" s="12"/>
       <c r="D1562" s="12"/>
@@ -16737,7 +16708,7 @@
       <c r="H1562" s="12"/>
       <c r="I1562" s="12"/>
       <c r="J1562" s="14" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="K1562" s="12"/>
       <c r="L1562" s="12"/>
@@ -16748,7 +16719,7 @@
       <c r="Q1562" s="12"/>
       <c r="R1562" s="12"/>
       <c r="S1562" s="14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="T1562" s="12"/>
       <c r="U1562" s="12"/>
@@ -16756,7 +16727,7 @@
       <c r="W1562" s="12"/>
       <c r="X1562" s="12"/>
       <c r="Y1562" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1562" s="12"/>
       <c r="AA1562" s="29"/>
@@ -16766,7 +16737,7 @@
     </row>
     <row r="1563" ht="15.75" customHeight="1">
       <c r="B1563" s="23" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C1563" s="12"/>
       <c r="D1563" s="12"/>
@@ -16776,7 +16747,7 @@
       <c r="H1563" s="12"/>
       <c r="I1563" s="12"/>
       <c r="J1563" s="14" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="K1563" s="12"/>
       <c r="L1563" s="12"/>
@@ -16787,7 +16758,7 @@
       <c r="Q1563" s="12"/>
       <c r="R1563" s="12"/>
       <c r="S1563" s="14" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="T1563" s="12"/>
       <c r="U1563" s="12"/>
@@ -16795,11 +16766,11 @@
       <c r="W1563" s="12"/>
       <c r="X1563" s="12"/>
       <c r="Y1563" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1563" s="12"/>
       <c r="AA1563" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1563" s="12"/>
       <c r="AC1563" s="12"/>
@@ -16807,7 +16778,7 @@
     </row>
     <row r="1564" ht="15.75" customHeight="1">
       <c r="B1564" s="23" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C1564" s="12"/>
       <c r="D1564" s="12"/>
@@ -16817,7 +16788,7 @@
       <c r="H1564" s="12"/>
       <c r="I1564" s="12"/>
       <c r="J1564" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="K1564" s="12"/>
       <c r="L1564" s="12"/>
@@ -16828,7 +16799,7 @@
       <c r="Q1564" s="12"/>
       <c r="R1564" s="12"/>
       <c r="S1564" s="14" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="T1564" s="12"/>
       <c r="U1564" s="12"/>
@@ -16836,11 +16807,11 @@
       <c r="W1564" s="12"/>
       <c r="X1564" s="12"/>
       <c r="Y1564" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1564" s="12"/>
       <c r="AA1564" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1564" s="12"/>
       <c r="AC1564" s="12"/>
@@ -16848,7 +16819,7 @@
     </row>
     <row r="1565" ht="15.75" customHeight="1">
       <c r="B1565" s="23" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C1565" s="12"/>
       <c r="D1565" s="12"/>
@@ -16858,7 +16829,7 @@
       <c r="H1565" s="12"/>
       <c r="I1565" s="12"/>
       <c r="J1565" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K1565" s="12"/>
       <c r="L1565" s="12"/>
@@ -16877,11 +16848,11 @@
       <c r="W1565" s="12"/>
       <c r="X1565" s="12"/>
       <c r="Y1565" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1565" s="12"/>
       <c r="AA1565" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1565" s="12"/>
       <c r="AC1565" s="12"/>
@@ -16889,7 +16860,7 @@
     </row>
     <row r="1566" ht="15.75" customHeight="1">
       <c r="B1566" s="11" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C1566" s="12"/>
       <c r="D1566" s="12"/>
@@ -16899,7 +16870,7 @@
       <c r="H1566" s="12"/>
       <c r="I1566" s="12"/>
       <c r="J1566" s="14" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="K1566" s="12"/>
       <c r="L1566" s="12"/>
@@ -16910,7 +16881,7 @@
       <c r="Q1566" s="12"/>
       <c r="R1566" s="12"/>
       <c r="S1566" s="14" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="T1566" s="12"/>
       <c r="U1566" s="12"/>
@@ -16918,11 +16889,11 @@
       <c r="W1566" s="12"/>
       <c r="X1566" s="12"/>
       <c r="Y1566" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1566" s="12"/>
       <c r="AA1566" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1566" s="12"/>
       <c r="AC1566" s="12"/>
@@ -16931,7 +16902,7 @@
     <row r="1567" ht="15.75" customHeight="1">
       <c r="B1567" s="10"/>
       <c r="J1567" s="30" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="S1567" s="15"/>
       <c r="Y1567" s="15"/>
@@ -16941,7 +16912,7 @@
     <row r="1568" ht="15.75" customHeight="1">
       <c r="B1568" s="10"/>
       <c r="J1568" s="14" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="K1568" s="12"/>
       <c r="L1568" s="12"/>
@@ -16952,7 +16923,7 @@
       <c r="Q1568" s="12"/>
       <c r="R1568" s="12"/>
       <c r="S1568" s="14" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="T1568" s="12"/>
       <c r="U1568" s="12"/>
@@ -16960,7 +16931,7 @@
       <c r="W1568" s="12"/>
       <c r="X1568" s="12"/>
       <c r="Y1568" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1568" s="12"/>
       <c r="AA1568" s="15"/>
@@ -16969,7 +16940,7 @@
     <row r="1569" ht="15.75" customHeight="1">
       <c r="B1569" s="10"/>
       <c r="J1569" s="14" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K1569" s="12"/>
       <c r="L1569" s="12"/>
@@ -16980,7 +16951,7 @@
       <c r="Q1569" s="12"/>
       <c r="R1569" s="12"/>
       <c r="S1569" s="14" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="T1569" s="12"/>
       <c r="U1569" s="12"/>
@@ -16988,7 +16959,7 @@
       <c r="W1569" s="12"/>
       <c r="X1569" s="12"/>
       <c r="Y1569" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1569" s="12"/>
       <c r="AA1569" s="15"/>
@@ -16996,7 +16967,7 @@
     </row>
     <row r="1570" ht="15.75" customHeight="1">
       <c r="B1570" s="23" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C1570" s="12"/>
       <c r="D1570" s="12"/>
@@ -17006,7 +16977,7 @@
       <c r="H1570" s="12"/>
       <c r="I1570" s="12"/>
       <c r="J1570" s="14" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="K1570" s="12"/>
       <c r="L1570" s="12"/>
@@ -17017,7 +16988,7 @@
       <c r="Q1570" s="12"/>
       <c r="R1570" s="12"/>
       <c r="S1570" s="14" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="T1570" s="12"/>
       <c r="U1570" s="12"/>
@@ -17025,11 +16996,11 @@
       <c r="W1570" s="12"/>
       <c r="X1570" s="12"/>
       <c r="Y1570" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1570" s="12"/>
       <c r="AA1570" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1570" s="12"/>
       <c r="AC1570" s="12"/>
@@ -17037,7 +17008,7 @@
     </row>
     <row r="1571" ht="15.75" customHeight="1">
       <c r="B1571" s="23" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C1571" s="12"/>
       <c r="D1571" s="12"/>
@@ -17047,7 +17018,7 @@
       <c r="H1571" s="12"/>
       <c r="I1571" s="12"/>
       <c r="J1571" s="14" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="K1571" s="12"/>
       <c r="L1571" s="12"/>
@@ -17058,7 +17029,7 @@
       <c r="Q1571" s="12"/>
       <c r="R1571" s="12"/>
       <c r="S1571" s="14" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T1571" s="12"/>
       <c r="U1571" s="12"/>
@@ -17066,11 +17037,11 @@
       <c r="W1571" s="12"/>
       <c r="X1571" s="12"/>
       <c r="Y1571" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1571" s="12"/>
       <c r="AA1571" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1571" s="12"/>
       <c r="AC1571" s="12"/>
@@ -17078,7 +17049,7 @@
     </row>
     <row r="1572" ht="15.75" customHeight="1">
       <c r="B1572" s="23" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C1572" s="12"/>
       <c r="D1572" s="12"/>
@@ -17088,7 +17059,7 @@
       <c r="H1572" s="12"/>
       <c r="I1572" s="12"/>
       <c r="J1572" s="14" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K1572" s="12"/>
       <c r="L1572" s="12"/>
@@ -17099,7 +17070,7 @@
       <c r="Q1572" s="12"/>
       <c r="R1572" s="12"/>
       <c r="S1572" s="14" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="T1572" s="12"/>
       <c r="U1572" s="12"/>
@@ -17107,11 +17078,11 @@
       <c r="W1572" s="12"/>
       <c r="X1572" s="12"/>
       <c r="Y1572" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1572" s="12"/>
       <c r="AA1572" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1572" s="12"/>
       <c r="AC1572" s="12"/>
@@ -17119,7 +17090,7 @@
     </row>
     <row r="1573" ht="15.75" customHeight="1">
       <c r="B1573" s="23" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C1573" s="12"/>
       <c r="D1573" s="12"/>
@@ -17129,7 +17100,7 @@
       <c r="H1573" s="12"/>
       <c r="I1573" s="12"/>
       <c r="J1573" s="14" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="K1573" s="12"/>
       <c r="L1573" s="12"/>
@@ -17140,7 +17111,7 @@
       <c r="Q1573" s="12"/>
       <c r="R1573" s="12"/>
       <c r="S1573" s="14" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="T1573" s="12"/>
       <c r="U1573" s="12"/>
@@ -17148,11 +17119,11 @@
       <c r="W1573" s="12"/>
       <c r="X1573" s="12"/>
       <c r="Y1573" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1573" s="12"/>
       <c r="AA1573" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1573" s="12"/>
       <c r="AC1573" s="12"/>
@@ -17160,7 +17131,7 @@
     </row>
     <row r="1574" ht="15.75" customHeight="1">
       <c r="B1574" s="11" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C1574" s="12"/>
       <c r="D1574" s="12"/>
@@ -17170,7 +17141,7 @@
       <c r="H1574" s="12"/>
       <c r="I1574" s="12"/>
       <c r="J1574" s="14" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="K1574" s="12"/>
       <c r="L1574" s="12"/>
@@ -17181,7 +17152,7 @@
       <c r="Q1574" s="12"/>
       <c r="R1574" s="12"/>
       <c r="S1574" s="14" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="T1574" s="12"/>
       <c r="U1574" s="12"/>
@@ -17189,11 +17160,11 @@
       <c r="W1574" s="12"/>
       <c r="X1574" s="12"/>
       <c r="Y1574" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1574" s="12"/>
       <c r="AA1574" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1574" s="12"/>
       <c r="AC1574" s="12"/>
@@ -17202,7 +17173,7 @@
     <row r="1575" ht="15.75" customHeight="1">
       <c r="B1575" s="10"/>
       <c r="J1575" s="14" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="K1575" s="12"/>
       <c r="L1575" s="12"/>
@@ -17213,7 +17184,7 @@
       <c r="Q1575" s="12"/>
       <c r="R1575" s="12"/>
       <c r="S1575" s="14" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="T1575" s="12"/>
       <c r="U1575" s="12"/>
@@ -17221,7 +17192,7 @@
       <c r="W1575" s="12"/>
       <c r="X1575" s="12"/>
       <c r="Y1575" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1575" s="12"/>
       <c r="AA1575" s="15"/>
@@ -17229,7 +17200,7 @@
     </row>
     <row r="1576" ht="15.75" customHeight="1">
       <c r="B1576" s="23" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C1576" s="12"/>
       <c r="D1576" s="12"/>
@@ -17239,7 +17210,7 @@
       <c r="H1576" s="12"/>
       <c r="I1576" s="12"/>
       <c r="J1576" s="14" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="K1576" s="12"/>
       <c r="L1576" s="12"/>
@@ -17250,7 +17221,7 @@
       <c r="Q1576" s="12"/>
       <c r="R1576" s="12"/>
       <c r="S1576" s="14" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="T1576" s="12"/>
       <c r="U1576" s="12"/>
@@ -17258,11 +17229,11 @@
       <c r="W1576" s="12"/>
       <c r="X1576" s="12"/>
       <c r="Y1576" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1576" s="12"/>
       <c r="AA1576" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1576" s="12"/>
       <c r="AC1576" s="12"/>
@@ -17270,7 +17241,7 @@
     </row>
     <row r="1577" ht="15.75" customHeight="1">
       <c r="B1577" s="23" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C1577" s="12"/>
       <c r="D1577" s="12"/>
@@ -17280,7 +17251,7 @@
       <c r="H1577" s="12"/>
       <c r="I1577" s="12"/>
       <c r="J1577" s="14" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K1577" s="12"/>
       <c r="L1577" s="12"/>
@@ -17291,7 +17262,7 @@
       <c r="Q1577" s="12"/>
       <c r="R1577" s="12"/>
       <c r="S1577" s="14" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="T1577" s="12"/>
       <c r="U1577" s="12"/>
@@ -17299,11 +17270,11 @@
       <c r="W1577" s="12"/>
       <c r="X1577" s="12"/>
       <c r="Y1577" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1577" s="12"/>
       <c r="AA1577" s="14" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AB1577" s="12"/>
       <c r="AC1577" s="12"/>
@@ -17311,11 +17282,11 @@
     </row>
     <row r="1578" ht="15.75" customHeight="1">
       <c r="B1578" s="31" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="J1578" s="15"/>
       <c r="S1578" s="30" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Y1578" s="15"/>
       <c r="AA1578" s="15"/>
@@ -17354,33 +17325,33 @@
     </row>
     <row r="1580" ht="15.75" customHeight="1">
       <c r="C1580" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="1581" ht="15.75" customHeight="1"/>
     <row r="1582" ht="15.75" customHeight="1">
       <c r="D1582" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="1583" ht="15.75" customHeight="1"/>
     <row r="1584" ht="15.75" customHeight="1">
       <c r="E1584" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="T1584" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="1585" ht="15.75" customHeight="1"/>
     <row r="1586" ht="15.75" customHeight="1">
       <c r="E1586" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1587" ht="15.75" customHeight="1">
       <c r="E1587" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1588" ht="15.75" customHeight="1"/>
@@ -17396,92 +17367,92 @@
     <row r="1598" ht="15.75" customHeight="1"/>
     <row r="1599" ht="15.75" customHeight="1">
       <c r="E1599" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="1600" ht="15.75" customHeight="1">
       <c r="F1600" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="1601" ht="15.75" customHeight="1"/>
     <row r="1602" ht="15.75" customHeight="1">
       <c r="F1602" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J1602" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1602" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1603" ht="15.75" customHeight="1">
       <c r="H1603" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J1603" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1603" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1604" ht="15.75" customHeight="1">
       <c r="H1604" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="J1604" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1604" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1605" ht="15.75" customHeight="1">
       <c r="H1605" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="J1605" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1605" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1606" ht="15.75" customHeight="1"/>
     <row r="1607" ht="15.75" customHeight="1">
       <c r="E1607" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1608" ht="15.75" customHeight="1">
       <c r="E1608" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1609" ht="15.75" customHeight="1">
       <c r="E1609" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1610" ht="15.75" customHeight="1">
       <c r="E1610" s="7" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F1610" s="8"/>
       <c r="G1610" s="8"/>
       <c r="H1610" s="8"/>
       <c r="I1610" s="8"/>
       <c r="J1610" s="9" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="K1610" s="8"/>
       <c r="L1610" s="8"/>
       <c r="M1610" s="8"/>
       <c r="N1610" s="8"/>
       <c r="O1610" s="9" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="P1610" s="8"/>
       <c r="Q1610" s="8"/>
@@ -17498,14 +17469,14 @@
     </row>
     <row r="1611" ht="15.75" customHeight="1">
       <c r="E1611" s="11" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F1611" s="12"/>
       <c r="G1611" s="12"/>
       <c r="H1611" s="12"/>
       <c r="I1611" s="12"/>
       <c r="J1611" s="14" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="K1611" s="12"/>
       <c r="L1611" s="12"/>
@@ -17530,7 +17501,7 @@
     <row r="1612" ht="15.75" customHeight="1">
       <c r="E1612" s="10"/>
       <c r="J1612" s="14" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="K1612" s="12"/>
       <c r="L1612" s="12"/>
@@ -17578,183 +17549,183 @@
     </row>
     <row r="1614" ht="15.75" customHeight="1">
       <c r="E1614" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="T1614" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="1615" ht="15.75" customHeight="1"/>
     <row r="1616" ht="15.75" customHeight="1">
       <c r="E1616" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1617" ht="15.75" customHeight="1">
       <c r="E1617" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1618" ht="15.75" customHeight="1"/>
     <row r="1619" ht="15.75" customHeight="1">
       <c r="E1619" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1620" ht="15.75" customHeight="1">
       <c r="F1620" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1621" ht="15.75" customHeight="1">
       <c r="F1621" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1622" ht="15.75" customHeight="1"/>
     <row r="1623" ht="15.75" customHeight="1">
       <c r="F1623" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J1623" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1623" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1624" ht="15.75" customHeight="1">
       <c r="H1624" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J1624" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1624" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="1625" ht="15.75" customHeight="1">
       <c r="H1625" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="J1625" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1625" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="1626" ht="15.75" customHeight="1">
       <c r="H1626" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J1626" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1626" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1627" ht="15.75" customHeight="1">
       <c r="H1627" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J1627" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1627" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1628" ht="15.75" customHeight="1">
       <c r="H1628" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J1628" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1628" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="1629" ht="15.75" customHeight="1">
       <c r="H1629" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J1629" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1629" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="1630" ht="15.75" customHeight="1">
       <c r="H1630" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J1630" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1630" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1631" ht="15.75" customHeight="1">
       <c r="H1631" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J1631" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1631" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="1632" ht="15.75" customHeight="1">
       <c r="H1632" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="J1632" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1632" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1633" ht="15.75" customHeight="1"/>
     <row r="1634" ht="15.75" customHeight="1">
       <c r="E1634" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1635" ht="15.75" customHeight="1">
       <c r="E1635" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1636" ht="15.75" customHeight="1">
       <c r="E1636" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="1637" ht="15.75" customHeight="1">
       <c r="E1637" s="7" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F1637" s="8"/>
       <c r="G1637" s="8"/>
       <c r="H1637" s="8"/>
       <c r="I1637" s="8"/>
       <c r="J1637" s="9" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="K1637" s="8"/>
       <c r="L1637" s="8"/>
       <c r="M1637" s="8"/>
       <c r="N1637" s="8"/>
       <c r="O1637" s="9" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="P1637" s="8"/>
       <c r="Q1637" s="8"/>
@@ -17771,14 +17742,14 @@
     </row>
     <row r="1638" ht="15.75" customHeight="1">
       <c r="E1638" s="23" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F1638" s="12"/>
       <c r="G1638" s="12"/>
       <c r="H1638" s="12"/>
       <c r="I1638" s="12"/>
       <c r="J1638" s="14" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K1638" s="12"/>
       <c r="L1638" s="12"/>
@@ -17826,43 +17797,43 @@
     </row>
     <row r="1640" ht="15.75" customHeight="1">
       <c r="D1640" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="S1640" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="1641" ht="15.75" customHeight="1"/>
     <row r="1642" ht="15.75" customHeight="1">
       <c r="E1642" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="1643" ht="15.75" customHeight="1">
       <c r="E1643" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="1644" ht="15.75" customHeight="1">
       <c r="E1644" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1645" ht="15.75" customHeight="1"/>
     <row r="1646" ht="15.75" customHeight="1">
       <c r="D1646" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="1647" ht="15.75" customHeight="1"/>
     <row r="1648" ht="15.75" customHeight="1">
       <c r="B1648" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="1649" ht="15.75" customHeight="1">
       <c r="B1649" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1649" s="8"/>
       <c r="D1649" s="8"/>
@@ -17873,7 +17844,7 @@
       <c r="I1649" s="8"/>
       <c r="J1649" s="8"/>
       <c r="K1649" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L1649" s="8"/>
       <c r="M1649" s="8"/>
@@ -17882,7 +17853,7 @@
       <c r="P1649" s="8"/>
       <c r="Q1649" s="8"/>
       <c r="R1649" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S1649" s="8"/>
       <c r="T1649" s="8"/>
@@ -17891,7 +17862,7 @@
       <c r="W1649" s="8"/>
       <c r="X1649" s="8"/>
       <c r="Y1649" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z1649" s="8"/>
       <c r="AA1649" s="9" t="s">
@@ -17903,12 +17874,12 @@
     </row>
     <row r="1650" ht="15.75" customHeight="1">
       <c r="B1650" s="11" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C1650" s="12"/>
       <c r="D1650" s="12"/>
       <c r="E1650" s="14" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F1650" s="12"/>
       <c r="G1650" s="12"/>
@@ -17916,7 +17887,7 @@
       <c r="I1650" s="12"/>
       <c r="J1650" s="12"/>
       <c r="K1650" s="14" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="L1650" s="12"/>
       <c r="M1650" s="12"/>
@@ -17925,7 +17896,7 @@
       <c r="P1650" s="12"/>
       <c r="Q1650" s="12"/>
       <c r="R1650" s="14" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="S1650" s="12"/>
       <c r="T1650" s="12"/>
@@ -17934,11 +17905,11 @@
       <c r="W1650" s="12"/>
       <c r="X1650" s="12"/>
       <c r="Y1650" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1650" s="12"/>
       <c r="AA1650" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1650" s="12"/>
       <c r="AC1650" s="12"/>
@@ -17946,10 +17917,10 @@
     </row>
     <row r="1651" ht="15.75" customHeight="1">
       <c r="B1651" s="33" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E1651" s="14" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F1651" s="12"/>
       <c r="G1651" s="12"/>
@@ -17957,7 +17928,7 @@
       <c r="I1651" s="12"/>
       <c r="J1651" s="12"/>
       <c r="K1651" s="14" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="L1651" s="12"/>
       <c r="M1651" s="12"/>
@@ -17966,7 +17937,7 @@
       <c r="P1651" s="12"/>
       <c r="Q1651" s="12"/>
       <c r="R1651" s="14" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="S1651" s="12"/>
       <c r="T1651" s="12"/>
@@ -17975,7 +17946,7 @@
       <c r="W1651" s="12"/>
       <c r="X1651" s="12"/>
       <c r="Y1651" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1651" s="12"/>
       <c r="AA1651" s="15"/>
@@ -17983,10 +17954,10 @@
     </row>
     <row r="1652" ht="15.75" customHeight="1">
       <c r="B1652" s="33" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E1652" s="14" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F1652" s="12"/>
       <c r="G1652" s="12"/>
@@ -17994,7 +17965,7 @@
       <c r="I1652" s="12"/>
       <c r="J1652" s="12"/>
       <c r="K1652" s="14" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="L1652" s="12"/>
       <c r="M1652" s="12"/>
@@ -18003,7 +17974,7 @@
       <c r="P1652" s="12"/>
       <c r="Q1652" s="12"/>
       <c r="R1652" s="14" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="S1652" s="12"/>
       <c r="T1652" s="12"/>
@@ -18012,7 +17983,7 @@
       <c r="W1652" s="12"/>
       <c r="X1652" s="12"/>
       <c r="Y1652" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1652" s="12"/>
       <c r="AA1652" s="15"/>
@@ -18020,7 +17991,7 @@
     </row>
     <row r="1653" ht="15.75" customHeight="1">
       <c r="B1653" s="11" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C1653" s="12"/>
       <c r="D1653" s="12"/>
@@ -18031,7 +18002,7 @@
       <c r="I1653" s="12"/>
       <c r="J1653" s="12"/>
       <c r="K1653" s="14" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="L1653" s="12"/>
       <c r="M1653" s="12"/>
@@ -18040,7 +18011,7 @@
       <c r="P1653" s="12"/>
       <c r="Q1653" s="12"/>
       <c r="R1653" s="14" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="S1653" s="12"/>
       <c r="T1653" s="12"/>
@@ -18049,11 +18020,11 @@
       <c r="W1653" s="12"/>
       <c r="X1653" s="12"/>
       <c r="Y1653" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z1653" s="12"/>
       <c r="AA1653" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB1653" s="12"/>
       <c r="AC1653" s="12"/>
@@ -18063,7 +18034,7 @@
       <c r="B1654" s="10"/>
       <c r="K1654" s="15"/>
       <c r="R1654" s="30" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="Y1654" s="15"/>
       <c r="AA1654" s="15"/>
@@ -18138,7 +18109,7 @@
     <row r="1691" ht="15.75" customHeight="1"/>
     <row r="1692" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1534">
+  <mergeCells count="1526">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="C5:E5"/>
@@ -18678,18 +18649,15 @@
     <mergeCell ref="E731:X731"/>
     <mergeCell ref="E733:AD733"/>
     <mergeCell ref="E734:AB734"/>
-    <mergeCell ref="E735:AD735"/>
-    <mergeCell ref="E736:J736"/>
-    <mergeCell ref="E738:R738"/>
-    <mergeCell ref="E740:AC740"/>
-    <mergeCell ref="E741:X741"/>
-    <mergeCell ref="E742:AD742"/>
-    <mergeCell ref="E743:J743"/>
-    <mergeCell ref="D745:M745"/>
-    <mergeCell ref="S745:Z745"/>
-    <mergeCell ref="E747:AD747"/>
-    <mergeCell ref="E748:AD748"/>
-    <mergeCell ref="E749:J749"/>
+    <mergeCell ref="E735:T735"/>
+    <mergeCell ref="E737:R737"/>
+    <mergeCell ref="E739:AC739"/>
+    <mergeCell ref="E740:X740"/>
+    <mergeCell ref="E741:T741"/>
+    <mergeCell ref="D743:M743"/>
+    <mergeCell ref="S743:Z743"/>
+    <mergeCell ref="E745:AD745"/>
+    <mergeCell ref="E746:T746"/>
     <mergeCell ref="D753:Q753"/>
     <mergeCell ref="S753:Z753"/>
     <mergeCell ref="E755:AD755"/>
@@ -18704,40 +18672,39 @@
     <mergeCell ref="E764:AD764"/>
     <mergeCell ref="E765:AD765"/>
     <mergeCell ref="E766:W766"/>
-    <mergeCell ref="E767:AD767"/>
-    <mergeCell ref="E768:F768"/>
-    <mergeCell ref="D770:H770"/>
-    <mergeCell ref="S770:Z770"/>
+    <mergeCell ref="E767:P767"/>
+    <mergeCell ref="D769:H769"/>
+    <mergeCell ref="S769:Z769"/>
+    <mergeCell ref="E771:AD771"/>
     <mergeCell ref="E772:AD772"/>
-    <mergeCell ref="E773:AD773"/>
-    <mergeCell ref="E774:M774"/>
-    <mergeCell ref="J776:Q776"/>
-    <mergeCell ref="S776:U776"/>
-    <mergeCell ref="M777:Q777"/>
-    <mergeCell ref="S777:T777"/>
+    <mergeCell ref="E773:M773"/>
+    <mergeCell ref="J775:Q775"/>
+    <mergeCell ref="S775:U775"/>
+    <mergeCell ref="M776:Q776"/>
+    <mergeCell ref="S776:T776"/>
+    <mergeCell ref="J777:Q777"/>
+    <mergeCell ref="S777:Z777"/>
     <mergeCell ref="J778:Q778"/>
-    <mergeCell ref="S778:Z778"/>
-    <mergeCell ref="J779:Q779"/>
-    <mergeCell ref="S779:U779"/>
-    <mergeCell ref="M780:Q780"/>
-    <mergeCell ref="S780:T780"/>
-    <mergeCell ref="J781:Q781"/>
-    <mergeCell ref="S781:Z781"/>
-    <mergeCell ref="E783:I783"/>
-    <mergeCell ref="E784:K784"/>
-    <mergeCell ref="L784:S784"/>
+    <mergeCell ref="S778:U778"/>
+    <mergeCell ref="M779:Q779"/>
+    <mergeCell ref="S779:T779"/>
+    <mergeCell ref="J780:Q780"/>
+    <mergeCell ref="S780:Z780"/>
+    <mergeCell ref="E782:I782"/>
+    <mergeCell ref="E783:K783"/>
+    <mergeCell ref="L783:S783"/>
+    <mergeCell ref="T783:AC783"/>
+    <mergeCell ref="E784:K786"/>
+    <mergeCell ref="L784:S786"/>
     <mergeCell ref="T784:AC784"/>
-    <mergeCell ref="E785:K787"/>
-    <mergeCell ref="L785:S787"/>
     <mergeCell ref="T785:AC785"/>
     <mergeCell ref="T786:AC786"/>
+    <mergeCell ref="E787:K789"/>
+    <mergeCell ref="L787:S789"/>
     <mergeCell ref="T787:AC787"/>
-    <mergeCell ref="E788:K790"/>
-    <mergeCell ref="L788:S790"/>
     <mergeCell ref="T788:AC788"/>
     <mergeCell ref="T789:AC789"/>
-    <mergeCell ref="T790:AC790"/>
-    <mergeCell ref="E792:T792"/>
+    <mergeCell ref="E791:T791"/>
     <mergeCell ref="D800:M800"/>
     <mergeCell ref="O800:AB800"/>
     <mergeCell ref="E802:AD802"/>
@@ -18864,18 +18831,15 @@
     <mergeCell ref="E917:X917"/>
     <mergeCell ref="E919:AD919"/>
     <mergeCell ref="E920:AB920"/>
-    <mergeCell ref="E921:AD921"/>
-    <mergeCell ref="E922:J922"/>
-    <mergeCell ref="E924:R924"/>
-    <mergeCell ref="E926:AC926"/>
-    <mergeCell ref="E927:X927"/>
-    <mergeCell ref="E928:AD928"/>
-    <mergeCell ref="E929:J929"/>
-    <mergeCell ref="D931:M931"/>
-    <mergeCell ref="S931:Z931"/>
-    <mergeCell ref="E933:AD933"/>
-    <mergeCell ref="E934:AD934"/>
-    <mergeCell ref="E935:J935"/>
+    <mergeCell ref="E921:T921"/>
+    <mergeCell ref="E923:R923"/>
+    <mergeCell ref="E925:AC925"/>
+    <mergeCell ref="E926:X926"/>
+    <mergeCell ref="E927:T927"/>
+    <mergeCell ref="D929:M929"/>
+    <mergeCell ref="S929:Z929"/>
+    <mergeCell ref="E931:AD931"/>
+    <mergeCell ref="E932:T932"/>
     <mergeCell ref="D941:Q941"/>
     <mergeCell ref="S941:Z941"/>
     <mergeCell ref="E943:AD943"/>
@@ -18890,40 +18854,39 @@
     <mergeCell ref="E952:AD952"/>
     <mergeCell ref="E953:AD953"/>
     <mergeCell ref="E954:W954"/>
-    <mergeCell ref="E955:AD955"/>
-    <mergeCell ref="E956:F956"/>
-    <mergeCell ref="D958:H958"/>
-    <mergeCell ref="S958:Z958"/>
+    <mergeCell ref="E955:P955"/>
+    <mergeCell ref="D957:H957"/>
+    <mergeCell ref="S957:Z957"/>
+    <mergeCell ref="E959:AD959"/>
     <mergeCell ref="E960:AD960"/>
-    <mergeCell ref="E961:AD961"/>
-    <mergeCell ref="E962:M962"/>
-    <mergeCell ref="J964:Q964"/>
-    <mergeCell ref="S964:U964"/>
-    <mergeCell ref="M965:Q965"/>
-    <mergeCell ref="S965:T965"/>
+    <mergeCell ref="E961:M961"/>
+    <mergeCell ref="J963:Q963"/>
+    <mergeCell ref="S963:U963"/>
+    <mergeCell ref="M964:Q964"/>
+    <mergeCell ref="S964:T964"/>
+    <mergeCell ref="J965:Q965"/>
+    <mergeCell ref="S965:Z965"/>
     <mergeCell ref="J966:Q966"/>
-    <mergeCell ref="S966:Z966"/>
-    <mergeCell ref="J967:Q967"/>
-    <mergeCell ref="S967:U967"/>
-    <mergeCell ref="M968:Q968"/>
-    <mergeCell ref="S968:T968"/>
-    <mergeCell ref="J969:Q969"/>
-    <mergeCell ref="S969:Z969"/>
-    <mergeCell ref="E971:I971"/>
-    <mergeCell ref="E972:K972"/>
-    <mergeCell ref="L972:S972"/>
+    <mergeCell ref="S966:U966"/>
+    <mergeCell ref="M967:Q967"/>
+    <mergeCell ref="S967:T967"/>
+    <mergeCell ref="J968:Q968"/>
+    <mergeCell ref="S968:Z968"/>
+    <mergeCell ref="E970:I970"/>
+    <mergeCell ref="E971:K971"/>
+    <mergeCell ref="L971:S971"/>
+    <mergeCell ref="T971:AC971"/>
+    <mergeCell ref="E972:K974"/>
+    <mergeCell ref="L972:S974"/>
     <mergeCell ref="T972:AC972"/>
-    <mergeCell ref="E973:K975"/>
-    <mergeCell ref="L973:S975"/>
     <mergeCell ref="T973:AC973"/>
     <mergeCell ref="T974:AC974"/>
+    <mergeCell ref="E975:K977"/>
+    <mergeCell ref="L975:S977"/>
     <mergeCell ref="T975:AC975"/>
-    <mergeCell ref="E976:K978"/>
-    <mergeCell ref="L976:S978"/>
     <mergeCell ref="T976:AC976"/>
     <mergeCell ref="T977:AC977"/>
-    <mergeCell ref="T978:AC978"/>
-    <mergeCell ref="E980:T980"/>
+    <mergeCell ref="E979:T979"/>
     <mergeCell ref="D988:M988"/>
     <mergeCell ref="O988:AB988"/>
     <mergeCell ref="E990:AD990"/>

--- a/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
+++ b/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
@@ -1777,7 +1777,7 @@
     <t>上側 軸方向鉄筋ピッチ</t>
   </si>
   <si>
-    <t>183.9 mm</t>
+    <t>177.0 mm</t>
   </si>
   <si>
     <t>上側 主鉄筋径</t>
@@ -1789,13 +1789,13 @@
     <t>上側 軸方向鉄筋のあき</t>
   </si>
   <si>
-    <t>183.9 − 32 = 151.9 mm</t>
+    <t>177.0 − 32 = 145.0 mm</t>
   </si>
   <si>
     <t>下側 軸方向鉄筋ピッチ</t>
   </si>
   <si>
-    <t>265.6 mm</t>
+    <t>257.5 mm</t>
   </si>
   <si>
     <t>下側 主鉄筋径</t>
@@ -1807,13 +1807,13 @@
     <t>下側 軸方向鉄筋のあき</t>
   </si>
   <si>
-    <t>265.6 − 16 = 249.6 mm</t>
+    <t>257.5 − 16 = 241.5 mm</t>
   </si>
   <si>
     <t>梁（上側）</t>
   </si>
   <si>
-    <t>軸方向鉄筋のあき 151.9</t>
+    <t>軸方向鉄筋のあき 145.0</t>
   </si>
   <si>
     <t>≧ 20 mm</t>
@@ -1825,7 +1825,7 @@
     <t>梁（下側）</t>
   </si>
   <si>
-    <t>軸方向鉄筋のあき 249.6</t>
+    <t>軸方向鉄筋のあき 241.5</t>
   </si>
   <si>
     <t>≧ 16 = 16.0 mm</t>

--- a/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
+++ b/.claude/docs/Example橋脚4/export/0400_照査の前提.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="774">
   <si>
     <t>§4. 照査の前提</t>
   </si>
@@ -2241,6 +2241,24 @@
     <t>鋼管外径Dに対して　17 ／ 800 ＝ 0.0213 ≧ 0.0125</t>
   </si>
   <si>
+    <t>・段落し以深の鋼管（段落し後の鋼管厚 14 mm、SKK490）についても、同じ条件で照査す</t>
+  </si>
+  <si>
+    <t>14 mm</t>
+  </si>
+  <si>
+    <t>13 mm　（腐食代　1 mm考慮）</t>
+  </si>
+  <si>
+    <t>鋼管外径Dに対して　14 ／ 800 ＝ 0.0175 ≧ 0.01</t>
+  </si>
+  <si>
+    <t>鋼管外径Dに対して　13 ／ 800 ＝ 0.0163 ≧ 0.0125</t>
+  </si>
+  <si>
+    <t>となるため、段落し以深の鋼管も上記条件を満足する。</t>
+  </si>
+  <si>
     <t>3) 鋼管の継手</t>
   </si>
   <si>
@@ -2277,6 +2295,12 @@
     <t>のとし、上記条件を満足する。</t>
   </si>
   <si>
+    <t>継手位置の検討については「0711_線路方向非線形解析 杭の段落し図」と「0721_線路直角方</t>
+  </si>
+  <si>
+    <t>向非線形解析 杭の段落し図」にて行う。</t>
+  </si>
+  <si>
     <t>4) 杭先端部</t>
   </si>
   <si>
@@ -2425,6 +2449,21 @@
   </si>
   <si>
     <t>t/D ＝ 2.13 %</t>
+  </si>
+  <si>
+    <t>段落し以深の製造時の肉厚</t>
+  </si>
+  <si>
+    <t>1.75 %</t>
+  </si>
+  <si>
+    <t>段落し以深の有効肉厚</t>
+  </si>
+  <si>
+    <t>t ＝ 13 mm</t>
+  </si>
+  <si>
+    <t>t/D ＝ 1.63 %</t>
   </si>
   <si>
     <t>ずれ止めの取付け長</t>
@@ -13427,71 +13466,60 @@
         <v>306</v>
       </c>
     </row>
-    <row r="1110" ht="15.75" customHeight="1"/>
+    <row r="1110" ht="15.75" customHeight="1">
+      <c r="E1110" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
     <row r="1111" ht="15.75" customHeight="1">
-      <c r="D1111" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="S1111" s="1" t="s">
-        <v>313</v>
+      <c r="E1111" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="1112" ht="15.75" customHeight="1"/>
     <row r="1113" ht="15.75" customHeight="1">
-      <c r="E1113" s="2" t="s">
+      <c r="K1113" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="R1113" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1113" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="1114" ht="15.75" customHeight="1">
+      <c r="L1114" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="R1114" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1114" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="1114" ht="15.75" customHeight="1">
-      <c r="E1114" s="2" t="s">
+    <row r="1115" ht="15.75" customHeight="1"/>
+    <row r="1116" ht="15.75" customHeight="1">
+      <c r="F1116" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="1115" ht="15.75" customHeight="1">
-      <c r="E1115" s="2" t="s">
+    <row r="1117" ht="15.75" customHeight="1">
+      <c r="F1117" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="1116" ht="15.75" customHeight="1">
-      <c r="E1116" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="1117" ht="15.75" customHeight="1">
-      <c r="E1117" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="1118" ht="15.75" customHeight="1">
-      <c r="E1118" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
+    <row r="1118" ht="15.75" customHeight="1"/>
     <row r="1119" ht="15.75" customHeight="1">
       <c r="E1119" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="1120" ht="15.75" customHeight="1">
-      <c r="E1120" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="1121" ht="15.75" customHeight="1">
-      <c r="E1121" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="1122" ht="15.75" customHeight="1">
-      <c r="E1122" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="1123" ht="15.75" customHeight="1">
-      <c r="E1123" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="1120" ht="15.75" customHeight="1"/>
+    <row r="1121" ht="15.75" customHeight="1"/>
+    <row r="1122" ht="15.75" customHeight="1"/>
+    <row r="1123" ht="15.75" customHeight="1"/>
     <row r="1124" ht="15.75" customHeight="1"/>
     <row r="1125" ht="15.75" customHeight="1"/>
     <row r="1126" ht="15.75" customHeight="1"/>
@@ -13499,376 +13527,397 @@
     <row r="1128" ht="15.75" customHeight="1"/>
     <row r="1129" ht="15.75" customHeight="1">
       <c r="D1129" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
+      </c>
+      <c r="S1129" s="1" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="1130" ht="15.75" customHeight="1"/>
     <row r="1131" ht="15.75" customHeight="1">
-      <c r="E1131" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="S1131" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="1132" ht="15.75" customHeight="1"/>
+      <c r="E1131" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="1132" ht="15.75" customHeight="1">
+      <c r="E1132" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
     <row r="1133" ht="15.75" customHeight="1">
       <c r="E1133" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="1134" ht="15.75" customHeight="1">
       <c r="E1134" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1135" ht="15.75" customHeight="1">
       <c r="E1135" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1136" ht="15.75" customHeight="1">
       <c r="E1136" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1137" ht="15.75" customHeight="1">
+      <c r="E1137" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="1138" ht="15.75" customHeight="1">
+      <c r="E1138" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="1139" ht="15.75" customHeight="1">
+      <c r="E1139" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="1140" ht="15.75" customHeight="1">
+      <c r="E1140" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="1141" ht="15.75" customHeight="1">
+      <c r="E1141" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="1142" ht="15.75" customHeight="1">
+      <c r="E1142" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="1137" ht="15.75" customHeight="1">
-      <c r="E1137" s="18"/>
-      <c r="F1137" s="20" t="s">
+    <row r="1143" ht="15.75" customHeight="1">
+      <c r="E1143" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="G1137" s="8"/>
-      <c r="H1137" s="8"/>
-      <c r="I1137" s="8"/>
-      <c r="J1137" s="19"/>
-      <c r="K1137" s="20" t="s">
+    </row>
+    <row r="1144" ht="15.75" customHeight="1"/>
+    <row r="1145" ht="15.75" customHeight="1">
+      <c r="D1145" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="L1137" s="8"/>
-      <c r="M1137" s="8"/>
-      <c r="N1137" s="8"/>
-      <c r="O1137" s="19"/>
-      <c r="P1137" s="20" t="s">
+    </row>
+    <row r="1146" ht="15.75" customHeight="1"/>
+    <row r="1147" ht="15.75" customHeight="1">
+      <c r="E1147" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="Q1137" s="8"/>
-      <c r="R1137" s="8"/>
-      <c r="S1137" s="8"/>
-      <c r="T1137" s="19"/>
-      <c r="U1137" s="20" t="s">
+      <c r="S1147" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="V1137" s="8"/>
-      <c r="W1137" s="8"/>
-      <c r="X1137" s="8"/>
-      <c r="Y1137" s="19"/>
-      <c r="Z1137" s="20" t="s">
+    </row>
+    <row r="1148" ht="15.75" customHeight="1"/>
+    <row r="1149" ht="15.75" customHeight="1">
+      <c r="E1149" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="AA1137" s="8"/>
-      <c r="AB1137" s="8"/>
-      <c r="AC1137" s="8"/>
-      <c r="AD1137" s="10"/>
-    </row>
-    <row r="1138" ht="15.75" customHeight="1">
-      <c r="E1138" s="10"/>
-      <c r="F1138" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="J1138" s="15"/>
-      <c r="K1138" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="O1138" s="15"/>
-      <c r="P1138" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="T1138" s="15"/>
-      <c r="U1138" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="Y1138" s="15"/>
-      <c r="Z1138" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="AD1138" s="10"/>
-    </row>
-    <row r="1139" ht="15.75" customHeight="1">
-      <c r="E1139" s="27">
-        <v>800</v>
-      </c>
-      <c r="F1139" s="12"/>
-      <c r="G1139" s="12"/>
-      <c r="H1139" s="12"/>
-      <c r="I1139" s="12"/>
-      <c r="J1139" s="28">
-        <v>4</v>
-      </c>
-      <c r="K1139" s="12"/>
-      <c r="L1139" s="12"/>
-      <c r="M1139" s="12"/>
-      <c r="N1139" s="12"/>
-      <c r="O1139" s="28">
-        <v>300</v>
-      </c>
-      <c r="P1139" s="12"/>
-      <c r="Q1139" s="12"/>
-      <c r="R1139" s="12"/>
-      <c r="S1139" s="12"/>
-      <c r="T1139" s="28">
-        <v>250</v>
-      </c>
-      <c r="U1139" s="12"/>
-      <c r="V1139" s="12"/>
-      <c r="W1139" s="12"/>
-      <c r="X1139" s="12"/>
-      <c r="Y1139" s="28">
-        <v>1050</v>
-      </c>
-      <c r="Z1139" s="12"/>
-      <c r="AA1139" s="12"/>
-      <c r="AB1139" s="12"/>
-      <c r="AC1139" s="12"/>
-      <c r="AD1139" s="10"/>
-    </row>
-    <row r="1140" ht="15.75" customHeight="1">
-      <c r="E1140" s="27">
-        <v>900</v>
-      </c>
-      <c r="F1140" s="12"/>
-      <c r="G1140" s="12"/>
-      <c r="H1140" s="12"/>
-      <c r="I1140" s="12"/>
-      <c r="J1140" s="28">
-        <v>5</v>
-      </c>
-      <c r="K1140" s="12"/>
-      <c r="L1140" s="12"/>
-      <c r="M1140" s="12"/>
-      <c r="N1140" s="12"/>
-      <c r="O1140" s="28">
-        <v>300</v>
-      </c>
-      <c r="P1140" s="12"/>
-      <c r="Q1140" s="12"/>
-      <c r="R1140" s="12"/>
-      <c r="S1140" s="12"/>
-      <c r="T1140" s="28">
-        <v>250</v>
-      </c>
-      <c r="U1140" s="12"/>
-      <c r="V1140" s="12"/>
-      <c r="W1140" s="12"/>
-      <c r="X1140" s="12"/>
-      <c r="Y1140" s="28">
-        <v>1300</v>
-      </c>
-      <c r="Z1140" s="12"/>
-      <c r="AA1140" s="12"/>
-      <c r="AB1140" s="12"/>
-      <c r="AC1140" s="12"/>
-      <c r="AD1140" s="10"/>
-    </row>
-    <row r="1141" ht="15.75" customHeight="1">
-      <c r="E1141" s="27">
-        <v>1000</v>
-      </c>
-      <c r="F1141" s="12"/>
-      <c r="G1141" s="12"/>
-      <c r="H1141" s="12"/>
-      <c r="I1141" s="12"/>
-      <c r="J1141" s="28">
-        <v>5</v>
-      </c>
-      <c r="K1141" s="12"/>
-      <c r="L1141" s="12"/>
-      <c r="M1141" s="12"/>
-      <c r="N1141" s="12"/>
-      <c r="O1141" s="28">
-        <v>300</v>
-      </c>
-      <c r="P1141" s="12"/>
-      <c r="Q1141" s="12"/>
-      <c r="R1141" s="12"/>
-      <c r="S1141" s="12"/>
-      <c r="T1141" s="28">
-        <v>250</v>
-      </c>
-      <c r="U1141" s="12"/>
-      <c r="V1141" s="12"/>
-      <c r="W1141" s="12"/>
-      <c r="X1141" s="12"/>
-      <c r="Y1141" s="28">
-        <v>1300</v>
-      </c>
-      <c r="Z1141" s="12"/>
-      <c r="AA1141" s="12"/>
-      <c r="AB1141" s="12"/>
-      <c r="AC1141" s="12"/>
-      <c r="AD1141" s="10"/>
-    </row>
-    <row r="1142" ht="15.75" customHeight="1">
-      <c r="E1142" s="27">
-        <v>1100</v>
-      </c>
-      <c r="F1142" s="12"/>
-      <c r="G1142" s="12"/>
-      <c r="H1142" s="12"/>
-      <c r="I1142" s="12"/>
-      <c r="J1142" s="28">
-        <v>5</v>
-      </c>
-      <c r="K1142" s="12"/>
-      <c r="L1142" s="12"/>
-      <c r="M1142" s="12"/>
-      <c r="N1142" s="12"/>
-      <c r="O1142" s="28">
-        <v>300</v>
-      </c>
-      <c r="P1142" s="12"/>
-      <c r="Q1142" s="12"/>
-      <c r="R1142" s="12"/>
-      <c r="S1142" s="12"/>
-      <c r="T1142" s="28">
-        <v>300</v>
-      </c>
-      <c r="U1142" s="12"/>
-      <c r="V1142" s="12"/>
-      <c r="W1142" s="12"/>
-      <c r="X1142" s="12"/>
-      <c r="Y1142" s="28">
-        <v>1500</v>
-      </c>
-      <c r="Z1142" s="12"/>
-      <c r="AA1142" s="12"/>
-      <c r="AB1142" s="12"/>
-      <c r="AC1142" s="12"/>
-      <c r="AD1142" s="10"/>
-    </row>
-    <row r="1143" ht="15.75" customHeight="1">
-      <c r="E1143" s="27">
-        <v>1200</v>
-      </c>
-      <c r="F1143" s="12"/>
-      <c r="G1143" s="12"/>
-      <c r="H1143" s="12"/>
-      <c r="I1143" s="12"/>
-      <c r="J1143" s="28">
-        <v>6</v>
-      </c>
-      <c r="K1143" s="12"/>
-      <c r="L1143" s="12"/>
-      <c r="M1143" s="12"/>
-      <c r="N1143" s="12"/>
-      <c r="O1143" s="28">
-        <v>300</v>
-      </c>
-      <c r="P1143" s="12"/>
-      <c r="Q1143" s="12"/>
-      <c r="R1143" s="12"/>
-      <c r="S1143" s="12"/>
-      <c r="T1143" s="28">
-        <v>300</v>
-      </c>
-      <c r="U1143" s="12"/>
-      <c r="V1143" s="12"/>
-      <c r="W1143" s="12"/>
-      <c r="X1143" s="12"/>
-      <c r="Y1143" s="28">
-        <v>1800</v>
-      </c>
-      <c r="Z1143" s="12"/>
-      <c r="AA1143" s="12"/>
-      <c r="AB1143" s="12"/>
-      <c r="AC1143" s="12"/>
-      <c r="AD1143" s="10"/>
-    </row>
-    <row r="1144" ht="15.75" customHeight="1">
-      <c r="E1144" s="8"/>
-      <c r="F1144" s="8"/>
-      <c r="G1144" s="8"/>
-      <c r="H1144" s="8"/>
-      <c r="I1144" s="8"/>
-      <c r="J1144" s="8"/>
-      <c r="K1144" s="8"/>
-      <c r="L1144" s="8"/>
-      <c r="M1144" s="8"/>
-      <c r="N1144" s="8"/>
-      <c r="O1144" s="8"/>
-      <c r="P1144" s="8"/>
-      <c r="Q1144" s="8"/>
-      <c r="R1144" s="8"/>
-      <c r="S1144" s="8"/>
-      <c r="T1144" s="8"/>
-      <c r="U1144" s="8"/>
-      <c r="V1144" s="8"/>
-      <c r="W1144" s="8"/>
-      <c r="X1144" s="8"/>
-      <c r="Y1144" s="8"/>
-      <c r="Z1144" s="8"/>
-      <c r="AA1144" s="8"/>
-      <c r="AB1144" s="8"/>
-      <c r="AC1144" s="8"/>
-    </row>
-    <row r="1145" ht="15.75" customHeight="1">
-      <c r="E1145" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="1146" ht="15.75" customHeight="1">
-      <c r="E1146" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="1147" ht="15.75" customHeight="1"/>
-    <row r="1148" ht="15.75" customHeight="1">
-      <c r="E1148" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="S1148" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="1149" ht="15.75" customHeight="1"/>
+    </row>
     <row r="1150" ht="15.75" customHeight="1">
       <c r="E1150" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="1151" ht="15.75" customHeight="1">
+      <c r="E1151" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="1152" ht="15.75" customHeight="1">
+      <c r="E1152" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="1153" ht="15.75" customHeight="1">
+      <c r="E1153" s="18"/>
+      <c r="F1153" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="G1153" s="8"/>
+      <c r="H1153" s="8"/>
+      <c r="I1153" s="8"/>
+      <c r="J1153" s="19"/>
+      <c r="K1153" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="L1153" s="8"/>
+      <c r="M1153" s="8"/>
+      <c r="N1153" s="8"/>
+      <c r="O1153" s="19"/>
+      <c r="P1153" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q1153" s="8"/>
+      <c r="R1153" s="8"/>
+      <c r="S1153" s="8"/>
+      <c r="T1153" s="19"/>
+      <c r="U1153" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="V1153" s="8"/>
+      <c r="W1153" s="8"/>
+      <c r="X1153" s="8"/>
+      <c r="Y1153" s="19"/>
+      <c r="Z1153" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="AA1153" s="8"/>
+      <c r="AB1153" s="8"/>
+      <c r="AC1153" s="8"/>
+      <c r="AD1153" s="10"/>
+    </row>
+    <row r="1154" ht="15.75" customHeight="1">
+      <c r="E1154" s="10"/>
+      <c r="F1154" s="4" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="1151" ht="15.75" customHeight="1"/>
-    <row r="1152" ht="15.75" customHeight="1">
-      <c r="F1152" s="2" t="s">
+      <c r="J1154" s="15"/>
+      <c r="K1154" s="4" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="1153" ht="15.75" customHeight="1"/>
-    <row r="1154" ht="15.75" customHeight="1">
-      <c r="E1154" s="2" t="s">
+      <c r="O1154" s="15"/>
+      <c r="P1154" s="4" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="1155" ht="15.75" customHeight="1"/>
+      <c r="T1154" s="15"/>
+      <c r="U1154" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y1154" s="15"/>
+      <c r="Z1154" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="AD1154" s="10"/>
+    </row>
+    <row r="1155" ht="15.75" customHeight="1">
+      <c r="E1155" s="27">
+        <v>800</v>
+      </c>
+      <c r="F1155" s="12"/>
+      <c r="G1155" s="12"/>
+      <c r="H1155" s="12"/>
+      <c r="I1155" s="12"/>
+      <c r="J1155" s="28">
+        <v>4</v>
+      </c>
+      <c r="K1155" s="12"/>
+      <c r="L1155" s="12"/>
+      <c r="M1155" s="12"/>
+      <c r="N1155" s="12"/>
+      <c r="O1155" s="28">
+        <v>300</v>
+      </c>
+      <c r="P1155" s="12"/>
+      <c r="Q1155" s="12"/>
+      <c r="R1155" s="12"/>
+      <c r="S1155" s="12"/>
+      <c r="T1155" s="28">
+        <v>250</v>
+      </c>
+      <c r="U1155" s="12"/>
+      <c r="V1155" s="12"/>
+      <c r="W1155" s="12"/>
+      <c r="X1155" s="12"/>
+      <c r="Y1155" s="28">
+        <v>1050</v>
+      </c>
+      <c r="Z1155" s="12"/>
+      <c r="AA1155" s="12"/>
+      <c r="AB1155" s="12"/>
+      <c r="AC1155" s="12"/>
+      <c r="AD1155" s="10"/>
+    </row>
     <row r="1156" ht="15.75" customHeight="1">
-      <c r="E1156" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="S1156" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="1157" ht="15.75" customHeight="1"/>
+      <c r="E1156" s="27">
+        <v>900</v>
+      </c>
+      <c r="F1156" s="12"/>
+      <c r="G1156" s="12"/>
+      <c r="H1156" s="12"/>
+      <c r="I1156" s="12"/>
+      <c r="J1156" s="28">
+        <v>5</v>
+      </c>
+      <c r="K1156" s="12"/>
+      <c r="L1156" s="12"/>
+      <c r="M1156" s="12"/>
+      <c r="N1156" s="12"/>
+      <c r="O1156" s="28">
+        <v>300</v>
+      </c>
+      <c r="P1156" s="12"/>
+      <c r="Q1156" s="12"/>
+      <c r="R1156" s="12"/>
+      <c r="S1156" s="12"/>
+      <c r="T1156" s="28">
+        <v>250</v>
+      </c>
+      <c r="U1156" s="12"/>
+      <c r="V1156" s="12"/>
+      <c r="W1156" s="12"/>
+      <c r="X1156" s="12"/>
+      <c r="Y1156" s="28">
+        <v>1300</v>
+      </c>
+      <c r="Z1156" s="12"/>
+      <c r="AA1156" s="12"/>
+      <c r="AB1156" s="12"/>
+      <c r="AC1156" s="12"/>
+      <c r="AD1156" s="10"/>
+    </row>
+    <row r="1157" ht="15.75" customHeight="1">
+      <c r="E1157" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F1157" s="12"/>
+      <c r="G1157" s="12"/>
+      <c r="H1157" s="12"/>
+      <c r="I1157" s="12"/>
+      <c r="J1157" s="28">
+        <v>5</v>
+      </c>
+      <c r="K1157" s="12"/>
+      <c r="L1157" s="12"/>
+      <c r="M1157" s="12"/>
+      <c r="N1157" s="12"/>
+      <c r="O1157" s="28">
+        <v>300</v>
+      </c>
+      <c r="P1157" s="12"/>
+      <c r="Q1157" s="12"/>
+      <c r="R1157" s="12"/>
+      <c r="S1157" s="12"/>
+      <c r="T1157" s="28">
+        <v>250</v>
+      </c>
+      <c r="U1157" s="12"/>
+      <c r="V1157" s="12"/>
+      <c r="W1157" s="12"/>
+      <c r="X1157" s="12"/>
+      <c r="Y1157" s="28">
+        <v>1300</v>
+      </c>
+      <c r="Z1157" s="12"/>
+      <c r="AA1157" s="12"/>
+      <c r="AB1157" s="12"/>
+      <c r="AC1157" s="12"/>
+      <c r="AD1157" s="10"/>
+    </row>
     <row r="1158" ht="15.75" customHeight="1">
-      <c r="E1158" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="1159" ht="15.75" customHeight="1"/>
+      <c r="E1158" s="27">
+        <v>1100</v>
+      </c>
+      <c r="F1158" s="12"/>
+      <c r="G1158" s="12"/>
+      <c r="H1158" s="12"/>
+      <c r="I1158" s="12"/>
+      <c r="J1158" s="28">
+        <v>5</v>
+      </c>
+      <c r="K1158" s="12"/>
+      <c r="L1158" s="12"/>
+      <c r="M1158" s="12"/>
+      <c r="N1158" s="12"/>
+      <c r="O1158" s="28">
+        <v>300</v>
+      </c>
+      <c r="P1158" s="12"/>
+      <c r="Q1158" s="12"/>
+      <c r="R1158" s="12"/>
+      <c r="S1158" s="12"/>
+      <c r="T1158" s="28">
+        <v>300</v>
+      </c>
+      <c r="U1158" s="12"/>
+      <c r="V1158" s="12"/>
+      <c r="W1158" s="12"/>
+      <c r="X1158" s="12"/>
+      <c r="Y1158" s="28">
+        <v>1500</v>
+      </c>
+      <c r="Z1158" s="12"/>
+      <c r="AA1158" s="12"/>
+      <c r="AB1158" s="12"/>
+      <c r="AC1158" s="12"/>
+      <c r="AD1158" s="10"/>
+    </row>
+    <row r="1159" ht="15.75" customHeight="1">
+      <c r="E1159" s="27">
+        <v>1200</v>
+      </c>
+      <c r="F1159" s="12"/>
+      <c r="G1159" s="12"/>
+      <c r="H1159" s="12"/>
+      <c r="I1159" s="12"/>
+      <c r="J1159" s="28">
+        <v>6</v>
+      </c>
+      <c r="K1159" s="12"/>
+      <c r="L1159" s="12"/>
+      <c r="M1159" s="12"/>
+      <c r="N1159" s="12"/>
+      <c r="O1159" s="28">
+        <v>300</v>
+      </c>
+      <c r="P1159" s="12"/>
+      <c r="Q1159" s="12"/>
+      <c r="R1159" s="12"/>
+      <c r="S1159" s="12"/>
+      <c r="T1159" s="28">
+        <v>300</v>
+      </c>
+      <c r="U1159" s="12"/>
+      <c r="V1159" s="12"/>
+      <c r="W1159" s="12"/>
+      <c r="X1159" s="12"/>
+      <c r="Y1159" s="28">
+        <v>1800</v>
+      </c>
+      <c r="Z1159" s="12"/>
+      <c r="AA1159" s="12"/>
+      <c r="AB1159" s="12"/>
+      <c r="AC1159" s="12"/>
+      <c r="AD1159" s="10"/>
+    </row>
     <row r="1160" ht="15.75" customHeight="1">
-      <c r="F1160" s="2" t="s">
+      <c r="E1160" s="8"/>
+      <c r="F1160" s="8"/>
+      <c r="G1160" s="8"/>
+      <c r="H1160" s="8"/>
+      <c r="I1160" s="8"/>
+      <c r="J1160" s="8"/>
+      <c r="K1160" s="8"/>
+      <c r="L1160" s="8"/>
+      <c r="M1160" s="8"/>
+      <c r="N1160" s="8"/>
+      <c r="O1160" s="8"/>
+      <c r="P1160" s="8"/>
+      <c r="Q1160" s="8"/>
+      <c r="R1160" s="8"/>
+      <c r="S1160" s="8"/>
+      <c r="T1160" s="8"/>
+      <c r="U1160" s="8"/>
+      <c r="V1160" s="8"/>
+      <c r="W1160" s="8"/>
+      <c r="X1160" s="8"/>
+      <c r="Y1160" s="8"/>
+      <c r="Z1160" s="8"/>
+      <c r="AA1160" s="8"/>
+      <c r="AB1160" s="8"/>
+      <c r="AC1160" s="8"/>
+    </row>
+    <row r="1161" ht="15.75" customHeight="1">
+      <c r="E1161" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="1161" ht="15.75" customHeight="1"/>
     <row r="1162" ht="15.75" customHeight="1">
       <c r="E1162" s="2" t="s">
         <v>350</v>
@@ -13880,7 +13929,7 @@
         <v>351</v>
       </c>
       <c r="S1164" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="1165" ht="15.75" customHeight="1"/>
@@ -13907,1409 +13956,1534 @@
     <row r="1174" ht="15.75" customHeight="1"/>
     <row r="1175" ht="15.75" customHeight="1"/>
     <row r="1176" ht="15.75" customHeight="1">
-      <c r="D1176" s="1" t="s">
+      <c r="E1176" s="1" t="s">
         <v>355</v>
+      </c>
+      <c r="S1176" s="1" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="1177" ht="15.75" customHeight="1"/>
     <row r="1178" ht="15.75" customHeight="1">
-      <c r="B1178" s="2" t="s">
+      <c r="E1178" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="1179" ht="15.75" customHeight="1">
-      <c r="B1179" s="7" t="s">
+    <row r="1179" ht="15.75" customHeight="1"/>
+    <row r="1180" ht="15.75" customHeight="1">
+      <c r="F1180" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C1179" s="8"/>
-      <c r="D1179" s="8"/>
-      <c r="E1179" s="8"/>
-      <c r="F1179" s="8"/>
-      <c r="G1179" s="8"/>
-      <c r="H1179" s="8"/>
-      <c r="I1179" s="8"/>
-      <c r="J1179" s="9" t="s">
+    </row>
+    <row r="1181" ht="15.75" customHeight="1"/>
+    <row r="1182" ht="15.75" customHeight="1">
+      <c r="E1182" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="K1179" s="8"/>
-      <c r="L1179" s="8"/>
-      <c r="M1179" s="8"/>
-      <c r="N1179" s="8"/>
-      <c r="O1179" s="8"/>
-      <c r="P1179" s="8"/>
-      <c r="Q1179" s="8"/>
-      <c r="R1179" s="8"/>
-      <c r="S1179" s="9" t="s">
+    </row>
+    <row r="1183" ht="15.75" customHeight="1"/>
+    <row r="1184" ht="15.75" customHeight="1">
+      <c r="E1184" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="T1179" s="8"/>
-      <c r="U1179" s="8"/>
-      <c r="V1179" s="8"/>
-      <c r="W1179" s="8"/>
-      <c r="X1179" s="8"/>
-      <c r="Y1179" s="9" t="s">
+      <c r="S1184" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="1185" ht="15.75" customHeight="1"/>
+    <row r="1186" ht="15.75" customHeight="1">
+      <c r="E1186" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="Z1179" s="8"/>
-      <c r="AA1179" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB1179" s="8"/>
-      <c r="AC1179" s="8"/>
-      <c r="AD1179" s="21"/>
-    </row>
-    <row r="1180" ht="15.75" customHeight="1">
-      <c r="B1180" s="23" t="s">
+    </row>
+    <row r="1187" ht="15.75" customHeight="1"/>
+    <row r="1188" ht="15.75" customHeight="1">
+      <c r="F1188" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C1180" s="12"/>
-      <c r="D1180" s="12"/>
-      <c r="E1180" s="12"/>
-      <c r="F1180" s="12"/>
-      <c r="G1180" s="12"/>
-      <c r="H1180" s="12"/>
-      <c r="I1180" s="12"/>
-      <c r="J1180" s="14" t="s">
+    </row>
+    <row r="1189" ht="15.75" customHeight="1"/>
+    <row r="1190" ht="15.75" customHeight="1">
+      <c r="E1190" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="K1180" s="12"/>
-      <c r="L1180" s="12"/>
-      <c r="M1180" s="12"/>
-      <c r="N1180" s="12"/>
-      <c r="O1180" s="12"/>
-      <c r="P1180" s="12"/>
-      <c r="Q1180" s="12"/>
-      <c r="R1180" s="12"/>
-      <c r="S1180" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="T1180" s="12"/>
-      <c r="U1180" s="12"/>
-      <c r="V1180" s="12"/>
-      <c r="W1180" s="12"/>
-      <c r="X1180" s="12"/>
-      <c r="Y1180" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1180" s="12"/>
-      <c r="AA1180" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB1180" s="12"/>
-      <c r="AC1180" s="12"/>
-      <c r="AD1180" s="26"/>
-    </row>
-    <row r="1181" ht="15.75" customHeight="1">
-      <c r="B1181" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="C1181" s="12"/>
-      <c r="D1181" s="12"/>
-      <c r="E1181" s="12"/>
-      <c r="F1181" s="12"/>
-      <c r="G1181" s="12"/>
-      <c r="H1181" s="12"/>
-      <c r="I1181" s="12"/>
-      <c r="J1181" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="K1181" s="12"/>
-      <c r="L1181" s="12"/>
-      <c r="M1181" s="12"/>
-      <c r="N1181" s="12"/>
-      <c r="O1181" s="12"/>
-      <c r="P1181" s="12"/>
-      <c r="Q1181" s="12"/>
-      <c r="R1181" s="12"/>
-      <c r="S1181" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="T1181" s="12"/>
-      <c r="U1181" s="12"/>
-      <c r="V1181" s="12"/>
-      <c r="W1181" s="12"/>
-      <c r="X1181" s="12"/>
-      <c r="Y1181" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1181" s="12"/>
-      <c r="AA1181" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB1181" s="12"/>
-      <c r="AC1181" s="12"/>
-      <c r="AD1181" s="26"/>
-    </row>
-    <row r="1182" ht="15.75" customHeight="1">
-      <c r="B1182" s="10"/>
-      <c r="J1182" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="K1182" s="12"/>
-      <c r="L1182" s="12"/>
-      <c r="M1182" s="12"/>
-      <c r="N1182" s="12"/>
-      <c r="O1182" s="12"/>
-      <c r="P1182" s="12"/>
-      <c r="Q1182" s="12"/>
-      <c r="R1182" s="12"/>
-      <c r="S1182" s="14" t="s">
-        <v>368</v>
-      </c>
-      <c r="T1182" s="12"/>
-      <c r="U1182" s="12"/>
-      <c r="V1182" s="12"/>
-      <c r="W1182" s="12"/>
-      <c r="X1182" s="12"/>
-      <c r="Y1182" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1182" s="12"/>
-      <c r="AA1182" s="15"/>
-      <c r="AD1182" s="22"/>
-    </row>
-    <row r="1183" ht="15.75" customHeight="1">
-      <c r="B1183" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="C1183" s="12"/>
-      <c r="D1183" s="12"/>
-      <c r="E1183" s="12"/>
-      <c r="F1183" s="12"/>
-      <c r="G1183" s="12"/>
-      <c r="H1183" s="12"/>
-      <c r="I1183" s="12"/>
-      <c r="J1183" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="K1183" s="12"/>
-      <c r="L1183" s="12"/>
-      <c r="M1183" s="12"/>
-      <c r="N1183" s="12"/>
-      <c r="O1183" s="12"/>
-      <c r="P1183" s="12"/>
-      <c r="Q1183" s="12"/>
-      <c r="R1183" s="12"/>
-      <c r="S1183" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="T1183" s="12"/>
-      <c r="U1183" s="12"/>
-      <c r="V1183" s="12"/>
-      <c r="W1183" s="12"/>
-      <c r="X1183" s="12"/>
-      <c r="Y1183" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1183" s="12"/>
-      <c r="AA1183" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB1183" s="12"/>
-      <c r="AC1183" s="12"/>
-      <c r="AD1183" s="26"/>
-    </row>
-    <row r="1184" ht="15.75" customHeight="1">
-      <c r="B1184" s="10"/>
-      <c r="J1184" s="14" t="s">
-        <v>372</v>
-      </c>
-      <c r="K1184" s="12"/>
-      <c r="L1184" s="12"/>
-      <c r="M1184" s="12"/>
-      <c r="N1184" s="12"/>
-      <c r="O1184" s="12"/>
-      <c r="P1184" s="12"/>
-      <c r="Q1184" s="12"/>
-      <c r="R1184" s="12"/>
-      <c r="S1184" s="14" t="s">
-        <v>373</v>
-      </c>
-      <c r="T1184" s="12"/>
-      <c r="U1184" s="12"/>
-      <c r="V1184" s="12"/>
-      <c r="W1184" s="12"/>
-      <c r="X1184" s="12"/>
-      <c r="Y1184" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1184" s="12"/>
-      <c r="AA1184" s="15"/>
-      <c r="AD1184" s="22"/>
-    </row>
-    <row r="1185" ht="15.75" customHeight="1">
-      <c r="B1185" s="23" t="s">
-        <v>374</v>
-      </c>
-      <c r="C1185" s="12"/>
-      <c r="D1185" s="12"/>
-      <c r="E1185" s="12"/>
-      <c r="F1185" s="12"/>
-      <c r="G1185" s="12"/>
-      <c r="H1185" s="12"/>
-      <c r="I1185" s="12"/>
-      <c r="J1185" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="K1185" s="12"/>
-      <c r="L1185" s="12"/>
-      <c r="M1185" s="12"/>
-      <c r="N1185" s="12"/>
-      <c r="O1185" s="12"/>
-      <c r="P1185" s="12"/>
-      <c r="Q1185" s="12"/>
-      <c r="R1185" s="12"/>
-      <c r="S1185" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="T1185" s="12"/>
-      <c r="U1185" s="12"/>
-      <c r="V1185" s="12"/>
-      <c r="W1185" s="12"/>
-      <c r="X1185" s="12"/>
-      <c r="Y1185" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1185" s="12"/>
-      <c r="AA1185" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB1185" s="12"/>
-      <c r="AC1185" s="12"/>
-      <c r="AD1185" s="26"/>
-    </row>
-    <row r="1186" ht="15.75" customHeight="1">
-      <c r="B1186" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="C1186" s="12"/>
-      <c r="D1186" s="12"/>
-      <c r="E1186" s="12"/>
-      <c r="F1186" s="12"/>
-      <c r="G1186" s="12"/>
-      <c r="H1186" s="12"/>
-      <c r="I1186" s="12"/>
-      <c r="J1186" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="K1186" s="12"/>
-      <c r="L1186" s="12"/>
-      <c r="M1186" s="12"/>
-      <c r="N1186" s="12"/>
-      <c r="O1186" s="12"/>
-      <c r="P1186" s="12"/>
-      <c r="Q1186" s="12"/>
-      <c r="R1186" s="12"/>
-      <c r="S1186" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="T1186" s="12"/>
-      <c r="U1186" s="12"/>
-      <c r="V1186" s="12"/>
-      <c r="W1186" s="12"/>
-      <c r="X1186" s="12"/>
-      <c r="Y1186" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1186" s="12"/>
-      <c r="AA1186" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB1186" s="12"/>
-      <c r="AC1186" s="12"/>
-      <c r="AD1186" s="26"/>
-    </row>
-    <row r="1187" ht="15.75" customHeight="1">
-      <c r="B1187" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="C1187" s="12"/>
-      <c r="D1187" s="12"/>
-      <c r="E1187" s="12"/>
-      <c r="F1187" s="12"/>
-      <c r="G1187" s="12"/>
-      <c r="H1187" s="12"/>
-      <c r="I1187" s="12"/>
-      <c r="J1187" s="14" t="s">
-        <v>381</v>
-      </c>
-      <c r="K1187" s="12"/>
-      <c r="L1187" s="12"/>
-      <c r="M1187" s="12"/>
-      <c r="N1187" s="12"/>
-      <c r="O1187" s="12"/>
-      <c r="P1187" s="12"/>
-      <c r="Q1187" s="12"/>
-      <c r="R1187" s="12"/>
-      <c r="S1187" s="14" t="s">
-        <v>382</v>
-      </c>
-      <c r="T1187" s="12"/>
-      <c r="U1187" s="12"/>
-      <c r="V1187" s="12"/>
-      <c r="W1187" s="12"/>
-      <c r="X1187" s="12"/>
-      <c r="Y1187" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1187" s="12"/>
-      <c r="AA1187" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB1187" s="12"/>
-      <c r="AC1187" s="12"/>
-      <c r="AD1187" s="26"/>
-    </row>
-    <row r="1188" ht="15.75" customHeight="1">
-      <c r="B1188" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="C1188" s="12"/>
-      <c r="D1188" s="12"/>
-      <c r="E1188" s="12"/>
-      <c r="F1188" s="12"/>
-      <c r="G1188" s="12"/>
-      <c r="H1188" s="12"/>
-      <c r="I1188" s="12"/>
-      <c r="J1188" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="K1188" s="12"/>
-      <c r="L1188" s="12"/>
-      <c r="M1188" s="12"/>
-      <c r="N1188" s="12"/>
-      <c r="O1188" s="12"/>
-      <c r="P1188" s="12"/>
-      <c r="Q1188" s="12"/>
-      <c r="R1188" s="12"/>
-      <c r="S1188" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="T1188" s="12"/>
-      <c r="U1188" s="12"/>
-      <c r="V1188" s="12"/>
-      <c r="W1188" s="12"/>
-      <c r="X1188" s="12"/>
-      <c r="Y1188" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="Z1188" s="12"/>
-      <c r="AA1188" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB1188" s="12"/>
-      <c r="AC1188" s="12"/>
-      <c r="AD1188" s="26"/>
-    </row>
-    <row r="1189" ht="15.75" customHeight="1">
-      <c r="B1189" s="8"/>
-      <c r="C1189" s="8"/>
-      <c r="D1189" s="8"/>
-      <c r="E1189" s="8"/>
-      <c r="F1189" s="8"/>
-      <c r="G1189" s="8"/>
-      <c r="H1189" s="8"/>
-      <c r="I1189" s="8"/>
-      <c r="J1189" s="8"/>
-      <c r="K1189" s="8"/>
-      <c r="L1189" s="8"/>
-      <c r="M1189" s="8"/>
-      <c r="N1189" s="8"/>
-      <c r="O1189" s="8"/>
-      <c r="P1189" s="8"/>
-      <c r="Q1189" s="8"/>
-      <c r="R1189" s="8"/>
-      <c r="S1189" s="8"/>
-      <c r="T1189" s="8"/>
-      <c r="U1189" s="8"/>
-      <c r="V1189" s="8"/>
-      <c r="W1189" s="8"/>
-      <c r="X1189" s="8"/>
-      <c r="Y1189" s="8"/>
-      <c r="Z1189" s="8"/>
-      <c r="AA1189" s="8"/>
-      <c r="AB1189" s="8"/>
-      <c r="AC1189" s="8"/>
-      <c r="AD1189" s="8"/>
-    </row>
-    <row r="1190" ht="15.75" customHeight="1">
-      <c r="C1190" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="1191" ht="15.75" customHeight="1"/>
     <row r="1192" ht="15.75" customHeight="1">
       <c r="D1192" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="S1192" s="1" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
     </row>
     <row r="1193" ht="15.75" customHeight="1"/>
     <row r="1194" ht="15.75" customHeight="1">
-      <c r="E1194" s="2" t="s">
+      <c r="B1194" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="1195" ht="15.75" customHeight="1">
+      <c r="B1195" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1195" s="8"/>
+      <c r="D1195" s="8"/>
+      <c r="E1195" s="8"/>
+      <c r="F1195" s="8"/>
+      <c r="G1195" s="8"/>
+      <c r="H1195" s="8"/>
+      <c r="I1195" s="8"/>
+      <c r="J1195" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="K1195" s="8"/>
+      <c r="L1195" s="8"/>
+      <c r="M1195" s="8"/>
+      <c r="N1195" s="8"/>
+      <c r="O1195" s="8"/>
+      <c r="P1195" s="8"/>
+      <c r="Q1195" s="8"/>
+      <c r="R1195" s="8"/>
+      <c r="S1195" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="T1195" s="8"/>
+      <c r="U1195" s="8"/>
+      <c r="V1195" s="8"/>
+      <c r="W1195" s="8"/>
+      <c r="X1195" s="8"/>
+      <c r="Y1195" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="Z1195" s="8"/>
+      <c r="AA1195" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB1195" s="8"/>
+      <c r="AC1195" s="8"/>
+      <c r="AD1195" s="21"/>
+    </row>
+    <row r="1196" ht="15.75" customHeight="1">
+      <c r="B1196" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1196" s="12"/>
+      <c r="D1196" s="12"/>
+      <c r="E1196" s="12"/>
+      <c r="F1196" s="12"/>
+      <c r="G1196" s="12"/>
+      <c r="H1196" s="12"/>
+      <c r="I1196" s="12"/>
+      <c r="J1196" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="K1196" s="12"/>
+      <c r="L1196" s="12"/>
+      <c r="M1196" s="12"/>
+      <c r="N1196" s="12"/>
+      <c r="O1196" s="12"/>
+      <c r="P1196" s="12"/>
+      <c r="Q1196" s="12"/>
+      <c r="R1196" s="12"/>
+      <c r="S1196" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="T1196" s="12"/>
+      <c r="U1196" s="12"/>
+      <c r="V1196" s="12"/>
+      <c r="W1196" s="12"/>
+      <c r="X1196" s="12"/>
+      <c r="Y1196" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1196" s="12"/>
+      <c r="AA1196" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1196" s="12"/>
+      <c r="AC1196" s="12"/>
+      <c r="AD1196" s="26"/>
+    </row>
+    <row r="1197" ht="15.75" customHeight="1">
+      <c r="B1197" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1197" s="12"/>
+      <c r="D1197" s="12"/>
+      <c r="E1197" s="12"/>
+      <c r="F1197" s="12"/>
+      <c r="G1197" s="12"/>
+      <c r="H1197" s="12"/>
+      <c r="I1197" s="12"/>
+      <c r="J1197" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="K1197" s="12"/>
+      <c r="L1197" s="12"/>
+      <c r="M1197" s="12"/>
+      <c r="N1197" s="12"/>
+      <c r="O1197" s="12"/>
+      <c r="P1197" s="12"/>
+      <c r="Q1197" s="12"/>
+      <c r="R1197" s="12"/>
+      <c r="S1197" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="T1197" s="12"/>
+      <c r="U1197" s="12"/>
+      <c r="V1197" s="12"/>
+      <c r="W1197" s="12"/>
+      <c r="X1197" s="12"/>
+      <c r="Y1197" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1197" s="12"/>
+      <c r="AA1197" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1197" s="12"/>
+      <c r="AC1197" s="12"/>
+      <c r="AD1197" s="26"/>
+    </row>
+    <row r="1198" ht="15.75" customHeight="1">
+      <c r="B1198" s="10"/>
+      <c r="J1198" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="K1198" s="12"/>
+      <c r="L1198" s="12"/>
+      <c r="M1198" s="12"/>
+      <c r="N1198" s="12"/>
+      <c r="O1198" s="12"/>
+      <c r="P1198" s="12"/>
+      <c r="Q1198" s="12"/>
+      <c r="R1198" s="12"/>
+      <c r="S1198" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="T1198" s="12"/>
+      <c r="U1198" s="12"/>
+      <c r="V1198" s="12"/>
+      <c r="W1198" s="12"/>
+      <c r="X1198" s="12"/>
+      <c r="Y1198" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1198" s="12"/>
+      <c r="AA1198" s="15"/>
+      <c r="AD1198" s="22"/>
+    </row>
+    <row r="1199" ht="15.75" customHeight="1">
+      <c r="B1199" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1199" s="12"/>
+      <c r="D1199" s="12"/>
+      <c r="E1199" s="12"/>
+      <c r="F1199" s="12"/>
+      <c r="G1199" s="12"/>
+      <c r="H1199" s="12"/>
+      <c r="I1199" s="12"/>
+      <c r="J1199" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="K1199" s="12"/>
+      <c r="L1199" s="12"/>
+      <c r="M1199" s="12"/>
+      <c r="N1199" s="12"/>
+      <c r="O1199" s="12"/>
+      <c r="P1199" s="12"/>
+      <c r="Q1199" s="12"/>
+      <c r="R1199" s="12"/>
+      <c r="S1199" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="T1199" s="12"/>
+      <c r="U1199" s="12"/>
+      <c r="V1199" s="12"/>
+      <c r="W1199" s="12"/>
+      <c r="X1199" s="12"/>
+      <c r="Y1199" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1199" s="12"/>
+      <c r="AA1199" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1199" s="12"/>
+      <c r="AC1199" s="12"/>
+      <c r="AD1199" s="26"/>
+    </row>
+    <row r="1200" ht="15.75" customHeight="1">
+      <c r="B1200" s="10"/>
+      <c r="J1200" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="K1200" s="12"/>
+      <c r="L1200" s="12"/>
+      <c r="M1200" s="12"/>
+      <c r="N1200" s="12"/>
+      <c r="O1200" s="12"/>
+      <c r="P1200" s="12"/>
+      <c r="Q1200" s="12"/>
+      <c r="R1200" s="12"/>
+      <c r="S1200" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="T1200" s="12"/>
+      <c r="U1200" s="12"/>
+      <c r="V1200" s="12"/>
+      <c r="W1200" s="12"/>
+      <c r="X1200" s="12"/>
+      <c r="Y1200" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1200" s="12"/>
+      <c r="AA1200" s="15"/>
+      <c r="AD1200" s="22"/>
+    </row>
+    <row r="1201" ht="15.75" customHeight="1">
+      <c r="B1201" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1201" s="12"/>
+      <c r="D1201" s="12"/>
+      <c r="E1201" s="12"/>
+      <c r="F1201" s="12"/>
+      <c r="G1201" s="12"/>
+      <c r="H1201" s="12"/>
+      <c r="I1201" s="12"/>
+      <c r="J1201" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="K1201" s="12"/>
+      <c r="L1201" s="12"/>
+      <c r="M1201" s="12"/>
+      <c r="N1201" s="12"/>
+      <c r="O1201" s="12"/>
+      <c r="P1201" s="12"/>
+      <c r="Q1201" s="12"/>
+      <c r="R1201" s="12"/>
+      <c r="S1201" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="T1201" s="12"/>
+      <c r="U1201" s="12"/>
+      <c r="V1201" s="12"/>
+      <c r="W1201" s="12"/>
+      <c r="X1201" s="12"/>
+      <c r="Y1201" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1201" s="12"/>
+      <c r="AA1201" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1201" s="12"/>
+      <c r="AC1201" s="12"/>
+      <c r="AD1201" s="26"/>
+    </row>
+    <row r="1202" ht="15.75" customHeight="1">
+      <c r="B1202" s="10"/>
+      <c r="J1202" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="K1202" s="12"/>
+      <c r="L1202" s="12"/>
+      <c r="M1202" s="12"/>
+      <c r="N1202" s="12"/>
+      <c r="O1202" s="12"/>
+      <c r="P1202" s="12"/>
+      <c r="Q1202" s="12"/>
+      <c r="R1202" s="12"/>
+      <c r="S1202" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="T1202" s="12"/>
+      <c r="U1202" s="12"/>
+      <c r="V1202" s="12"/>
+      <c r="W1202" s="12"/>
+      <c r="X1202" s="12"/>
+      <c r="Y1202" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1202" s="12"/>
+      <c r="AA1202" s="15"/>
+      <c r="AD1202" s="22"/>
+    </row>
+    <row r="1203" ht="15.75" customHeight="1">
+      <c r="B1203" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="C1203" s="12"/>
+      <c r="D1203" s="12"/>
+      <c r="E1203" s="12"/>
+      <c r="F1203" s="12"/>
+      <c r="G1203" s="12"/>
+      <c r="H1203" s="12"/>
+      <c r="I1203" s="12"/>
+      <c r="J1203" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="K1203" s="12"/>
+      <c r="L1203" s="12"/>
+      <c r="M1203" s="12"/>
+      <c r="N1203" s="12"/>
+      <c r="O1203" s="12"/>
+      <c r="P1203" s="12"/>
+      <c r="Q1203" s="12"/>
+      <c r="R1203" s="12"/>
+      <c r="S1203" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="T1203" s="12"/>
+      <c r="U1203" s="12"/>
+      <c r="V1203" s="12"/>
+      <c r="W1203" s="12"/>
+      <c r="X1203" s="12"/>
+      <c r="Y1203" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1203" s="12"/>
+      <c r="AA1203" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1203" s="12"/>
+      <c r="AC1203" s="12"/>
+      <c r="AD1203" s="26"/>
+    </row>
+    <row r="1204" ht="15.75" customHeight="1">
+      <c r="B1204" s="10"/>
+      <c r="J1204" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="K1204" s="12"/>
+      <c r="L1204" s="12"/>
+      <c r="M1204" s="12"/>
+      <c r="N1204" s="12"/>
+      <c r="O1204" s="12"/>
+      <c r="P1204" s="12"/>
+      <c r="Q1204" s="12"/>
+      <c r="R1204" s="12"/>
+      <c r="S1204" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="T1204" s="12"/>
+      <c r="U1204" s="12"/>
+      <c r="V1204" s="12"/>
+      <c r="W1204" s="12"/>
+      <c r="X1204" s="12"/>
+      <c r="Y1204" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1204" s="12"/>
+      <c r="AA1204" s="15"/>
+      <c r="AD1204" s="22"/>
+    </row>
+    <row r="1205" ht="15.75" customHeight="1">
+      <c r="B1205" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1205" s="12"/>
+      <c r="D1205" s="12"/>
+      <c r="E1205" s="12"/>
+      <c r="F1205" s="12"/>
+      <c r="G1205" s="12"/>
+      <c r="H1205" s="12"/>
+      <c r="I1205" s="12"/>
+      <c r="J1205" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="K1205" s="12"/>
+      <c r="L1205" s="12"/>
+      <c r="M1205" s="12"/>
+      <c r="N1205" s="12"/>
+      <c r="O1205" s="12"/>
+      <c r="P1205" s="12"/>
+      <c r="Q1205" s="12"/>
+      <c r="R1205" s="12"/>
+      <c r="S1205" s="14" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="1195" ht="15.75" customHeight="1">
-      <c r="E1195" s="2" t="s">
+      <c r="T1205" s="12"/>
+      <c r="U1205" s="12"/>
+      <c r="V1205" s="12"/>
+      <c r="W1205" s="12"/>
+      <c r="X1205" s="12"/>
+      <c r="Y1205" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1205" s="12"/>
+      <c r="AA1205" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1205" s="12"/>
+      <c r="AC1205" s="12"/>
+      <c r="AD1205" s="26"/>
+    </row>
+    <row r="1206" ht="15.75" customHeight="1">
+      <c r="B1206" s="23" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="1196" ht="15.75" customHeight="1">
-      <c r="E1196" s="2" t="s">
+      <c r="C1206" s="12"/>
+      <c r="D1206" s="12"/>
+      <c r="E1206" s="12"/>
+      <c r="F1206" s="12"/>
+      <c r="G1206" s="12"/>
+      <c r="H1206" s="12"/>
+      <c r="I1206" s="12"/>
+      <c r="J1206" s="14" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="1197" ht="15.75" customHeight="1"/>
-    <row r="1198" ht="15.75" customHeight="1">
-      <c r="D1198" s="1" t="s">
+      <c r="K1206" s="12"/>
+      <c r="L1206" s="12"/>
+      <c r="M1206" s="12"/>
+      <c r="N1206" s="12"/>
+      <c r="O1206" s="12"/>
+      <c r="P1206" s="12"/>
+      <c r="Q1206" s="12"/>
+      <c r="R1206" s="12"/>
+      <c r="S1206" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="S1198" s="1" t="s">
+      <c r="T1206" s="12"/>
+      <c r="U1206" s="12"/>
+      <c r="V1206" s="12"/>
+      <c r="W1206" s="12"/>
+      <c r="X1206" s="12"/>
+      <c r="Y1206" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1206" s="12"/>
+      <c r="AA1206" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1206" s="12"/>
+      <c r="AC1206" s="12"/>
+      <c r="AD1206" s="26"/>
+    </row>
+    <row r="1207" ht="15.75" customHeight="1">
+      <c r="B1207" s="23" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="1199" ht="15.75" customHeight="1"/>
-    <row r="1200" ht="15.75" customHeight="1">
-      <c r="E1200" s="2" t="s">
+      <c r="C1207" s="12"/>
+      <c r="D1207" s="12"/>
+      <c r="E1207" s="12"/>
+      <c r="F1207" s="12"/>
+      <c r="G1207" s="12"/>
+      <c r="H1207" s="12"/>
+      <c r="I1207" s="12"/>
+      <c r="J1207" s="14" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="1201" ht="15.75" customHeight="1"/>
-    <row r="1202" ht="15.75" customHeight="1">
-      <c r="E1202" s="2" t="s">
+      <c r="K1207" s="12"/>
+      <c r="L1207" s="12"/>
+      <c r="M1207" s="12"/>
+      <c r="N1207" s="12"/>
+      <c r="O1207" s="12"/>
+      <c r="P1207" s="12"/>
+      <c r="Q1207" s="12"/>
+      <c r="R1207" s="12"/>
+      <c r="S1207" s="14" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="1203" ht="15.75" customHeight="1">
-      <c r="E1203" s="2" t="s">
+      <c r="T1207" s="12"/>
+      <c r="U1207" s="12"/>
+      <c r="V1207" s="12"/>
+      <c r="W1207" s="12"/>
+      <c r="X1207" s="12"/>
+      <c r="Y1207" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1207" s="12"/>
+      <c r="AA1207" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1207" s="12"/>
+      <c r="AC1207" s="12"/>
+      <c r="AD1207" s="26"/>
+    </row>
+    <row r="1208" ht="15.75" customHeight="1">
+      <c r="B1208" s="23" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="1204" ht="15.75" customHeight="1">
-      <c r="F1204" s="2" t="s">
+      <c r="C1208" s="12"/>
+      <c r="D1208" s="12"/>
+      <c r="E1208" s="12"/>
+      <c r="F1208" s="12"/>
+      <c r="G1208" s="12"/>
+      <c r="H1208" s="12"/>
+      <c r="I1208" s="12"/>
+      <c r="J1208" s="14" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="1205" ht="15.75" customHeight="1"/>
-    <row r="1206" ht="15.75" customHeight="1">
-      <c r="E1206" s="2" t="s">
+      <c r="K1208" s="12"/>
+      <c r="L1208" s="12"/>
+      <c r="M1208" s="12"/>
+      <c r="N1208" s="12"/>
+      <c r="O1208" s="12"/>
+      <c r="P1208" s="12"/>
+      <c r="Q1208" s="12"/>
+      <c r="R1208" s="12"/>
+      <c r="S1208" s="14" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="1207" ht="15.75" customHeight="1"/>
-    <row r="1208" ht="15.75" customHeight="1"/>
-    <row r="1209" ht="15.75" customHeight="1"/>
-    <row r="1210" ht="15.75" customHeight="1"/>
+      <c r="T1208" s="12"/>
+      <c r="U1208" s="12"/>
+      <c r="V1208" s="12"/>
+      <c r="W1208" s="12"/>
+      <c r="X1208" s="12"/>
+      <c r="Y1208" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1208" s="12"/>
+      <c r="AA1208" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB1208" s="12"/>
+      <c r="AC1208" s="12"/>
+      <c r="AD1208" s="26"/>
+    </row>
+    <row r="1209" ht="15.75" customHeight="1">
+      <c r="B1209" s="8"/>
+      <c r="C1209" s="8"/>
+      <c r="D1209" s="8"/>
+      <c r="E1209" s="8"/>
+      <c r="F1209" s="8"/>
+      <c r="G1209" s="8"/>
+      <c r="H1209" s="8"/>
+      <c r="I1209" s="8"/>
+      <c r="J1209" s="8"/>
+      <c r="K1209" s="8"/>
+      <c r="L1209" s="8"/>
+      <c r="M1209" s="8"/>
+      <c r="N1209" s="8"/>
+      <c r="O1209" s="8"/>
+      <c r="P1209" s="8"/>
+      <c r="Q1209" s="8"/>
+      <c r="R1209" s="8"/>
+      <c r="S1209" s="8"/>
+      <c r="T1209" s="8"/>
+      <c r="U1209" s="8"/>
+      <c r="V1209" s="8"/>
+      <c r="W1209" s="8"/>
+      <c r="X1209" s="8"/>
+      <c r="Y1209" s="8"/>
+      <c r="Z1209" s="8"/>
+      <c r="AA1209" s="8"/>
+      <c r="AB1209" s="8"/>
+      <c r="AC1209" s="8"/>
+      <c r="AD1209" s="8"/>
+    </row>
+    <row r="1210" ht="15.75" customHeight="1">
+      <c r="C1210" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
     <row r="1211" ht="15.75" customHeight="1"/>
-    <row r="1212" ht="15.75" customHeight="1"/>
+    <row r="1212" ht="15.75" customHeight="1">
+      <c r="D1212" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="S1212" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
     <row r="1213" ht="15.75" customHeight="1"/>
-    <row r="1214" ht="15.75" customHeight="1"/>
-    <row r="1215" ht="15.75" customHeight="1"/>
-    <row r="1216" ht="15.75" customHeight="1"/>
+    <row r="1214" ht="15.75" customHeight="1">
+      <c r="E1214" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="1215" ht="15.75" customHeight="1">
+      <c r="E1215" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="1216" ht="15.75" customHeight="1">
+      <c r="E1216" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
     <row r="1217" ht="15.75" customHeight="1"/>
-    <row r="1218" ht="15.75" customHeight="1"/>
+    <row r="1218" ht="15.75" customHeight="1">
+      <c r="D1218" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="S1218" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
     <row r="1219" ht="15.75" customHeight="1"/>
-    <row r="1220" ht="15.75" customHeight="1"/>
+    <row r="1220" ht="15.75" customHeight="1">
+      <c r="E1220" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
     <row r="1221" ht="15.75" customHeight="1"/>
     <row r="1222" ht="15.75" customHeight="1"/>
     <row r="1223" ht="15.75" customHeight="1">
-      <c r="D1223" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="S1223" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="1224" ht="15.75" customHeight="1"/>
+      <c r="E1223" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="1224" ht="15.75" customHeight="1">
+      <c r="E1224" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
     <row r="1225" ht="15.75" customHeight="1">
-      <c r="E1225" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="1226" ht="15.75" customHeight="1">
-      <c r="E1226" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="1227" ht="15.75" customHeight="1"/>
-    <row r="1228" ht="15.75" customHeight="1">
-      <c r="F1228" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="1229" ht="15.75" customHeight="1"/>
-    <row r="1230" ht="15.75" customHeight="1">
-      <c r="L1230" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="R1230" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1230" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
+      <c r="F1225" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1226" ht="15.75" customHeight="1"/>
+    <row r="1227" ht="15.75" customHeight="1">
+      <c r="E1227" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1228" ht="15.75" customHeight="1"/>
+    <row r="1229" ht="15.75" customHeight="1">
+      <c r="D1229" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="S1229" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1230" ht="15.75" customHeight="1"/>
     <row r="1231" ht="15.75" customHeight="1">
-      <c r="M1231" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="R1231" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1231" s="2" t="s">
-        <v>406</v>
+      <c r="E1231" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="1232" ht="15.75" customHeight="1">
-      <c r="L1232" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="R1232" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1232" s="2" t="s">
-        <v>407</v>
+      <c r="E1232" s="2" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="1233" ht="15.75" customHeight="1"/>
     <row r="1234" ht="15.75" customHeight="1">
-      <c r="E1234" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="1235" ht="15.75" customHeight="1">
-      <c r="E1235" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1235" s="8"/>
-      <c r="G1235" s="8"/>
-      <c r="H1235" s="8"/>
-      <c r="I1235" s="8"/>
-      <c r="J1235" s="8"/>
-      <c r="K1235" s="8"/>
-      <c r="L1235" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1235" s="8"/>
-      <c r="N1235" s="8"/>
-      <c r="O1235" s="8"/>
-      <c r="P1235" s="8"/>
-      <c r="Q1235" s="8"/>
-      <c r="R1235" s="8"/>
-      <c r="S1235" s="8"/>
-      <c r="T1235" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="U1235" s="8"/>
-      <c r="V1235" s="8"/>
-      <c r="W1235" s="8"/>
-      <c r="X1235" s="8"/>
-      <c r="Y1235" s="8"/>
-      <c r="Z1235" s="8"/>
-      <c r="AA1235" s="8"/>
-      <c r="AB1235" s="8"/>
-      <c r="AC1235" s="8"/>
-      <c r="AD1235" s="10"/>
-    </row>
+      <c r="F1234" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="1235" ht="15.75" customHeight="1"/>
     <row r="1236" ht="15.75" customHeight="1">
-      <c r="E1236" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="F1236" s="12"/>
-      <c r="G1236" s="12"/>
-      <c r="H1236" s="12"/>
-      <c r="I1236" s="12"/>
-      <c r="J1236" s="12"/>
-      <c r="K1236" s="12"/>
-      <c r="L1236" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="M1236" s="12"/>
-      <c r="N1236" s="12"/>
-      <c r="O1236" s="12"/>
-      <c r="P1236" s="12"/>
-      <c r="Q1236" s="12"/>
-      <c r="R1236" s="12"/>
-      <c r="S1236" s="12"/>
-      <c r="T1236" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="U1236" s="12"/>
-      <c r="V1236" s="12"/>
-      <c r="W1236" s="12"/>
-      <c r="X1236" s="12"/>
-      <c r="Y1236" s="12"/>
-      <c r="Z1236" s="12"/>
-      <c r="AA1236" s="12"/>
-      <c r="AB1236" s="12"/>
-      <c r="AC1236" s="12"/>
-      <c r="AD1236" s="10"/>
+      <c r="L1236" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="R1236" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1236" s="2" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="1237" ht="15.75" customHeight="1">
-      <c r="E1237" s="10"/>
-      <c r="L1237" s="15"/>
-      <c r="T1237" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="U1237" s="12"/>
-      <c r="V1237" s="12"/>
-      <c r="W1237" s="12"/>
-      <c r="X1237" s="12"/>
-      <c r="Y1237" s="12"/>
-      <c r="Z1237" s="12"/>
-      <c r="AA1237" s="12"/>
-      <c r="AB1237" s="12"/>
-      <c r="AC1237" s="12"/>
-      <c r="AD1237" s="10"/>
+      <c r="M1237" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="R1237" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1237" s="2" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="1238" ht="15.75" customHeight="1">
-      <c r="E1238" s="10"/>
-      <c r="L1238" s="15"/>
-      <c r="T1238" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="U1238" s="12"/>
-      <c r="V1238" s="12"/>
-      <c r="W1238" s="12"/>
-      <c r="X1238" s="12"/>
-      <c r="Y1238" s="12"/>
-      <c r="Z1238" s="12"/>
-      <c r="AA1238" s="12"/>
-      <c r="AB1238" s="12"/>
-      <c r="AC1238" s="12"/>
-      <c r="AD1238" s="10"/>
-    </row>
-    <row r="1239" ht="15.75" customHeight="1">
-      <c r="E1239" s="8"/>
-      <c r="F1239" s="8"/>
-      <c r="G1239" s="8"/>
-      <c r="H1239" s="8"/>
-      <c r="I1239" s="8"/>
-      <c r="J1239" s="8"/>
-      <c r="K1239" s="8"/>
-      <c r="L1239" s="8"/>
-      <c r="M1239" s="8"/>
-      <c r="N1239" s="8"/>
-      <c r="O1239" s="8"/>
-      <c r="P1239" s="8"/>
-      <c r="Q1239" s="8"/>
-      <c r="R1239" s="8"/>
-      <c r="S1239" s="8"/>
-      <c r="T1239" s="8"/>
-      <c r="U1239" s="8"/>
-      <c r="V1239" s="8"/>
-      <c r="W1239" s="8"/>
-      <c r="X1239" s="8"/>
-      <c r="Y1239" s="8"/>
-      <c r="Z1239" s="8"/>
-      <c r="AA1239" s="8"/>
-      <c r="AB1239" s="8"/>
-      <c r="AC1239" s="8"/>
-    </row>
+      <c r="L1238" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1238" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1238" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="1239" ht="15.75" customHeight="1"/>
     <row r="1240" ht="15.75" customHeight="1">
       <c r="E1240" s="2" t="s">
-        <v>412</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1241" ht="15.75" customHeight="1">
-      <c r="E1241" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="1242" ht="15.75" customHeight="1"/>
+      <c r="E1241" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1241" s="8"/>
+      <c r="G1241" s="8"/>
+      <c r="H1241" s="8"/>
+      <c r="I1241" s="8"/>
+      <c r="J1241" s="8"/>
+      <c r="K1241" s="8"/>
+      <c r="L1241" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1241" s="8"/>
+      <c r="N1241" s="8"/>
+      <c r="O1241" s="8"/>
+      <c r="P1241" s="8"/>
+      <c r="Q1241" s="8"/>
+      <c r="R1241" s="8"/>
+      <c r="S1241" s="8"/>
+      <c r="T1241" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="U1241" s="8"/>
+      <c r="V1241" s="8"/>
+      <c r="W1241" s="8"/>
+      <c r="X1241" s="8"/>
+      <c r="Y1241" s="8"/>
+      <c r="Z1241" s="8"/>
+      <c r="AA1241" s="8"/>
+      <c r="AB1241" s="8"/>
+      <c r="AC1241" s="8"/>
+      <c r="AD1241" s="10"/>
+    </row>
+    <row r="1242" ht="15.75" customHeight="1">
+      <c r="E1242" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="F1242" s="12"/>
+      <c r="G1242" s="12"/>
+      <c r="H1242" s="12"/>
+      <c r="I1242" s="12"/>
+      <c r="J1242" s="12"/>
+      <c r="K1242" s="12"/>
+      <c r="L1242" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="M1242" s="12"/>
+      <c r="N1242" s="12"/>
+      <c r="O1242" s="12"/>
+      <c r="P1242" s="12"/>
+      <c r="Q1242" s="12"/>
+      <c r="R1242" s="12"/>
+      <c r="S1242" s="12"/>
+      <c r="T1242" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="U1242" s="12"/>
+      <c r="V1242" s="12"/>
+      <c r="W1242" s="12"/>
+      <c r="X1242" s="12"/>
+      <c r="Y1242" s="12"/>
+      <c r="Z1242" s="12"/>
+      <c r="AA1242" s="12"/>
+      <c r="AB1242" s="12"/>
+      <c r="AC1242" s="12"/>
+      <c r="AD1242" s="10"/>
+    </row>
     <row r="1243" ht="15.75" customHeight="1">
-      <c r="E1243" s="2" t="s">
-        <v>414</v>
-      </c>
+      <c r="E1243" s="10"/>
+      <c r="L1243" s="15"/>
+      <c r="T1243" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="U1243" s="12"/>
+      <c r="V1243" s="12"/>
+      <c r="W1243" s="12"/>
+      <c r="X1243" s="12"/>
+      <c r="Y1243" s="12"/>
+      <c r="Z1243" s="12"/>
+      <c r="AA1243" s="12"/>
+      <c r="AB1243" s="12"/>
+      <c r="AC1243" s="12"/>
+      <c r="AD1243" s="10"/>
     </row>
     <row r="1244" ht="15.75" customHeight="1">
-      <c r="F1244" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="1245" ht="15.75" customHeight="1"/>
+      <c r="E1244" s="10"/>
+      <c r="L1244" s="15"/>
+      <c r="T1244" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="U1244" s="12"/>
+      <c r="V1244" s="12"/>
+      <c r="W1244" s="12"/>
+      <c r="X1244" s="12"/>
+      <c r="Y1244" s="12"/>
+      <c r="Z1244" s="12"/>
+      <c r="AA1244" s="12"/>
+      <c r="AB1244" s="12"/>
+      <c r="AC1244" s="12"/>
+      <c r="AD1244" s="10"/>
+    </row>
+    <row r="1245" ht="15.75" customHeight="1">
+      <c r="E1245" s="8"/>
+      <c r="F1245" s="8"/>
+      <c r="G1245" s="8"/>
+      <c r="H1245" s="8"/>
+      <c r="I1245" s="8"/>
+      <c r="J1245" s="8"/>
+      <c r="K1245" s="8"/>
+      <c r="L1245" s="8"/>
+      <c r="M1245" s="8"/>
+      <c r="N1245" s="8"/>
+      <c r="O1245" s="8"/>
+      <c r="P1245" s="8"/>
+      <c r="Q1245" s="8"/>
+      <c r="R1245" s="8"/>
+      <c r="S1245" s="8"/>
+      <c r="T1245" s="8"/>
+      <c r="U1245" s="8"/>
+      <c r="V1245" s="8"/>
+      <c r="W1245" s="8"/>
+      <c r="X1245" s="8"/>
+      <c r="Y1245" s="8"/>
+      <c r="Z1245" s="8"/>
+      <c r="AA1245" s="8"/>
+      <c r="AB1245" s="8"/>
+      <c r="AC1245" s="8"/>
+    </row>
     <row r="1246" ht="15.75" customHeight="1">
       <c r="E1246" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="1247" ht="15.75" customHeight="1"/>
-    <row r="1248" ht="15.75" customHeight="1">
-      <c r="D1248" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="S1248" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="1249" ht="15.75" customHeight="1"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="1247" ht="15.75" customHeight="1">
+      <c r="E1247" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="1248" ht="15.75" customHeight="1"/>
+    <row r="1249" ht="15.75" customHeight="1">
+      <c r="E1249" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
     <row r="1250" ht="15.75" customHeight="1">
-      <c r="E1250" s="2" t="s">
-        <v>417</v>
+      <c r="F1250" s="2" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="1251" ht="15.75" customHeight="1"/>
     <row r="1252" ht="15.75" customHeight="1">
       <c r="E1252" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="1253" ht="15.75" customHeight="1">
-      <c r="F1253" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="1254" ht="15.75" customHeight="1"/>
-    <row r="1255" ht="15.75" customHeight="1">
-      <c r="F1255" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="J1255" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1255" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="1253" ht="15.75" customHeight="1"/>
+    <row r="1254" ht="15.75" customHeight="1">
+      <c r="D1254" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="S1254" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1255" ht="15.75" customHeight="1"/>
     <row r="1256" ht="15.75" customHeight="1">
-      <c r="I1256" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="J1256" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1256" s="2" t="s">
-        <v>423</v>
+      <c r="E1256" s="2" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="1257" ht="15.75" customHeight="1"/>
     <row r="1258" ht="15.75" customHeight="1">
-      <c r="H1258" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="I1258" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1258" s="5">
-        <v>18240</v>
-      </c>
-      <c r="M1258" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1258" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="T1258" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1258" s="6">
-        <v>100</v>
-      </c>
-      <c r="Y1258" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1258" s="17">
-        <v>3.63</v>
-      </c>
-      <c r="AC1258" s="2" t="s">
-        <v>142</v>
+      <c r="E1258" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="1259" ht="15.75" customHeight="1">
       <c r="F1259" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="1260" ht="15.75" customHeight="1"/>
     <row r="1261" ht="15.75" customHeight="1">
-      <c r="E1261" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="1262" ht="15.75" customHeight="1"/>
-    <row r="1263" ht="15.75" customHeight="1">
-      <c r="D1263" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="S1263" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="1264" ht="15.75" customHeight="1"/>
+      <c r="F1261" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="J1261" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1261" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="1262" ht="15.75" customHeight="1">
+      <c r="I1262" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J1262" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1262" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="1263" ht="15.75" customHeight="1"/>
+    <row r="1264" ht="15.75" customHeight="1">
+      <c r="H1264" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="I1264" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1264" s="5">
+        <v>18240</v>
+      </c>
+      <c r="M1264" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1264" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="T1264" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1264" s="6">
+        <v>100</v>
+      </c>
+      <c r="Y1264" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1264" s="17">
+        <v>3.63</v>
+      </c>
+      <c r="AC1264" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
     <row r="1265" ht="15.75" customHeight="1">
-      <c r="E1265" s="2" t="s">
-        <v>428</v>
+      <c r="F1265" s="2" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="1266" ht="15.75" customHeight="1"/>
-    <row r="1267" ht="15.75" customHeight="1"/>
+    <row r="1267" ht="15.75" customHeight="1">
+      <c r="E1267" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
     <row r="1268" ht="15.75" customHeight="1"/>
     <row r="1269" ht="15.75" customHeight="1"/>
     <row r="1270" ht="15.75" customHeight="1">
-      <c r="E1270" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="1271" ht="15.75" customHeight="1">
-      <c r="H1271" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="I1271" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1271" s="5">
-        <v>18240</v>
-      </c>
-      <c r="M1271" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1271" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="T1271" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1271" s="6">
-        <v>100</v>
-      </c>
-      <c r="Y1271" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1271" s="17">
-        <v>3.63</v>
-      </c>
-      <c r="AC1271" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
+      <c r="D1270" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="S1270" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1271" ht="15.75" customHeight="1"/>
     <row r="1272" ht="15.75" customHeight="1">
-      <c r="F1272" s="2" t="s">
-        <v>429</v>
+      <c r="E1272" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="1273" ht="15.75" customHeight="1"/>
     <row r="1274" ht="15.75" customHeight="1">
       <c r="E1274" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="1275" ht="15.75" customHeight="1"/>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="1275" ht="15.75" customHeight="1">
+      <c r="H1275" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="I1275" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1275" s="5">
+        <v>18240</v>
+      </c>
+      <c r="M1275" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1275" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="T1275" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1275" s="6">
+        <v>100</v>
+      </c>
+      <c r="Y1275" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1275" s="17">
+        <v>3.63</v>
+      </c>
+      <c r="AC1275" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
     <row r="1276" ht="15.75" customHeight="1">
-      <c r="D1276" s="1" t="s">
-        <v>430</v>
+      <c r="F1276" s="2" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="1277" ht="15.75" customHeight="1"/>
     <row r="1278" ht="15.75" customHeight="1">
-      <c r="E1278" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="T1278" s="1" t="s">
-        <v>432</v>
+      <c r="E1278" s="2" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="1279" ht="15.75" customHeight="1"/>
     <row r="1280" ht="15.75" customHeight="1">
-      <c r="E1280" s="2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="1281" ht="15.75" customHeight="1">
-      <c r="F1281" s="2" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="1282" ht="15.75" customHeight="1"/>
-    <row r="1283" ht="15.75" customHeight="1">
-      <c r="E1283" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="J1283" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1283" s="2" t="s">
-        <v>436</v>
-      </c>
-    </row>
+      <c r="D1280" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="1281" ht="15.75" customHeight="1"/>
+    <row r="1282" ht="15.75" customHeight="1">
+      <c r="E1282" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="T1282" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="1283" ht="15.75" customHeight="1"/>
     <row r="1284" ht="15.75" customHeight="1">
-      <c r="H1284" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="J1284" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1284" s="2" t="s">
-        <v>438</v>
+      <c r="E1284" s="2" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="1285" ht="15.75" customHeight="1">
-      <c r="H1285" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J1285" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1285" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="1286" ht="15.75" customHeight="1">
-      <c r="H1286" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J1286" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1286" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
+      <c r="F1285" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="1286" ht="15.75" customHeight="1"/>
     <row r="1287" ht="15.75" customHeight="1">
-      <c r="H1287" s="3" t="s">
-        <v>441</v>
+      <c r="E1287" s="3" t="s">
+        <v>448</v>
       </c>
       <c r="J1287" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1287" s="2" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1288" ht="15.75" customHeight="1">
       <c r="H1288" s="3" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="J1288" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1288" s="2" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1289" ht="15.75" customHeight="1">
       <c r="H1289" s="3" t="s">
-        <v>445</v>
+        <v>157</v>
       </c>
       <c r="J1289" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1289" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1290" ht="15.75" customHeight="1">
       <c r="H1290" s="3" t="s">
-        <v>447</v>
+        <v>159</v>
       </c>
       <c r="J1290" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1290" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="1291" ht="15.75" customHeight="1"/>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="1291" ht="15.75" customHeight="1">
+      <c r="H1291" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="J1291" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1291" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
     <row r="1292" ht="15.75" customHeight="1">
-      <c r="G1292" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I1292" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1292" s="5">
-        <v>27</v>
-      </c>
-      <c r="L1292" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1292" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="Y1292" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1292" s="5">
-        <v>20.8</v>
-      </c>
-      <c r="AC1292" s="2" t="s">
-        <v>449</v>
+      <c r="H1292" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="J1292" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1292" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="1293" ht="15.75" customHeight="1">
       <c r="H1293" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="I1293" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1293" s="6">
-        <v>1</v>
-      </c>
-      <c r="K1293" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="L1293" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="N1293" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1293" s="6">
-        <v>38</v>
-      </c>
-      <c r="P1293" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1293" s="6">
-        <v>128</v>
-      </c>
-      <c r="Y1293" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1293" s="17">
-        <v>1.15</v>
+        <v>458</v>
+      </c>
+      <c r="J1293" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1293" s="2" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="1294" ht="15.75" customHeight="1">
-      <c r="G1294" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="I1294" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1294" s="17">
-        <v>1.15</v>
-      </c>
-      <c r="L1294" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1294" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="U1294" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="V1294" s="6">
-        <v>38</v>
-      </c>
-      <c r="Y1294" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1294" s="6">
-        <v>1054</v>
-      </c>
-      <c r="AC1294" s="2" t="s">
-        <v>106</v>
+      <c r="H1294" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J1294" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1294" s="2" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="1295" ht="15.75" customHeight="1"/>
     <row r="1296" ht="15.75" customHeight="1">
-      <c r="E1296" s="2" t="s">
-        <v>453</v>
+      <c r="G1296" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1296" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1296" s="5">
+        <v>27</v>
+      </c>
+      <c r="L1296" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1296" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="Y1296" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1296" s="5">
+        <v>20.8</v>
+      </c>
+      <c r="AC1296" s="2" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="1297" ht="15.75" customHeight="1">
-      <c r="E1297" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="1298" ht="15.75" customHeight="1"/>
-    <row r="1299" ht="15.75" customHeight="1">
-      <c r="F1299" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="1300" ht="15.75" customHeight="1"/>
+      <c r="H1297" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="I1297" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1297" s="6">
+        <v>1</v>
+      </c>
+      <c r="K1297" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="L1297" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N1297" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1297" s="6">
+        <v>38</v>
+      </c>
+      <c r="P1297" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1297" s="6">
+        <v>128</v>
+      </c>
+      <c r="Y1297" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1297" s="17">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="1298" ht="15.75" customHeight="1">
+      <c r="G1298" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="I1298" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1298" s="17">
+        <v>1.15</v>
+      </c>
+      <c r="L1298" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1298" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="U1298" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1298" s="6">
+        <v>38</v>
+      </c>
+      <c r="Y1298" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1298" s="6">
+        <v>1054</v>
+      </c>
+      <c r="AC1298" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1299" ht="15.75" customHeight="1"/>
+    <row r="1300" ht="15.75" customHeight="1">
+      <c r="E1300" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
     <row r="1301" ht="15.75" customHeight="1">
       <c r="E1301" s="2" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1302" ht="15.75" customHeight="1"/>
     <row r="1303" ht="15.75" customHeight="1">
       <c r="F1303" s="2" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1304" ht="15.75" customHeight="1"/>
     <row r="1305" ht="15.75" customHeight="1">
-      <c r="E1305" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="S1305" s="1" t="s">
-        <v>400</v>
+      <c r="E1305" s="2" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="1306" ht="15.75" customHeight="1"/>
     <row r="1307" ht="15.75" customHeight="1">
-      <c r="E1307" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="1308" ht="15.75" customHeight="1">
-      <c r="E1308" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
+      <c r="F1307" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1308" ht="15.75" customHeight="1"/>
     <row r="1309" ht="15.75" customHeight="1"/>
-    <row r="1310" ht="15.75" customHeight="1">
-      <c r="F1310" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
+    <row r="1310" ht="15.75" customHeight="1"/>
     <row r="1311" ht="15.75" customHeight="1"/>
-    <row r="1312" ht="15.75" customHeight="1">
-      <c r="F1312" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="J1312" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1312" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="1313" ht="15.75" customHeight="1">
-      <c r="H1313" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="J1313" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1313" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
+    <row r="1312" ht="15.75" customHeight="1"/>
+    <row r="1313" ht="15.75" customHeight="1"/>
     <row r="1314" ht="15.75" customHeight="1"/>
-    <row r="1315" ht="15.75" customHeight="1">
-      <c r="F1315" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="1316" ht="15.75" customHeight="1">
-      <c r="F1316" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
+    <row r="1315" ht="15.75" customHeight="1"/>
+    <row r="1316" ht="15.75" customHeight="1"/>
     <row r="1317" ht="15.75" customHeight="1">
       <c r="E1317" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="S1317" s="1" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
     </row>
     <row r="1318" ht="15.75" customHeight="1"/>
     <row r="1319" ht="15.75" customHeight="1">
       <c r="E1319" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1320" ht="15.75" customHeight="1">
       <c r="E1320" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="1321" ht="15.75" customHeight="1">
-      <c r="E1321" s="2" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="1322" ht="15.75" customHeight="1"/>
-    <row r="1323" ht="15.75" customHeight="1">
-      <c r="F1323" s="2" t="s">
-        <v>472</v>
-      </c>
-    </row>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1321" ht="15.75" customHeight="1"/>
+    <row r="1322" ht="15.75" customHeight="1">
+      <c r="F1322" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="1323" ht="15.75" customHeight="1"/>
     <row r="1324" ht="15.75" customHeight="1">
-      <c r="F1324" s="2" t="s">
-        <v>473</v>
+      <c r="F1324" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J1324" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1324" s="2" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="1325" ht="15.75" customHeight="1">
-      <c r="G1325" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="I1325" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1325" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="L1325" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1325" s="6">
-        <v>390</v>
-      </c>
-      <c r="O1325" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1325" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="T1325" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1325" s="6">
-        <v>38</v>
-      </c>
-      <c r="Y1325" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1325" s="6">
-        <v>1170</v>
-      </c>
-      <c r="AC1325" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="1326" ht="15.75" customHeight="1">
-      <c r="H1326" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="I1326" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1326" s="6">
-        <v>100</v>
-      </c>
-      <c r="L1326" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="M1326" s="6">
-        <v>1170</v>
-      </c>
-      <c r="Y1326" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1326" s="6">
-        <v>1270</v>
-      </c>
-      <c r="AC1326" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="1327" ht="15.75" customHeight="1"/>
+      <c r="H1325" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="J1325" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1325" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1326" ht="15.75" customHeight="1"/>
+    <row r="1327" ht="15.75" customHeight="1">
+      <c r="F1327" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
     <row r="1328" ht="15.75" customHeight="1">
-      <c r="D1328" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="S1328" s="1" t="s">
-        <v>400</v>
+      <c r="F1328" s="2" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="1329" ht="15.75" customHeight="1"/>
     <row r="1330" ht="15.75" customHeight="1">
-      <c r="E1330" s="2" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="1331" ht="15.75" customHeight="1">
-      <c r="E1331" s="2" t="s">
-        <v>479</v>
-      </c>
-    </row>
+      <c r="E1330" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="S1330" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1331" ht="15.75" customHeight="1"/>
     <row r="1332" ht="15.75" customHeight="1">
       <c r="E1332" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="1333" ht="15.75" customHeight="1"/>
+        <v>482</v>
+      </c>
+    </row>
+    <row r="1333" ht="15.75" customHeight="1">
+      <c r="E1333" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
     <row r="1334" ht="15.75" customHeight="1">
-      <c r="F1334" s="2" t="s">
-        <v>480</v>
+      <c r="E1334" s="2" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="1335" ht="15.75" customHeight="1"/>
     <row r="1336" ht="15.75" customHeight="1">
-      <c r="F1336" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="J1336" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1336" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="1337" ht="15.75" customHeight="1"/>
+      <c r="F1336" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="1337" ht="15.75" customHeight="1">
+      <c r="F1337" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
     <row r="1338" ht="15.75" customHeight="1">
-      <c r="F1338" s="2" t="s">
-        <v>483</v>
+      <c r="G1338" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="I1338" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1338" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="L1338" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1338" s="6">
+        <v>390</v>
+      </c>
+      <c r="O1338" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1338" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="T1338" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1338" s="6">
+        <v>38</v>
+      </c>
+      <c r="Y1338" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1338" s="6">
+        <v>1170</v>
+      </c>
+      <c r="AC1338" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="1339" ht="15.75" customHeight="1">
-      <c r="F1339" s="2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="1340" ht="15.75" customHeight="1">
-      <c r="F1340" s="2" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="1341" ht="15.75" customHeight="1"/>
-    <row r="1342" ht="15.75" customHeight="1">
-      <c r="D1342" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="1343" ht="15.75" customHeight="1"/>
+      <c r="H1339" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="I1339" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1339" s="6">
+        <v>100</v>
+      </c>
+      <c r="L1339" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="M1339" s="6">
+        <v>1170</v>
+      </c>
+      <c r="Y1339" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1339" s="6">
+        <v>1270</v>
+      </c>
+      <c r="AC1339" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1340" ht="15.75" customHeight="1"/>
+    <row r="1341" ht="15.75" customHeight="1">
+      <c r="D1341" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="S1341" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1342" ht="15.75" customHeight="1"/>
+    <row r="1343" ht="15.75" customHeight="1">
+      <c r="E1343" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
     <row r="1344" ht="15.75" customHeight="1">
-      <c r="E1344" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="S1344" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="1345" ht="15.75" customHeight="1"/>
-    <row r="1346" ht="15.75" customHeight="1">
-      <c r="E1346" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
+      <c r="E1344" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="1345" ht="15.75" customHeight="1">
+      <c r="E1345" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1346" ht="15.75" customHeight="1"/>
     <row r="1347" ht="15.75" customHeight="1">
-      <c r="E1347" s="2" t="s">
-        <v>489</v>
+      <c r="F1347" s="2" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="1348" ht="15.75" customHeight="1"/>
     <row r="1349" ht="15.75" customHeight="1">
-      <c r="L1349" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="R1349" s="4" t="s">
+      <c r="F1349" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="J1349" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S1349" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="1350" ht="15.75" customHeight="1">
-      <c r="N1350" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="R1350" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1350" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="1351" ht="15.75" customHeight="1"/>
+      <c r="K1349" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1350" ht="15.75" customHeight="1"/>
+    <row r="1351" ht="15.75" customHeight="1">
+      <c r="F1351" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
     <row r="1352" ht="15.75" customHeight="1">
-      <c r="E1352" s="2" t="s">
-        <v>492</v>
+      <c r="F1352" s="2" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="1353" ht="15.75" customHeight="1">
-      <c r="E1353" s="2" t="s">
-        <v>493</v>
+      <c r="F1353" s="2" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="1354" ht="15.75" customHeight="1"/>
@@ -15323,229 +15497,276 @@
     <row r="1362" ht="15.75" customHeight="1"/>
     <row r="1363" ht="15.75" customHeight="1"/>
     <row r="1364" ht="15.75" customHeight="1">
-      <c r="E1364" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="S1364" s="1" t="s">
-        <v>400</v>
+      <c r="D1364" s="1" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="1365" ht="15.75" customHeight="1"/>
     <row r="1366" ht="15.75" customHeight="1">
-      <c r="E1366" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="1367" ht="15.75" customHeight="1">
-      <c r="E1367" s="2" t="s">
-        <v>496</v>
-      </c>
-    </row>
+      <c r="E1366" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="S1366" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1367" ht="15.75" customHeight="1"/>
     <row r="1368" ht="15.75" customHeight="1">
       <c r="E1368" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1369" ht="15.75" customHeight="1">
       <c r="E1369" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="1370" ht="15.75" customHeight="1">
-      <c r="E1370" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="F1370" s="8"/>
-      <c r="G1370" s="8"/>
-      <c r="H1370" s="8"/>
-      <c r="I1370" s="8"/>
-      <c r="J1370" s="8"/>
-      <c r="K1370" s="8"/>
-      <c r="L1370" s="8"/>
-      <c r="M1370" s="8"/>
-      <c r="N1370" s="8"/>
-      <c r="O1370" s="8"/>
-      <c r="P1370" s="8"/>
-      <c r="Q1370" s="8"/>
-      <c r="R1370" s="8"/>
-      <c r="S1370" s="8"/>
-      <c r="T1370" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="U1370" s="8"/>
-      <c r="V1370" s="8"/>
-      <c r="W1370" s="8"/>
-      <c r="X1370" s="8"/>
-      <c r="Y1370" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="Z1370" s="8"/>
-      <c r="AA1370" s="8"/>
-      <c r="AB1370" s="8"/>
-      <c r="AC1370" s="8"/>
-      <c r="AD1370" s="10"/>
-    </row>
+        <v>502</v>
+      </c>
+    </row>
+    <row r="1370" ht="15.75" customHeight="1"/>
     <row r="1371" ht="15.75" customHeight="1">
-      <c r="E1371" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="F1371" s="12"/>
-      <c r="G1371" s="12"/>
-      <c r="H1371" s="12"/>
-      <c r="I1371" s="12"/>
-      <c r="J1371" s="14" t="s">
-        <v>502</v>
-      </c>
-      <c r="K1371" s="12"/>
-      <c r="L1371" s="12"/>
-      <c r="M1371" s="12"/>
-      <c r="N1371" s="12"/>
-      <c r="O1371" s="12"/>
-      <c r="P1371" s="12"/>
-      <c r="Q1371" s="12"/>
-      <c r="R1371" s="12"/>
-      <c r="S1371" s="12"/>
-      <c r="T1371" s="14" t="s">
+      <c r="L1371" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="U1371" s="12"/>
-      <c r="V1371" s="12"/>
-      <c r="W1371" s="12"/>
-      <c r="X1371" s="12"/>
-      <c r="Y1371" s="14" t="s">
+      <c r="R1371" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1371" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1372" ht="15.75" customHeight="1">
+      <c r="N1372" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="Z1371" s="12"/>
-      <c r="AA1371" s="12"/>
-      <c r="AB1371" s="12"/>
-      <c r="AC1371" s="12"/>
-      <c r="AD1371" s="10"/>
-    </row>
-    <row r="1372" ht="15.75" customHeight="1">
-      <c r="E1372" s="10"/>
-      <c r="J1372" s="14" t="s">
+      <c r="R1372" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1372" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="1373" ht="15.75" customHeight="1"/>
+    <row r="1374" ht="15.75" customHeight="1">
+      <c r="E1374" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="K1372" s="12"/>
-      <c r="L1372" s="12"/>
-      <c r="M1372" s="12"/>
-      <c r="N1372" s="12"/>
-      <c r="O1372" s="12"/>
-      <c r="P1372" s="12"/>
-      <c r="Q1372" s="12"/>
-      <c r="R1372" s="12"/>
-      <c r="S1372" s="12"/>
-      <c r="T1372" s="14" t="s">
+    </row>
+    <row r="1375" ht="15.75" customHeight="1">
+      <c r="E1375" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="U1372" s="12"/>
-      <c r="V1372" s="12"/>
-      <c r="W1372" s="12"/>
-      <c r="X1372" s="12"/>
-      <c r="Y1372" s="14" t="s">
+    </row>
+    <row r="1376" ht="15.75" customHeight="1"/>
+    <row r="1377" ht="15.75" customHeight="1">
+      <c r="E1377" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="Z1372" s="12"/>
-      <c r="AA1372" s="12"/>
-      <c r="AB1372" s="12"/>
-      <c r="AC1372" s="12"/>
-      <c r="AD1372" s="10"/>
-    </row>
-    <row r="1373" ht="15.75" customHeight="1">
-      <c r="E1373" s="23" t="s">
-        <v>508</v>
-      </c>
-      <c r="F1373" s="12"/>
-      <c r="G1373" s="12"/>
-      <c r="H1373" s="12"/>
-      <c r="I1373" s="12"/>
-      <c r="J1373" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="K1373" s="12"/>
-      <c r="L1373" s="12"/>
-      <c r="M1373" s="12"/>
-      <c r="N1373" s="12"/>
-      <c r="O1373" s="12"/>
-      <c r="P1373" s="12"/>
-      <c r="Q1373" s="12"/>
-      <c r="R1373" s="12"/>
-      <c r="S1373" s="12"/>
-      <c r="T1373" s="13" t="s">
-        <v>510</v>
-      </c>
-      <c r="U1373" s="12"/>
-      <c r="V1373" s="12"/>
-      <c r="W1373" s="12"/>
-      <c r="X1373" s="12"/>
-      <c r="Y1373" s="12"/>
-      <c r="Z1373" s="12"/>
-      <c r="AA1373" s="12"/>
-      <c r="AB1373" s="12"/>
-      <c r="AC1373" s="12"/>
-      <c r="AD1373" s="10"/>
-    </row>
-    <row r="1374" ht="15.75" customHeight="1">
-      <c r="E1374" s="8"/>
-      <c r="F1374" s="8"/>
-      <c r="G1374" s="8"/>
-      <c r="H1374" s="8"/>
-      <c r="I1374" s="8"/>
-      <c r="J1374" s="8"/>
-      <c r="K1374" s="8"/>
-      <c r="L1374" s="8"/>
-      <c r="M1374" s="8"/>
-      <c r="N1374" s="8"/>
-      <c r="O1374" s="8"/>
-      <c r="P1374" s="8"/>
-      <c r="Q1374" s="8"/>
-      <c r="R1374" s="8"/>
-      <c r="S1374" s="8"/>
-      <c r="T1374" s="8"/>
-      <c r="U1374" s="8"/>
-      <c r="V1374" s="8"/>
-      <c r="W1374" s="8"/>
-      <c r="X1374" s="8"/>
-      <c r="Y1374" s="8"/>
-      <c r="Z1374" s="8"/>
-      <c r="AA1374" s="8"/>
-      <c r="AB1374" s="8"/>
-      <c r="AC1374" s="8"/>
-    </row>
-    <row r="1375" ht="15.75" customHeight="1">
-      <c r="F1375" s="2" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="1376" ht="15.75" customHeight="1">
-      <c r="F1376" s="2" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="1377" ht="15.75" customHeight="1">
-      <c r="F1377" s="2" t="s">
-        <v>513</v>
+      <c r="S1377" s="1" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="1378" ht="15.75" customHeight="1"/>
     <row r="1379" ht="15.75" customHeight="1">
       <c r="E1379" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="1380" ht="15.75" customHeight="1">
+      <c r="E1380" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="1381" ht="15.75" customHeight="1">
+      <c r="E1381" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="1382" ht="15.75" customHeight="1">
+      <c r="E1382" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="1383" ht="15.75" customHeight="1">
+      <c r="E1383" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="F1383" s="8"/>
+      <c r="G1383" s="8"/>
+      <c r="H1383" s="8"/>
+      <c r="I1383" s="8"/>
+      <c r="J1383" s="8"/>
+      <c r="K1383" s="8"/>
+      <c r="L1383" s="8"/>
+      <c r="M1383" s="8"/>
+      <c r="N1383" s="8"/>
+      <c r="O1383" s="8"/>
+      <c r="P1383" s="8"/>
+      <c r="Q1383" s="8"/>
+      <c r="R1383" s="8"/>
+      <c r="S1383" s="8"/>
+      <c r="T1383" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="U1383" s="8"/>
+      <c r="V1383" s="8"/>
+      <c r="W1383" s="8"/>
+      <c r="X1383" s="8"/>
+      <c r="Y1383" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="Z1383" s="8"/>
+      <c r="AA1383" s="8"/>
+      <c r="AB1383" s="8"/>
+      <c r="AC1383" s="8"/>
+      <c r="AD1383" s="10"/>
+    </row>
+    <row r="1384" ht="15.75" customHeight="1">
+      <c r="E1384" s="11" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="1380" ht="15.75" customHeight="1"/>
-    <row r="1381" ht="15.75" customHeight="1"/>
-    <row r="1382" ht="15.75" customHeight="1"/>
-    <row r="1383" ht="15.75" customHeight="1"/>
-    <row r="1384" ht="15.75" customHeight="1"/>
-    <row r="1385" ht="15.75" customHeight="1"/>
-    <row r="1386" ht="15.75" customHeight="1"/>
-    <row r="1387" ht="15.75" customHeight="1"/>
-    <row r="1388" ht="15.75" customHeight="1"/>
-    <row r="1389" ht="15.75" customHeight="1"/>
-    <row r="1390" ht="15.75" customHeight="1"/>
+      <c r="F1384" s="12"/>
+      <c r="G1384" s="12"/>
+      <c r="H1384" s="12"/>
+      <c r="I1384" s="12"/>
+      <c r="J1384" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="K1384" s="12"/>
+      <c r="L1384" s="12"/>
+      <c r="M1384" s="12"/>
+      <c r="N1384" s="12"/>
+      <c r="O1384" s="12"/>
+      <c r="P1384" s="12"/>
+      <c r="Q1384" s="12"/>
+      <c r="R1384" s="12"/>
+      <c r="S1384" s="12"/>
+      <c r="T1384" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="U1384" s="12"/>
+      <c r="V1384" s="12"/>
+      <c r="W1384" s="12"/>
+      <c r="X1384" s="12"/>
+      <c r="Y1384" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="Z1384" s="12"/>
+      <c r="AA1384" s="12"/>
+      <c r="AB1384" s="12"/>
+      <c r="AC1384" s="12"/>
+      <c r="AD1384" s="10"/>
+    </row>
+    <row r="1385" ht="15.75" customHeight="1">
+      <c r="E1385" s="10"/>
+      <c r="J1385" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="K1385" s="12"/>
+      <c r="L1385" s="12"/>
+      <c r="M1385" s="12"/>
+      <c r="N1385" s="12"/>
+      <c r="O1385" s="12"/>
+      <c r="P1385" s="12"/>
+      <c r="Q1385" s="12"/>
+      <c r="R1385" s="12"/>
+      <c r="S1385" s="12"/>
+      <c r="T1385" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="U1385" s="12"/>
+      <c r="V1385" s="12"/>
+      <c r="W1385" s="12"/>
+      <c r="X1385" s="12"/>
+      <c r="Y1385" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="Z1385" s="12"/>
+      <c r="AA1385" s="12"/>
+      <c r="AB1385" s="12"/>
+      <c r="AC1385" s="12"/>
+      <c r="AD1385" s="10"/>
+    </row>
+    <row r="1386" ht="15.75" customHeight="1">
+      <c r="E1386" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="F1386" s="12"/>
+      <c r="G1386" s="12"/>
+      <c r="H1386" s="12"/>
+      <c r="I1386" s="12"/>
+      <c r="J1386" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="K1386" s="12"/>
+      <c r="L1386" s="12"/>
+      <c r="M1386" s="12"/>
+      <c r="N1386" s="12"/>
+      <c r="O1386" s="12"/>
+      <c r="P1386" s="12"/>
+      <c r="Q1386" s="12"/>
+      <c r="R1386" s="12"/>
+      <c r="S1386" s="12"/>
+      <c r="T1386" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="U1386" s="12"/>
+      <c r="V1386" s="12"/>
+      <c r="W1386" s="12"/>
+      <c r="X1386" s="12"/>
+      <c r="Y1386" s="12"/>
+      <c r="Z1386" s="12"/>
+      <c r="AA1386" s="12"/>
+      <c r="AB1386" s="12"/>
+      <c r="AC1386" s="12"/>
+      <c r="AD1386" s="10"/>
+    </row>
+    <row r="1387" ht="15.75" customHeight="1">
+      <c r="E1387" s="8"/>
+      <c r="F1387" s="8"/>
+      <c r="G1387" s="8"/>
+      <c r="H1387" s="8"/>
+      <c r="I1387" s="8"/>
+      <c r="J1387" s="8"/>
+      <c r="K1387" s="8"/>
+      <c r="L1387" s="8"/>
+      <c r="M1387" s="8"/>
+      <c r="N1387" s="8"/>
+      <c r="O1387" s="8"/>
+      <c r="P1387" s="8"/>
+      <c r="Q1387" s="8"/>
+      <c r="R1387" s="8"/>
+      <c r="S1387" s="8"/>
+      <c r="T1387" s="8"/>
+      <c r="U1387" s="8"/>
+      <c r="V1387" s="8"/>
+      <c r="W1387" s="8"/>
+      <c r="X1387" s="8"/>
+      <c r="Y1387" s="8"/>
+      <c r="Z1387" s="8"/>
+      <c r="AA1387" s="8"/>
+      <c r="AB1387" s="8"/>
+      <c r="AC1387" s="8"/>
+    </row>
+    <row r="1388" ht="15.75" customHeight="1">
+      <c r="F1388" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="1389" ht="15.75" customHeight="1">
+      <c r="F1389" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="1390" ht="15.75" customHeight="1">
+      <c r="F1390" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
     <row r="1391" ht="15.75" customHeight="1"/>
-    <row r="1392" ht="15.75" customHeight="1"/>
+    <row r="1392" ht="15.75" customHeight="1">
+      <c r="E1392" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
     <row r="1393" ht="15.75" customHeight="1"/>
     <row r="1394" ht="15.75" customHeight="1"/>
     <row r="1395" ht="15.75" customHeight="1"/>
@@ -15566,32 +15787,32 @@
     <row r="1410" ht="15.75" customHeight="1"/>
     <row r="1411" ht="15.75" customHeight="1">
       <c r="D1411" s="1" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1412" ht="15.75" customHeight="1"/>
     <row r="1413" ht="15.75" customHeight="1">
       <c r="E1413" s="1" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="S1413" s="1" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="1414" ht="15.75" customHeight="1"/>
     <row r="1415" ht="15.75" customHeight="1">
       <c r="E1415" s="2" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1416" ht="15.75" customHeight="1">
       <c r="E1416" s="2" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1417" ht="15.75" customHeight="1">
       <c r="E1417" s="2" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1418" ht="15.75" customHeight="1"/>
@@ -15608,68 +15829,68 @@
     </row>
     <row r="1420" ht="15.75" customHeight="1">
       <c r="L1420" s="3" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="R1420" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1420" s="2" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1421" ht="15.75" customHeight="1"/>
     <row r="1422" ht="15.75" customHeight="1">
       <c r="E1422" s="2" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="1423" ht="15.75" customHeight="1">
       <c r="E1423" s="2" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1424" ht="15.75" customHeight="1"/>
     <row r="1425" ht="15.75" customHeight="1">
       <c r="J1425" s="3" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="R1425" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1425" s="2" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1426" ht="15.75" customHeight="1">
       <c r="M1426" s="3" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="R1426" s="4" t="s">
         <v>15</v>
       </c>
       <c r="S1426" s="2" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1427" ht="15.75" customHeight="1"/>
     <row r="1428" ht="15.75" customHeight="1">
       <c r="E1428" s="2" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="1429" ht="15.75" customHeight="1">
       <c r="E1429" s="2" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1430" ht="15.75" customHeight="1">
       <c r="E1430" s="2" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1431" ht="15.75" customHeight="1">
       <c r="E1431" s="7" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="F1431" s="8"/>
       <c r="G1431" s="8"/>
@@ -15677,25 +15898,25 @@
       <c r="I1431" s="8"/>
       <c r="J1431" s="8"/>
       <c r="K1431" s="9" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="L1431" s="8"/>
       <c r="M1431" s="8"/>
       <c r="N1431" s="8"/>
       <c r="O1431" s="9" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="P1431" s="8"/>
       <c r="Q1431" s="8"/>
       <c r="R1431" s="8"/>
       <c r="S1431" s="9" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="T1431" s="8"/>
       <c r="U1431" s="8"/>
       <c r="V1431" s="8"/>
       <c r="W1431" s="9" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="X1431" s="8"/>
       <c r="Y1431" s="8"/>
@@ -15704,7 +15925,7 @@
     </row>
     <row r="1432" ht="15.75" customHeight="1">
       <c r="E1432" s="23" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="F1432" s="12"/>
       <c r="G1432" s="12"/>
@@ -15763,87 +15984,87 @@
     </row>
     <row r="1434" ht="15.75" customHeight="1">
       <c r="F1434" s="2" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1435" ht="15.75" customHeight="1"/>
     <row r="1436" ht="15.75" customHeight="1">
       <c r="E1436" s="2" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1437" ht="15.75" customHeight="1">
       <c r="E1437" s="2" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1438" ht="15.75" customHeight="1">
       <c r="E1438" s="2" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1439" ht="15.75" customHeight="1">
       <c r="E1439" s="2" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1440" ht="15.75" customHeight="1"/>
     <row r="1441" ht="15.75" customHeight="1">
       <c r="F1441" s="2" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1442" ht="15.75" customHeight="1">
       <c r="F1442" s="2" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1443" ht="15.75" customHeight="1"/>
     <row r="1444" ht="15.75" customHeight="1">
       <c r="E1444" s="2" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
     </row>
     <row r="1445" ht="15.75" customHeight="1">
       <c r="E1445" s="2" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
     </row>
     <row r="1446" ht="15.75" customHeight="1">
       <c r="E1446" s="2" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="1447" ht="15.75" customHeight="1">
       <c r="E1447" s="2" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
     </row>
     <row r="1448" ht="15.75" customHeight="1">
       <c r="E1448" s="2" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
     </row>
     <row r="1449" ht="15.75" customHeight="1"/>
     <row r="1450" ht="15.75" customHeight="1">
       <c r="E1450" s="1" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
     </row>
     <row r="1451" ht="15.75" customHeight="1"/>
     <row r="1452" ht="15.75" customHeight="1">
       <c r="E1452" s="2" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
     </row>
     <row r="1453" ht="15.75" customHeight="1">
       <c r="E1453" s="2" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
     </row>
     <row r="1454" ht="15.75" customHeight="1">
       <c r="E1454" s="2" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
     </row>
     <row r="1455" ht="15.75" customHeight="1"/>
@@ -15851,40 +16072,40 @@
     <row r="1457" ht="15.75" customHeight="1"/>
     <row r="1458" ht="15.75" customHeight="1">
       <c r="E1458" s="2" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
     </row>
     <row r="1459" ht="15.75" customHeight="1">
       <c r="E1459" s="2" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
     </row>
     <row r="1460" ht="15.75" customHeight="1">
       <c r="E1460" s="2" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
     </row>
     <row r="1461" ht="15.75" customHeight="1"/>
     <row r="1462" ht="15.75" customHeight="1">
       <c r="F1462" s="2" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
     </row>
     <row r="1463" ht="15.75" customHeight="1">
       <c r="F1463" s="2" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
     </row>
     <row r="1464" ht="15.75" customHeight="1"/>
     <row r="1465" ht="15.75" customHeight="1">
       <c r="E1465" s="3" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="J1465" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1465" s="2" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
     </row>
     <row r="1466" ht="15.75" customHeight="1">
@@ -15892,161 +16113,161 @@
         <v>15</v>
       </c>
       <c r="K1466" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1467" ht="15.75" customHeight="1">
       <c r="H1467" s="3" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="J1467" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1467" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1468" ht="15.75" customHeight="1">
       <c r="H1468" s="3" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="J1468" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1468" s="2" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1469" ht="15.75" customHeight="1">
       <c r="I1469" s="3" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="J1469" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1469" s="2" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1470" ht="15.75" customHeight="1">
       <c r="I1470" s="3" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="J1470" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1470" s="2" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
     </row>
     <row r="1471" ht="15.75" customHeight="1">
       <c r="H1471" s="3" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="J1471" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1471" s="2" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1472" ht="15.75" customHeight="1"/>
     <row r="1473" ht="15.75" customHeight="1">
       <c r="F1473" s="2" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1474" ht="15.75" customHeight="1">
       <c r="F1474" s="2" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1475" ht="15.75" customHeight="1">
       <c r="G1475" s="2" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1476" ht="15.75" customHeight="1"/>
     <row r="1477" ht="15.75" customHeight="1">
       <c r="E1477" s="2" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1478" ht="15.75" customHeight="1">
       <c r="E1478" s="2" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1479" ht="15.75" customHeight="1"/>
     <row r="1480" ht="15.75" customHeight="1">
       <c r="F1480" s="2" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1481" ht="15.75" customHeight="1">
       <c r="F1481" s="2" t="s">
-        <v>573</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1482" ht="15.75" customHeight="1"/>
     <row r="1483" ht="15.75" customHeight="1">
       <c r="F1483" s="3" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="J1483" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1483" s="2" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1484" ht="15.75" customHeight="1">
       <c r="H1484" s="3" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="J1484" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1484" s="2" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1485" ht="15.75" customHeight="1">
       <c r="H1485" s="3" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="J1485" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1485" s="2" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1486" ht="15.75" customHeight="1"/>
     <row r="1487" ht="15.75" customHeight="1">
       <c r="E1487" s="2" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1488" ht="15.75" customHeight="1">
       <c r="E1488" s="2" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1489" ht="15.75" customHeight="1">
       <c r="E1489" s="2" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1490" ht="15.75" customHeight="1"/>
     <row r="1491" ht="15.75" customHeight="1">
       <c r="F1491" s="2" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1492" ht="15.75" customHeight="1">
       <c r="H1492" s="3" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="I1492" s="4" t="s">
         <v>26</v>
@@ -16064,13 +16285,13 @@
         <v>28</v>
       </c>
       <c r="N1492" s="3" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="O1492" s="4" t="s">
         <v>28</v>
       </c>
       <c r="P1492" s="3" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="Y1492" s="4" t="s">
         <v>26</v>
@@ -16084,12 +16305,12 @@
     </row>
     <row r="1493" ht="15.75" customHeight="1">
       <c r="F1493" s="2" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1494" ht="15.75" customHeight="1">
       <c r="H1494" s="3" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="I1494" s="4" t="s">
         <v>26</v>
@@ -16119,10 +16340,10 @@
         <v>26</v>
       </c>
       <c r="Z1494" s="3" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="AC1494" s="2" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1495" ht="15.75" customHeight="1"/>
@@ -16137,77 +16358,77 @@
     <row r="1504" ht="15.75" customHeight="1"/>
     <row r="1505" ht="15.75" customHeight="1">
       <c r="E1505" s="2" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1506" ht="15.75" customHeight="1">
       <c r="E1506" s="2" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
     </row>
     <row r="1507" ht="15.75" customHeight="1">
       <c r="E1507" s="2" t="s">
-        <v>590</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1508" ht="15.75" customHeight="1">
       <c r="E1508" s="2" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1509" ht="15.75" customHeight="1"/>
     <row r="1510" ht="15.75" customHeight="1">
       <c r="F1510" s="2" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1511" ht="15.75" customHeight="1">
       <c r="F1511" s="2" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1512" ht="15.75" customHeight="1">
       <c r="F1512" s="2" t="s">
-        <v>594</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1513" ht="15.75" customHeight="1">
       <c r="F1513" s="2" t="s">
-        <v>595</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1514" ht="15.75" customHeight="1"/>
     <row r="1515" ht="15.75" customHeight="1">
       <c r="F1515" s="3" t="s">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="J1515" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1515" s="2" t="s">
-        <v>597</v>
+        <v>610</v>
       </c>
     </row>
     <row r="1516" ht="15.75" customHeight="1">
       <c r="I1516" s="3" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="J1516" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1516" s="2" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
     </row>
     <row r="1517" ht="15.75" customHeight="1">
       <c r="H1517" s="3" t="s">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="J1517" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1517" s="2" t="s">
-        <v>600</v>
+        <v>613</v>
       </c>
     </row>
     <row r="1518" ht="15.75" customHeight="1">
@@ -16215,40 +16436,40 @@
         <v>15</v>
       </c>
       <c r="K1518" s="2" t="s">
-        <v>601</v>
+        <v>614</v>
       </c>
     </row>
     <row r="1519" ht="15.75" customHeight="1">
       <c r="I1519" s="3" t="s">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="J1519" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1519" s="2" t="s">
-        <v>603</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1520" ht="15.75" customHeight="1">
       <c r="H1520" s="3" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="J1520" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1520" s="2" t="s">
-        <v>604</v>
+        <v>617</v>
       </c>
     </row>
     <row r="1521" ht="15.75" customHeight="1">
       <c r="H1521" s="3" t="s">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="J1521" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1521" s="2" t="s">
-        <v>606</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1522" ht="15.75" customHeight="1">
@@ -16256,29 +16477,29 @@
         <v>15</v>
       </c>
       <c r="K1522" s="2" t="s">
-        <v>607</v>
+        <v>620</v>
       </c>
     </row>
     <row r="1523" ht="15.75" customHeight="1">
       <c r="H1523" s="3" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="J1523" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1523" s="2" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
     </row>
     <row r="1524" ht="15.75" customHeight="1">
       <c r="H1524" s="3" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="J1524" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1524" s="2" t="s">
-        <v>610</v>
+        <v>623</v>
       </c>
     </row>
     <row r="1525" ht="15.75" customHeight="1">
@@ -16286,18 +16507,18 @@
         <v>15</v>
       </c>
       <c r="K1525" s="2" t="s">
-        <v>611</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1526" ht="15.75" customHeight="1">
       <c r="H1526" s="3" t="s">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="J1526" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1526" s="2" t="s">
-        <v>613</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1527" ht="15.75" customHeight="1">
@@ -16305,93 +16526,93 @@
         <v>15</v>
       </c>
       <c r="K1527" s="2" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1528" ht="15.75" customHeight="1">
       <c r="H1528" s="3" t="s">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="J1528" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1528" s="2" t="s">
-        <v>616</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1529" ht="15.75" customHeight="1">
       <c r="H1529" s="3" t="s">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="J1529" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1529" s="2" t="s">
-        <v>618</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1530" ht="15.75" customHeight="1"/>
     <row r="1531" ht="15.75" customHeight="1">
       <c r="E1531" s="2" t="s">
-        <v>619</v>
+        <v>632</v>
       </c>
     </row>
     <row r="1532" ht="15.75" customHeight="1">
       <c r="E1532" s="2" t="s">
-        <v>620</v>
+        <v>633</v>
       </c>
     </row>
     <row r="1533" ht="15.75" customHeight="1">
       <c r="E1533" s="2" t="s">
-        <v>621</v>
+        <v>634</v>
       </c>
     </row>
     <row r="1534" ht="15.75" customHeight="1">
       <c r="E1534" s="2" t="s">
-        <v>622</v>
+        <v>635</v>
       </c>
     </row>
     <row r="1535" ht="15.75" customHeight="1">
       <c r="E1535" s="2" t="s">
-        <v>623</v>
+        <v>636</v>
       </c>
     </row>
     <row r="1536" ht="15.75" customHeight="1"/>
     <row r="1537" ht="15.75" customHeight="1">
       <c r="E1537" s="2" t="s">
-        <v>624</v>
+        <v>637</v>
       </c>
     </row>
     <row r="1538" ht="15.75" customHeight="1">
       <c r="F1538" s="2" t="s">
-        <v>625</v>
+        <v>638</v>
       </c>
     </row>
     <row r="1539" ht="15.75" customHeight="1">
       <c r="F1539" s="2" t="s">
-        <v>626</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1540" ht="15.75" customHeight="1"/>
     <row r="1541" ht="15.75" customHeight="1">
       <c r="E1541" s="2" t="s">
-        <v>627</v>
+        <v>640</v>
       </c>
     </row>
     <row r="1542" ht="15.75" customHeight="1">
       <c r="F1542" s="2" t="s">
-        <v>628</v>
+        <v>641</v>
       </c>
     </row>
     <row r="1543" ht="15.75" customHeight="1">
       <c r="F1543" s="2" t="s">
-        <v>629</v>
+        <v>642</v>
       </c>
     </row>
     <row r="1544" ht="15.75" customHeight="1"/>
     <row r="1545" ht="15.75" customHeight="1">
       <c r="E1545" s="2" t="s">
-        <v>630</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1546" ht="15.75" customHeight="1"/>
@@ -16402,18 +16623,18 @@
     <row r="1551" ht="15.75" customHeight="1"/>
     <row r="1552" ht="15.75" customHeight="1">
       <c r="D1552" s="1" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
     </row>
     <row r="1553" ht="15.75" customHeight="1"/>
     <row r="1554" ht="15.75" customHeight="1">
       <c r="B1554" s="2" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="1555" ht="15.75" customHeight="1">
       <c r="B1555" s="7" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C1555" s="8"/>
       <c r="D1555" s="8"/>
@@ -16423,7 +16644,7 @@
       <c r="H1555" s="8"/>
       <c r="I1555" s="8"/>
       <c r="J1555" s="9" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="K1555" s="8"/>
       <c r="L1555" s="8"/>
@@ -16434,7 +16655,7 @@
       <c r="Q1555" s="8"/>
       <c r="R1555" s="8"/>
       <c r="S1555" s="9" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="T1555" s="8"/>
       <c r="U1555" s="8"/>
@@ -16442,7 +16663,7 @@
       <c r="W1555" s="8"/>
       <c r="X1555" s="8"/>
       <c r="Y1555" s="9" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Z1555" s="8"/>
       <c r="AA1555" s="9" t="s">
@@ -16454,7 +16675,7 @@
     </row>
     <row r="1556" ht="15.75" customHeight="1">
       <c r="B1556" s="23" t="s">
-        <v>632</v>
+        <v>645</v>
       </c>
       <c r="C1556" s="12"/>
       <c r="D1556" s="12"/>
@@ -16464,7 +16685,7 @@
       <c r="H1556" s="12"/>
       <c r="I1556" s="12"/>
       <c r="J1556" s="14" t="s">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="K1556" s="12"/>
       <c r="L1556" s="12"/>
@@ -16475,7 +16696,7 @@
       <c r="Q1556" s="12"/>
       <c r="R1556" s="12"/>
       <c r="S1556" s="14" t="s">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="T1556" s="12"/>
       <c r="U1556" s="12"/>
@@ -16483,11 +16704,11 @@
       <c r="W1556" s="12"/>
       <c r="X1556" s="12"/>
       <c r="Y1556" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1556" s="12"/>
       <c r="AA1556" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1556" s="12"/>
       <c r="AC1556" s="12"/>
@@ -16495,7 +16716,7 @@
     </row>
     <row r="1557" ht="15.75" customHeight="1">
       <c r="B1557" s="23" t="s">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="C1557" s="12"/>
       <c r="D1557" s="12"/>
@@ -16505,7 +16726,7 @@
       <c r="H1557" s="12"/>
       <c r="I1557" s="12"/>
       <c r="J1557" s="14" t="s">
-        <v>636</v>
+        <v>649</v>
       </c>
       <c r="K1557" s="12"/>
       <c r="L1557" s="12"/>
@@ -16524,11 +16745,11 @@
       <c r="W1557" s="12"/>
       <c r="X1557" s="12"/>
       <c r="Y1557" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1557" s="12"/>
       <c r="AA1557" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1557" s="12"/>
       <c r="AC1557" s="12"/>
@@ -16536,7 +16757,7 @@
     </row>
     <row r="1558" ht="15.75" customHeight="1">
       <c r="B1558" s="23" t="s">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="C1558" s="12"/>
       <c r="D1558" s="12"/>
@@ -16546,7 +16767,7 @@
       <c r="H1558" s="12"/>
       <c r="I1558" s="12"/>
       <c r="J1558" s="14" t="s">
-        <v>638</v>
+        <v>651</v>
       </c>
       <c r="K1558" s="12"/>
       <c r="L1558" s="12"/>
@@ -16557,7 +16778,7 @@
       <c r="Q1558" s="12"/>
       <c r="R1558" s="12"/>
       <c r="S1558" s="14" t="s">
-        <v>639</v>
+        <v>652</v>
       </c>
       <c r="T1558" s="12"/>
       <c r="U1558" s="12"/>
@@ -16565,11 +16786,11 @@
       <c r="W1558" s="12"/>
       <c r="X1558" s="12"/>
       <c r="Y1558" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1558" s="12"/>
       <c r="AA1558" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1558" s="12"/>
       <c r="AC1558" s="12"/>
@@ -16577,7 +16798,7 @@
     </row>
     <row r="1559" ht="15.75" customHeight="1">
       <c r="B1559" s="23" t="s">
-        <v>640</v>
+        <v>653</v>
       </c>
       <c r="C1559" s="12"/>
       <c r="D1559" s="12"/>
@@ -16587,7 +16808,7 @@
       <c r="H1559" s="12"/>
       <c r="I1559" s="12"/>
       <c r="J1559" s="14" t="s">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="K1559" s="12"/>
       <c r="L1559" s="12"/>
@@ -16598,7 +16819,7 @@
       <c r="Q1559" s="12"/>
       <c r="R1559" s="12"/>
       <c r="S1559" s="14" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="T1559" s="12"/>
       <c r="U1559" s="12"/>
@@ -16606,11 +16827,11 @@
       <c r="W1559" s="12"/>
       <c r="X1559" s="12"/>
       <c r="Y1559" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1559" s="12"/>
       <c r="AA1559" s="14" t="s">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="AB1559" s="12"/>
       <c r="AC1559" s="12"/>
@@ -16618,7 +16839,7 @@
     </row>
     <row r="1560" ht="15.75" customHeight="1">
       <c r="B1560" s="23" t="s">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="C1560" s="12"/>
       <c r="D1560" s="12"/>
@@ -16628,7 +16849,7 @@
       <c r="H1560" s="12"/>
       <c r="I1560" s="12"/>
       <c r="J1560" s="14" t="s">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="K1560" s="12"/>
       <c r="L1560" s="12"/>
@@ -16639,7 +16860,7 @@
       <c r="Q1560" s="12"/>
       <c r="R1560" s="12"/>
       <c r="S1560" s="14" t="s">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="T1560" s="12"/>
       <c r="U1560" s="12"/>
@@ -16647,11 +16868,11 @@
       <c r="W1560" s="12"/>
       <c r="X1560" s="12"/>
       <c r="Y1560" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1560" s="12"/>
       <c r="AA1560" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1560" s="12"/>
       <c r="AC1560" s="12"/>
@@ -16659,7 +16880,7 @@
     </row>
     <row r="1561" ht="15.75" customHeight="1">
       <c r="B1561" s="23" t="s">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="C1561" s="12"/>
       <c r="D1561" s="12"/>
@@ -16669,7 +16890,7 @@
       <c r="H1561" s="12"/>
       <c r="I1561" s="12"/>
       <c r="J1561" s="14" t="s">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="K1561" s="12"/>
       <c r="L1561" s="12"/>
@@ -16680,7 +16901,7 @@
       <c r="Q1561" s="12"/>
       <c r="R1561" s="12"/>
       <c r="S1561" s="14" t="s">
-        <v>649</v>
+        <v>662</v>
       </c>
       <c r="T1561" s="12"/>
       <c r="U1561" s="12"/>
@@ -16688,7 +16909,7 @@
       <c r="W1561" s="12"/>
       <c r="X1561" s="12"/>
       <c r="Y1561" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1561" s="12"/>
       <c r="AA1561" s="29"/>
@@ -16698,7 +16919,7 @@
     </row>
     <row r="1562" ht="15.75" customHeight="1">
       <c r="B1562" s="23" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="C1562" s="12"/>
       <c r="D1562" s="12"/>
@@ -16708,7 +16929,7 @@
       <c r="H1562" s="12"/>
       <c r="I1562" s="12"/>
       <c r="J1562" s="14" t="s">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="K1562" s="12"/>
       <c r="L1562" s="12"/>
@@ -16719,7 +16940,7 @@
       <c r="Q1562" s="12"/>
       <c r="R1562" s="12"/>
       <c r="S1562" s="14" t="s">
-        <v>649</v>
+        <v>662</v>
       </c>
       <c r="T1562" s="12"/>
       <c r="U1562" s="12"/>
@@ -16727,7 +16948,7 @@
       <c r="W1562" s="12"/>
       <c r="X1562" s="12"/>
       <c r="Y1562" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1562" s="12"/>
       <c r="AA1562" s="29"/>
@@ -16737,7 +16958,7 @@
     </row>
     <row r="1563" ht="15.75" customHeight="1">
       <c r="B1563" s="23" t="s">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="C1563" s="12"/>
       <c r="D1563" s="12"/>
@@ -16747,7 +16968,7 @@
       <c r="H1563" s="12"/>
       <c r="I1563" s="12"/>
       <c r="J1563" s="14" t="s">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="K1563" s="12"/>
       <c r="L1563" s="12"/>
@@ -16758,7 +16979,7 @@
       <c r="Q1563" s="12"/>
       <c r="R1563" s="12"/>
       <c r="S1563" s="14" t="s">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="T1563" s="12"/>
       <c r="U1563" s="12"/>
@@ -16766,11 +16987,11 @@
       <c r="W1563" s="12"/>
       <c r="X1563" s="12"/>
       <c r="Y1563" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1563" s="12"/>
       <c r="AA1563" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1563" s="12"/>
       <c r="AC1563" s="12"/>
@@ -16778,7 +16999,7 @@
     </row>
     <row r="1564" ht="15.75" customHeight="1">
       <c r="B1564" s="23" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="C1564" s="12"/>
       <c r="D1564" s="12"/>
@@ -16788,7 +17009,7 @@
       <c r="H1564" s="12"/>
       <c r="I1564" s="12"/>
       <c r="J1564" s="14" t="s">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="K1564" s="12"/>
       <c r="L1564" s="12"/>
@@ -16799,7 +17020,7 @@
       <c r="Q1564" s="12"/>
       <c r="R1564" s="12"/>
       <c r="S1564" s="14" t="s">
-        <v>657</v>
+        <v>670</v>
       </c>
       <c r="T1564" s="12"/>
       <c r="U1564" s="12"/>
@@ -16807,11 +17028,11 @@
       <c r="W1564" s="12"/>
       <c r="X1564" s="12"/>
       <c r="Y1564" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1564" s="12"/>
       <c r="AA1564" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1564" s="12"/>
       <c r="AC1564" s="12"/>
@@ -16819,7 +17040,7 @@
     </row>
     <row r="1565" ht="15.75" customHeight="1">
       <c r="B1565" s="23" t="s">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="C1565" s="12"/>
       <c r="D1565" s="12"/>
@@ -16829,7 +17050,7 @@
       <c r="H1565" s="12"/>
       <c r="I1565" s="12"/>
       <c r="J1565" s="14" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="K1565" s="12"/>
       <c r="L1565" s="12"/>
@@ -16848,11 +17069,11 @@
       <c r="W1565" s="12"/>
       <c r="X1565" s="12"/>
       <c r="Y1565" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1565" s="12"/>
       <c r="AA1565" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1565" s="12"/>
       <c r="AC1565" s="12"/>
@@ -16860,7 +17081,7 @@
     </row>
     <row r="1566" ht="15.75" customHeight="1">
       <c r="B1566" s="11" t="s">
-        <v>660</v>
+        <v>673</v>
       </c>
       <c r="C1566" s="12"/>
       <c r="D1566" s="12"/>
@@ -16870,7 +17091,7 @@
       <c r="H1566" s="12"/>
       <c r="I1566" s="12"/>
       <c r="J1566" s="14" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="K1566" s="12"/>
       <c r="L1566" s="12"/>
@@ -16881,7 +17102,7 @@
       <c r="Q1566" s="12"/>
       <c r="R1566" s="12"/>
       <c r="S1566" s="14" t="s">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="T1566" s="12"/>
       <c r="U1566" s="12"/>
@@ -16889,11 +17110,11 @@
       <c r="W1566" s="12"/>
       <c r="X1566" s="12"/>
       <c r="Y1566" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1566" s="12"/>
       <c r="AA1566" s="13" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1566" s="12"/>
       <c r="AC1566" s="12"/>
@@ -16902,7 +17123,7 @@
     <row r="1567" ht="15.75" customHeight="1">
       <c r="B1567" s="10"/>
       <c r="J1567" s="30" t="s">
-        <v>663</v>
+        <v>676</v>
       </c>
       <c r="S1567" s="15"/>
       <c r="Y1567" s="15"/>
@@ -16912,7 +17133,7 @@
     <row r="1568" ht="15.75" customHeight="1">
       <c r="B1568" s="10"/>
       <c r="J1568" s="14" t="s">
-        <v>664</v>
+        <v>677</v>
       </c>
       <c r="K1568" s="12"/>
       <c r="L1568" s="12"/>
@@ -16923,7 +17144,7 @@
       <c r="Q1568" s="12"/>
       <c r="R1568" s="12"/>
       <c r="S1568" s="14" t="s">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="T1568" s="12"/>
       <c r="U1568" s="12"/>
@@ -16931,7 +17152,7 @@
       <c r="W1568" s="12"/>
       <c r="X1568" s="12"/>
       <c r="Y1568" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1568" s="12"/>
       <c r="AA1568" s="15"/>
@@ -16940,7 +17161,7 @@
     <row r="1569" ht="15.75" customHeight="1">
       <c r="B1569" s="10"/>
       <c r="J1569" s="14" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="K1569" s="12"/>
       <c r="L1569" s="12"/>
@@ -16951,7 +17172,7 @@
       <c r="Q1569" s="12"/>
       <c r="R1569" s="12"/>
       <c r="S1569" s="14" t="s">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="T1569" s="12"/>
       <c r="U1569" s="12"/>
@@ -16959,7 +17180,7 @@
       <c r="W1569" s="12"/>
       <c r="X1569" s="12"/>
       <c r="Y1569" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1569" s="12"/>
       <c r="AA1569" s="15"/>
@@ -16967,7 +17188,7 @@
     </row>
     <row r="1570" ht="15.75" customHeight="1">
       <c r="B1570" s="23" t="s">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="C1570" s="12"/>
       <c r="D1570" s="12"/>
@@ -16977,7 +17198,7 @@
       <c r="H1570" s="12"/>
       <c r="I1570" s="12"/>
       <c r="J1570" s="14" t="s">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="K1570" s="12"/>
       <c r="L1570" s="12"/>
@@ -16988,7 +17209,7 @@
       <c r="Q1570" s="12"/>
       <c r="R1570" s="12"/>
       <c r="S1570" s="14" t="s">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="T1570" s="12"/>
       <c r="U1570" s="12"/>
@@ -16996,11 +17217,11 @@
       <c r="W1570" s="12"/>
       <c r="X1570" s="12"/>
       <c r="Y1570" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1570" s="12"/>
       <c r="AA1570" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1570" s="12"/>
       <c r="AC1570" s="12"/>
@@ -17008,7 +17229,7 @@
     </row>
     <row r="1571" ht="15.75" customHeight="1">
       <c r="B1571" s="23" t="s">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="C1571" s="12"/>
       <c r="D1571" s="12"/>
@@ -17018,7 +17239,7 @@
       <c r="H1571" s="12"/>
       <c r="I1571" s="12"/>
       <c r="J1571" s="14" t="s">
-        <v>672</v>
+        <v>685</v>
       </c>
       <c r="K1571" s="12"/>
       <c r="L1571" s="12"/>
@@ -17029,7 +17250,7 @@
       <c r="Q1571" s="12"/>
       <c r="R1571" s="12"/>
       <c r="S1571" s="14" t="s">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="T1571" s="12"/>
       <c r="U1571" s="12"/>
@@ -17037,11 +17258,11 @@
       <c r="W1571" s="12"/>
       <c r="X1571" s="12"/>
       <c r="Y1571" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1571" s="12"/>
       <c r="AA1571" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1571" s="12"/>
       <c r="AC1571" s="12"/>
@@ -17049,7 +17270,7 @@
     </row>
     <row r="1572" ht="15.75" customHeight="1">
       <c r="B1572" s="23" t="s">
-        <v>674</v>
+        <v>687</v>
       </c>
       <c r="C1572" s="12"/>
       <c r="D1572" s="12"/>
@@ -17059,7 +17280,7 @@
       <c r="H1572" s="12"/>
       <c r="I1572" s="12"/>
       <c r="J1572" s="14" t="s">
-        <v>675</v>
+        <v>688</v>
       </c>
       <c r="K1572" s="12"/>
       <c r="L1572" s="12"/>
@@ -17070,7 +17291,7 @@
       <c r="Q1572" s="12"/>
       <c r="R1572" s="12"/>
       <c r="S1572" s="14" t="s">
-        <v>676</v>
+        <v>689</v>
       </c>
       <c r="T1572" s="12"/>
       <c r="U1572" s="12"/>
@@ -17078,11 +17299,11 @@
       <c r="W1572" s="12"/>
       <c r="X1572" s="12"/>
       <c r="Y1572" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1572" s="12"/>
       <c r="AA1572" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1572" s="12"/>
       <c r="AC1572" s="12"/>
@@ -17090,7 +17311,7 @@
     </row>
     <row r="1573" ht="15.75" customHeight="1">
       <c r="B1573" s="23" t="s">
-        <v>677</v>
+        <v>690</v>
       </c>
       <c r="C1573" s="12"/>
       <c r="D1573" s="12"/>
@@ -17100,7 +17321,7 @@
       <c r="H1573" s="12"/>
       <c r="I1573" s="12"/>
       <c r="J1573" s="14" t="s">
-        <v>678</v>
+        <v>691</v>
       </c>
       <c r="K1573" s="12"/>
       <c r="L1573" s="12"/>
@@ -17111,7 +17332,7 @@
       <c r="Q1573" s="12"/>
       <c r="R1573" s="12"/>
       <c r="S1573" s="14" t="s">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="T1573" s="12"/>
       <c r="U1573" s="12"/>
@@ -17119,11 +17340,11 @@
       <c r="W1573" s="12"/>
       <c r="X1573" s="12"/>
       <c r="Y1573" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1573" s="12"/>
       <c r="AA1573" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1573" s="12"/>
       <c r="AC1573" s="12"/>
@@ -17131,7 +17352,7 @@
     </row>
     <row r="1574" ht="15.75" customHeight="1">
       <c r="B1574" s="11" t="s">
-        <v>679</v>
+        <v>692</v>
       </c>
       <c r="C1574" s="12"/>
       <c r="D1574" s="12"/>
@@ -17141,7 +17362,7 @@
       <c r="H1574" s="12"/>
       <c r="I1574" s="12"/>
       <c r="J1574" s="14" t="s">
-        <v>680</v>
+        <v>693</v>
       </c>
       <c r="K1574" s="12"/>
       <c r="L1574" s="12"/>
@@ -17152,7 +17373,7 @@
       <c r="Q1574" s="12"/>
       <c r="R1574" s="12"/>
       <c r="S1574" s="14" t="s">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="T1574" s="12"/>
       <c r="U1574" s="12"/>
@@ -17160,11 +17381,11 @@
       <c r="W1574" s="12"/>
       <c r="X1574" s="12"/>
       <c r="Y1574" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1574" s="12"/>
       <c r="AA1574" s="13" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1574" s="12"/>
       <c r="AC1574" s="12"/>
@@ -17173,7 +17394,7 @@
     <row r="1575" ht="15.75" customHeight="1">
       <c r="B1575" s="10"/>
       <c r="J1575" s="14" t="s">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="K1575" s="12"/>
       <c r="L1575" s="12"/>
@@ -17184,7 +17405,7 @@
       <c r="Q1575" s="12"/>
       <c r="R1575" s="12"/>
       <c r="S1575" s="14" t="s">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="T1575" s="12"/>
       <c r="U1575" s="12"/>
@@ -17192,7 +17413,7 @@
       <c r="W1575" s="12"/>
       <c r="X1575" s="12"/>
       <c r="Y1575" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1575" s="12"/>
       <c r="AA1575" s="15"/>
@@ -17200,7 +17421,7 @@
     </row>
     <row r="1576" ht="15.75" customHeight="1">
       <c r="B1576" s="23" t="s">
-        <v>683</v>
+        <v>696</v>
       </c>
       <c r="C1576" s="12"/>
       <c r="D1576" s="12"/>
@@ -17210,7 +17431,7 @@
       <c r="H1576" s="12"/>
       <c r="I1576" s="12"/>
       <c r="J1576" s="14" t="s">
-        <v>684</v>
+        <v>697</v>
       </c>
       <c r="K1576" s="12"/>
       <c r="L1576" s="12"/>
@@ -17221,7 +17442,7 @@
       <c r="Q1576" s="12"/>
       <c r="R1576" s="12"/>
       <c r="S1576" s="14" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="T1576" s="12"/>
       <c r="U1576" s="12"/>
@@ -17229,11 +17450,11 @@
       <c r="W1576" s="12"/>
       <c r="X1576" s="12"/>
       <c r="Y1576" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1576" s="12"/>
       <c r="AA1576" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1576" s="12"/>
       <c r="AC1576" s="12"/>
@@ -17241,7 +17462,7 @@
     </row>
     <row r="1577" ht="15.75" customHeight="1">
       <c r="B1577" s="23" t="s">
-        <v>686</v>
+        <v>699</v>
       </c>
       <c r="C1577" s="12"/>
       <c r="D1577" s="12"/>
@@ -17251,7 +17472,7 @@
       <c r="H1577" s="12"/>
       <c r="I1577" s="12"/>
       <c r="J1577" s="14" t="s">
-        <v>687</v>
+        <v>700</v>
       </c>
       <c r="K1577" s="12"/>
       <c r="L1577" s="12"/>
@@ -17262,7 +17483,7 @@
       <c r="Q1577" s="12"/>
       <c r="R1577" s="12"/>
       <c r="S1577" s="14" t="s">
-        <v>688</v>
+        <v>701</v>
       </c>
       <c r="T1577" s="12"/>
       <c r="U1577" s="12"/>
@@ -17270,11 +17491,11 @@
       <c r="W1577" s="12"/>
       <c r="X1577" s="12"/>
       <c r="Y1577" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1577" s="12"/>
       <c r="AA1577" s="14" t="s">
-        <v>689</v>
+        <v>702</v>
       </c>
       <c r="AB1577" s="12"/>
       <c r="AC1577" s="12"/>
@@ -17282,11 +17503,11 @@
     </row>
     <row r="1578" ht="15.75" customHeight="1">
       <c r="B1578" s="31" t="s">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="J1578" s="15"/>
       <c r="S1578" s="30" t="s">
-        <v>691</v>
+        <v>704</v>
       </c>
       <c r="Y1578" s="15"/>
       <c r="AA1578" s="15"/>
@@ -17325,28 +17546,28 @@
     </row>
     <row r="1580" ht="15.75" customHeight="1">
       <c r="C1580" s="1" t="s">
-        <v>692</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1581" ht="15.75" customHeight="1"/>
     <row r="1582" ht="15.75" customHeight="1">
       <c r="D1582" s="1" t="s">
-        <v>693</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1583" ht="15.75" customHeight="1"/>
     <row r="1584" ht="15.75" customHeight="1">
       <c r="E1584" s="1" t="s">
-        <v>694</v>
+        <v>707</v>
       </c>
       <c r="T1584" s="1" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1585" ht="15.75" customHeight="1"/>
     <row r="1586" ht="15.75" customHeight="1">
       <c r="E1586" s="2" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1587" ht="15.75" customHeight="1">
@@ -17367,92 +17588,92 @@
     <row r="1598" ht="15.75" customHeight="1"/>
     <row r="1599" ht="15.75" customHeight="1">
       <c r="E1599" s="2" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1600" ht="15.75" customHeight="1">
       <c r="F1600" s="2" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1601" ht="15.75" customHeight="1"/>
     <row r="1602" ht="15.75" customHeight="1">
       <c r="F1602" s="3" t="s">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="J1602" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1602" s="2" t="s">
-        <v>700</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1603" ht="15.75" customHeight="1">
       <c r="H1603" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="J1603" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1603" s="2" t="s">
-        <v>702</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1604" ht="15.75" customHeight="1">
       <c r="H1604" s="3" t="s">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="J1604" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1604" s="2" t="s">
-        <v>704</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1605" ht="15.75" customHeight="1">
       <c r="H1605" s="3" t="s">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="J1605" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1605" s="2" t="s">
-        <v>706</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1606" ht="15.75" customHeight="1"/>
     <row r="1607" ht="15.75" customHeight="1">
       <c r="E1607" s="2" t="s">
-        <v>707</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1608" ht="15.75" customHeight="1">
       <c r="E1608" s="2" t="s">
-        <v>708</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1609" ht="15.75" customHeight="1">
       <c r="E1609" s="2" t="s">
-        <v>709</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1610" ht="15.75" customHeight="1">
       <c r="E1610" s="7" t="s">
-        <v>710</v>
+        <v>723</v>
       </c>
       <c r="F1610" s="8"/>
       <c r="G1610" s="8"/>
       <c r="H1610" s="8"/>
       <c r="I1610" s="8"/>
       <c r="J1610" s="9" t="s">
-        <v>711</v>
+        <v>724</v>
       </c>
       <c r="K1610" s="8"/>
       <c r="L1610" s="8"/>
       <c r="M1610" s="8"/>
       <c r="N1610" s="8"/>
       <c r="O1610" s="9" t="s">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="P1610" s="8"/>
       <c r="Q1610" s="8"/>
@@ -17469,14 +17690,14 @@
     </row>
     <row r="1611" ht="15.75" customHeight="1">
       <c r="E1611" s="11" t="s">
-        <v>713</v>
+        <v>726</v>
       </c>
       <c r="F1611" s="12"/>
       <c r="G1611" s="12"/>
       <c r="H1611" s="12"/>
       <c r="I1611" s="12"/>
       <c r="J1611" s="14" t="s">
-        <v>714</v>
+        <v>727</v>
       </c>
       <c r="K1611" s="12"/>
       <c r="L1611" s="12"/>
@@ -17501,7 +17722,7 @@
     <row r="1612" ht="15.75" customHeight="1">
       <c r="E1612" s="10"/>
       <c r="J1612" s="14" t="s">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="K1612" s="12"/>
       <c r="L1612" s="12"/>
@@ -17549,183 +17770,183 @@
     </row>
     <row r="1614" ht="15.75" customHeight="1">
       <c r="E1614" s="1" t="s">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="T1614" s="1" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1615" ht="15.75" customHeight="1"/>
     <row r="1616" ht="15.75" customHeight="1">
       <c r="E1616" s="2" t="s">
-        <v>717</v>
+        <v>730</v>
       </c>
     </row>
     <row r="1617" ht="15.75" customHeight="1">
       <c r="E1617" s="2" t="s">
-        <v>718</v>
+        <v>731</v>
       </c>
     </row>
     <row r="1618" ht="15.75" customHeight="1"/>
     <row r="1619" ht="15.75" customHeight="1">
       <c r="E1619" s="2" t="s">
-        <v>719</v>
+        <v>732</v>
       </c>
     </row>
     <row r="1620" ht="15.75" customHeight="1">
       <c r="F1620" s="2" t="s">
-        <v>720</v>
+        <v>733</v>
       </c>
     </row>
     <row r="1621" ht="15.75" customHeight="1">
       <c r="F1621" s="2" t="s">
-        <v>721</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1622" ht="15.75" customHeight="1"/>
     <row r="1623" ht="15.75" customHeight="1">
       <c r="F1623" s="3" t="s">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="J1623" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1623" s="2" t="s">
-        <v>700</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1624" ht="15.75" customHeight="1">
       <c r="H1624" s="3" t="s">
-        <v>722</v>
+        <v>735</v>
       </c>
       <c r="J1624" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1624" s="2" t="s">
-        <v>723</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1625" ht="15.75" customHeight="1">
       <c r="H1625" s="3" t="s">
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="J1625" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1625" s="2" t="s">
-        <v>725</v>
+        <v>738</v>
       </c>
     </row>
     <row r="1626" ht="15.75" customHeight="1">
       <c r="H1626" s="3" t="s">
-        <v>726</v>
+        <v>739</v>
       </c>
       <c r="J1626" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1626" s="2" t="s">
-        <v>727</v>
+        <v>740</v>
       </c>
     </row>
     <row r="1627" ht="15.75" customHeight="1">
       <c r="H1627" s="3" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="J1627" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1627" s="2" t="s">
-        <v>729</v>
+        <v>742</v>
       </c>
     </row>
     <row r="1628" ht="15.75" customHeight="1">
       <c r="H1628" s="3" t="s">
-        <v>730</v>
+        <v>743</v>
       </c>
       <c r="J1628" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1628" s="2" t="s">
-        <v>731</v>
+        <v>744</v>
       </c>
     </row>
     <row r="1629" ht="15.75" customHeight="1">
       <c r="H1629" s="3" t="s">
-        <v>732</v>
+        <v>745</v>
       </c>
       <c r="J1629" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1629" s="2" t="s">
-        <v>733</v>
+        <v>746</v>
       </c>
     </row>
     <row r="1630" ht="15.75" customHeight="1">
       <c r="H1630" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="J1630" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1630" s="2" t="s">
-        <v>702</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1631" ht="15.75" customHeight="1">
       <c r="H1631" s="3" t="s">
-        <v>734</v>
+        <v>747</v>
       </c>
       <c r="J1631" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1631" s="2" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="1632" ht="15.75" customHeight="1">
       <c r="H1632" s="3" t="s">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="J1632" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K1632" s="2" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="1633" ht="15.75" customHeight="1"/>
     <row r="1634" ht="15.75" customHeight="1">
       <c r="E1634" s="2" t="s">
-        <v>707</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1635" ht="15.75" customHeight="1">
       <c r="E1635" s="2" t="s">
-        <v>708</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1636" ht="15.75" customHeight="1">
       <c r="E1636" s="2" t="s">
-        <v>737</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1637" ht="15.75" customHeight="1">
       <c r="E1637" s="7" t="s">
-        <v>710</v>
+        <v>723</v>
       </c>
       <c r="F1637" s="8"/>
       <c r="G1637" s="8"/>
       <c r="H1637" s="8"/>
       <c r="I1637" s="8"/>
       <c r="J1637" s="9" t="s">
-        <v>711</v>
+        <v>724</v>
       </c>
       <c r="K1637" s="8"/>
       <c r="L1637" s="8"/>
       <c r="M1637" s="8"/>
       <c r="N1637" s="8"/>
       <c r="O1637" s="9" t="s">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="P1637" s="8"/>
       <c r="Q1637" s="8"/>
@@ -17742,14 +17963,14 @@
     </row>
     <row r="1638" ht="15.75" customHeight="1">
       <c r="E1638" s="23" t="s">
-        <v>738</v>
+        <v>751</v>
       </c>
       <c r="F1638" s="12"/>
       <c r="G1638" s="12"/>
       <c r="H1638" s="12"/>
       <c r="I1638" s="12"/>
       <c r="J1638" s="14" t="s">
-        <v>739</v>
+        <v>752</v>
       </c>
       <c r="K1638" s="12"/>
       <c r="L1638" s="12"/>
@@ -17797,21 +18018,21 @@
     </row>
     <row r="1640" ht="15.75" customHeight="1">
       <c r="D1640" s="1" t="s">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="S1640" s="1" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1641" ht="15.75" customHeight="1"/>
     <row r="1642" ht="15.75" customHeight="1">
       <c r="E1642" s="2" t="s">
-        <v>741</v>
+        <v>754</v>
       </c>
     </row>
     <row r="1643" ht="15.75" customHeight="1">
       <c r="E1643" s="2" t="s">
-        <v>742</v>
+        <v>755</v>
       </c>
     </row>
     <row r="1644" ht="15.75" customHeight="1">
@@ -17822,18 +18043,18 @@
     <row r="1645" ht="15.75" customHeight="1"/>
     <row r="1646" ht="15.75" customHeight="1">
       <c r="D1646" s="1" t="s">
-        <v>743</v>
+        <v>756</v>
       </c>
     </row>
     <row r="1647" ht="15.75" customHeight="1"/>
     <row r="1648" ht="15.75" customHeight="1">
       <c r="B1648" s="2" t="s">
-        <v>744</v>
+        <v>757</v>
       </c>
     </row>
     <row r="1649" ht="15.75" customHeight="1">
       <c r="B1649" s="7" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C1649" s="8"/>
       <c r="D1649" s="8"/>
@@ -17844,7 +18065,7 @@
       <c r="I1649" s="8"/>
       <c r="J1649" s="8"/>
       <c r="K1649" s="9" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="L1649" s="8"/>
       <c r="M1649" s="8"/>
@@ -17853,7 +18074,7 @@
       <c r="P1649" s="8"/>
       <c r="Q1649" s="8"/>
       <c r="R1649" s="9" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="S1649" s="8"/>
       <c r="T1649" s="8"/>
@@ -17862,7 +18083,7 @@
       <c r="W1649" s="8"/>
       <c r="X1649" s="8"/>
       <c r="Y1649" s="9" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Z1649" s="8"/>
       <c r="AA1649" s="9" t="s">
@@ -17874,12 +18095,12 @@
     </row>
     <row r="1650" ht="15.75" customHeight="1">
       <c r="B1650" s="11" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="C1650" s="12"/>
       <c r="D1650" s="12"/>
       <c r="E1650" s="14" t="s">
-        <v>746</v>
+        <v>759</v>
       </c>
       <c r="F1650" s="12"/>
       <c r="G1650" s="12"/>
@@ -17887,7 +18108,7 @@
       <c r="I1650" s="12"/>
       <c r="J1650" s="12"/>
       <c r="K1650" s="14" t="s">
-        <v>747</v>
+        <v>760</v>
       </c>
       <c r="L1650" s="12"/>
       <c r="M1650" s="12"/>
@@ -17896,7 +18117,7 @@
       <c r="P1650" s="12"/>
       <c r="Q1650" s="12"/>
       <c r="R1650" s="14" t="s">
-        <v>748</v>
+        <v>761</v>
       </c>
       <c r="S1650" s="12"/>
       <c r="T1650" s="12"/>
@@ -17905,11 +18126,11 @@
       <c r="W1650" s="12"/>
       <c r="X1650" s="12"/>
       <c r="Y1650" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1650" s="12"/>
       <c r="AA1650" s="13" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1650" s="12"/>
       <c r="AC1650" s="12"/>
@@ -17917,10 +18138,10 @@
     </row>
     <row r="1651" ht="15.75" customHeight="1">
       <c r="B1651" s="33" t="s">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="E1651" s="14" t="s">
-        <v>750</v>
+        <v>763</v>
       </c>
       <c r="F1651" s="12"/>
       <c r="G1651" s="12"/>
@@ -17928,7 +18149,7 @@
       <c r="I1651" s="12"/>
       <c r="J1651" s="12"/>
       <c r="K1651" s="14" t="s">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="L1651" s="12"/>
       <c r="M1651" s="12"/>
@@ -17937,7 +18158,7 @@
       <c r="P1651" s="12"/>
       <c r="Q1651" s="12"/>
       <c r="R1651" s="14" t="s">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="S1651" s="12"/>
       <c r="T1651" s="12"/>
@@ -17946,7 +18167,7 @@
       <c r="W1651" s="12"/>
       <c r="X1651" s="12"/>
       <c r="Y1651" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1651" s="12"/>
       <c r="AA1651" s="15"/>
@@ -17954,10 +18175,10 @@
     </row>
     <row r="1652" ht="15.75" customHeight="1">
       <c r="B1652" s="33" t="s">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="E1652" s="14" t="s">
-        <v>754</v>
+        <v>767</v>
       </c>
       <c r="F1652" s="12"/>
       <c r="G1652" s="12"/>
@@ -17965,7 +18186,7 @@
       <c r="I1652" s="12"/>
       <c r="J1652" s="12"/>
       <c r="K1652" s="14" t="s">
-        <v>755</v>
+        <v>768</v>
       </c>
       <c r="L1652" s="12"/>
       <c r="M1652" s="12"/>
@@ -17974,7 +18195,7 @@
       <c r="P1652" s="12"/>
       <c r="Q1652" s="12"/>
       <c r="R1652" s="14" t="s">
-        <v>756</v>
+        <v>769</v>
       </c>
       <c r="S1652" s="12"/>
       <c r="T1652" s="12"/>
@@ -17983,7 +18204,7 @@
       <c r="W1652" s="12"/>
       <c r="X1652" s="12"/>
       <c r="Y1652" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1652" s="12"/>
       <c r="AA1652" s="15"/>
@@ -17991,7 +18212,7 @@
     </row>
     <row r="1653" ht="15.75" customHeight="1">
       <c r="B1653" s="11" t="s">
-        <v>757</v>
+        <v>770</v>
       </c>
       <c r="C1653" s="12"/>
       <c r="D1653" s="12"/>
@@ -18002,7 +18223,7 @@
       <c r="I1653" s="12"/>
       <c r="J1653" s="12"/>
       <c r="K1653" s="14" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="L1653" s="12"/>
       <c r="M1653" s="12"/>
@@ -18011,7 +18232,7 @@
       <c r="P1653" s="12"/>
       <c r="Q1653" s="12"/>
       <c r="R1653" s="14" t="s">
-        <v>759</v>
+        <v>772</v>
       </c>
       <c r="S1653" s="12"/>
       <c r="T1653" s="12"/>
@@ -18020,11 +18241,11 @@
       <c r="W1653" s="12"/>
       <c r="X1653" s="12"/>
       <c r="Y1653" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Z1653" s="12"/>
       <c r="AA1653" s="14" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AB1653" s="12"/>
       <c r="AC1653" s="12"/>
@@ -18034,7 +18255,7 @@
       <c r="B1654" s="10"/>
       <c r="K1654" s="15"/>
       <c r="R1654" s="30" t="s">
-        <v>760</v>
+        <v>773</v>
       </c>
       <c r="Y1654" s="15"/>
       <c r="AA1654" s="15"/>
@@ -18109,7 +18330,7 @@
     <row r="1691" ht="15.75" customHeight="1"/>
     <row r="1692" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1526">
+  <mergeCells count="1553">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="C5:E5"/>
@@ -19011,297 +19232,324 @@
     <mergeCell ref="S1105:AB1105"/>
     <mergeCell ref="F1107:V1107"/>
     <mergeCell ref="E1109:O1109"/>
-    <mergeCell ref="D1111:H1111"/>
-    <mergeCell ref="S1111:Z1111"/>
-    <mergeCell ref="E1113:AD1113"/>
-    <mergeCell ref="E1114:AD1114"/>
-    <mergeCell ref="E1115:AD1115"/>
-    <mergeCell ref="E1116:V1116"/>
-    <mergeCell ref="E1117:AC1117"/>
-    <mergeCell ref="E1118:F1118"/>
-    <mergeCell ref="E1119:Z1119"/>
-    <mergeCell ref="E1120:AD1120"/>
-    <mergeCell ref="E1121:AC1121"/>
-    <mergeCell ref="E1122:AD1122"/>
-    <mergeCell ref="E1123:N1123"/>
-    <mergeCell ref="D1129:G1129"/>
-    <mergeCell ref="E1131:K1131"/>
-    <mergeCell ref="S1131:AA1131"/>
+    <mergeCell ref="E1110:AC1110"/>
+    <mergeCell ref="E1111:F1111"/>
+    <mergeCell ref="K1113:Q1113"/>
+    <mergeCell ref="S1113:T1113"/>
+    <mergeCell ref="L1114:Q1114"/>
+    <mergeCell ref="S1114:AB1114"/>
+    <mergeCell ref="F1116:U1116"/>
+    <mergeCell ref="F1117:V1117"/>
+    <mergeCell ref="E1119:U1119"/>
+    <mergeCell ref="D1129:H1129"/>
+    <mergeCell ref="S1129:Z1129"/>
+    <mergeCell ref="E1131:AD1131"/>
+    <mergeCell ref="E1132:AD1132"/>
     <mergeCell ref="E1133:AD1133"/>
-    <mergeCell ref="E1134:AD1134"/>
+    <mergeCell ref="E1134:V1134"/>
     <mergeCell ref="E1135:AC1135"/>
-    <mergeCell ref="E1136:K1136"/>
-    <mergeCell ref="F1137:H1137"/>
-    <mergeCell ref="K1137:M1137"/>
-    <mergeCell ref="P1137:R1137"/>
-    <mergeCell ref="U1137:W1137"/>
-    <mergeCell ref="Z1137:AB1137"/>
-    <mergeCell ref="F1138:H1138"/>
-    <mergeCell ref="K1138:M1138"/>
-    <mergeCell ref="P1138:R1138"/>
-    <mergeCell ref="U1138:W1138"/>
-    <mergeCell ref="Z1138:AB1138"/>
-    <mergeCell ref="E1139:I1139"/>
-    <mergeCell ref="J1139:N1139"/>
-    <mergeCell ref="O1139:S1139"/>
-    <mergeCell ref="T1139:X1139"/>
-    <mergeCell ref="Y1139:AC1139"/>
-    <mergeCell ref="E1140:I1140"/>
-    <mergeCell ref="J1140:N1140"/>
-    <mergeCell ref="O1140:S1140"/>
-    <mergeCell ref="T1140:X1140"/>
-    <mergeCell ref="Y1140:AC1140"/>
-    <mergeCell ref="E1141:I1141"/>
-    <mergeCell ref="J1141:N1141"/>
-    <mergeCell ref="O1141:S1141"/>
-    <mergeCell ref="T1141:X1141"/>
-    <mergeCell ref="Y1141:AC1141"/>
-    <mergeCell ref="E1142:I1142"/>
-    <mergeCell ref="J1142:N1142"/>
-    <mergeCell ref="O1142:S1142"/>
-    <mergeCell ref="T1142:X1142"/>
-    <mergeCell ref="Y1142:AC1142"/>
-    <mergeCell ref="E1143:I1143"/>
-    <mergeCell ref="J1143:N1143"/>
-    <mergeCell ref="O1143:S1143"/>
-    <mergeCell ref="T1143:X1143"/>
-    <mergeCell ref="Y1143:AC1143"/>
-    <mergeCell ref="E1145:AC1145"/>
-    <mergeCell ref="E1146:AB1146"/>
-    <mergeCell ref="E1148:J1148"/>
-    <mergeCell ref="S1148:AA1148"/>
-    <mergeCell ref="E1150:W1150"/>
-    <mergeCell ref="F1152:T1152"/>
-    <mergeCell ref="E1154:Z1154"/>
-    <mergeCell ref="E1156:H1156"/>
-    <mergeCell ref="S1156:AA1156"/>
-    <mergeCell ref="E1158:AD1158"/>
-    <mergeCell ref="F1160:W1160"/>
-    <mergeCell ref="E1162:W1162"/>
-    <mergeCell ref="E1164:I1164"/>
+    <mergeCell ref="E1136:F1136"/>
+    <mergeCell ref="E1137:Z1137"/>
+    <mergeCell ref="E1138:AD1138"/>
+    <mergeCell ref="E1139:AC1139"/>
+    <mergeCell ref="E1140:AD1140"/>
+    <mergeCell ref="E1141:N1141"/>
+    <mergeCell ref="E1142:AD1142"/>
+    <mergeCell ref="E1143:Q1143"/>
+    <mergeCell ref="D1145:G1145"/>
+    <mergeCell ref="E1147:K1147"/>
+    <mergeCell ref="S1147:AA1147"/>
+    <mergeCell ref="E1149:AD1149"/>
+    <mergeCell ref="E1150:AD1150"/>
+    <mergeCell ref="E1151:AC1151"/>
+    <mergeCell ref="E1152:K1152"/>
+    <mergeCell ref="F1153:H1153"/>
+    <mergeCell ref="K1153:M1153"/>
+    <mergeCell ref="P1153:R1153"/>
+    <mergeCell ref="U1153:W1153"/>
+    <mergeCell ref="Z1153:AB1153"/>
+    <mergeCell ref="F1154:H1154"/>
+    <mergeCell ref="K1154:M1154"/>
+    <mergeCell ref="P1154:R1154"/>
+    <mergeCell ref="U1154:W1154"/>
+    <mergeCell ref="Z1154:AB1154"/>
+    <mergeCell ref="E1155:I1155"/>
+    <mergeCell ref="J1155:N1155"/>
+    <mergeCell ref="O1155:S1155"/>
+    <mergeCell ref="T1155:X1155"/>
+    <mergeCell ref="Y1155:AC1155"/>
+    <mergeCell ref="E1156:I1156"/>
+    <mergeCell ref="J1156:N1156"/>
+    <mergeCell ref="O1156:S1156"/>
+    <mergeCell ref="T1156:X1156"/>
+    <mergeCell ref="Y1156:AC1156"/>
+    <mergeCell ref="E1157:I1157"/>
+    <mergeCell ref="J1157:N1157"/>
+    <mergeCell ref="O1157:S1157"/>
+    <mergeCell ref="T1157:X1157"/>
+    <mergeCell ref="Y1157:AC1157"/>
+    <mergeCell ref="E1158:I1158"/>
+    <mergeCell ref="J1158:N1158"/>
+    <mergeCell ref="O1158:S1158"/>
+    <mergeCell ref="T1158:X1158"/>
+    <mergeCell ref="Y1158:AC1158"/>
+    <mergeCell ref="E1159:I1159"/>
+    <mergeCell ref="J1159:N1159"/>
+    <mergeCell ref="O1159:S1159"/>
+    <mergeCell ref="T1159:X1159"/>
+    <mergeCell ref="Y1159:AC1159"/>
+    <mergeCell ref="E1161:AC1161"/>
+    <mergeCell ref="E1162:AB1162"/>
+    <mergeCell ref="E1164:J1164"/>
     <mergeCell ref="S1164:AA1164"/>
-    <mergeCell ref="E1166:V1166"/>
-    <mergeCell ref="F1168:P1168"/>
-    <mergeCell ref="E1170:X1170"/>
-    <mergeCell ref="D1176:I1176"/>
-    <mergeCell ref="B1178:H1178"/>
-    <mergeCell ref="B1179:I1179"/>
-    <mergeCell ref="J1179:R1179"/>
-    <mergeCell ref="S1179:X1179"/>
-    <mergeCell ref="Y1179:Z1179"/>
-    <mergeCell ref="AA1179:AD1179"/>
-    <mergeCell ref="B1180:I1180"/>
-    <mergeCell ref="J1180:R1180"/>
-    <mergeCell ref="S1180:X1180"/>
-    <mergeCell ref="Y1180:Z1180"/>
-    <mergeCell ref="AA1180:AD1180"/>
-    <mergeCell ref="B1181:I1182"/>
-    <mergeCell ref="J1181:R1181"/>
-    <mergeCell ref="S1181:X1181"/>
-    <mergeCell ref="Y1181:Z1181"/>
-    <mergeCell ref="AA1181:AD1182"/>
-    <mergeCell ref="J1182:R1182"/>
-    <mergeCell ref="S1182:X1182"/>
-    <mergeCell ref="Y1182:Z1182"/>
-    <mergeCell ref="B1183:I1184"/>
-    <mergeCell ref="J1183:R1183"/>
-    <mergeCell ref="S1183:X1183"/>
-    <mergeCell ref="Y1183:Z1183"/>
-    <mergeCell ref="AA1183:AD1184"/>
-    <mergeCell ref="J1184:R1184"/>
-    <mergeCell ref="S1184:X1184"/>
-    <mergeCell ref="Y1184:Z1184"/>
-    <mergeCell ref="B1185:I1185"/>
-    <mergeCell ref="J1185:R1185"/>
-    <mergeCell ref="S1185:X1185"/>
-    <mergeCell ref="Y1185:Z1185"/>
-    <mergeCell ref="AA1185:AD1185"/>
-    <mergeCell ref="B1186:I1186"/>
-    <mergeCell ref="J1186:R1186"/>
-    <mergeCell ref="S1186:X1186"/>
-    <mergeCell ref="Y1186:Z1186"/>
-    <mergeCell ref="AA1186:AD1186"/>
-    <mergeCell ref="B1187:I1187"/>
-    <mergeCell ref="J1187:R1187"/>
-    <mergeCell ref="S1187:X1187"/>
-    <mergeCell ref="Y1187:Z1187"/>
-    <mergeCell ref="AA1187:AD1187"/>
-    <mergeCell ref="B1188:I1188"/>
-    <mergeCell ref="J1188:R1188"/>
-    <mergeCell ref="S1188:X1188"/>
-    <mergeCell ref="Y1188:Z1188"/>
-    <mergeCell ref="AA1188:AD1188"/>
-    <mergeCell ref="C1190:K1190"/>
-    <mergeCell ref="D1192:M1192"/>
-    <mergeCell ref="S1192:AC1192"/>
-    <mergeCell ref="E1194:AD1194"/>
-    <mergeCell ref="E1195:I1195"/>
-    <mergeCell ref="E1196:AB1196"/>
-    <mergeCell ref="D1198:G1198"/>
-    <mergeCell ref="S1198:AB1198"/>
-    <mergeCell ref="E1200:Q1200"/>
-    <mergeCell ref="E1202:AD1202"/>
-    <mergeCell ref="E1203:G1203"/>
-    <mergeCell ref="F1204:R1204"/>
-    <mergeCell ref="E1206:V1206"/>
-    <mergeCell ref="D1223:H1223"/>
-    <mergeCell ref="S1223:AA1223"/>
-    <mergeCell ref="E1225:AD1225"/>
-    <mergeCell ref="E1226:L1226"/>
-    <mergeCell ref="F1228:Y1228"/>
-    <mergeCell ref="L1230:Q1230"/>
-    <mergeCell ref="S1230:U1230"/>
-    <mergeCell ref="M1231:Q1231"/>
-    <mergeCell ref="S1231:T1231"/>
-    <mergeCell ref="L1232:Q1232"/>
-    <mergeCell ref="S1232:AA1232"/>
-    <mergeCell ref="E1234:I1234"/>
-    <mergeCell ref="E1235:K1235"/>
-    <mergeCell ref="L1235:S1235"/>
-    <mergeCell ref="T1235:AC1235"/>
-    <mergeCell ref="E1236:K1238"/>
-    <mergeCell ref="L1236:S1238"/>
-    <mergeCell ref="T1236:AC1236"/>
-    <mergeCell ref="T1237:AC1237"/>
-    <mergeCell ref="T1238:AC1238"/>
-    <mergeCell ref="E1240:N1240"/>
-    <mergeCell ref="E1241:V1241"/>
-    <mergeCell ref="E1243:P1243"/>
-    <mergeCell ref="F1244:V1244"/>
+    <mergeCell ref="E1166:W1166"/>
+    <mergeCell ref="F1168:T1168"/>
+    <mergeCell ref="E1170:Z1170"/>
+    <mergeCell ref="E1176:H1176"/>
+    <mergeCell ref="S1176:AA1176"/>
+    <mergeCell ref="E1178:AD1178"/>
+    <mergeCell ref="F1180:W1180"/>
+    <mergeCell ref="E1182:W1182"/>
+    <mergeCell ref="E1184:I1184"/>
+    <mergeCell ref="S1184:AA1184"/>
+    <mergeCell ref="E1186:V1186"/>
+    <mergeCell ref="F1188:P1188"/>
+    <mergeCell ref="E1190:X1190"/>
+    <mergeCell ref="D1192:I1192"/>
+    <mergeCell ref="B1194:H1194"/>
+    <mergeCell ref="B1195:I1195"/>
+    <mergeCell ref="J1195:R1195"/>
+    <mergeCell ref="S1195:X1195"/>
+    <mergeCell ref="Y1195:Z1195"/>
+    <mergeCell ref="AA1195:AD1195"/>
+    <mergeCell ref="B1196:I1196"/>
+    <mergeCell ref="J1196:R1196"/>
+    <mergeCell ref="S1196:X1196"/>
+    <mergeCell ref="Y1196:Z1196"/>
+    <mergeCell ref="AA1196:AD1196"/>
+    <mergeCell ref="B1197:I1198"/>
+    <mergeCell ref="J1197:R1197"/>
+    <mergeCell ref="S1197:X1197"/>
+    <mergeCell ref="Y1197:Z1197"/>
+    <mergeCell ref="AA1197:AD1198"/>
+    <mergeCell ref="J1198:R1198"/>
+    <mergeCell ref="S1198:X1198"/>
+    <mergeCell ref="Y1198:Z1198"/>
+    <mergeCell ref="B1199:I1200"/>
+    <mergeCell ref="J1199:R1199"/>
+    <mergeCell ref="S1199:X1199"/>
+    <mergeCell ref="Y1199:Z1199"/>
+    <mergeCell ref="AA1199:AD1200"/>
+    <mergeCell ref="J1200:R1200"/>
+    <mergeCell ref="S1200:X1200"/>
+    <mergeCell ref="Y1200:Z1200"/>
+    <mergeCell ref="B1201:I1202"/>
+    <mergeCell ref="J1201:R1201"/>
+    <mergeCell ref="S1201:X1201"/>
+    <mergeCell ref="Y1201:Z1201"/>
+    <mergeCell ref="AA1201:AD1202"/>
+    <mergeCell ref="J1202:R1202"/>
+    <mergeCell ref="S1202:X1202"/>
+    <mergeCell ref="Y1202:Z1202"/>
+    <mergeCell ref="B1203:I1204"/>
+    <mergeCell ref="J1203:R1203"/>
+    <mergeCell ref="S1203:X1203"/>
+    <mergeCell ref="Y1203:Z1203"/>
+    <mergeCell ref="AA1203:AD1204"/>
+    <mergeCell ref="J1204:R1204"/>
+    <mergeCell ref="S1204:X1204"/>
+    <mergeCell ref="Y1204:Z1204"/>
+    <mergeCell ref="B1205:I1205"/>
+    <mergeCell ref="J1205:R1205"/>
+    <mergeCell ref="S1205:X1205"/>
+    <mergeCell ref="Y1205:Z1205"/>
+    <mergeCell ref="AA1205:AD1205"/>
+    <mergeCell ref="B1206:I1206"/>
+    <mergeCell ref="J1206:R1206"/>
+    <mergeCell ref="S1206:X1206"/>
+    <mergeCell ref="Y1206:Z1206"/>
+    <mergeCell ref="AA1206:AD1206"/>
+    <mergeCell ref="B1207:I1207"/>
+    <mergeCell ref="J1207:R1207"/>
+    <mergeCell ref="S1207:X1207"/>
+    <mergeCell ref="Y1207:Z1207"/>
+    <mergeCell ref="AA1207:AD1207"/>
+    <mergeCell ref="B1208:I1208"/>
+    <mergeCell ref="J1208:R1208"/>
+    <mergeCell ref="S1208:X1208"/>
+    <mergeCell ref="Y1208:Z1208"/>
+    <mergeCell ref="AA1208:AD1208"/>
+    <mergeCell ref="C1210:K1210"/>
+    <mergeCell ref="D1212:M1212"/>
+    <mergeCell ref="S1212:AC1212"/>
+    <mergeCell ref="E1214:AD1214"/>
+    <mergeCell ref="E1215:I1215"/>
+    <mergeCell ref="E1216:AB1216"/>
+    <mergeCell ref="D1218:G1218"/>
+    <mergeCell ref="S1218:AB1218"/>
+    <mergeCell ref="E1220:Q1220"/>
+    <mergeCell ref="E1223:AD1223"/>
+    <mergeCell ref="E1224:G1224"/>
+    <mergeCell ref="F1225:R1225"/>
+    <mergeCell ref="E1227:V1227"/>
+    <mergeCell ref="D1229:H1229"/>
+    <mergeCell ref="S1229:AA1229"/>
+    <mergeCell ref="E1231:AD1231"/>
+    <mergeCell ref="E1232:L1232"/>
+    <mergeCell ref="F1234:Y1234"/>
+    <mergeCell ref="L1236:Q1236"/>
+    <mergeCell ref="S1236:U1236"/>
+    <mergeCell ref="M1237:Q1237"/>
+    <mergeCell ref="S1237:T1237"/>
+    <mergeCell ref="L1238:Q1238"/>
+    <mergeCell ref="S1238:AA1238"/>
+    <mergeCell ref="E1240:I1240"/>
+    <mergeCell ref="E1241:K1241"/>
+    <mergeCell ref="L1241:S1241"/>
+    <mergeCell ref="T1241:AC1241"/>
+    <mergeCell ref="E1242:K1244"/>
+    <mergeCell ref="L1242:S1244"/>
+    <mergeCell ref="T1242:AC1242"/>
+    <mergeCell ref="T1243:AC1243"/>
+    <mergeCell ref="T1244:AC1244"/>
     <mergeCell ref="E1246:N1246"/>
-    <mergeCell ref="D1248:H1248"/>
-    <mergeCell ref="S1248:AA1248"/>
-    <mergeCell ref="E1250:Q1250"/>
-    <mergeCell ref="E1252:L1252"/>
-    <mergeCell ref="F1253:L1253"/>
-    <mergeCell ref="F1255:I1255"/>
-    <mergeCell ref="K1255:AA1255"/>
-    <mergeCell ref="K1256:Q1256"/>
-    <mergeCell ref="J1258:L1258"/>
-    <mergeCell ref="N1258:S1258"/>
-    <mergeCell ref="U1258:V1258"/>
-    <mergeCell ref="Z1258:AA1258"/>
-    <mergeCell ref="F1259:J1259"/>
-    <mergeCell ref="E1261:N1261"/>
-    <mergeCell ref="D1263:H1263"/>
-    <mergeCell ref="S1263:AA1263"/>
-    <mergeCell ref="E1265:Q1265"/>
-    <mergeCell ref="E1270:L1270"/>
-    <mergeCell ref="J1271:L1271"/>
-    <mergeCell ref="N1271:S1271"/>
-    <mergeCell ref="U1271:V1271"/>
-    <mergeCell ref="Z1271:AA1271"/>
-    <mergeCell ref="F1272:J1272"/>
-    <mergeCell ref="E1274:N1274"/>
-    <mergeCell ref="D1276:K1276"/>
-    <mergeCell ref="E1278:S1278"/>
-    <mergeCell ref="T1278:AD1278"/>
-    <mergeCell ref="E1280:U1280"/>
-    <mergeCell ref="F1281:Q1281"/>
-    <mergeCell ref="E1283:I1283"/>
-    <mergeCell ref="K1283:Y1283"/>
-    <mergeCell ref="H1284:I1284"/>
-    <mergeCell ref="K1284:X1284"/>
-    <mergeCell ref="H1285:I1285"/>
-    <mergeCell ref="K1285:S1285"/>
-    <mergeCell ref="H1286:I1286"/>
-    <mergeCell ref="K1286:Z1286"/>
-    <mergeCell ref="H1287:I1287"/>
-    <mergeCell ref="K1287:Q1287"/>
+    <mergeCell ref="E1247:V1247"/>
+    <mergeCell ref="E1249:P1249"/>
+    <mergeCell ref="F1250:V1250"/>
+    <mergeCell ref="E1252:N1252"/>
+    <mergeCell ref="D1254:H1254"/>
+    <mergeCell ref="S1254:AA1254"/>
+    <mergeCell ref="E1256:Q1256"/>
+    <mergeCell ref="E1258:L1258"/>
+    <mergeCell ref="F1259:L1259"/>
+    <mergeCell ref="F1261:I1261"/>
+    <mergeCell ref="K1261:AA1261"/>
+    <mergeCell ref="K1262:Q1262"/>
+    <mergeCell ref="J1264:L1264"/>
+    <mergeCell ref="N1264:S1264"/>
+    <mergeCell ref="U1264:V1264"/>
+    <mergeCell ref="Z1264:AA1264"/>
+    <mergeCell ref="F1265:J1265"/>
+    <mergeCell ref="E1267:N1267"/>
+    <mergeCell ref="D1270:H1270"/>
+    <mergeCell ref="S1270:AA1270"/>
+    <mergeCell ref="E1272:Q1272"/>
+    <mergeCell ref="E1274:L1274"/>
+    <mergeCell ref="J1275:L1275"/>
+    <mergeCell ref="N1275:S1275"/>
+    <mergeCell ref="U1275:V1275"/>
+    <mergeCell ref="Z1275:AA1275"/>
+    <mergeCell ref="F1276:J1276"/>
+    <mergeCell ref="E1278:N1278"/>
+    <mergeCell ref="D1280:K1280"/>
+    <mergeCell ref="E1282:S1282"/>
+    <mergeCell ref="T1282:AD1282"/>
+    <mergeCell ref="E1284:U1284"/>
+    <mergeCell ref="F1285:Q1285"/>
+    <mergeCell ref="E1287:I1287"/>
+    <mergeCell ref="K1287:Y1287"/>
     <mergeCell ref="H1288:I1288"/>
-    <mergeCell ref="K1288:U1288"/>
+    <mergeCell ref="K1288:X1288"/>
     <mergeCell ref="H1289:I1289"/>
-    <mergeCell ref="K1289:Q1289"/>
+    <mergeCell ref="K1289:S1289"/>
     <mergeCell ref="H1290:I1290"/>
-    <mergeCell ref="K1290:AA1290"/>
-    <mergeCell ref="G1292:H1292"/>
-    <mergeCell ref="J1292:K1292"/>
-    <mergeCell ref="M1292:N1292"/>
-    <mergeCell ref="Z1292:AA1292"/>
-    <mergeCell ref="AC1292:AD1292"/>
-    <mergeCell ref="L1293:M1293"/>
-    <mergeCell ref="Q1293:R1293"/>
-    <mergeCell ref="Z1293:AA1293"/>
-    <mergeCell ref="G1294:H1294"/>
-    <mergeCell ref="J1294:K1294"/>
-    <mergeCell ref="M1294:T1294"/>
-    <mergeCell ref="Z1294:AA1294"/>
-    <mergeCell ref="E1296:AC1296"/>
-    <mergeCell ref="E1297:P1297"/>
-    <mergeCell ref="F1299:Z1299"/>
-    <mergeCell ref="E1301:Q1301"/>
-    <mergeCell ref="F1303:J1303"/>
-    <mergeCell ref="E1305:R1305"/>
-    <mergeCell ref="S1305:AA1305"/>
-    <mergeCell ref="E1307:AD1307"/>
-    <mergeCell ref="E1308:S1308"/>
-    <mergeCell ref="F1310:J1310"/>
-    <mergeCell ref="F1312:I1312"/>
-    <mergeCell ref="K1312:R1312"/>
-    <mergeCell ref="H1313:I1313"/>
-    <mergeCell ref="K1313:AC1313"/>
-    <mergeCell ref="F1315:S1315"/>
-    <mergeCell ref="F1316:T1316"/>
-    <mergeCell ref="E1317:P1317"/>
+    <mergeCell ref="K1290:Z1290"/>
+    <mergeCell ref="H1291:I1291"/>
+    <mergeCell ref="K1291:Q1291"/>
+    <mergeCell ref="H1292:I1292"/>
+    <mergeCell ref="K1292:U1292"/>
+    <mergeCell ref="H1293:I1293"/>
+    <mergeCell ref="K1293:Q1293"/>
+    <mergeCell ref="H1294:I1294"/>
+    <mergeCell ref="K1294:AA1294"/>
+    <mergeCell ref="G1296:H1296"/>
+    <mergeCell ref="J1296:K1296"/>
+    <mergeCell ref="M1296:N1296"/>
+    <mergeCell ref="Z1296:AA1296"/>
+    <mergeCell ref="AC1296:AD1296"/>
+    <mergeCell ref="L1297:M1297"/>
+    <mergeCell ref="Q1297:R1297"/>
+    <mergeCell ref="Z1297:AA1297"/>
+    <mergeCell ref="G1298:H1298"/>
+    <mergeCell ref="J1298:K1298"/>
+    <mergeCell ref="M1298:T1298"/>
+    <mergeCell ref="Z1298:AA1298"/>
+    <mergeCell ref="E1300:AC1300"/>
+    <mergeCell ref="E1301:P1301"/>
+    <mergeCell ref="F1303:Z1303"/>
+    <mergeCell ref="E1305:Q1305"/>
+    <mergeCell ref="F1307:J1307"/>
+    <mergeCell ref="E1317:R1317"/>
     <mergeCell ref="S1317:AA1317"/>
     <mergeCell ref="E1319:AD1319"/>
-    <mergeCell ref="E1320:AC1320"/>
-    <mergeCell ref="E1321:N1321"/>
-    <mergeCell ref="F1323:S1323"/>
-    <mergeCell ref="F1324:AD1324"/>
-    <mergeCell ref="G1325:H1325"/>
-    <mergeCell ref="J1325:K1325"/>
-    <mergeCell ref="M1325:N1325"/>
-    <mergeCell ref="P1325:S1325"/>
-    <mergeCell ref="Z1325:AA1325"/>
-    <mergeCell ref="J1326:K1326"/>
-    <mergeCell ref="M1326:N1326"/>
-    <mergeCell ref="Z1326:AA1326"/>
-    <mergeCell ref="D1328:L1328"/>
-    <mergeCell ref="S1328:AA1328"/>
-    <mergeCell ref="E1330:AD1330"/>
-    <mergeCell ref="E1331:AD1331"/>
-    <mergeCell ref="E1332:F1332"/>
-    <mergeCell ref="F1334:T1334"/>
-    <mergeCell ref="F1336:I1336"/>
-    <mergeCell ref="K1336:AC1336"/>
-    <mergeCell ref="F1338:O1338"/>
-    <mergeCell ref="F1339:AA1339"/>
-    <mergeCell ref="F1340:P1340"/>
-    <mergeCell ref="D1342:G1342"/>
-    <mergeCell ref="E1344:I1344"/>
-    <mergeCell ref="S1344:AA1344"/>
-    <mergeCell ref="E1346:AC1346"/>
-    <mergeCell ref="E1347:U1347"/>
-    <mergeCell ref="L1349:Q1349"/>
-    <mergeCell ref="S1349:T1349"/>
-    <mergeCell ref="N1350:Q1350"/>
-    <mergeCell ref="S1350:U1350"/>
-    <mergeCell ref="E1352:T1352"/>
-    <mergeCell ref="E1353:V1353"/>
-    <mergeCell ref="E1364:K1364"/>
-    <mergeCell ref="S1364:AA1364"/>
-    <mergeCell ref="E1366:AC1366"/>
-    <mergeCell ref="E1367:AD1367"/>
-    <mergeCell ref="E1368:AA1368"/>
-    <mergeCell ref="E1369:Q1369"/>
-    <mergeCell ref="E1370:S1370"/>
-    <mergeCell ref="T1370:X1370"/>
-    <mergeCell ref="Y1370:AC1370"/>
-    <mergeCell ref="E1371:I1372"/>
-    <mergeCell ref="J1371:S1371"/>
-    <mergeCell ref="T1371:X1371"/>
-    <mergeCell ref="Y1371:AC1371"/>
-    <mergeCell ref="J1372:S1372"/>
-    <mergeCell ref="T1372:X1372"/>
-    <mergeCell ref="Y1372:AC1372"/>
-    <mergeCell ref="E1373:I1373"/>
-    <mergeCell ref="J1373:S1373"/>
-    <mergeCell ref="T1373:AC1373"/>
-    <mergeCell ref="F1375:U1375"/>
-    <mergeCell ref="F1376:S1376"/>
-    <mergeCell ref="F1377:Q1377"/>
-    <mergeCell ref="E1379:O1379"/>
+    <mergeCell ref="E1320:S1320"/>
+    <mergeCell ref="F1322:J1322"/>
+    <mergeCell ref="F1324:I1324"/>
+    <mergeCell ref="K1324:R1324"/>
+    <mergeCell ref="H1325:I1325"/>
+    <mergeCell ref="K1325:AC1325"/>
+    <mergeCell ref="F1327:S1327"/>
+    <mergeCell ref="F1328:T1328"/>
+    <mergeCell ref="E1330:P1330"/>
+    <mergeCell ref="S1330:AA1330"/>
+    <mergeCell ref="E1332:AD1332"/>
+    <mergeCell ref="E1333:AC1333"/>
+    <mergeCell ref="E1334:N1334"/>
+    <mergeCell ref="F1336:S1336"/>
+    <mergeCell ref="F1337:AD1337"/>
+    <mergeCell ref="G1338:H1338"/>
+    <mergeCell ref="J1338:K1338"/>
+    <mergeCell ref="M1338:N1338"/>
+    <mergeCell ref="P1338:S1338"/>
+    <mergeCell ref="Z1338:AA1338"/>
+    <mergeCell ref="J1339:K1339"/>
+    <mergeCell ref="M1339:N1339"/>
+    <mergeCell ref="Z1339:AA1339"/>
+    <mergeCell ref="D1341:L1341"/>
+    <mergeCell ref="S1341:AA1341"/>
+    <mergeCell ref="E1343:AD1343"/>
+    <mergeCell ref="E1344:AD1344"/>
+    <mergeCell ref="E1345:F1345"/>
+    <mergeCell ref="F1347:T1347"/>
+    <mergeCell ref="F1349:I1349"/>
+    <mergeCell ref="K1349:AC1349"/>
+    <mergeCell ref="F1351:O1351"/>
+    <mergeCell ref="F1352:AA1352"/>
+    <mergeCell ref="F1353:P1353"/>
+    <mergeCell ref="D1364:G1364"/>
+    <mergeCell ref="E1366:I1366"/>
+    <mergeCell ref="S1366:AA1366"/>
+    <mergeCell ref="E1368:AC1368"/>
+    <mergeCell ref="E1369:U1369"/>
+    <mergeCell ref="L1371:Q1371"/>
+    <mergeCell ref="S1371:T1371"/>
+    <mergeCell ref="N1372:Q1372"/>
+    <mergeCell ref="S1372:U1372"/>
+    <mergeCell ref="E1374:T1374"/>
+    <mergeCell ref="E1375:V1375"/>
+    <mergeCell ref="E1377:K1377"/>
+    <mergeCell ref="S1377:AA1377"/>
+    <mergeCell ref="E1379:AC1379"/>
+    <mergeCell ref="E1380:AD1380"/>
+    <mergeCell ref="E1381:AA1381"/>
+    <mergeCell ref="E1382:Q1382"/>
+    <mergeCell ref="E1383:S1383"/>
+    <mergeCell ref="T1383:X1383"/>
+    <mergeCell ref="Y1383:AC1383"/>
+    <mergeCell ref="E1384:I1385"/>
+    <mergeCell ref="J1384:S1384"/>
+    <mergeCell ref="T1384:X1384"/>
+    <mergeCell ref="Y1384:AC1384"/>
+    <mergeCell ref="J1385:S1385"/>
+    <mergeCell ref="T1385:X1385"/>
+    <mergeCell ref="Y1385:AC1385"/>
+    <mergeCell ref="E1386:I1386"/>
+    <mergeCell ref="J1386:S1386"/>
+    <mergeCell ref="T1386:AC1386"/>
+    <mergeCell ref="F1388:U1388"/>
+    <mergeCell ref="F1389:S1389"/>
+    <mergeCell ref="F1390:Q1390"/>
+    <mergeCell ref="E1392:O1392"/>
     <mergeCell ref="D1411:G1411"/>
     <mergeCell ref="E1413:P1413"/>
     <mergeCell ref="S1413:AC1413"/>
